--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965505003929138</t>
+    <t xml:space="preserve">0.965504765510559</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892954826355</t>
+    <t xml:space="preserve">0.994892716407776</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978407084941864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169192790985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053874015808</t>
+    <t xml:space="preserve">0.97840690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169312000275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053754806519</t>
   </si>
   <si>
     <t xml:space="preserve">0.966938495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960487484931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9447181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473690986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386274814606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994539260864</t>
+    <t xml:space="preserve">0.960487365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816041469574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994420051575</t>
   </si>
   <si>
     <t xml:space="preserve">0.878057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887375593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560928344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844182491302</t>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428090572357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899561047554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606528759003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844063282013</t>
   </si>
   <si>
     <t xml:space="preserve">0.866588950157166</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">0.807812929153442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.74545294046402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117308139801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704238057136536</t>
+    <t xml:space="preserve">0.745452880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713197767734528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704237937927246</t>
   </si>
   <si>
     <t xml:space="preserve">0.723949491977692</t>
@@ -134,232 +134,235 @@
     <t xml:space="preserve">0.788459777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80279541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298918247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802307128906</t>
+    <t xml:space="preserve">0.800645172595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802795350551605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802366733551</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804945707321167</t>
+    <t xml:space="preserve">0.804945766925812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333837032318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634610176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88665896654129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88020783662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351236820221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040020465851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340614795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809323310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393171787262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977079868317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225415229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852970242500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889723300934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305874824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924582481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860138058662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704447746277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120539665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536512374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784788131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82644921541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79921156167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893329143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292021274567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80924654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131102085114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431815624237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980685710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113583087921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396777629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928367137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512215614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697610378265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921470165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788572788239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655675411224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204545497894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470459461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372540473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673134803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575156211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77555775642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380527019501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872163951396942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937121868134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772298812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85360723733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864741206169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83727753162384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401127338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.835050642490387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658906936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351415634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819766521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87304013967514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87734067440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809323310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892392992973328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225415229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889723300934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305815219879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924582481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830749928951263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704507350922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120480060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536571979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784907341003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82644921541214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79921156167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893329143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547194004059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858469963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781292021274567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246480464935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917745113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431756019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113523483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396777629852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928367137909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194102287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026226520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697610378265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921350955963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655675411224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204545497894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470459461212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779141664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372540473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673075199127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775557696819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627653598785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159064292908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380407810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937360286713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029922962189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853607296943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576502323151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864741325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834066867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277472019196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401186943054</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.829112529754639</t>
   </si>
   <si>
     <t xml:space="preserve">0.83059698343277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85880321264267</t>
+    <t xml:space="preserve">0.858803153038025</t>
   </si>
   <si>
     <t xml:space="preserve">0.839504301548004</t>
@@ -371,16 +374,16 @@
     <t xml:space="preserve">0.843957841396332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846184611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835792899131775</t>
+    <t xml:space="preserve">0.84618467092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83579295873642</t>
   </si>
   <si>
     <t xml:space="preserve">0.833566009998322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838761985301971</t>
+    <t xml:space="preserve">0.838761925697327</t>
   </si>
   <si>
     <t xml:space="preserve">0.816493928432465</t>
@@ -401,16 +404,16 @@
     <t xml:space="preserve">0.81797844171524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818720817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819462954998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143443584442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812782645225525</t>
+    <t xml:space="preserve">0.818720757961273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819463014602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81278270483017</t>
   </si>
   <si>
     <t xml:space="preserve">0.808328986167908</t>
@@ -419,19 +422,19 @@
     <t xml:space="preserve">0.803133130073547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805359959602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796452760696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906360149384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514647960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999220848083</t>
+    <t xml:space="preserve">0.805359899997711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796452701091766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906300544739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
     <t xml:space="preserve">0.791256904602051</t>
@@ -440,16 +443,16 @@
     <t xml:space="preserve">0.807586789131165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267098903656</t>
+    <t xml:space="preserve">0.814267218112946</t>
   </si>
   <si>
     <t xml:space="preserve">0.804617643356323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79867959022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225990772247</t>
+    <t xml:space="preserve">0.798679530620575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225931167603</t>
   </si>
   <si>
     <t xml:space="preserve">0.786803185939789</t>
@@ -461,43 +464,43 @@
     <t xml:space="preserve">0.777153849601746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777895987033844</t>
+    <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
     <t xml:space="preserve">0.788287818431854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77195793390274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838019728660583</t>
+    <t xml:space="preserve">0.771957874298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838019669055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.806844472885132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774927079677582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442506790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783834159374237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765277564525604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778638303279877</t>
+    <t xml:space="preserve">0.774927020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442566394806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783834218978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765277504920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778638362884521</t>
   </si>
   <si>
     <t xml:space="preserve">0.783091843128204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787545502185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786060929298401</t>
+    <t xml:space="preserve">0.787545561790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78606104850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.774184703826904</t>
@@ -506,70 +509,70 @@
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102216243744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452548980713</t>
+    <t xml:space="preserve">0.806102275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452668190002</t>
   </si>
   <si>
     <t xml:space="preserve">0.841731011867523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848411321640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215525150299</t>
+    <t xml:space="preserve">0.848411440849304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215644359589</t>
   </si>
   <si>
     <t xml:space="preserve">0.852865159511566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845442473888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390840530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866225838661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855091869831085</t>
+    <t xml:space="preserve">0.845442414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390780925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86251437664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866225898265839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85509181022644</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823872566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834308326244354</t>
+    <t xml:space="preserve">0.832823812961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834308385848999</t>
   </si>
   <si>
     <t xml:space="preserve">0.827628016471863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860287725925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349672794342</t>
+    <t xml:space="preserve">0.860287845134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349553585052</t>
   </si>
   <si>
     <t xml:space="preserve">0.867710411548615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880328893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648524284363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669091701508</t>
+    <t xml:space="preserve">0.880329012870789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669151306152</t>
   </si>
   <si>
     <t xml:space="preserve">0.923380434513092</t>
@@ -581,28 +584,28 @@
     <t xml:space="preserve">0.916700065135956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927091777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545317173004</t>
+    <t xml:space="preserve">0.927091836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545376777649</t>
   </si>
   <si>
     <t xml:space="preserve">0.915957748889923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911504089832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535063266754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885548114777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792654514313</t>
+    <t xml:space="preserve">0.91150426864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991669058799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792773723602</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768968582153</t>
@@ -611,10 +614,10 @@
     <t xml:space="preserve">1.06960701942444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0748028755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06886494159698</t>
+    <t xml:space="preserve">1.07480299472809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0688648223877</t>
   </si>
   <si>
     <t xml:space="preserve">1.0465966463089</t>
@@ -623,13 +626,13 @@
     <t xml:space="preserve">1.05327713489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05179274082184</t>
+    <t xml:space="preserve">1.05179286003113</t>
   </si>
   <si>
     <t xml:space="preserve">1.03249371051788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02432870864868</t>
+    <t xml:space="preserve">1.02432882785797</t>
   </si>
   <si>
     <t xml:space="preserve">1.03175151348114</t>
@@ -641,10 +644,10 @@
     <t xml:space="preserve">1.00206077098846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0228443145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03026700019836</t>
+    <t xml:space="preserve">1.02284419536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03026688098907</t>
   </si>
   <si>
     <t xml:space="preserve">1.05921542644501</t>
@@ -653,13 +656,13 @@
     <t xml:space="preserve">1.06812250614166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585456848145</t>
+    <t xml:space="preserve">1.04585444927216</t>
   </si>
   <si>
     <t xml:space="preserve">1.06663811206818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449349880219</t>
+    <t xml:space="preserve">1.10449361801147</t>
   </si>
   <si>
     <t xml:space="preserve">1.11191630363464</t>
@@ -668,10 +671,10 @@
     <t xml:space="preserve">1.11933898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.117112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12898850440979</t>
+    <t xml:space="preserve">1.11711227893829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1289883852005</t>
   </si>
   <si>
     <t xml:space="preserve">1.14160692691803</t>
@@ -680,16 +683,16 @@
     <t xml:space="preserve">1.18762743473053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2150913476944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2314213514328</t>
+    <t xml:space="preserve">1.21509146690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23142123222351</t>
   </si>
   <si>
     <t xml:space="preserve">1.2173182964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22177195549011</t>
+    <t xml:space="preserve">1.22177183628082</t>
   </si>
   <si>
     <t xml:space="preserve">1.21880269050598</t>
@@ -701,25 +704,25 @@
     <t xml:space="preserve">1.22845220565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23513245582581</t>
+    <t xml:space="preserve">1.23513269424438</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474086284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286463737488</t>
+    <t xml:space="preserve">1.21286475658417</t>
   </si>
   <si>
     <t xml:space="preserve">1.21360683441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20098853111267</t>
+    <t xml:space="preserve">1.20098829269409</t>
   </si>
   <si>
     <t xml:space="preserve">1.24700891971588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26779234409332</t>
+    <t xml:space="preserve">1.26779222488403</t>
   </si>
   <si>
     <t xml:space="preserve">1.24923574924469</t>
@@ -728,10 +731,10 @@
     <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26036977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888538360596</t>
+    <t xml:space="preserve">1.26036965847015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888514518738</t>
   </si>
   <si>
     <t xml:space="preserve">1.26927697658539</t>
@@ -743,43 +746,43 @@
     <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34424614906311</t>
+    <t xml:space="preserve">1.34424602985382</t>
   </si>
   <si>
     <t xml:space="preserve">1.239586353302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2032151222229</t>
+    <t xml:space="preserve">1.20321524143219</t>
   </si>
   <si>
     <t xml:space="preserve">1.17426669597626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17278206348419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1653596162796</t>
+    <t xml:space="preserve">1.17278230190277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16535949707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.17055535316467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1772358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649364471436</t>
+    <t xml:space="preserve">1.17723572254181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.16387510299683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16164827346802</t>
+    <t xml:space="preserve">1.16164815425873</t>
   </si>
   <si>
     <t xml:space="preserve">1.15051424503326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15348339080811</t>
+    <t xml:space="preserve">1.15348327159882</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824630737305</t>
@@ -788,7 +791,7 @@
     <t xml:space="preserve">1.14383387565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18911194801331</t>
+    <t xml:space="preserve">1.18911218643188</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
@@ -800,7 +803,7 @@
     <t xml:space="preserve">1.28486454486847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31307065486908</t>
+    <t xml:space="preserve">1.31307077407837</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
@@ -809,61 +812,61 @@
     <t xml:space="preserve">1.32791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35834908485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3435035943985</t>
+    <t xml:space="preserve">1.35834896564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34350347518921</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311200141907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057294368744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34374022483826</t>
+    <t xml:space="preserve">1.35057282447815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
     <t xml:space="preserve">1.32855689525604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35816466808319</t>
+    <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
     <t xml:space="preserve">1.35512793064117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37031137943268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36651563644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37410736083984</t>
+    <t xml:space="preserve">1.37031161785126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3665155172348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37410724163055</t>
   </si>
   <si>
     <t xml:space="preserve">1.39080917835236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39688265323639</t>
+    <t xml:space="preserve">1.39688277244568</t>
   </si>
   <si>
     <t xml:space="preserve">1.38169920444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3680340051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36727488040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3915684223175</t>
+    <t xml:space="preserve">1.36803388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36727476119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39156830310822</t>
   </si>
   <si>
     <t xml:space="preserve">1.39232754707336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38549494743347</t>
+    <t xml:space="preserve">1.38549506664276</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258911132812</t>
@@ -875,7 +878,7 @@
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120140552521</t>
+    <t xml:space="preserve">1.36120128631592</t>
   </si>
   <si>
     <t xml:space="preserve">1.35133218765259</t>
@@ -884,7 +887,7 @@
     <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842599391937</t>
+    <t xml:space="preserve">1.33842611312866</t>
   </si>
   <si>
     <t xml:space="preserve">1.34298121929169</t>
@@ -893,7 +896,7 @@
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363477230072</t>
+    <t xml:space="preserve">1.29363489151001</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
@@ -905,7 +908,7 @@
     <t xml:space="preserve">1.320965051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31413245201111</t>
+    <t xml:space="preserve">1.31413233280182</t>
   </si>
   <si>
     <t xml:space="preserve">1.36955237388611</t>
@@ -914,19 +917,19 @@
     <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37562572956085</t>
+    <t xml:space="preserve">1.37562584877014</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143764019012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38625407218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397669792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38929104804993</t>
+    <t xml:space="preserve">1.38625419139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397657871246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38929080963135</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
@@ -935,13 +938,13 @@
     <t xml:space="preserve">1.37866234779358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473582267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34829533100128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42497229576111</t>
+    <t xml:space="preserve">1.38473570346832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34829545021057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
     <t xml:space="preserve">1.4523024559021</t>
@@ -950,7 +953,7 @@
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
+    <t xml:space="preserve">1.47735524177551</t>
   </si>
   <si>
     <t xml:space="preserve">1.55630946159363</t>
@@ -959,7 +962,7 @@
     <t xml:space="preserve">1.51835060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54568099975586</t>
+    <t xml:space="preserve">1.54568111896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.51379573345184</t>
@@ -974,7 +977,7 @@
     <t xml:space="preserve">1.52897906303406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50316715240479</t>
+    <t xml:space="preserve">1.50316739082336</t>
   </si>
   <si>
     <t xml:space="preserve">1.53049755096436</t>
@@ -998,7 +1001,7 @@
     <t xml:space="preserve">1.40599274635315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38777256011963</t>
+    <t xml:space="preserve">1.38777267932892</t>
   </si>
   <si>
     <t xml:space="preserve">1.33614861965179</t>
@@ -1010,7 +1013,7 @@
     <t xml:space="preserve">1.29970812797546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30502247810364</t>
+    <t xml:space="preserve">1.30502235889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.42573130130768</t>
@@ -1019,7 +1022,7 @@
     <t xml:space="preserve">1.47052252292633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47659611701965</t>
+    <t xml:space="preserve">1.47659599781036</t>
   </si>
   <si>
     <t xml:space="preserve">1.48798370361328</t>
@@ -1043,58 +1046,58 @@
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371513366699</t>
+    <t xml:space="preserve">1.40371525287628</t>
   </si>
   <si>
     <t xml:space="preserve">1.37182986736298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36271977424622</t>
+    <t xml:space="preserve">1.36271965503693</t>
   </si>
   <si>
     <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35209143161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36499726772308</t>
+    <t xml:space="preserve">1.35209131240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36499738693237</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575639247894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37107074260712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4272495508194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039186000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4993714094162</t>
+    <t xml:space="preserve">1.37107062339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42724967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49937129020691</t>
   </si>
   <si>
     <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49177968502045</t>
+    <t xml:space="preserve">1.49177944660187</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761656761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43863713741302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37790334224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33235263824463</t>
+    <t xml:space="preserve">1.45761668682098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4386373758316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37790322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
     <t xml:space="preserve">1.30957758426666</t>
@@ -1106,22 +1109,22 @@
     <t xml:space="preserve">1.32476091384888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34753620624542</t>
+    <t xml:space="preserve">1.34753632545471</t>
   </si>
   <si>
     <t xml:space="preserve">1.31337332725525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27161860466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40827035903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.27161872386932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716930866241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40827023983002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
@@ -1130,16 +1133,16 @@
     <t xml:space="preserve">1.44243323802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45382082462311</t>
+    <t xml:space="preserve">1.45382070541382</t>
   </si>
   <si>
     <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418796062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46520829200745</t>
+    <t xml:space="preserve">1.48418784141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
     <t xml:space="preserve">1.42345380783081</t>
@@ -1154,16 +1157,13 @@
     <t xml:space="preserve">1.46141254901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54112589359283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47280025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51455497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418772220612</t>
+    <t xml:space="preserve">1.54112601280212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47280037403107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51455473899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.51551628112793</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">1.50768411159515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52726447582245</t>
+    <t xml:space="preserve">1.52726459503174</t>
   </si>
   <si>
     <t xml:space="preserve">1.51943242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50376808643341</t>
+    <t xml:space="preserve">1.5037682056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48027181625366</t>
+    <t xml:space="preserve">1.46852362155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48027169704437</t>
   </si>
   <si>
     <t xml:space="preserve">1.46069145202637</t>
@@ -1196,40 +1196,40 @@
     <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4646075963974</t>
+    <t xml:space="preserve">1.46460747718811</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677530765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47243964672089</t>
+    <t xml:space="preserve">1.47243976593018</t>
   </si>
   <si>
     <t xml:space="preserve">1.47635567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44111108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42544686794281</t>
+    <t xml:space="preserve">1.44111120700836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
     <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40978264808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42153096199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936289310455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43327915668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45285940170288</t>
+    <t xml:space="preserve">1.40978252887726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42153084278107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936301231384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43327903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45285928249359</t>
   </si>
   <si>
     <t xml:space="preserve">1.39803445339203</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">1.30796504020691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404877662659</t>
+    <t xml:space="preserve">1.30404889583588</t>
   </si>
   <si>
     <t xml:space="preserve">1.33146142959595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28055250644684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29621684551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31188094615936</t>
+    <t xml:space="preserve">1.28055262565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2962167263031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31188106536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.34320962429047</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">1.35104179382324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38628613948822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4058666229248</t>
+    <t xml:space="preserve">1.38628625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40586650371552</t>
   </si>
   <si>
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845408916473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32754528522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838467597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195035934448</t>
+    <t xml:space="preserve">1.37845396995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3275454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838455677032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195047855377</t>
   </si>
   <si>
     <t xml:space="preserve">1.30013287067413</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230082035065</t>
+    <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28446865081787</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31971311569214</t>
+    <t xml:space="preserve">1.31971323490143</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1319,49 +1319,49 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761469841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48810398578644</t>
+    <t xml:space="preserve">1.41761457920074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48810386657715</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49985206127167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51160025596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334856987</t>
+    <t xml:space="preserve">1.49985194206238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51160037517548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334845066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509676456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55076086521149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59775376319885</t>
+    <t xml:space="preserve">1.55076098442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
     <t xml:space="preserve">1.58992147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62124979496002</t>
+    <t xml:space="preserve">1.6212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.60558569431305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61341798305511</t>
+    <t xml:space="preserve">1.61341774463654</t>
   </si>
   <si>
     <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62908220291138</t>
+    <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
     <t xml:space="preserve">1.64474630355835</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65257847309113</t>
+    <t xml:space="preserve">1.65257835388184</t>
   </si>
   <si>
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824293136597</t>
+    <t xml:space="preserve">1.66824305057526</t>
   </si>
   <si>
     <t xml:space="preserve">1.70740354061127</t>
@@ -1394,37 +1394,37 @@
     <t xml:space="preserve">1.80138885974884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838163852692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006042003632</t>
+    <t xml:space="preserve">1.84838175773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006018161774</t>
   </si>
   <si>
     <t xml:space="preserve">1.77789258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82488524913788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922102928162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271729946136</t>
+    <t xml:space="preserve">1.82488512992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922091007233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271753787994</t>
   </si>
   <si>
     <t xml:space="preserve">1.84054958820343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87971031665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187826633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404585838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85621392726898</t>
+    <t xml:space="preserve">1.87971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8562136888504</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355680942535</t>
@@ -1445,37 +1445,37 @@
     <t xml:space="preserve">1.96586346626282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93453526496887</t>
+    <t xml:space="preserve">1.93453502655029</t>
   </si>
   <si>
     <t xml:space="preserve">1.91887080669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92670285701752</t>
+    <t xml:space="preserve">1.9267030954361</t>
   </si>
   <si>
     <t xml:space="preserve">1.98178458213806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94942879676819</t>
+    <t xml:space="preserve">1.94942903518677</t>
   </si>
   <si>
     <t xml:space="preserve">1.96560668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87662875652313</t>
+    <t xml:space="preserve">1.87662851810455</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338410377502</t>
+    <t xml:space="preserve">1.76338398456573</t>
   </si>
   <si>
     <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78765058517456</t>
+    <t xml:space="preserve">1.78765070438385</t>
   </si>
   <si>
     <t xml:space="preserve">1.79573953151703</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">1.85236203670502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89280641078949</t>
+    <t xml:space="preserve">1.89280664920807</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8847177028656</t>
+    <t xml:space="preserve">1.88471746444702</t>
   </si>
   <si>
     <t xml:space="preserve">1.84427309036255</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">1.83618402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77147281169891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90898418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9413400888443</t>
+    <t xml:space="preserve">1.7714729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90898442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94134032726288</t>
   </si>
   <si>
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987352848053</t>
+    <t xml:space="preserve">1.98987376689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.95751798152924</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">1.92516231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7472060918808</t>
+    <t xml:space="preserve">1.74720597267151</t>
   </si>
   <si>
     <t xml:space="preserve">1.75529491901398</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56116080284119</t>
+    <t xml:space="preserve">1.56116092205048</t>
   </si>
   <si>
     <t xml:space="preserve">1.49644958972931</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">1.34276020526886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31849348545074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29827105998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17289304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715976715088</t>
+    <t xml:space="preserve">1.31849336624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29827117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17289292812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715964794159</t>
   </si>
   <si>
     <t xml:space="preserve">1.22951531410217</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">1.1648041009903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03538143634796</t>
+    <t xml:space="preserve">1.03538131713867</t>
   </si>
   <si>
     <t xml:space="preserve">1.07178151607513</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">1.09604823589325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18502616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18907082080841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13649272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075944900513</t>
+    <t xml:space="preserve">1.18502628803253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18907070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1364928483963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075956821442</t>
   </si>
   <si>
     <t xml:space="preserve">1.24569320678711</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">1.26995992660522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25378203392029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524871349335</t>
+    <t xml:space="preserve">1.25378215312958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524859428406</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">1.12031507492065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14458155632019</t>
+    <t xml:space="preserve">1.14458167552948</t>
   </si>
   <si>
     <t xml:space="preserve">1.11627054214478</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22142624855042</t>
+    <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
     <t xml:space="preserve">1.11222612857819</t>
@@ -1718,10 +1718,10 @@
     <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0798704624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0556036233902</t>
+    <t xml:space="preserve">1.07987034320831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560350418091</t>
   </si>
   <si>
     <t xml:space="preserve">1.05155909061432</t>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">0.982803344726562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97067004442215</t>
+    <t xml:space="preserve">0.954492211341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970670163631439</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">1.32658231258392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680449962616</t>
+    <t xml:space="preserve">1.34680461883545</t>
   </si>
   <si>
     <t xml:space="preserve">1.33467125892639</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46813833713531</t>
+    <t xml:space="preserve">1.4681384563446</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55307197570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57733869552612</t>
+    <t xml:space="preserve">1.5530720949173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57733881473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
@@ -1832,52 +1832,52 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947217464447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57329440116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56520545482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836064338684</t>
+    <t xml:space="preserve">1.58947205543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57329428195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56520533561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836076259613</t>
   </si>
   <si>
     <t xml:space="preserve">1.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54902756214142</t>
+    <t xml:space="preserve">1.54902744293213</t>
   </si>
   <si>
     <t xml:space="preserve">1.52476072311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52880537509918</t>
+    <t xml:space="preserve">1.52880525588989</t>
   </si>
   <si>
     <t xml:space="preserve">1.65822780132294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70676136016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69867253303528</t>
+    <t xml:space="preserve">1.70676124095917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69867241382599</t>
   </si>
   <si>
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249475955963</t>
+    <t xml:space="preserve">1.68249464035034</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440581321716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72293937206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61373889446259</t>
+    <t xml:space="preserve">1.72293949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6137387752533</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60565006732941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205014705658</t>
+    <t xml:space="preserve">1.60564994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205002784729</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">1.55711650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48431622982025</t>
+    <t xml:space="preserve">1.48431634902954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49240517616272</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">1.33062672615051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3589380979538</t>
+    <t xml:space="preserve">1.35893797874451</t>
   </si>
   <si>
     <t xml:space="preserve">1.44791603088379</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60160553455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59756112098694</t>
+    <t xml:space="preserve">1.60160565376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59756100177765</t>
   </si>
   <si>
     <t xml:space="preserve">1.609694480896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75187587738037</t>
+    <t xml:space="preserve">1.75187575817108</t>
   </si>
   <si>
     <t xml:space="preserve">1.72660839557648</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7097635269165</t>
+    <t xml:space="preserve">1.70976340770721</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68028485774994</t>
+    <t xml:space="preserve">1.68028473854065</t>
   </si>
   <si>
     <t xml:space="preserve">1.68449604511261</t>
@@ -1976,28 +1976,28 @@
     <t xml:space="preserve">1.64659488201141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343986988068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63817250728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62974989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66765105724335</t>
+    <t xml:space="preserve">1.66343975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63817238807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62974977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66765117645264</t>
   </si>
   <si>
     <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61711609363556</t>
+    <t xml:space="preserve">1.61711621284485</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54973638057709</t>
+    <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
     <t xml:space="preserve">1.58342635631561</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">1.56658136844635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54552507400513</t>
+    <t xml:space="preserve">1.54552519321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815887451172</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289151191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51183521747589</t>
+    <t xml:space="preserve">1.53289139270782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5118350982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.47393405437469</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4486665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41497671604156</t>
+    <t xml:space="preserve">1.44866669178009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41497659683228</t>
   </si>
   <si>
     <t xml:space="preserve">1.44024407863617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41076529026031</t>
+    <t xml:space="preserve">1.4107654094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40234291553497</t>
+    <t xml:space="preserve">1.40234303474426</t>
   </si>
   <si>
     <t xml:space="preserve">1.46130037307739</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49077904224396</t>
+    <t xml:space="preserve">1.49077892303467</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131388664246</t>
+    <t xml:space="preserve">1.54131376743317</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868008613586</t>
+    <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553858757019</t>
+    <t xml:space="preserve">1.62553870677948</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501749515533</t>
+    <t xml:space="preserve">1.65501737594604</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184885025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51604640483856</t>
+    <t xml:space="preserve">1.61290490627289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184873104095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51604628562927</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761039733887</t>
+    <t xml:space="preserve">1.42761051654816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2156,43 +2156,43 @@
     <t xml:space="preserve">1.65922856330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79398834705353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84452319145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83931910991669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584770679474</t>
+    <t xml:space="preserve">1.79398846626282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84452331066132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8393189907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584758758545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510474205017</t>
+    <t xml:space="preserve">1.79510462284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9277480840683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700488090515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237654209137</t>
+    <t xml:space="preserve">1.92774796485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237642288208</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365907907486</t>
+    <t xml:space="preserve">1.91006219387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93659090995789</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154824256897</t>
+    <t xml:space="preserve">2.05154800415039</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923389434814</t>
+    <t xml:space="preserve">2.0869197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923413276672</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039118766785</t>
+    <t xml:space="preserve">2.06039094924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353359699249</t>
+    <t xml:space="preserve">1.88353371620178</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427656173706</t>
+    <t xml:space="preserve">1.95427668094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163333892822</t>
+    <t xml:space="preserve">1.82163321971893</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783294200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130446434021</t>
+    <t xml:space="preserve">1.69783306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130434513092</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940432548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6270899772644</t>
+    <t xml:space="preserve">1.60940420627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62709009647369</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171843528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6049827337265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824715137482</t>
+    <t xml:space="preserve">1.59171831607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60498285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824703216553</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72436165809631</t>
+    <t xml:space="preserve">1.73762595653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7243617773056</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -7226,7 +7226,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7252,7 +7252,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7278,7 +7278,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7304,7 +7304,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7356,7 +7356,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7382,7 +7382,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7408,7 +7408,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7434,7 +7434,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7460,7 +7460,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7486,7 +7486,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7512,7 +7512,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7538,7 +7538,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7564,7 +7564,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7616,7 +7616,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7642,7 +7642,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7668,7 +7668,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7720,7 +7720,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7746,7 +7746,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7772,7 +7772,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7798,7 +7798,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7824,7 +7824,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7850,7 +7850,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7876,7 +7876,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7902,7 +7902,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7928,7 +7928,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7954,7 +7954,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7980,7 +7980,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8006,7 +8006,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8032,7 +8032,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8084,7 +8084,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8110,7 +8110,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8136,7 +8136,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8188,7 +8188,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8214,7 +8214,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8266,7 +8266,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8292,7 +8292,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8318,7 +8318,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8344,7 +8344,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8370,7 +8370,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8396,7 +8396,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8448,7 +8448,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8474,7 +8474,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8500,7 +8500,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8526,7 +8526,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8552,7 +8552,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8604,7 +8604,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8630,7 +8630,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8656,7 +8656,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8682,7 +8682,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8708,7 +8708,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8734,7 +8734,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8760,7 +8760,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8786,7 +8786,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8812,7 +8812,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8864,7 +8864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8890,7 +8890,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8916,7 +8916,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8968,7 +8968,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8994,7 +8994,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9020,7 +9020,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9072,7 +9072,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9098,7 +9098,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9124,7 +9124,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9150,7 +9150,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9176,7 +9176,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9202,7 +9202,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9228,7 +9228,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9254,7 +9254,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9280,7 +9280,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9306,7 +9306,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9332,7 +9332,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9358,7 +9358,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9384,7 +9384,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9410,7 +9410,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9462,7 +9462,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9488,7 +9488,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9514,7 +9514,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9540,7 +9540,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9566,7 +9566,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9592,7 +9592,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9618,7 +9618,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9644,7 +9644,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9670,7 +9670,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9722,7 +9722,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9748,7 +9748,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9800,7 +9800,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9878,7 +9878,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9904,7 +9904,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9930,7 +9930,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10034,7 +10034,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10060,7 +10060,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10086,7 +10086,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10112,7 +10112,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10164,7 +10164,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10190,7 +10190,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10216,7 +10216,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10242,7 +10242,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10268,7 +10268,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10294,7 +10294,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10346,7 +10346,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10372,7 +10372,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10398,7 +10398,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10424,7 +10424,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10476,7 +10476,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10606,7 +10606,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10632,7 +10632,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10658,7 +10658,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10684,7 +10684,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10736,7 +10736,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10762,7 +10762,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10788,7 +10788,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10814,7 +10814,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10840,7 +10840,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10892,7 +10892,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10918,7 +10918,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10944,7 +10944,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10970,7 +10970,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10996,7 +10996,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11022,7 +11022,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11048,7 +11048,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11100,7 +11100,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11126,7 +11126,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11152,7 +11152,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11178,7 +11178,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11204,7 +11204,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11230,7 +11230,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11256,7 +11256,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11282,7 +11282,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11308,7 +11308,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11360,7 +11360,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11386,7 +11386,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11438,7 +11438,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11464,7 +11464,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11490,7 +11490,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11516,7 +11516,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11542,7 +11542,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11568,7 +11568,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11594,7 +11594,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11620,7 +11620,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11646,7 +11646,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11672,7 +11672,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11698,7 +11698,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11724,7 +11724,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11776,7 +11776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11802,7 +11802,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11828,7 +11828,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11854,7 +11854,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11880,7 +11880,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11906,7 +11906,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11932,7 +11932,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11958,7 +11958,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11984,7 +11984,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12010,7 +12010,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12036,7 +12036,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12062,7 +12062,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12088,7 +12088,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12114,7 +12114,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12140,7 +12140,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12166,7 +12166,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12192,7 +12192,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12218,7 +12218,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12244,7 +12244,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12270,7 +12270,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12322,7 +12322,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12348,7 +12348,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12374,7 +12374,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12400,7 +12400,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12426,7 +12426,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12452,7 +12452,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12478,7 +12478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12504,7 +12504,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12530,7 +12530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12582,7 +12582,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12608,7 +12608,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12634,7 +12634,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12686,7 +12686,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12712,7 +12712,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12738,7 +12738,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12790,7 +12790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12842,7 +12842,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12868,7 +12868,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12894,7 +12894,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12920,7 +12920,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12946,7 +12946,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12972,7 +12972,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12998,7 +12998,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13024,7 +13024,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13050,7 +13050,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13102,7 +13102,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13128,7 +13128,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13154,7 +13154,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13180,7 +13180,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13206,7 +13206,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13232,7 +13232,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13258,7 +13258,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13284,7 +13284,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13310,7 +13310,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13336,7 +13336,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13362,7 +13362,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13388,7 +13388,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13414,7 +13414,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13440,7 +13440,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13466,7 +13466,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13492,7 +13492,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13518,7 +13518,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13570,7 +13570,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13596,7 +13596,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13622,7 +13622,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13700,7 +13700,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13726,7 +13726,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13752,7 +13752,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13778,7 +13778,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13804,7 +13804,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13830,7 +13830,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13856,7 +13856,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13882,7 +13882,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13908,7 +13908,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13934,7 +13934,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13960,7 +13960,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13986,7 +13986,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14012,7 +14012,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14038,7 +14038,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14064,7 +14064,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14090,7 +14090,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14116,7 +14116,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14142,7 +14142,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14168,7 +14168,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14194,7 +14194,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14220,7 +14220,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14246,7 +14246,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14272,7 +14272,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14298,7 +14298,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14324,7 +14324,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14350,7 +14350,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14376,7 +14376,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14402,7 +14402,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14428,7 +14428,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14454,7 +14454,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14480,7 +14480,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14506,7 +14506,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14532,7 +14532,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14558,7 +14558,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14584,7 +14584,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14610,7 +14610,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14636,7 +14636,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14662,7 +14662,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14688,7 +14688,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14714,7 +14714,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14740,7 +14740,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14766,7 +14766,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14792,7 +14792,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14818,7 +14818,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14844,7 +14844,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14870,7 +14870,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14896,7 +14896,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14922,7 +14922,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14948,7 +14948,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14974,7 +14974,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15000,7 +15000,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15026,7 +15026,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15052,7 +15052,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15078,7 +15078,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15104,7 +15104,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15130,7 +15130,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15156,7 +15156,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15182,7 +15182,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15208,7 +15208,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15234,7 +15234,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15260,7 +15260,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15286,7 +15286,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15312,7 +15312,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15338,7 +15338,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15364,7 +15364,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15390,7 +15390,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15416,7 +15416,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15442,7 +15442,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15468,7 +15468,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15494,7 +15494,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15520,7 +15520,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15546,7 +15546,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15572,7 +15572,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15598,7 +15598,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15624,7 +15624,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15650,7 +15650,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15676,7 +15676,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15702,7 +15702,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15728,7 +15728,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15754,7 +15754,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15780,7 +15780,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15806,7 +15806,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15832,7 +15832,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15858,7 +15858,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15884,7 +15884,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15910,7 +15910,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15936,7 +15936,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15962,7 +15962,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15988,7 +15988,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16014,7 +16014,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16040,7 +16040,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16066,7 +16066,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16092,7 +16092,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16118,7 +16118,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16144,7 +16144,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16170,7 +16170,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16196,7 +16196,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16222,7 +16222,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16248,7 +16248,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16274,7 +16274,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16300,7 +16300,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16326,7 +16326,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16352,7 +16352,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16378,7 +16378,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16404,7 +16404,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16430,7 +16430,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16456,7 +16456,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16482,7 +16482,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16508,7 +16508,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16534,7 +16534,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16560,7 +16560,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16586,7 +16586,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16612,7 +16612,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16638,7 +16638,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16664,7 +16664,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16690,7 +16690,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16716,7 +16716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16742,7 +16742,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16768,7 +16768,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16794,7 +16794,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16820,7 +16820,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16846,7 +16846,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16872,7 +16872,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16898,7 +16898,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16924,7 +16924,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16950,7 +16950,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16976,7 +16976,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17002,7 +17002,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17028,7 +17028,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17054,7 +17054,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17080,7 +17080,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17106,7 +17106,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17132,7 +17132,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17158,7 +17158,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17184,7 +17184,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17210,7 +17210,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17236,7 +17236,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17262,7 +17262,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17288,7 +17288,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17314,7 +17314,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17340,7 +17340,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17366,7 +17366,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17392,7 +17392,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17418,7 +17418,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17444,7 +17444,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17470,7 +17470,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17496,7 +17496,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17522,7 +17522,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17548,7 +17548,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17574,7 +17574,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17600,7 +17600,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17626,7 +17626,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17652,7 +17652,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17678,7 +17678,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17704,7 +17704,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17730,7 +17730,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17756,7 +17756,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17782,7 +17782,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17808,7 +17808,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17834,7 +17834,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17860,7 +17860,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17886,7 +17886,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17912,7 +17912,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17938,7 +17938,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17964,7 +17964,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17990,7 +17990,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18016,7 +18016,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18042,7 +18042,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18068,7 +18068,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18094,7 +18094,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18120,7 +18120,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18146,7 +18146,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18172,7 +18172,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18198,7 +18198,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18224,7 +18224,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18250,7 +18250,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18276,7 +18276,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18302,7 +18302,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18328,7 +18328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18354,7 +18354,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18380,7 +18380,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18406,7 +18406,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18432,7 +18432,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18458,7 +18458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18484,7 +18484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18510,7 +18510,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18536,7 +18536,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18562,7 +18562,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18588,7 +18588,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18614,7 +18614,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18640,7 +18640,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18666,7 +18666,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18692,7 +18692,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18718,7 +18718,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18744,7 +18744,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18770,7 +18770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18796,7 +18796,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18822,7 +18822,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18848,7 +18848,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18874,7 +18874,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18900,7 +18900,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18926,7 +18926,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18952,7 +18952,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18978,7 +18978,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19004,7 +19004,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19030,7 +19030,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19056,7 +19056,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19082,7 +19082,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19108,7 +19108,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19134,7 +19134,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19160,7 +19160,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19186,7 +19186,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19212,7 +19212,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19238,7 +19238,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19264,7 +19264,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19290,7 +19290,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19316,7 +19316,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19342,7 +19342,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19368,7 +19368,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19394,7 +19394,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19420,7 +19420,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19446,7 +19446,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19472,7 +19472,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19498,7 +19498,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19524,7 +19524,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19550,7 +19550,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19576,7 +19576,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19602,7 +19602,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19628,7 +19628,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19654,7 +19654,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19680,7 +19680,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19706,7 +19706,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19732,7 +19732,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19758,7 +19758,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19784,7 +19784,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19810,7 +19810,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19836,7 +19836,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19862,7 +19862,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19888,7 +19888,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19914,7 +19914,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19940,7 +19940,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19966,7 +19966,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19992,7 +19992,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20018,7 +20018,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -67554,7 +67554,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6495486111</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>101922</v>
@@ -67575,6 +67575,32 @@
         <v>855</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6495486111</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>14579</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>2.41000008583069</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>855</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504765510559</t>
+    <t xml:space="preserve">0.965505003929138</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892716407776</t>
+    <t xml:space="preserve">0.994892835617065</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97840690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169312000275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938495635986</t>
+    <t xml:space="preserve">0.978407025337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169431209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053933620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938376426697</t>
   </si>
   <si>
     <t xml:space="preserve">0.960487365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944718182086945</t>
+    <t xml:space="preserve">0.944718241691589</t>
   </si>
   <si>
     <t xml:space="preserve">0.931816041469574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863005042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386215209961</t>
+    <t xml:space="preserve">0.863005101680756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473631381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386155605316</t>
   </si>
   <si>
     <t xml:space="preserve">0.900994420051575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878057479858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375712394714</t>
+    <t xml:space="preserve">0.878057658672333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375771999359</t>
   </si>
   <si>
     <t xml:space="preserve">0.902428090572357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899561047554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606528759003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844063282013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866588950157166</t>
+    <t xml:space="preserve">0.899560987949371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606469154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866589069366455</t>
   </si>
   <si>
     <t xml:space="preserve">0.831466674804688</t>
@@ -110,19 +110,19 @@
     <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745452880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713197767734528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704237937927246</t>
+    <t xml:space="preserve">0.807812869548798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74545294046402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117308139801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704237878322601</t>
   </si>
   <si>
     <t xml:space="preserve">0.723949491977692</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">0.774124205112457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788459777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800645172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802795350551605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298858642578</t>
+    <t xml:space="preserve">0.788459837436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800644993782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298918247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.845802366733551</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">0.804945766925812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835050582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834333837032318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634610176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88665896654129</t>
+    <t xml:space="preserve">0.835050642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634431362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658847332001</t>
   </si>
   <si>
     <t xml:space="preserve">0.88020783662796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839351236820221</t>
+    <t xml:space="preserve">0.83935135602951</t>
   </si>
   <si>
     <t xml:space="preserve">0.850819826126099</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">0.873040020465851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877340614795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809323310852</t>
+    <t xml:space="preserve">0.877340793609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809263706207</t>
   </si>
   <si>
     <t xml:space="preserve">0.892393171787262</t>
@@ -188,61 +188,61 @@
     <t xml:space="preserve">0.895977079868317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885225415229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852970242500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889723300934</t>
+    <t xml:space="preserve">0.885225355625153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852970063686371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889782905579</t>
   </si>
   <si>
     <t xml:space="preserve">0.867305874824524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880924582481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
+    <t xml:space="preserve">0.880924701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86013799905777</t>
   </si>
   <si>
     <t xml:space="preserve">0.830749988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858704447746277</t>
+    <t xml:space="preserve">0.858704388141632</t>
   </si>
   <si>
     <t xml:space="preserve">0.855120539665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851536512374878</t>
+    <t xml:space="preserve">0.851536452770233</t>
   </si>
   <si>
     <t xml:space="preserve">0.859421253204346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840784788131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82644921541214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79921156167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893329143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858469963074</t>
+    <t xml:space="preserve">0.840784847736359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799211502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893388748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547194004059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858529567719</t>
   </si>
   <si>
     <t xml:space="preserve">0.781292021274567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784875869750977</t>
+    <t xml:space="preserve">0.784875988960266</t>
   </si>
   <si>
     <t xml:space="preserve">0.80924654006958</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">0.817131102085114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837917804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431815624237</t>
+    <t xml:space="preserve">0.837917745113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431756019592</t>
   </si>
   <si>
     <t xml:space="preserve">0.814980685710907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812113583087921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396777629852</t>
+    <t xml:space="preserve">0.812113642692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396837234497</t>
   </si>
   <si>
     <t xml:space="preserve">0.799928367137909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.794194221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026286125183</t>
+    <t xml:space="preserve">0.794194042682648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026345729828</t>
   </si>
   <si>
     <t xml:space="preserve">0.803512215614319</t>
@@ -284,181 +284,178 @@
     <t xml:space="preserve">0.756921470165253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759788572788239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655675411224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204545497894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470459461212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779141664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372540473938</t>
+    <t xml:space="preserve">0.759788513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77914172410965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372421264648</t>
   </si>
   <si>
     <t xml:space="preserve">0.767673134803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780575156211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77555775642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159064292908</t>
+    <t xml:space="preserve">0.780575275421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557816028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627653598785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159123897552</t>
   </si>
   <si>
     <t xml:space="preserve">0.842218399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851380527019501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937121868134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029863357544</t>
+    <t xml:space="preserve">0.851380467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872164070606232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937300682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029922962189</t>
   </si>
   <si>
     <t xml:space="preserve">0.861772298812866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576442718506</t>
+    <t xml:space="preserve">0.853607356548309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576502323151</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855834007263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83727753162384</t>
+    <t xml:space="preserve">0.855834186077118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277472019196</t>
   </si>
   <si>
     <t xml:space="preserve">0.825401127338409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835050642490387</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.829112529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83059698343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858803153038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504301548004</t>
+    <t xml:space="preserve">0.830597043037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85880309343338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504182338715</t>
   </si>
   <si>
     <t xml:space="preserve">0.844700157642365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843957841396332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84618467092514</t>
+    <t xml:space="preserve">0.843957781791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846184611320496</t>
   </si>
   <si>
     <t xml:space="preserve">0.83579295873642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833566009998322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838761925697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816493928432465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809813439846039</t>
+    <t xml:space="preserve">0.833566129207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838762044906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816493988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">0.823916673660278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810555815696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81797844171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720757961273</t>
+    <t xml:space="preserve">0.810555934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801648676395416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817978501319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720817565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.819463014602661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278270483017</t>
+    <t xml:space="preserve">0.826143562793732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81278258562088</t>
   </si>
   <si>
     <t xml:space="preserve">0.808328986167908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803133130073547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805359899997711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796452701091766</t>
+    <t xml:space="preserve">0.803133189678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805360019207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796452760696411</t>
   </si>
   <si>
     <t xml:space="preserve">0.800906300544739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790514707565308</t>
+    <t xml:space="preserve">0.790514588356018</t>
   </si>
   <si>
     <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256904602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586789131165</t>
+    <t xml:space="preserve">0.791256785392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807586908340454</t>
   </si>
   <si>
     <t xml:space="preserve">0.814267218112946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804617643356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803185939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779380559921265</t>
+    <t xml:space="preserve">0.804617702960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79867947101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225990772247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77938050031662</t>
   </si>
   <si>
     <t xml:space="preserve">0.777153849601746</t>
@@ -467,22 +464,22 @@
     <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788287818431854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771957874298096</t>
+    <t xml:space="preserve">0.788287878036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771957814693451</t>
   </si>
   <si>
     <t xml:space="preserve">0.838019669055939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806844472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442566394806</t>
+    <t xml:space="preserve">0.806844413280487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774926960468292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442447185516</t>
   </si>
   <si>
     <t xml:space="preserve">0.783834218978882</t>
@@ -491,13 +488,13 @@
     <t xml:space="preserve">0.765277504920959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778638362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091843128204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545561790466</t>
+    <t xml:space="preserve">0.778638422489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091902732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545442581177</t>
   </si>
   <si>
     <t xml:space="preserve">0.78606104850769</t>
@@ -506,43 +503,43 @@
     <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318672657013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806102275848389</t>
+    <t xml:space="preserve">0.785318732261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806102156639099</t>
   </si>
   <si>
     <t xml:space="preserve">0.868452668190002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411440849304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215644359589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865159511566</t>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411500453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215525150299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865099906921</t>
   </si>
   <si>
     <t xml:space="preserve">0.845442414283752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849153697490692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390780925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86251437664032</t>
+    <t xml:space="preserve">0.849153757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514495849609</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85509181022644</t>
+    <t xml:space="preserve">0.855091631412506</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
@@ -551,31 +548,31 @@
     <t xml:space="preserve">0.832823812961578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834308385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827628016471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860287845134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349553585052</t>
+    <t xml:space="preserve">0.834308326244354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827627897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86028778553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349613189697</t>
   </si>
   <si>
     <t xml:space="preserve">0.867710411548615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880329012870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648643493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380434513092</t>
+    <t xml:space="preserve">0.880328893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648524284363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919668912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380374908447</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
@@ -584,28 +581,28 @@
     <t xml:space="preserve">0.916700065135956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927091836929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545376777649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915957748889923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91150426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885607719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991669058799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792773723602</t>
+    <t xml:space="preserve">0.927091658115387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545317173004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915957808494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504089832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535122871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885548114777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991668999195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792654514313</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768968582153</t>
@@ -617,7 +614,7 @@
     <t xml:space="preserve">1.07480299472809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0688648223877</t>
+    <t xml:space="preserve">1.06886494159698</t>
   </si>
   <si>
     <t xml:space="preserve">1.0465966463089</t>
@@ -626,25 +623,25 @@
     <t xml:space="preserve">1.05327713489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05179286003113</t>
+    <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
     <t xml:space="preserve">1.03249371051788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02432882785797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03175151348114</t>
+    <t xml:space="preserve">1.02432870864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03175139427185</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467931270599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00206077098846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02284419536591</t>
+    <t xml:space="preserve">1.00206089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0228443145752</t>
   </si>
   <si>
     <t xml:space="preserve">1.03026688098907</t>
@@ -656,16 +653,16 @@
     <t xml:space="preserve">1.06812250614166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585444927216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06663811206818</t>
+    <t xml:space="preserve">1.04585468769073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06663799285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.10449361801147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11191630363464</t>
+    <t xml:space="preserve">1.11191618442535</t>
   </si>
   <si>
     <t xml:space="preserve">1.11933898925781</t>
@@ -677,16 +674,16 @@
     <t xml:space="preserve">1.1289883852005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14160692691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18762743473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21509146690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23142123222351</t>
+    <t xml:space="preserve">1.14160704612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18762767314911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21509158611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2314213514328</t>
   </si>
   <si>
     <t xml:space="preserve">1.2173182964325</t>
@@ -695,13 +692,13 @@
     <t xml:space="preserve">1.22177183628082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21880269050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23216366767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22845220565796</t>
+    <t xml:space="preserve">1.21880292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23216342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22845232486725</t>
   </si>
   <si>
     <t xml:space="preserve">1.23513269424438</t>
@@ -710,46 +707,46 @@
     <t xml:space="preserve">1.22474086284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286475658417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21360683441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20098829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24700891971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779222488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923574924469</t>
+    <t xml:space="preserve">1.21286463737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21360695362091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20098841190338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2470086812973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2677925825119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2492356300354</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26036965847015</t>
+    <t xml:space="preserve">1.26036977767944</t>
   </si>
   <si>
     <t xml:space="preserve">1.25888514518738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26927697658539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639028549194</t>
+    <t xml:space="preserve">1.26927709579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521526813507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639040470123</t>
   </si>
   <si>
     <t xml:space="preserve">1.34424602985382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.239586353302</t>
+    <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
@@ -761,10 +758,10 @@
     <t xml:space="preserve">1.17278230190277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055535316467</t>
+    <t xml:space="preserve">1.1653596162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055547237396</t>
   </si>
   <si>
     <t xml:space="preserve">1.17723572254181</t>
@@ -773,25 +770,25 @@
     <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16387510299683</t>
+    <t xml:space="preserve">1.16387486457825</t>
   </si>
   <si>
     <t xml:space="preserve">1.16164815425873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15051424503326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15348327159882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12824630737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14383387565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18911218643188</t>
+    <t xml:space="preserve">1.15051412582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12824618816376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14383399486542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
@@ -800,28 +797,28 @@
     <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28486454486847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31307077407837</t>
+    <t xml:space="preserve">1.28486442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31307089328766</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35834896564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34350347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33311200141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057282447815</t>
+    <t xml:space="preserve">1.327916264534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35834908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3435035943985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33311176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057306289673</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
@@ -836,40 +833,40 @@
     <t xml:space="preserve">1.35512793064117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37031161785126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3665155172348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37410724163055</t>
+    <t xml:space="preserve">1.37031149864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36651575565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
     <t xml:space="preserve">1.39080917835236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39688277244568</t>
+    <t xml:space="preserve">1.39688265323639</t>
   </si>
   <si>
     <t xml:space="preserve">1.38169920444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36803388595581</t>
+    <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
     <t xml:space="preserve">1.36727476119995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39156830310822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39232754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549506664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258911132812</t>
+    <t xml:space="preserve">1.39156854152679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39232766628265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258899211884</t>
   </si>
   <si>
     <t xml:space="preserve">1.38701331615448</t>
@@ -881,22 +878,22 @@
     <t xml:space="preserve">1.36120128631592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35133218765259</t>
+    <t xml:space="preserve">1.3513320684433</t>
   </si>
   <si>
     <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842611312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34298121929169</t>
+    <t xml:space="preserve">1.33842623233795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34298133850098</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363489151001</t>
+    <t xml:space="preserve">1.29363477230072</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
@@ -905,31 +902,31 @@
     <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.320965051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31413233280182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36955237388611</t>
+    <t xml:space="preserve">1.32096493244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31413245201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36955225467682</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37562584877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40143764019012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625419139862</t>
+    <t xml:space="preserve">1.37562572956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40143775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625431060791</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397657871246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929080963135</t>
+    <t xml:space="preserve">1.38929092884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
@@ -938,10 +935,10 @@
     <t xml:space="preserve">1.37866234779358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473570346832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34829545021057</t>
+    <t xml:space="preserve">1.38473582267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34829556941986</t>
   </si>
   <si>
     <t xml:space="preserve">1.42497217655182</t>
@@ -956,16 +953,16 @@
     <t xml:space="preserve">1.47735524177551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55630946159363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51835060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568111896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379573345184</t>
+    <t xml:space="preserve">1.55630958080292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51835072040558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379561424255</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594244480133</t>
@@ -974,55 +971,55 @@
     <t xml:space="preserve">1.51075887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52897906303406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50316739082336</t>
+    <t xml:space="preserve">1.52897918224335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50316727161407</t>
   </si>
   <si>
     <t xml:space="preserve">1.53049755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53353428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746093273163</t>
+    <t xml:space="preserve">1.53353404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746069431305</t>
   </si>
   <si>
     <t xml:space="preserve">1.51607310771942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47887361049652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43484139442444</t>
+    <t xml:space="preserve">1.47887349128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
     <t xml:space="preserve">1.40599274635315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38777267932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33614861965179</t>
+    <t xml:space="preserve">1.38777244091034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33614873886108</t>
   </si>
   <si>
     <t xml:space="preserve">1.2905980348587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29970812797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30502235889435</t>
+    <t xml:space="preserve">1.29970824718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30502247810364</t>
   </si>
   <si>
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052252292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659599781036</t>
+    <t xml:space="preserve">1.47052264213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659611701965</t>
   </si>
   <si>
     <t xml:space="preserve">1.48798370361328</t>
@@ -1031,10 +1028,10 @@
     <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269444465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41434371471405</t>
+    <t xml:space="preserve">1.42269456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41434359550476</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738045215607</t>
@@ -1046,13 +1043,13 @@
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371525287628</t>
+    <t xml:space="preserve">1.40371513366699</t>
   </si>
   <si>
     <t xml:space="preserve">1.37182986736298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36271965503693</t>
+    <t xml:space="preserve">1.36271977424622</t>
   </si>
   <si>
     <t xml:space="preserve">1.36423814296722</t>
@@ -1061,7 +1058,7 @@
     <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36499738693237</t>
+    <t xml:space="preserve">1.36499726772308</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575639247894</t>
@@ -1070,16 +1067,16 @@
     <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42724967002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49937129020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49557542800903</t>
+    <t xml:space="preserve">1.4272495508194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4993714094162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49557554721832</t>
   </si>
   <si>
     <t xml:space="preserve">1.49177944660187</t>
@@ -1088,40 +1085,40 @@
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761668682098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4386373758316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37790322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33235275745392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30957758426666</t>
+    <t xml:space="preserve">1.45761656761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43863725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37790334224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33235287666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30957746505737</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753632545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337332725525</t>
+    <t xml:space="preserve">1.32476103305817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753620624542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337344646454</t>
   </si>
   <si>
     <t xml:space="preserve">1.27161872386932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31716930866241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40827023983002</t>
+    <t xml:space="preserve">1.31716918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40827035903931</t>
   </si>
   <si>
     <t xml:space="preserve">1.41206610202789</t>
@@ -1130,10 +1127,10 @@
     <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44243323802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45382070541382</t>
+    <t xml:space="preserve">1.4424329996109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45382082462311</t>
   </si>
   <si>
     <t xml:space="preserve">1.46900427341461</t>
@@ -1145,10 +1142,10 @@
     <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42345380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586196422577</t>
+    <t xml:space="preserve">1.42345368862152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586208343506</t>
   </si>
   <si>
     <t xml:space="preserve">1.45002484321594</t>
@@ -1160,34 +1157,37 @@
     <t xml:space="preserve">1.54112601280212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47280037403107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51455473899841</t>
+    <t xml:space="preserve">1.47280025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5145548582077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.51551628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50768411159515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52726459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5037682056427</t>
+    <t xml:space="preserve">1.50768423080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52726447582245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943254470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376808643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852362155914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48027169704437</t>
+    <t xml:space="preserve">1.46852350234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48027181625366</t>
   </si>
   <si>
     <t xml:space="preserve">1.46069145202637</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46460747718811</t>
+    <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677530765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47243976593018</t>
+    <t xml:space="preserve">1.4724395275116</t>
   </si>
   <si>
     <t xml:space="preserve">1.47635567188263</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40978252887726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42153084278107</t>
+    <t xml:space="preserve">1.36278975009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40978276729584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42153096199036</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936301231384</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">1.43327903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45285928249359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39803445339203</t>
+    <t xml:space="preserve">1.45285940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39803433418274</t>
   </si>
   <si>
     <t xml:space="preserve">1.39411842823029</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">1.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488816738129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33929347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30796504020691</t>
+    <t xml:space="preserve">1.26488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33929359912872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
     <t xml:space="preserve">1.30404889583588</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">1.2962167263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188106536865</t>
+    <t xml:space="preserve">1.31188094615936</t>
   </si>
   <si>
     <t xml:space="preserve">1.34320962429047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35104179382324</t>
+    <t xml:space="preserve">1.35104167461395</t>
   </si>
   <si>
     <t xml:space="preserve">1.38628625869751</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845396995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3275454044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838455677032</t>
+    <t xml:space="preserve">1.37845420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32754528522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30013287067413</t>
+    <t xml:space="preserve">1.30013275146484</t>
   </si>
   <si>
     <t xml:space="preserve">1.33537745475769</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3157970905304</t>
+    <t xml:space="preserve">1.31579697132111</t>
   </si>
   <si>
     <t xml:space="preserve">1.31971323490143</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761457920074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48810386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49593603610992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49985194206238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51160037517548</t>
+    <t xml:space="preserve">1.41761469841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48810374736786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49593591690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49985206127167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5116001367569</t>
   </si>
   <si>
     <t xml:space="preserve">1.52334845066071</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992147445679</t>
+    <t xml:space="preserve">1.58992159366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.6212500333786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60558569431305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61341774463654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5820894241333</t>
+    <t xml:space="preserve">1.60558581352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61341786384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208930492401</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64474630355835</t>
+    <t xml:space="preserve">1.64474618434906</t>
   </si>
   <si>
     <t xml:space="preserve">1.63691425323486</t>
@@ -1376,58 +1376,58 @@
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824305057526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740354061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439620018005</t>
+    <t xml:space="preserve">1.66824281215668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740330219269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439608097076</t>
   </si>
   <si>
     <t xml:space="preserve">1.74656403064728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76222825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80138885974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838175773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006018161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77789258956909</t>
+    <t xml:space="preserve">1.76222836971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80138897895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006053924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7778924703598</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488512992859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80922091007233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271753787994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054958820343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971043586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187802791595</t>
+    <t xml:space="preserve">1.80922102928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271741867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054970741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187826633453</t>
   </si>
   <si>
     <t xml:space="preserve">1.86404609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8562136888504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79355680942535</t>
+    <t xml:space="preserve">1.85621380805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79355669021606</t>
   </si>
   <si>
     <t xml:space="preserve">1.94236743450165</t>
@@ -1436,49 +1436,49 @@
     <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369563579559</t>
+    <t xml:space="preserve">1.97369587421417</t>
   </si>
   <si>
     <t xml:space="preserve">1.99719202518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96586346626282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453502655029</t>
+    <t xml:space="preserve">1.96586358547211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453526496887</t>
   </si>
   <si>
     <t xml:space="preserve">1.91887080669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9267030954361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178458213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662851810455</t>
+    <t xml:space="preserve">1.92670297622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178470134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942891597748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9656069278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662863731384</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338398456573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765070438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573953151703</t>
+    <t xml:space="preserve">1.76338374614716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191742420197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573941230774</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
@@ -1487,85 +1487,85 @@
     <t xml:space="preserve">1.82000625133514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86045074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236203670502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89280664920807</t>
+    <t xml:space="preserve">1.8604508638382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809519767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236179828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8928062915802</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88471746444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427309036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86853969097137</t>
+    <t xml:space="preserve">1.88471758365631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427297115326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86853981018066</t>
   </si>
   <si>
     <t xml:space="preserve">1.83618402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7714729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90898442268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94134032726288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93325114250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987376689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751798152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.997962474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73911714553833</t>
+    <t xml:space="preserve">1.77147281169891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90898430347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94134020805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93325126171112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987364768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751774311066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796259403229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73911702632904</t>
   </si>
   <si>
     <t xml:space="preserve">1.92516231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74720597267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75529491901398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631674766541</t>
+    <t xml:space="preserve">1.7472060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75529503822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631686687469</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58542776107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56116092205048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49644958972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747141838074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4155604839325</t>
+    <t xml:space="preserve">1.58542764186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56116080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4964497089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747153759003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41556036472321</t>
   </si>
   <si>
     <t xml:space="preserve">1.34276020526886</t>
@@ -1574,25 +1574,25 @@
     <t xml:space="preserve">1.31849336624146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29827117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17289292812347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715964794159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951531410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15267062187195</t>
+    <t xml:space="preserve">1.29827105998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17289304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951543331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15267050266266</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01515901088715</t>
+    <t xml:space="preserve">1.01515913009644</t>
   </si>
   <si>
     <t xml:space="preserve">1.1648041009903</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">1.07178151607513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15671515464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1405371427536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693734169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09604823589325</t>
+    <t xml:space="preserve">1.15671503543854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14053726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693746089935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09604811668396</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18907070159912</t>
+    <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
     <t xml:space="preserve">1.1364928483963</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">1.30231559276581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995992660522</t>
+    <t xml:space="preserve">1.26995980739594</t>
   </si>
   <si>
     <t xml:space="preserve">1.25378215312958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20524859428406</t>
+    <t xml:space="preserve">1.20524871349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
+    <t xml:space="preserve">1.18098175525665</t>
   </si>
   <si>
     <t xml:space="preserve">1.21333742141724</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031507492065</t>
+    <t xml:space="preserve">1.12031483650208</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862608909607</t>
+    <t xml:space="preserve">1.14862620830536</t>
   </si>
   <si>
     <t xml:space="preserve">1.10009264945984</t>
@@ -1682,43 +1682,43 @@
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760426044464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21738195419312</t>
+    <t xml:space="preserve">1.23760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2173820734024</t>
   </si>
   <si>
     <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20929312705994</t>
+    <t xml:space="preserve">1.20929300785065</t>
   </si>
   <si>
     <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2214263677597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11222612857819</t>
+    <t xml:space="preserve">1.22142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1122260093689</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0596479177475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09200382232666</t>
+    <t xml:space="preserve">1.07582592964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05964803695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09200370311737</t>
   </si>
   <si>
     <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07987034320831</t>
+    <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
     <t xml:space="preserve">1.05560350418091</t>
@@ -1727,43 +1727,43 @@
     <t xml:space="preserve">1.05155909061432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02324783802032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0272923707962</t>
+    <t xml:space="preserve">1.0232480764389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02729249000549</t>
   </si>
   <si>
     <t xml:space="preserve">1.00302577018738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982803344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954492211341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970670163631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01111459732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986847817897797</t>
+    <t xml:space="preserve">0.982803463935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954492151737213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970670104026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01111471652985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986847937107086</t>
   </si>
   <si>
     <t xml:space="preserve">0.962581157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966625571250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758990764618</t>
+    <t xml:space="preserve">0.96662563085556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978758871555328</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10413706302643</t>
+    <t xml:space="preserve">1.10413718223572</t>
   </si>
   <si>
     <t xml:space="preserve">1.23355984687805</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31040441989899</t>
+    <t xml:space="preserve">1.31040453910828</t>
   </si>
   <si>
     <t xml:space="preserve">1.32253789901733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32658231258392</t>
+    <t xml:space="preserve">1.32658219337463</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680461883545</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">1.4681384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51262748241425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5530720949173</t>
+    <t xml:space="preserve">1.51262736320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55307197570801</t>
   </si>
   <si>
     <t xml:space="preserve">1.57733881473541</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">1.54498302936554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52071642875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53284966945648</t>
+    <t xml:space="preserve">1.52071630954742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453841686249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53284955024719</t>
   </si>
   <si>
     <t xml:space="preserve">1.51667189598083</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">1.58947205543518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57329428195953</t>
+    <t xml:space="preserve">1.57329440116882</t>
   </si>
   <si>
     <t xml:space="preserve">1.56520533561707</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">1.48836076259613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54902744293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52476072311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.50049388408661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54902756214142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5247608423233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5288051366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676124095917</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">1.68249464035034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67440581321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72293949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6137387752533</t>
+    <t xml:space="preserve">1.67440569400787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72293937206268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61373889446259</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205002784729</t>
+    <t xml:space="preserve">1.60565006732941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205014705658</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">1.61778330802917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71485030651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55711650848389</t>
+    <t xml:space="preserve">1.71485018730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55711627006531</t>
   </si>
   <si>
     <t xml:space="preserve">1.48431634902954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49240517616272</t>
+    <t xml:space="preserve">1.49240529537201</t>
   </si>
   <si>
     <t xml:space="preserve">1.47218286991119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59351670742035</t>
+    <t xml:space="preserve">1.59351658821106</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
@@ -1922,40 +1922,40 @@
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33062672615051</t>
+    <t xml:space="preserve">1.3306268453598</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893797874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44791603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409380435944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47622740268707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60160565376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59756100177765</t>
+    <t xml:space="preserve">1.44791615009308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409392356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47622728347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60160553455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59756112098694</t>
   </si>
   <si>
     <t xml:space="preserve">1.609694480896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75187575817108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72660839557648</t>
+    <t xml:space="preserve">1.75187587738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72660851478577</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70976340770721</t>
+    <t xml:space="preserve">1.7097635269165</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">1.64659488201141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63817238807678</t>
+    <t xml:space="preserve">1.66343986988068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63817250728607</t>
   </si>
   <si>
     <t xml:space="preserve">1.62974977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66765117645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64238369464874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61711621284485</t>
+    <t xml:space="preserve">1.66765105724335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64238357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61711609363556</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58342635631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500386238098</t>
+    <t xml:space="preserve">1.58342623710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500374317169</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59606003761292</t>
+    <t xml:space="preserve">1.59605991840363</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5118350982666</t>
+    <t xml:space="preserve">1.53289151191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51183521747589</t>
   </si>
   <si>
     <t xml:space="preserve">1.47393405437469</t>
@@ -2039,37 +2039,37 @@
     <t xml:space="preserve">1.38970923423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3981317281723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603301048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44866669178009</t>
+    <t xml:space="preserve">1.39813160896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4360328912735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4486665725708</t>
   </si>
   <si>
     <t xml:space="preserve">1.41497659683228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44024407863617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4107654094696</t>
+    <t xml:space="preserve">1.44024419784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41076529026031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40234303474426</t>
+    <t xml:space="preserve">1.40234291553497</t>
   </si>
   <si>
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49077892303467</t>
+    <t xml:space="preserve">1.49499022960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49077904224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131376743317</t>
+    <t xml:space="preserve">1.54131400585175</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868032455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869371891022</t>
+    <t xml:space="preserve">1.60869359970093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553870677948</t>
+    <t xml:space="preserve">1.62553858757019</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">1.59184873104095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604628562927</t>
+    <t xml:space="preserve">1.51604652404785</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2144,55 +2144,55 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025771141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57079255580902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58763742446899</t>
+    <t xml:space="preserve">1.52025759220123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57079243659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58763754367828</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79398846626282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84452331066132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8393189907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584758758545</t>
+    <t xml:space="preserve">1.79398834705353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84452319145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83931910991669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584770679474</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510462284088</t>
+    <t xml:space="preserve">1.79510474205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92774796485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700476169586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237642288208</t>
+    <t xml:space="preserve">1.9277480840683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700488090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237654209137</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006219387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93659090995789</t>
+    <t xml:space="preserve">1.91006231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365907907486</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154800415039</t>
+    <t xml:space="preserve">2.05154824256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0869197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923413276672</t>
+    <t xml:space="preserve">2.08691954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923389434814</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039094924927</t>
+    <t xml:space="preserve">2.06039118766785</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353371620178</t>
+    <t xml:space="preserve">1.88353359699249</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427668094635</t>
+    <t xml:space="preserve">1.95427656173706</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163321971893</t>
+    <t xml:space="preserve">1.82163333892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130434513092</t>
+    <t xml:space="preserve">1.69783294200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130446434021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940420627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62709009647369</t>
+    <t xml:space="preserve">1.60940432548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171831607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60498285293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824703216553</t>
+    <t xml:space="preserve">1.59171843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6049827337265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824715137482</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762595653534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7243617773056</t>
+    <t xml:space="preserve">1.73762607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72436165809631</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -7226,7 +7226,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7252,7 +7252,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7278,7 +7278,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7304,7 +7304,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7356,7 +7356,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7382,7 +7382,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7408,7 +7408,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7434,7 +7434,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7460,7 +7460,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7486,7 +7486,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7512,7 +7512,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7538,7 +7538,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7564,7 +7564,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7616,7 +7616,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7642,7 +7642,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7668,7 +7668,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7720,7 +7720,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7746,7 +7746,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7772,7 +7772,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7798,7 +7798,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7824,7 +7824,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7850,7 +7850,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7876,7 +7876,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7902,7 +7902,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7928,7 +7928,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7954,7 +7954,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7980,7 +7980,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8006,7 +8006,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8032,7 +8032,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8084,7 +8084,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8110,7 +8110,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8136,7 +8136,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8188,7 +8188,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8214,7 +8214,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8266,7 +8266,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8292,7 +8292,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8318,7 +8318,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8344,7 +8344,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8370,7 +8370,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8396,7 +8396,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8448,7 +8448,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8474,7 +8474,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8500,7 +8500,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8526,7 +8526,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8552,7 +8552,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8604,7 +8604,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8630,7 +8630,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8656,7 +8656,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8682,7 +8682,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8708,7 +8708,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8734,7 +8734,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8760,7 +8760,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8786,7 +8786,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8812,7 +8812,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8864,7 +8864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8890,7 +8890,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8916,7 +8916,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8968,7 +8968,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8994,7 +8994,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9020,7 +9020,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9072,7 +9072,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9098,7 +9098,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9124,7 +9124,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9150,7 +9150,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9176,7 +9176,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9202,7 +9202,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9228,7 +9228,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9254,7 +9254,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9280,7 +9280,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9306,7 +9306,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9332,7 +9332,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9358,7 +9358,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9384,7 +9384,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9410,7 +9410,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9462,7 +9462,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9488,7 +9488,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9514,7 +9514,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9540,7 +9540,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9566,7 +9566,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9592,7 +9592,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9618,7 +9618,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9644,7 +9644,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9670,7 +9670,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9722,7 +9722,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9748,7 +9748,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9800,7 +9800,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9878,7 +9878,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9904,7 +9904,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9930,7 +9930,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10034,7 +10034,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10060,7 +10060,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10086,7 +10086,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10112,7 +10112,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10164,7 +10164,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10190,7 +10190,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10216,7 +10216,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10242,7 +10242,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10268,7 +10268,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10294,7 +10294,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10346,7 +10346,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10372,7 +10372,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10398,7 +10398,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10424,7 +10424,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10476,7 +10476,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10606,7 +10606,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10632,7 +10632,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10658,7 +10658,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10684,7 +10684,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10736,7 +10736,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10762,7 +10762,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10788,7 +10788,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10814,7 +10814,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10840,7 +10840,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10892,7 +10892,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10918,7 +10918,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10944,7 +10944,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10970,7 +10970,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10996,7 +10996,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11022,7 +11022,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11048,7 +11048,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11100,7 +11100,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11126,7 +11126,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11152,7 +11152,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11178,7 +11178,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11204,7 +11204,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11230,7 +11230,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11256,7 +11256,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11282,7 +11282,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11308,7 +11308,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11360,7 +11360,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11386,7 +11386,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11438,7 +11438,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11464,7 +11464,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11490,7 +11490,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11516,7 +11516,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11542,7 +11542,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11568,7 +11568,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11594,7 +11594,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11620,7 +11620,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11646,7 +11646,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11672,7 +11672,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11698,7 +11698,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11724,7 +11724,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11776,7 +11776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11802,7 +11802,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11828,7 +11828,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11854,7 +11854,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11880,7 +11880,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11906,7 +11906,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11932,7 +11932,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11958,7 +11958,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11984,7 +11984,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12010,7 +12010,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12036,7 +12036,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12062,7 +12062,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12088,7 +12088,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12114,7 +12114,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12140,7 +12140,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12166,7 +12166,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12192,7 +12192,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12218,7 +12218,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12244,7 +12244,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12270,7 +12270,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12322,7 +12322,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12348,7 +12348,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12374,7 +12374,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12400,7 +12400,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12426,7 +12426,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12452,7 +12452,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12478,7 +12478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12504,7 +12504,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12530,7 +12530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12582,7 +12582,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12608,7 +12608,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12634,7 +12634,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12686,7 +12686,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12712,7 +12712,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12738,7 +12738,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12790,7 +12790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12842,7 +12842,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12868,7 +12868,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12894,7 +12894,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12920,7 +12920,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12946,7 +12946,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12972,7 +12972,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12998,7 +12998,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13024,7 +13024,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13050,7 +13050,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13102,7 +13102,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13128,7 +13128,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13154,7 +13154,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13180,7 +13180,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13206,7 +13206,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13232,7 +13232,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13258,7 +13258,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13284,7 +13284,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13310,7 +13310,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13336,7 +13336,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13362,7 +13362,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13388,7 +13388,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13414,7 +13414,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13440,7 +13440,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13466,7 +13466,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13492,7 +13492,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13518,7 +13518,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13570,7 +13570,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13596,7 +13596,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13622,7 +13622,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13700,7 +13700,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13726,7 +13726,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13752,7 +13752,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13778,7 +13778,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13804,7 +13804,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13830,7 +13830,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13856,7 +13856,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13882,7 +13882,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13908,7 +13908,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13934,7 +13934,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13960,7 +13960,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13986,7 +13986,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14012,7 +14012,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14038,7 +14038,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14064,7 +14064,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14090,7 +14090,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14116,7 +14116,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14142,7 +14142,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14168,7 +14168,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14194,7 +14194,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14220,7 +14220,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14246,7 +14246,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14272,7 +14272,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14298,7 +14298,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14324,7 +14324,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14350,7 +14350,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14376,7 +14376,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14402,7 +14402,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14428,7 +14428,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14454,7 +14454,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14480,7 +14480,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14506,7 +14506,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14532,7 +14532,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14558,7 +14558,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14584,7 +14584,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14610,7 +14610,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14636,7 +14636,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14662,7 +14662,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14688,7 +14688,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14714,7 +14714,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14740,7 +14740,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14766,7 +14766,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14792,7 +14792,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14818,7 +14818,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14844,7 +14844,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14870,7 +14870,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14896,7 +14896,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14922,7 +14922,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14948,7 +14948,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14974,7 +14974,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15000,7 +15000,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15026,7 +15026,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15052,7 +15052,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15078,7 +15078,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15104,7 +15104,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15130,7 +15130,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15156,7 +15156,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15182,7 +15182,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15208,7 +15208,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15234,7 +15234,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15260,7 +15260,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15286,7 +15286,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15312,7 +15312,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15338,7 +15338,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15364,7 +15364,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15390,7 +15390,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15416,7 +15416,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15442,7 +15442,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15468,7 +15468,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15494,7 +15494,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15520,7 +15520,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15546,7 +15546,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15572,7 +15572,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15598,7 +15598,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15624,7 +15624,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15650,7 +15650,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15676,7 +15676,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15702,7 +15702,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15728,7 +15728,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15754,7 +15754,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15780,7 +15780,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15806,7 +15806,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15832,7 +15832,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15858,7 +15858,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15884,7 +15884,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15910,7 +15910,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15936,7 +15936,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15962,7 +15962,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15988,7 +15988,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16014,7 +16014,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16040,7 +16040,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16066,7 +16066,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16092,7 +16092,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16118,7 +16118,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16144,7 +16144,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16170,7 +16170,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16196,7 +16196,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16222,7 +16222,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16248,7 +16248,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16274,7 +16274,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16300,7 +16300,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16326,7 +16326,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16352,7 +16352,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16378,7 +16378,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16404,7 +16404,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16430,7 +16430,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16456,7 +16456,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16482,7 +16482,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16508,7 +16508,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16534,7 +16534,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16560,7 +16560,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16586,7 +16586,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16612,7 +16612,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16638,7 +16638,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16664,7 +16664,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16690,7 +16690,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16716,7 +16716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16742,7 +16742,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16768,7 +16768,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16794,7 +16794,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16820,7 +16820,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16846,7 +16846,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16872,7 +16872,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16898,7 +16898,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16924,7 +16924,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16950,7 +16950,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16976,7 +16976,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17002,7 +17002,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17028,7 +17028,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17054,7 +17054,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17080,7 +17080,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17106,7 +17106,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17132,7 +17132,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17158,7 +17158,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17184,7 +17184,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17210,7 +17210,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17236,7 +17236,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17262,7 +17262,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17288,7 +17288,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17314,7 +17314,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17340,7 +17340,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17366,7 +17366,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17392,7 +17392,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17418,7 +17418,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17444,7 +17444,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17470,7 +17470,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17496,7 +17496,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17522,7 +17522,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17548,7 +17548,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17574,7 +17574,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17600,7 +17600,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17626,7 +17626,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17652,7 +17652,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17678,7 +17678,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17704,7 +17704,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17730,7 +17730,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17756,7 +17756,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17782,7 +17782,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17808,7 +17808,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17834,7 +17834,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17860,7 +17860,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17886,7 +17886,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17912,7 +17912,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17938,7 +17938,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17964,7 +17964,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17990,7 +17990,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18016,7 +18016,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18042,7 +18042,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18068,7 +18068,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18094,7 +18094,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18120,7 +18120,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18146,7 +18146,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18172,7 +18172,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18198,7 +18198,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18224,7 +18224,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18250,7 +18250,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18276,7 +18276,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18302,7 +18302,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18328,7 +18328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18354,7 +18354,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18380,7 +18380,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18406,7 +18406,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18432,7 +18432,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18458,7 +18458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18484,7 +18484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18510,7 +18510,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18536,7 +18536,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18562,7 +18562,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18588,7 +18588,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18614,7 +18614,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18640,7 +18640,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18666,7 +18666,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18692,7 +18692,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18718,7 +18718,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18744,7 +18744,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18770,7 +18770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18796,7 +18796,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18822,7 +18822,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18848,7 +18848,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18874,7 +18874,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18900,7 +18900,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18926,7 +18926,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18952,7 +18952,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18978,7 +18978,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19004,7 +19004,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19030,7 +19030,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19056,7 +19056,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19082,7 +19082,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19108,7 +19108,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19134,7 +19134,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19160,7 +19160,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19186,7 +19186,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19212,7 +19212,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19238,7 +19238,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19264,7 +19264,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19290,7 +19290,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19316,7 +19316,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19342,7 +19342,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19368,7 +19368,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19394,7 +19394,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19420,7 +19420,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19446,7 +19446,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19472,7 +19472,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19498,7 +19498,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19524,7 +19524,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19550,7 +19550,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19576,7 +19576,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19602,7 +19602,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19628,7 +19628,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19654,7 +19654,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19680,7 +19680,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19706,7 +19706,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19732,7 +19732,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19758,7 +19758,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19784,7 +19784,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19810,7 +19810,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19836,7 +19836,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19862,7 +19862,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19888,7 +19888,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19914,7 +19914,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19940,7 +19940,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19966,7 +19966,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19992,7 +19992,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20018,7 +20018,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -67580,7 +67580,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>14579</v>
@@ -67601,6 +67601,32 @@
         <v>855</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493981481</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>8496</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>850</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504944324493</t>
+    <t xml:space="preserve">0.965504765510559</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">0.994893014431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980557322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978406846523285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95116925239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938316822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944718062877655</t>
+    <t xml:space="preserve">0.980557203292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97840690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169371604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053814411163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938376426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487484931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718182086945</t>
   </si>
   <si>
     <t xml:space="preserve">0.931816101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863005101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473690986633</t>
+    <t xml:space="preserve">0.8630051612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473631381989</t>
   </si>
   <si>
     <t xml:space="preserve">0.849386215209961</t>
@@ -83,34 +83,34 @@
     <t xml:space="preserve">0.900994539260864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878057479858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375712394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902427971363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899561047554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606409549713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844003677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8665891289711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466674804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820714890956879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807812929153442</t>
+    <t xml:space="preserve">0.878057658672333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88737565279007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428030967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606469154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844122886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866589069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466734409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820715010166168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807812869548798</t>
   </si>
   <si>
     <t xml:space="preserve">0.745452880859375</t>
@@ -128,163 +128,163 @@
     <t xml:space="preserve">0.723949432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774124205112457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800645053386688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802795469760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802366733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827882766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804945886135101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050523281097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834333896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634550571442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658847332001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207777023315</t>
+    <t xml:space="preserve">0.774124264717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459718227386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298799037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827882826328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333956241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634371757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658906936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880207896232605</t>
   </si>
   <si>
     <t xml:space="preserve">0.839351296424866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850819826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873039960861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340853214264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809263706207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977139472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225355625153</t>
+    <t xml:space="preserve">0.850819766521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040080070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340734004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977079868317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225296020508</t>
   </si>
   <si>
     <t xml:space="preserve">0.852970242500305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870889782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305874824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924761295319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86013799905777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830750048160553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704388141632</t>
+    <t xml:space="preserve">0.870889723300934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305815219879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924582481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860138058662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704328536987</t>
   </si>
   <si>
     <t xml:space="preserve">0.855120480060577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851536452770233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784907341003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449334621429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79921156167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893507957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858529567719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781291902065277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246420860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131102085114</t>
+    <t xml:space="preserve">0.851536631584167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421193599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784788131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449155807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799211502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893448352814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547253608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858410358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292140483856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875988960266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246480464935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817130982875824</t>
   </si>
   <si>
     <t xml:space="preserve">0.837917745113373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821431815624237</t>
+    <t xml:space="preserve">0.821431756019592</t>
   </si>
   <si>
     <t xml:space="preserve">0.814980626106262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812113702297211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396777629852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928367137909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194161891937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512215614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697491168976</t>
+    <t xml:space="preserve">0.812113583087921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396896839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026345729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512275218964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697550773621</t>
   </si>
   <si>
     <t xml:space="preserve">0.756921470165253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759788453578949</t>
+    <t xml:space="preserve">0.759788513183594</t>
   </si>
   <si>
     <t xml:space="preserve">0.76265561580658</t>
@@ -293,94 +293,91 @@
     <t xml:space="preserve">0.756204545497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750470340251923</t>
+    <t xml:space="preserve">0.750470459461212</t>
   </si>
   <si>
     <t xml:space="preserve">0.77914160490036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763372480869293</t>
+    <t xml:space="preserve">0.763372540473938</t>
   </si>
   <si>
     <t xml:space="preserve">0.767673075199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780575275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77555787563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159123897552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218458652496</t>
+    <t xml:space="preserve">0.780575215816498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557696819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627534389496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159004688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218518257141</t>
   </si>
   <si>
     <t xml:space="preserve">0.851380407810211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872164011001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937300682068</t>
+    <t xml:space="preserve">0.872164070606232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937241077423</t>
   </si>
   <si>
     <t xml:space="preserve">0.861029922962189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861772298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853607296943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576502323151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864741206169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834186077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83727753162384</t>
+    <t xml:space="preserve">0.861772358417511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85360723733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576383113861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864741265773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277472019196</t>
   </si>
   <si>
     <t xml:space="preserve">0.825401127338409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835050642490387</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.829112470149994</t>
   </si>
   <si>
     <t xml:space="preserve">0.83059698343277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858803153038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504182338715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84470009803772</t>
+    <t xml:space="preserve">0.85880309343338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844700157642365</t>
   </si>
   <si>
     <t xml:space="preserve">0.843957722187042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84618467092514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835792899131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833566188812256</t>
+    <t xml:space="preserve">0.846184551715851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83579295873642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833566069602966</t>
   </si>
   <si>
     <t xml:space="preserve">0.838761985301971</t>
@@ -389,85 +386,85 @@
     <t xml:space="preserve">0.816493928432465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916614055634</t>
+    <t xml:space="preserve">0.809813439846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916554450989</t>
   </si>
   <si>
     <t xml:space="preserve">0.810555875301361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817978620529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720817565918</t>
+    <t xml:space="preserve">0.801648676395416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817978501319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720877170563</t>
   </si>
   <si>
     <t xml:space="preserve">0.819462954998016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278258562088</t>
+    <t xml:space="preserve">0.826143443584442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81278270483017</t>
   </si>
   <si>
     <t xml:space="preserve">0.808329045772552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803133249282837</t>
+    <t xml:space="preserve">0.803133189678192</t>
   </si>
   <si>
     <t xml:space="preserve">0.805360019207001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796452641487122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906419754028</t>
+    <t xml:space="preserve">0.796452760696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906300544739</t>
   </si>
   <si>
     <t xml:space="preserve">0.790514647960663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791999161243439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791256785392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586848735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814267218112946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617702960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803185939789</t>
+    <t xml:space="preserve">0.791999220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791256904602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80758672952652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814267098903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617583751678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79867947101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794226050376892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803245544434</t>
   </si>
   <si>
     <t xml:space="preserve">0.779380559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777153730392456</t>
+    <t xml:space="preserve">0.777153849601746</t>
   </si>
   <si>
     <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788287937641144</t>
+    <t xml:space="preserve">0.788287818431854</t>
   </si>
   <si>
     <t xml:space="preserve">0.771957874298096</t>
@@ -479,10 +476,10 @@
     <t xml:space="preserve">0.806844413280487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774926960468292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442506790161</t>
+    <t xml:space="preserve">0.774927020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442566394806</t>
   </si>
   <si>
     <t xml:space="preserve">0.783834218978882</t>
@@ -491,49 +488,49 @@
     <t xml:space="preserve">0.765277564525604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778638303279877</t>
+    <t xml:space="preserve">0.778638362884521</t>
   </si>
   <si>
     <t xml:space="preserve">0.783091843128204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787545382976532</t>
+    <t xml:space="preserve">0.787545502185822</t>
   </si>
   <si>
     <t xml:space="preserve">0.786060988903046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774184703826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785318732261658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806102156639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452668190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411500453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215525150299</t>
+    <t xml:space="preserve">0.77418464422226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785318672657013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806102216243744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452548980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411440849304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215644359589</t>
   </si>
   <si>
     <t xml:space="preserve">0.852865159511566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845442414283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390721321106</t>
+    <t xml:space="preserve">0.845442473888397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390840530396</t>
   </si>
   <si>
     <t xml:space="preserve">0.862514436244965</t>
@@ -542,10 +539,10 @@
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855091691017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857318639755249</t>
+    <t xml:space="preserve">0.855091869831085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857318699359894</t>
   </si>
   <si>
     <t xml:space="preserve">0.832823812961578</t>
@@ -557,55 +554,55 @@
     <t xml:space="preserve">0.827627956867218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860287845134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349613189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867710411548615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880328953266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648524284363</t>
+    <t xml:space="preserve">0.860287666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349553585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86771035194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880328834056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648583889008</t>
   </si>
   <si>
     <t xml:space="preserve">0.919668972492218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923380374908447</t>
+    <t xml:space="preserve">0.923380494117737</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916700065135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545436382294</t>
+    <t xml:space="preserve">0.916700005531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091777324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545317173004</t>
   </si>
   <si>
     <t xml:space="preserve">0.915957748889923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911504089832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535182476044</t>
+    <t xml:space="preserve">0.91150426864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535063266754</t>
   </si>
   <si>
     <t xml:space="preserve">0.898885548114777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991669058799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792654514313</t>
+    <t xml:space="preserve">0.991668879985809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792714118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768968582153</t>
@@ -617,46 +614,46 @@
     <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06886494159698</t>
+    <t xml:space="preserve">1.06886506080627</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659688472748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05327725410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03249371051788</t>
+    <t xml:space="preserve">1.05327701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05179274082184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03249394893646</t>
   </si>
   <si>
     <t xml:space="preserve">1.02432870864868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03175127506256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467943191528</t>
+    <t xml:space="preserve">1.03175151348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01467931270599</t>
   </si>
   <si>
     <t xml:space="preserve">1.00206077098846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0228443145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03026700019836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05921530723572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06812250614166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04585456848145</t>
+    <t xml:space="preserve">1.02284443378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03026688098907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05921542644501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06812274456024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04585468769073</t>
   </si>
   <si>
     <t xml:space="preserve">1.06663799285889</t>
@@ -668,7 +665,7 @@
     <t xml:space="preserve">1.11191618442535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11933898925781</t>
+    <t xml:space="preserve">1.1193391084671</t>
   </si>
   <si>
     <t xml:space="preserve">1.117112159729</t>
@@ -686,31 +683,31 @@
     <t xml:space="preserve">1.21509158611298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2314213514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2173182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177183628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23216342926025</t>
+    <t xml:space="preserve">1.23142147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21731841564178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177171707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880269050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23216354846954</t>
   </si>
   <si>
     <t xml:space="preserve">1.22845220565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23513269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22474074363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286463737488</t>
+    <t xml:space="preserve">1.2351325750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22474098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286475658417</t>
   </si>
   <si>
     <t xml:space="preserve">1.21360695362091</t>
@@ -722,25 +719,25 @@
     <t xml:space="preserve">1.24700891971588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26779234409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923574924469</t>
+    <t xml:space="preserve">1.26779246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923586845398</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26036989688873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888514518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26927709579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521526813507</t>
+    <t xml:space="preserve">1.26036965847015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888526439667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26927697658539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521514892578</t>
   </si>
   <si>
     <t xml:space="preserve">1.30639028549194</t>
@@ -749,13 +746,13 @@
     <t xml:space="preserve">1.34424591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23958623409271</t>
+    <t xml:space="preserve">1.239586353302</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17426681518555</t>
+    <t xml:space="preserve">1.17426657676697</t>
   </si>
   <si>
     <t xml:space="preserve">1.17278230190277</t>
@@ -764,25 +761,25 @@
     <t xml:space="preserve">1.1653596162796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17055559158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17723572254181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649352550507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16387486457825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16164803504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15051424503326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15348327159882</t>
+    <t xml:space="preserve">1.17055547237396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17723596096039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16387498378754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16164815425873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15051400661469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348339080811</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824618816376</t>
@@ -794,10 +791,10 @@
     <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247280597687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28412234783173</t>
+    <t xml:space="preserve">1.20247292518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28412222862244</t>
   </si>
   <si>
     <t xml:space="preserve">1.28486454486847</t>
@@ -806,10 +803,10 @@
     <t xml:space="preserve">1.31307077407837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018408298492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.327916264534</t>
+    <t xml:space="preserve">1.35018420219421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32791602611542</t>
   </si>
   <si>
     <t xml:space="preserve">1.35834908485413</t>
@@ -818,10 +815,10 @@
     <t xml:space="preserve">1.34350371360779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33311200141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057306289673</t>
+    <t xml:space="preserve">1.33311188220978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057282447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
@@ -830,19 +827,19 @@
     <t xml:space="preserve">1.32855689525604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35816490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512793064117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031161785126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36651563644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37410748004913</t>
+    <t xml:space="preserve">1.35816466808319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512816905975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031137943268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36651575565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
     <t xml:space="preserve">1.39080929756165</t>
@@ -857,13 +854,13 @@
     <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36727476119995</t>
+    <t xml:space="preserve">1.36727488040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.3915684223175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232754707336</t>
+    <t xml:space="preserve">1.39232766628265</t>
   </si>
   <si>
     <t xml:space="preserve">1.38549506664276</t>
@@ -872,7 +869,7 @@
     <t xml:space="preserve">1.37258899211884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38701343536377</t>
+    <t xml:space="preserve">1.38701331615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.36879312992096</t>
@@ -887,7 +884,7 @@
     <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842623233795</t>
+    <t xml:space="preserve">1.33842611312866</t>
   </si>
   <si>
     <t xml:space="preserve">1.34298121929169</t>
@@ -899,31 +896,31 @@
     <t xml:space="preserve">1.29363477230072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29818999767303</t>
+    <t xml:space="preserve">1.29818987846375</t>
   </si>
   <si>
     <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32096493244171</t>
+    <t xml:space="preserve">1.320965051651</t>
   </si>
   <si>
     <t xml:space="preserve">1.31413245201111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36955225467682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536428451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37562572956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625419139862</t>
+    <t xml:space="preserve">1.36955237388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536440372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37562561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40143764019012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625407218933</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397657871246</t>
@@ -935,10 +932,10 @@
     <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37866234779358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38473570346832</t>
+    <t xml:space="preserve">1.37866246700287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38473582267761</t>
   </si>
   <si>
     <t xml:space="preserve">1.34829533100128</t>
@@ -947,19 +944,19 @@
     <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45230233669281</t>
+    <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164878368378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4773553609848</t>
+    <t xml:space="preserve">1.47735512256622</t>
   </si>
   <si>
     <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51835072040558</t>
+    <t xml:space="preserve">1.51835060119629</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568099975586</t>
@@ -971,13 +968,13 @@
     <t xml:space="preserve">1.52594244480133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51075899600983</t>
+    <t xml:space="preserve">1.51075887680054</t>
   </si>
   <si>
     <t xml:space="preserve">1.52897918224335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50316727161407</t>
+    <t xml:space="preserve">1.50316715240479</t>
   </si>
   <si>
     <t xml:space="preserve">1.53049755096436</t>
@@ -995,7 +992,7 @@
     <t xml:space="preserve">1.47887361049652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43484139442444</t>
+    <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
     <t xml:space="preserve">1.40599274635315</t>
@@ -1004,10 +1001,10 @@
     <t xml:space="preserve">1.38777244091034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33614873886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29059815406799</t>
+    <t xml:space="preserve">1.33614861965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2905980348587</t>
   </si>
   <si>
     <t xml:space="preserve">1.29970812797546</t>
@@ -1019,13 +1016,13 @@
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052264213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659599781036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48798382282257</t>
+    <t xml:space="preserve">1.47052276134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659611701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
     <t xml:space="preserve">1.48722445964813</t>
@@ -1043,34 +1040,34 @@
     <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39308679103851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40371513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182986736298</t>
+    <t xml:space="preserve">1.3930869102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40371525287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182998657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.36271965503693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36423814296722</t>
+    <t xml:space="preserve">1.36423826217651</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36499714851379</t>
+    <t xml:space="preserve">1.36499726772308</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575651168823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37107074260712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4272495508194</t>
+    <t xml:space="preserve">1.37107062339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42724967002869</t>
   </si>
   <si>
     <t xml:space="preserve">1.48039197921753</t>
@@ -1082,19 +1079,19 @@
     <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49177956581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50696313381195</t>
+    <t xml:space="preserve">1.49177968502045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50696325302124</t>
   </si>
   <si>
     <t xml:space="preserve">1.45761656761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43863725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37790334224701</t>
+    <t xml:space="preserve">1.43863713741302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37790310382843</t>
   </si>
   <si>
     <t xml:space="preserve">1.33235287666321</t>
@@ -1106,31 +1103,31 @@
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476103305817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753632545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161860466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716918945312</t>
+    <t xml:space="preserve">1.32476091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753620624542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337332725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161872386932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716930866241</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4424329996109</t>
+    <t xml:space="preserve">1.44243323802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.4538209438324</t>
@@ -1163,7 +1160,10 @@
     <t xml:space="preserve">1.47280025482178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51455473899841</t>
+    <t xml:space="preserve">1.5145548582077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.51551628112793</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">1.50376808643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49201989173889</t>
+    <t xml:space="preserve">1.49202001094818</t>
   </si>
   <si>
     <t xml:space="preserve">1.46852350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48027169704437</t>
+    <t xml:space="preserve">1.48027181625366</t>
   </si>
   <si>
     <t xml:space="preserve">1.46069145202637</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677542686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4724395275116</t>
+    <t xml:space="preserve">1.45677530765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
     <t xml:space="preserve">1.47635567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44111120700836</t>
+    <t xml:space="preserve">1.44111108779907</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278975009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40978264808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42153096199036</t>
+    <t xml:space="preserve">1.36278986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40978276729584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42153072357178</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936301231384</t>
@@ -1232,31 +1232,31 @@
     <t xml:space="preserve">1.45285928249359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39803433418274</t>
+    <t xml:space="preserve">1.39803457260132</t>
   </si>
   <si>
     <t xml:space="preserve">1.394118309021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34712564945221</t>
+    <t xml:space="preserve">1.3471257686615</t>
   </si>
   <si>
     <t xml:space="preserve">1.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33929359912872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30796492099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146142959595</t>
+    <t xml:space="preserve">1.26488816738129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33929347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30796504020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30404877662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146131038666</t>
   </si>
   <si>
     <t xml:space="preserve">1.28055262565613</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">1.2962167263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188094615936</t>
+    <t xml:space="preserve">1.31188106536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.34320962429047</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845420837402</t>
+    <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
     <t xml:space="preserve">1.32754528522491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28838467597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195035934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30013275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33537745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230058193207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28446865081787</t>
+    <t xml:space="preserve">1.28838455677032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195047855377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30013287067413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537757396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230082035065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28446877002716</t>
   </si>
   <si>
     <t xml:space="preserve">1.3157970905304</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761481761932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48810374736786</t>
+    <t xml:space="preserve">1.41761469841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48810398578644</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593591690063</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">1.5116001367569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52334845066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53509676456451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55076098442078</t>
+    <t xml:space="preserve">1.52334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53509664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55076086521149</t>
   </si>
   <si>
     <t xml:space="preserve">1.59775364398956</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">1.58992159366608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62124991416931</t>
+    <t xml:space="preserve">1.62124979496002</t>
   </si>
   <si>
     <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61341774463654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208930492401</t>
+    <t xml:space="preserve">1.61341786384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64474630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63691437244415</t>
+    <t xml:space="preserve">1.64474642276764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
     <t xml:space="preserve">1.65257835388184</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824281215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740330219269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439620018005</t>
+    <t xml:space="preserve">1.66824293136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740365982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439608097076</t>
   </si>
   <si>
     <t xml:space="preserve">1.74656403064728</t>
@@ -1391,112 +1391,112 @@
     <t xml:space="preserve">1.76222825050354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80138885974884</t>
+    <t xml:space="preserve">1.80138874053955</t>
   </si>
   <si>
     <t xml:space="preserve">1.84838163852692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77006053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7778924703598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922102928162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054958820343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187826633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404609680176</t>
+    <t xml:space="preserve">1.77006042003632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77789270877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82488524913788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922114849091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271718025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054970741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404597759247</t>
   </si>
   <si>
     <t xml:space="preserve">1.85621380805969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79355669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94236731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95803153514862</t>
+    <t xml:space="preserve">1.79355680942535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94236719608307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
     <t xml:space="preserve">1.97369587421417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99719190597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9658637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453514575958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670297622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178470134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942891597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662875652313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77956163883209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76338386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191742420197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573953151703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8038284778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82000637054443</t>
+    <t xml:space="preserve">1.99719202518463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96586346626282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91887104511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92670285701752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942903518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9656069278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662863731384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77956187725067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76338398456573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191718578339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80382823944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82000613212585</t>
   </si>
   <si>
     <t xml:space="preserve">1.8604508638382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82809519767761</t>
+    <t xml:space="preserve">1.82809495925903</t>
   </si>
   <si>
     <t xml:space="preserve">1.85236191749573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8928062915802</t>
+    <t xml:space="preserve">1.89280652999878</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">1.7714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94134032726288</t>
+    <t xml:space="preserve">1.90898442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9413400888443</t>
   </si>
   <si>
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751786231995</t>
+    <t xml:space="preserve">1.98987352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751798152924</t>
   </si>
   <si>
     <t xml:space="preserve">1.997962474823</t>
@@ -1538,34 +1538,34 @@
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516231536865</t>
+    <t xml:space="preserve">1.92516219615936</t>
   </si>
   <si>
     <t xml:space="preserve">1.7472060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75529503822327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631686687469</t>
+    <t xml:space="preserve">1.75529491901398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631674766541</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58542764186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56116080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4964497089386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41556036472321</t>
+    <t xml:space="preserve">1.58542776107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56116092205048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49644958972931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747153759003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4155604839325</t>
   </si>
   <si>
     <t xml:space="preserve">1.34276020526886</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">1.31849336624146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29827105998993</t>
+    <t xml:space="preserve">1.29827117919922</t>
   </si>
   <si>
     <t xml:space="preserve">1.17289304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19715976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951543331146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15267050266266</t>
+    <t xml:space="preserve">1.19715964794159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951531410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15267062187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">1.07178151607513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15671503543854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14053726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693746089935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09604811668396</t>
+    <t xml:space="preserve">1.15671515464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1405371427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693734169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09604823589325</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502628803253</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13649272918701</t>
+    <t xml:space="preserve">1.1364928483963</t>
   </si>
   <si>
     <t xml:space="preserve">1.16075944900513</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">1.24569320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26187109947205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30231547355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995980739594</t>
+    <t xml:space="preserve">1.26187098026276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30231559276581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995992660522</t>
   </si>
   <si>
     <t xml:space="preserve">1.25378203392029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20524871349335</t>
+    <t xml:space="preserve">1.20524859428406</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">1.18098187446594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21333754062653</t>
+    <t xml:space="preserve">1.21333742141724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031483650208</t>
+    <t xml:space="preserve">1.12031507492065</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862620830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10009264945984</t>
+    <t xml:space="preserve">1.14862608909607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10009276866913</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840378284454</t>
+    <t xml:space="preserve">1.12840390205383</t>
   </si>
   <si>
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760426044464</t>
+    <t xml:space="preserve">1.23760414123535</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20929300785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2497376203537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22142648696899</t>
+    <t xml:space="preserve">1.20929312705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24973750114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
     <t xml:space="preserve">1.1122260093689</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582592964172</t>
+    <t xml:space="preserve">1.07582604885101</t>
   </si>
   <si>
     <t xml:space="preserve">1.05964803695679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09200370311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08391487598419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07987034320831</t>
+    <t xml:space="preserve">1.09200382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08391499519348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
     <t xml:space="preserve">1.0556036233902</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">1.05155909061432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0232480764389</t>
+    <t xml:space="preserve">1.02324795722961</t>
   </si>
   <si>
     <t xml:space="preserve">1.02729249000549</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">1.00302577018738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982803344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954492151737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970670163631439</t>
+    <t xml:space="preserve">0.982803463935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954492211341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97067004442215</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">0.986847937107086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962581157684326</t>
+    <t xml:space="preserve">0.962581098079681</t>
   </si>
   <si>
     <t xml:space="preserve">0.966625571250916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978758931159973</t>
+    <t xml:space="preserve">0.978758990764618</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">1.10413706302643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23355984687805</t>
+    <t xml:space="preserve">1.23355972766876</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">1.20120418071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29422676563263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31040453910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32253789901733</t>
+    <t xml:space="preserve">1.29422664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31040441989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32253777980804</t>
   </si>
   <si>
     <t xml:space="preserve">1.32658231258392</t>
@@ -1790,22 +1790,22 @@
     <t xml:space="preserve">1.34680461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3346711397171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3872492313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46813833713531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51262736320496</t>
+    <t xml:space="preserve">1.33467125892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724935054779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4681384563446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51262748241425</t>
   </si>
   <si>
     <t xml:space="preserve">1.55307197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57733881473541</t>
+    <t xml:space="preserve">1.57733869552612</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284955024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51667177677155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53689420223236</t>
+    <t xml:space="preserve">1.53284966945648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51667189598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53689408302307</t>
   </si>
   <si>
     <t xml:space="preserve">1.581383228302</t>
@@ -1835,40 +1835,40 @@
     <t xml:space="preserve">1.58947217464447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57329440116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56520521640778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836088180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50049388408661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54902744293213</t>
+    <t xml:space="preserve">1.57329428195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56520533561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836076259613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.5247608423233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5288051366806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70676124095917</t>
+    <t xml:space="preserve">1.52880525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822780132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70676147937775</t>
   </si>
   <si>
     <t xml:space="preserve">1.69867241382599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69058358669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68249464035034</t>
+    <t xml:space="preserve">1.69058346748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68249452114105</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440569400787</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">1.72293937206268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61373889446259</t>
+    <t xml:space="preserve">1.6137387752533</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65013897418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60565006732941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205014705658</t>
+    <t xml:space="preserve">1.65013885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60564994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205002784729</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">1.61778330802917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71485018730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5571163892746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48431622982025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49240529537201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47218298912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351658821106</t>
+    <t xml:space="preserve">1.71485042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55711650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48431634902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49240517616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47218286991119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351670742035</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">1.35893797874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44791603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409392356873</t>
+    <t xml:space="preserve">1.44791615009308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409380435944</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59756100177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.609694480896</t>
+    <t xml:space="preserve">1.59756112098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60969436168671</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70976340770721</t>
+    <t xml:space="preserve">1.7097635269165</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68028473854065</t>
+    <t xml:space="preserve">1.68028485774994</t>
   </si>
   <si>
     <t xml:space="preserve">1.68449604511261</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343975067139</t>
+    <t xml:space="preserve">1.64659488201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343986988068</t>
   </si>
   <si>
     <t xml:space="preserve">1.63817250728607</t>
@@ -1991,31 +1991,31 @@
     <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61711621284485</t>
+    <t xml:space="preserve">1.61711609363556</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54973649978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58342623710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500374317169</t>
+    <t xml:space="preserve">1.54973638057709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58342635631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500386238098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59605991840363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56658124923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54552519321442</t>
+    <t xml:space="preserve">1.59606003761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56658136844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54552507400513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815887451172</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">1.47393405437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43182158470154</t>
+    <t xml:space="preserve">1.43182170391083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38970923423767</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4360328912735</t>
+    <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">1.44024407863617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4107654094696</t>
+    <t xml:space="preserve">1.41076529026031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">1.40234291553497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4613002538681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499022960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49077892303467</t>
+    <t xml:space="preserve">1.46130037307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49077904224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.54131388664246</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868008613586</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553870677948</t>
+    <t xml:space="preserve">1.62553858757019</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501737594604</t>
+    <t xml:space="preserve">1.65501749515533</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186224460602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61290490627289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184873104095</t>
+    <t xml:space="preserve">1.67186236381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61290502548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184885025024</t>
   </si>
   <si>
     <t xml:space="preserve">1.51604640483856</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48235654830933</t>
+    <t xml:space="preserve">1.48235642910004</t>
   </si>
   <si>
     <t xml:space="preserve">1.45708906650543</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763754367828</t>
+    <t xml:space="preserve">1.58763742446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
@@ -2162,37 +2162,37 @@
     <t xml:space="preserve">1.84452319145203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8393189907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584758758545</t>
+    <t xml:space="preserve">1.83931910991669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584770679474</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510462284088</t>
+    <t xml:space="preserve">1.79510474205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92774796485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700476169586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237642288208</t>
+    <t xml:space="preserve">1.9277480840683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700488090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237654209137</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006219387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93659090995789</t>
+    <t xml:space="preserve">1.91006231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365907907486</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154800415039</t>
+    <t xml:space="preserve">2.05154824256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0869197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923413276672</t>
+    <t xml:space="preserve">2.08691954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923389434814</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039094924927</t>
+    <t xml:space="preserve">2.06039118766785</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353371620178</t>
+    <t xml:space="preserve">1.88353359699249</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427668094635</t>
+    <t xml:space="preserve">1.95427656173706</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163321971893</t>
+    <t xml:space="preserve">1.82163333892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130434513092</t>
+    <t xml:space="preserve">1.69783294200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130446434021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940420627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62709009647369</t>
+    <t xml:space="preserve">1.60940432548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171831607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60498285293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824703216553</t>
+    <t xml:space="preserve">1.59171843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6049827337265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824715137482</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762595653534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7243617773056</t>
+    <t xml:space="preserve">1.73762607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72436165809631</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -7226,7 +7226,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7252,7 +7252,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7278,7 +7278,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7304,7 +7304,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7356,7 +7356,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7382,7 +7382,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7408,7 +7408,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7434,7 +7434,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7460,7 +7460,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7486,7 +7486,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7512,7 +7512,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7538,7 +7538,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7564,7 +7564,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7616,7 +7616,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7642,7 +7642,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7668,7 +7668,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7720,7 +7720,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7746,7 +7746,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7772,7 +7772,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7798,7 +7798,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7824,7 +7824,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7850,7 +7850,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7876,7 +7876,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7902,7 +7902,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7928,7 +7928,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7954,7 +7954,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7980,7 +7980,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8006,7 +8006,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8032,7 +8032,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8084,7 +8084,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8110,7 +8110,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8136,7 +8136,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8188,7 +8188,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8214,7 +8214,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8266,7 +8266,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8292,7 +8292,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8318,7 +8318,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8344,7 +8344,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8370,7 +8370,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8396,7 +8396,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8448,7 +8448,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8474,7 +8474,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8500,7 +8500,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8526,7 +8526,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8552,7 +8552,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8604,7 +8604,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8630,7 +8630,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8656,7 +8656,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8682,7 +8682,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8708,7 +8708,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8734,7 +8734,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8760,7 +8760,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8786,7 +8786,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8812,7 +8812,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8864,7 +8864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8890,7 +8890,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8916,7 +8916,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8968,7 +8968,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8994,7 +8994,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9020,7 +9020,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9072,7 +9072,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9098,7 +9098,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9124,7 +9124,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9150,7 +9150,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9176,7 +9176,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9202,7 +9202,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9228,7 +9228,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9254,7 +9254,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9280,7 +9280,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9306,7 +9306,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9332,7 +9332,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9358,7 +9358,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9384,7 +9384,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9410,7 +9410,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9462,7 +9462,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9488,7 +9488,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9514,7 +9514,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9540,7 +9540,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9566,7 +9566,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9592,7 +9592,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9618,7 +9618,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9644,7 +9644,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9670,7 +9670,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9722,7 +9722,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9748,7 +9748,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9800,7 +9800,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9878,7 +9878,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9904,7 +9904,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9930,7 +9930,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10034,7 +10034,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10060,7 +10060,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10086,7 +10086,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10112,7 +10112,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10164,7 +10164,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10190,7 +10190,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10216,7 +10216,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10242,7 +10242,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10268,7 +10268,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10294,7 +10294,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10346,7 +10346,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10372,7 +10372,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10398,7 +10398,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10424,7 +10424,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10476,7 +10476,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10606,7 +10606,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10632,7 +10632,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10658,7 +10658,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10684,7 +10684,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10736,7 +10736,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10762,7 +10762,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10788,7 +10788,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10814,7 +10814,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10840,7 +10840,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10892,7 +10892,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10918,7 +10918,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10944,7 +10944,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10970,7 +10970,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10996,7 +10996,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11022,7 +11022,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11048,7 +11048,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11100,7 +11100,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11126,7 +11126,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11152,7 +11152,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11178,7 +11178,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11204,7 +11204,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11230,7 +11230,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11256,7 +11256,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11282,7 +11282,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11308,7 +11308,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11360,7 +11360,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11386,7 +11386,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11438,7 +11438,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11464,7 +11464,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11490,7 +11490,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11516,7 +11516,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11542,7 +11542,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11568,7 +11568,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11594,7 +11594,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11620,7 +11620,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11646,7 +11646,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11672,7 +11672,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11698,7 +11698,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11724,7 +11724,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11776,7 +11776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11802,7 +11802,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11828,7 +11828,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11854,7 +11854,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11880,7 +11880,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11906,7 +11906,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11932,7 +11932,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11958,7 +11958,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11984,7 +11984,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12010,7 +12010,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12036,7 +12036,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12062,7 +12062,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12088,7 +12088,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12114,7 +12114,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12140,7 +12140,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12166,7 +12166,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12192,7 +12192,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12218,7 +12218,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12244,7 +12244,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12270,7 +12270,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12322,7 +12322,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12348,7 +12348,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12374,7 +12374,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12400,7 +12400,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12426,7 +12426,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12452,7 +12452,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12478,7 +12478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12504,7 +12504,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12530,7 +12530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12582,7 +12582,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12608,7 +12608,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12634,7 +12634,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12686,7 +12686,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12712,7 +12712,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12738,7 +12738,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12790,7 +12790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12842,7 +12842,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12868,7 +12868,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12894,7 +12894,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12920,7 +12920,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12946,7 +12946,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12972,7 +12972,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12998,7 +12998,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13024,7 +13024,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13050,7 +13050,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13102,7 +13102,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13128,7 +13128,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13154,7 +13154,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13180,7 +13180,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13206,7 +13206,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13232,7 +13232,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13258,7 +13258,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13284,7 +13284,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13310,7 +13310,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13336,7 +13336,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13362,7 +13362,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13388,7 +13388,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13414,7 +13414,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13440,7 +13440,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13466,7 +13466,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13492,7 +13492,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13518,7 +13518,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13570,7 +13570,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13596,7 +13596,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13622,7 +13622,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13700,7 +13700,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13726,7 +13726,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13752,7 +13752,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13778,7 +13778,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13804,7 +13804,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13830,7 +13830,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13856,7 +13856,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13882,7 +13882,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13908,7 +13908,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13934,7 +13934,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13960,7 +13960,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13986,7 +13986,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14012,7 +14012,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14038,7 +14038,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14064,7 +14064,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14090,7 +14090,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14116,7 +14116,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14142,7 +14142,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14168,7 +14168,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14194,7 +14194,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14220,7 +14220,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14246,7 +14246,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14272,7 +14272,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14298,7 +14298,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14324,7 +14324,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14350,7 +14350,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14376,7 +14376,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14402,7 +14402,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14428,7 +14428,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14454,7 +14454,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14480,7 +14480,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14506,7 +14506,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14532,7 +14532,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14558,7 +14558,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14584,7 +14584,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14610,7 +14610,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14636,7 +14636,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14662,7 +14662,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14688,7 +14688,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14714,7 +14714,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14740,7 +14740,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14766,7 +14766,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14792,7 +14792,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14818,7 +14818,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14844,7 +14844,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14870,7 +14870,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14896,7 +14896,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14922,7 +14922,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14948,7 +14948,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14974,7 +14974,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15000,7 +15000,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15026,7 +15026,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15052,7 +15052,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15078,7 +15078,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15104,7 +15104,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15130,7 +15130,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15156,7 +15156,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15182,7 +15182,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15208,7 +15208,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15234,7 +15234,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15260,7 +15260,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15286,7 +15286,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15312,7 +15312,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15338,7 +15338,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15364,7 +15364,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15390,7 +15390,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15416,7 +15416,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15442,7 +15442,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15468,7 +15468,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15494,7 +15494,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15520,7 +15520,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15546,7 +15546,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15572,7 +15572,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15598,7 +15598,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15624,7 +15624,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15650,7 +15650,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15676,7 +15676,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15702,7 +15702,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15728,7 +15728,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15754,7 +15754,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15780,7 +15780,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15806,7 +15806,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15832,7 +15832,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15858,7 +15858,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15884,7 +15884,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15910,7 +15910,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15936,7 +15936,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15962,7 +15962,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15988,7 +15988,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16014,7 +16014,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16040,7 +16040,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16066,7 +16066,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16092,7 +16092,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16118,7 +16118,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16144,7 +16144,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16170,7 +16170,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16196,7 +16196,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16222,7 +16222,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16248,7 +16248,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16274,7 +16274,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16300,7 +16300,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16326,7 +16326,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16352,7 +16352,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16378,7 +16378,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16404,7 +16404,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16430,7 +16430,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16456,7 +16456,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16482,7 +16482,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16508,7 +16508,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16534,7 +16534,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16560,7 +16560,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16586,7 +16586,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16612,7 +16612,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16638,7 +16638,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16664,7 +16664,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16690,7 +16690,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16716,7 +16716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16742,7 +16742,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16768,7 +16768,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16794,7 +16794,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16820,7 +16820,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16846,7 +16846,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16872,7 +16872,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16898,7 +16898,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16924,7 +16924,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16950,7 +16950,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16976,7 +16976,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17002,7 +17002,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17028,7 +17028,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17054,7 +17054,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17080,7 +17080,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17106,7 +17106,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17132,7 +17132,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17158,7 +17158,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17184,7 +17184,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17210,7 +17210,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17236,7 +17236,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17262,7 +17262,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17288,7 +17288,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17314,7 +17314,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17340,7 +17340,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17366,7 +17366,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17392,7 +17392,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17418,7 +17418,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17444,7 +17444,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17470,7 +17470,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17496,7 +17496,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17522,7 +17522,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17548,7 +17548,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17574,7 +17574,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17600,7 +17600,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17626,7 +17626,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17652,7 +17652,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17678,7 +17678,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17704,7 +17704,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17730,7 +17730,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17756,7 +17756,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17782,7 +17782,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17808,7 +17808,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17834,7 +17834,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17860,7 +17860,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17886,7 +17886,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17912,7 +17912,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17938,7 +17938,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17964,7 +17964,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17990,7 +17990,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18016,7 +18016,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18042,7 +18042,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18068,7 +18068,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18094,7 +18094,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18120,7 +18120,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18146,7 +18146,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18172,7 +18172,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18198,7 +18198,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18224,7 +18224,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18250,7 +18250,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18276,7 +18276,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18302,7 +18302,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18328,7 +18328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18354,7 +18354,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18380,7 +18380,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18406,7 +18406,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18432,7 +18432,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18458,7 +18458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18484,7 +18484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18510,7 +18510,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18536,7 +18536,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18562,7 +18562,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18588,7 +18588,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18614,7 +18614,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18640,7 +18640,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18666,7 +18666,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18692,7 +18692,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18718,7 +18718,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18744,7 +18744,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18770,7 +18770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18796,7 +18796,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18822,7 +18822,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18848,7 +18848,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18874,7 +18874,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18900,7 +18900,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18926,7 +18926,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18952,7 +18952,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18978,7 +18978,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19004,7 +19004,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19030,7 +19030,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19056,7 +19056,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19082,7 +19082,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19108,7 +19108,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19134,7 +19134,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19160,7 +19160,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19186,7 +19186,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19212,7 +19212,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19238,7 +19238,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19264,7 +19264,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19290,7 +19290,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19316,7 +19316,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19342,7 +19342,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19368,7 +19368,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19394,7 +19394,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19420,7 +19420,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19446,7 +19446,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19472,7 +19472,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19498,7 +19498,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19524,7 +19524,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19550,7 +19550,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19576,7 +19576,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19602,7 +19602,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19628,7 +19628,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19654,7 +19654,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19680,7 +19680,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19706,7 +19706,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19732,7 +19732,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19758,7 +19758,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19784,7 +19784,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19810,7 +19810,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19836,7 +19836,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19862,7 +19862,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19888,7 +19888,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19914,7 +19914,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19940,7 +19940,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19966,7 +19966,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19992,7 +19992,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20018,7 +20018,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -67892,7 +67892,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6789583333</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>10515</v>
@@ -67913,6 +67913,32 @@
         <v>848</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6485185185</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>8211</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>843</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965505003929138</t>
+    <t xml:space="preserve">0.965504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">0.994892835617065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980557262897491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978407025337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169312000275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053874015808</t>
+    <t xml:space="preserve">0.980557322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978406965732574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95116925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053814411163</t>
   </si>
   <si>
     <t xml:space="preserve">0.966938495635986</t>
@@ -65,49 +65,49 @@
     <t xml:space="preserve">0.960487425327301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944718062877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005042076111</t>
+    <t xml:space="preserve">0.944718360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816220283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005101680756</t>
   </si>
   <si>
     <t xml:space="preserve">0.874473571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84938633441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994479656219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057599067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88737565279007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428030967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560868740082</t>
+    <t xml:space="preserve">0.849386215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994539260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428090572357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560928344727</t>
   </si>
   <si>
     <t xml:space="preserve">0.871606469154358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898844182491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866589069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466615200043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820715010166168</t>
+    <t xml:space="preserve">0.898844063282013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866588950157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466674804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820714950561523</t>
   </si>
   <si>
     <t xml:space="preserve">0.807812929153442</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704237937927246</t>
+    <t xml:space="preserve">0.713197827339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117188930511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
     <t xml:space="preserve">0.723949432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774124205112457</t>
+    <t xml:space="preserve">0.774124264717102</t>
   </si>
   <si>
     <t xml:space="preserve">0.788459837436676</t>
@@ -140,232 +140,232 @@
     <t xml:space="preserve">0.80279541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298918247223</t>
+    <t xml:space="preserve">0.824298799037933</t>
   </si>
   <si>
     <t xml:space="preserve">0.845802247524261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827882826328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804945886135101</t>
+    <t xml:space="preserve">0.827882766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804945766925812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333777427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634431362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658847332001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88020783662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351296424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040080070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87734067440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809263706207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393052577972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895976960659027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85297018289566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924642086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860138058662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120360851288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536571979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421133995056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784907341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82644921541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79921156167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893329143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547194004059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858529567719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292080879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875929355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817130982875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431875228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113583087921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396777629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026345729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512156009674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697610378265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921470165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788453578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655675411224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470340251923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372480869293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673134803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575156211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557696819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627534389496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872164011001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029982566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85360723733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576502323151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864741384983063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834126472473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83727753162384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401067733765</t>
   </si>
   <si>
     <t xml:space="preserve">0.835050582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634610176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658906936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351296424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873040080070496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977079868317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225355625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85297030210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305874824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830750167369843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704507350922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120480060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536571979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784907341003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449155807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893329143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547194004059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858469963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781291961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875988960266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246361255646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817130982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917745113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431934833527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980685710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113583087921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928247928619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194102287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026226520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512275218964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921470165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204545497894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779141664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372480869293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673075199127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575156211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77555775642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79562771320343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159123897552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937300682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853607356548309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864741265773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834066867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401186943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050642490387</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.829112529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830597102642059</t>
+    <t xml:space="preserve">0.830597162246704</t>
   </si>
   <si>
     <t xml:space="preserve">0.85880321264267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839504361152649</t>
+    <t xml:space="preserve">0.839504241943359</t>
   </si>
   <si>
     <t xml:space="preserve">0.844700157642365</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">0.846184551715851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83579295873642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833566188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838762044906616</t>
+    <t xml:space="preserve">0.835792899131775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833566129207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761925697327</t>
   </si>
   <si>
     <t xml:space="preserve">0.816493988037109</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">0.809813499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823916673660278</t>
+    <t xml:space="preserve">0.823916554450989</t>
   </si>
   <si>
     <t xml:space="preserve">0.810555875301361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801648616790771</t>
+    <t xml:space="preserve">0.801648676395416</t>
   </si>
   <si>
     <t xml:space="preserve">0.81797844171524</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">0.819463014602661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826143443584442</t>
+    <t xml:space="preserve">0.826143503189087</t>
   </si>
   <si>
     <t xml:space="preserve">0.812782645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808328926563263</t>
+    <t xml:space="preserve">0.808328986167908</t>
   </si>
   <si>
     <t xml:space="preserve">0.803133130073547</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">0.805359899997711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796452701091766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906240940094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514647960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999101638794</t>
+    <t xml:space="preserve">0.796452641487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906360149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514588356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
     <t xml:space="preserve">0.791256785392761</t>
@@ -443,103 +443,103 @@
     <t xml:space="preserve">0.807586789131165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267098903656</t>
+    <t xml:space="preserve">0.814267158508301</t>
   </si>
   <si>
     <t xml:space="preserve">0.804617643356323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803245544434</t>
+    <t xml:space="preserve">0.79867959022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225990772247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803185939789</t>
   </si>
   <si>
     <t xml:space="preserve">0.779380559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777895987033844</t>
+    <t xml:space="preserve">0.777153789997101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
     <t xml:space="preserve">0.788287818431854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771957874298096</t>
+    <t xml:space="preserve">0.77195793390274</t>
   </si>
   <si>
     <t xml:space="preserve">0.838019549846649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806844472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442447185516</t>
+    <t xml:space="preserve">0.806844532489777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774927079677582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442506790161</t>
   </si>
   <si>
     <t xml:space="preserve">0.783834218978882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765277504920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778638303279877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091843128204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545442581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786060988903046</t>
+    <t xml:space="preserve">0.765277564525604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778638362884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091902732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545502185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78606104850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.77418464422226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318672657013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806102156639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452727794647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215644359589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865159511566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442473888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153816699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390661716461</t>
+    <t xml:space="preserve">0.785318732261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806102216243744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452608585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411440849304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215584754944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865099906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390780925751</t>
   </si>
   <si>
     <t xml:space="preserve">0.862514555454254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866225838661194</t>
+    <t xml:space="preserve">0.866225957870483</t>
   </si>
   <si>
     <t xml:space="preserve">0.855091750621796</t>
@@ -548,109 +548,109 @@
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823872566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834308266639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827627897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86028790473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349613189697</t>
+    <t xml:space="preserve">0.832823812961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834308385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827628016471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287725925446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349672794342</t>
   </si>
   <si>
     <t xml:space="preserve">0.867710471153259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880329012870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648583889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669091701508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380434513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91373085975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916700005531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091896533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545317173004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915957748889923</t>
+    <t xml:space="preserve">0.880328953266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669032096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380374908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913730800151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916700065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091717720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545376777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915957629680634</t>
   </si>
   <si>
     <t xml:space="preserve">0.911504209041595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908535122871399</t>
+    <t xml:space="preserve">0.908535063266754</t>
   </si>
   <si>
     <t xml:space="preserve">0.898885607719421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99166876077652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792654514313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768968582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06960725784302</t>
+    <t xml:space="preserve">0.991668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792773723602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768956661224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06960701942444</t>
   </si>
   <si>
     <t xml:space="preserve">1.07480299472809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0688648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04659676551819</t>
+    <t xml:space="preserve">1.06886494159698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04659688472748</t>
   </si>
   <si>
     <t xml:space="preserve">1.05327725410461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05179274082184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03249371051788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02432870864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03175139427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467943191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00206089019775</t>
+    <t xml:space="preserve">1.05179262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03249382972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02432858943939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03175151348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0146791934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00206065177917</t>
   </si>
   <si>
     <t xml:space="preserve">1.0228443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03026688098907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05921530723572</t>
+    <t xml:space="preserve">1.03026676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05921542644501</t>
   </si>
   <si>
     <t xml:space="preserve">1.06812250614166</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">1.06663811206818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449361801147</t>
+    <t xml:space="preserve">1.10449373722076</t>
   </si>
   <si>
     <t xml:space="preserve">1.11191618442535</t>
@@ -671,22 +671,22 @@
     <t xml:space="preserve">1.11933898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11711227893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12898850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160704612732</t>
+    <t xml:space="preserve">1.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1289883852005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762767314911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21509158611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2314213514328</t>
+    <t xml:space="preserve">1.21509146690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23142123222351</t>
   </si>
   <si>
     <t xml:space="preserve">1.2173182964325</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">1.23216366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22845232486725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23513281345367</t>
+    <t xml:space="preserve">1.22845220565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23513269424438</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474098205566</t>
@@ -716,31 +716,31 @@
     <t xml:space="preserve">1.21360695362091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20098853111267</t>
+    <t xml:space="preserve">1.20098841190338</t>
   </si>
   <si>
     <t xml:space="preserve">1.24700891971588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26779246330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2492356300354</t>
+    <t xml:space="preserve">1.26779234409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923574924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26036965847015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888514518738</t>
+    <t xml:space="preserve">1.26036977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888526439667</t>
   </si>
   <si>
     <t xml:space="preserve">1.26927697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521514892578</t>
+    <t xml:space="preserve">1.27521526813507</t>
   </si>
   <si>
     <t xml:space="preserve">1.30639028549194</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">1.34424591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23958611488342</t>
+    <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17426681518555</t>
+    <t xml:space="preserve">1.17426657676697</t>
   </si>
   <si>
     <t xml:space="preserve">1.17278230190277</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">1.17055547237396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1772358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649364471436</t>
+    <t xml:space="preserve">1.17723572254181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.16387498378754</t>
@@ -779,40 +779,40 @@
     <t xml:space="preserve">1.16164827346802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15051412582397</t>
+    <t xml:space="preserve">1.15051424503326</t>
   </si>
   <si>
     <t xml:space="preserve">1.15348327159882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12824630737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14383387565613</t>
+    <t xml:space="preserve">1.12824618816376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14383375644684</t>
   </si>
   <si>
     <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247292518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28412246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28486454486847</t>
+    <t xml:space="preserve">1.20247280597687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28412234783173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28486442565918</t>
   </si>
   <si>
     <t xml:space="preserve">1.31307065486908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018396377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35834908485413</t>
+    <t xml:space="preserve">1.35018408298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32791602611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35834896564484</t>
   </si>
   <si>
     <t xml:space="preserve">1.34350371360779</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057282447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34374034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32855701446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35816478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512804985046</t>
+    <t xml:space="preserve">1.35057294368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34374046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32855677604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35816466808319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512816905975</t>
   </si>
   <si>
     <t xml:space="preserve">1.37031137943268</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39080917835236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39688265323639</t>
+    <t xml:space="preserve">1.39080929756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39688277244568</t>
   </si>
   <si>
     <t xml:space="preserve">1.38169920444489</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36727476119995</t>
+    <t xml:space="preserve">1.36727488040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.3915684223175</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">1.38549506664276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701319694519</t>
+    <t xml:space="preserve">1.37258887290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701331615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.36879312992096</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">1.36120140552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3513320684433</t>
+    <t xml:space="preserve">1.35133218765259</t>
   </si>
   <si>
     <t xml:space="preserve">1.31565082073212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842635154724</t>
+    <t xml:space="preserve">1.33842611312866</t>
   </si>
   <si>
     <t xml:space="preserve">1.34298121929169</t>
@@ -896,19 +896,19 @@
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363489151001</t>
+    <t xml:space="preserve">1.29363477230072</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30122637748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32096517086029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31413245201111</t>
+    <t xml:space="preserve">1.30122649669647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32096493244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3141325712204</t>
   </si>
   <si>
     <t xml:space="preserve">1.36955237388611</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">1.37562584877014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143764019012</t>
+    <t xml:space="preserve">1.40143752098083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38625419139862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38397645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38929092884064</t>
+    <t xml:space="preserve">1.38397669792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38929104804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
@@ -947,67 +947,67 @@
     <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45230233669281</t>
+    <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630934238434</t>
+    <t xml:space="preserve">1.47735524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.51835060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54568099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379561424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51075887680054</t>
+    <t xml:space="preserve">1.54568111896515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379573345184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594244480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51075899600983</t>
   </si>
   <si>
     <t xml:space="preserve">1.52897918224335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5031670331955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53049755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53353428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746081352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51607322692871</t>
+    <t xml:space="preserve">1.50316739082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53049743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53353416919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746093273163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51607310771942</t>
   </si>
   <si>
     <t xml:space="preserve">1.47887349128723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43484127521515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40599286556244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38777244091034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3361485004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29059827327728</t>
+    <t xml:space="preserve">1.43484151363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40599274635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38777256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33614861965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29059815406799</t>
   </si>
   <si>
     <t xml:space="preserve">1.29970824718475</t>
@@ -1019,55 +1019,55 @@
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052252292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659599781036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48798370361328</t>
+    <t xml:space="preserve">1.47052276134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659611701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48798358440399</t>
   </si>
   <si>
     <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269456386566</t>
+    <t xml:space="preserve">1.42269468307495</t>
   </si>
   <si>
     <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41738033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40447437763214</t>
+    <t xml:space="preserve">1.41738045215607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371525287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36271989345551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423814296722</t>
+    <t xml:space="preserve">1.40371513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182986736298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36271965503693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423802375793</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36499738693237</t>
+    <t xml:space="preserve">1.36499714851379</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575651168823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37107074260712</t>
+    <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
     <t xml:space="preserve">1.42724967002869</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49557554721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49177968502045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50696301460266</t>
+    <t xml:space="preserve">1.49557542800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49177956581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
     <t xml:space="preserve">1.45761668682098</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">1.43863725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37790322303772</t>
+    <t xml:space="preserve">1.37790334224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.33235275745392</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">1.30957746505737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33994448184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32476103305817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753620624542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337332725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161872386932</t>
+    <t xml:space="preserve">1.33994460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32476091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753632545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337320804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161860466003</t>
   </si>
   <si>
     <t xml:space="preserve">1.31716918945312</t>
@@ -1124,37 +1124,37 @@
     <t xml:space="preserve">1.40827035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206622123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41965782642365</t>
+    <t xml:space="preserve">1.41206610202789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
     <t xml:space="preserve">1.44243323802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45382070541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46900415420532</t>
+    <t xml:space="preserve">1.45382082462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418784141541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46520853042603</t>
+    <t xml:space="preserve">1.46520829200745</t>
   </si>
   <si>
     <t xml:space="preserve">1.42345380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41586208343506</t>
+    <t xml:space="preserve">1.41586196422577</t>
   </si>
   <si>
     <t xml:space="preserve">1.45002484321594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46141254901886</t>
+    <t xml:space="preserve">1.46141242980957</t>
   </si>
   <si>
     <t xml:space="preserve">1.54112589359283</t>
@@ -1163,31 +1163,31 @@
     <t xml:space="preserve">1.47280013561249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51455473899841</t>
+    <t xml:space="preserve">1.5145548582077</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51551628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768423080444</t>
+    <t xml:space="preserve">1.51551640033722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768411159515</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726459503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51943254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376808643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49202001094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46852362155914</t>
+    <t xml:space="preserve">1.51943242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5037682056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49201989173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46852350234985</t>
   </si>
   <si>
     <t xml:space="preserve">1.48027181625366</t>
@@ -1196,28 +1196,28 @@
     <t xml:space="preserve">1.46069145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44894313812256</t>
+    <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
     <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677530765533</t>
+    <t xml:space="preserve">1.45677542686462</t>
   </si>
   <si>
     <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47635579109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44111120700836</t>
+    <t xml:space="preserve">1.47635567188263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44111108779907</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278998851776</t>
+    <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
     <t xml:space="preserve">1.40978252887726</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">1.42153084278107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936301231384</t>
+    <t xml:space="preserve">1.42936289310455</t>
   </si>
   <si>
     <t xml:space="preserve">1.43327903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45285928249359</t>
+    <t xml:space="preserve">1.45285940170288</t>
   </si>
   <si>
     <t xml:space="preserve">1.39803445339203</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">1.394118309021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3471257686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362926006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.34712564945221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362949848175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
@@ -1256,64 +1256,64 @@
     <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146142959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055262565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2962167263031</t>
+    <t xml:space="preserve">1.30404877662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146131038666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055250644684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29621684551239</t>
   </si>
   <si>
     <t xml:space="preserve">1.31188106536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34320962429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35104167461395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38628625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40586650371552</t>
+    <t xml:space="preserve">1.34320950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35104179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38628613948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4058666229248</t>
   </si>
   <si>
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845396995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3275454044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838467597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195059776306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30013275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3353773355484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230082035065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28446853160858</t>
+    <t xml:space="preserve">1.37845408916473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32754528522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2883847951889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195047855377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30013298988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230070114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
     <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31971323490143</t>
+    <t xml:space="preserve">1.31971299648285</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810386657715</t>
+    <t xml:space="preserve">1.48810398578644</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593591690063</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">1.49985206127167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51160025596619</t>
+    <t xml:space="preserve">1.5116001367569</t>
   </si>
   <si>
     <t xml:space="preserve">1.52334845066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53509676456451</t>
+    <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55076086521149</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">1.58992147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62124979496002</t>
+    <t xml:space="preserve">1.62124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.60558581352234</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62908208370209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64474642276764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63691425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65257847309113</t>
+    <t xml:space="preserve">1.62908220291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64474630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63691437244415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65257859230042</t>
   </si>
   <si>
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824305057526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740342140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439608097076</t>
+    <t xml:space="preserve">1.66824293136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740354061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439620018005</t>
   </si>
   <si>
     <t xml:space="preserve">1.74656403064728</t>
@@ -1394,40 +1394,40 @@
     <t xml:space="preserve">1.76222836971283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80138897895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838163852692</t>
+    <t xml:space="preserve">1.80138874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006042003632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7778924703598</t>
+    <t xml:space="preserve">1.77789258956909</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488524913788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80922114849091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271718025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971043586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404621601105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8562136888504</t>
+    <t xml:space="preserve">1.80922102928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271729946136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054958820343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971031665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404597759247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85621392726898</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355680942535</t>
@@ -1436,31 +1436,31 @@
     <t xml:space="preserve">1.94236719608307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95803117752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97369587421417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99719202518463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96586334705353</t>
+    <t xml:space="preserve">1.95803141593933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97369563579559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99719190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96586358547211</t>
   </si>
   <si>
     <t xml:space="preserve">1.93453526496887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670273780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178470134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942915439606</t>
+    <t xml:space="preserve">1.91887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92670285701752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178446292877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942879676819</t>
   </si>
   <si>
     <t xml:space="preserve">1.9656069278717</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">1.87662863731384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77956187725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76338386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191718578339</t>
+    <t xml:space="preserve">1.77956163883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76338398456573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
     <t xml:space="preserve">1.78765070438385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80382823944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82000613212585</t>
+    <t xml:space="preserve">1.79573941230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8038284778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82000625133514</t>
   </si>
   <si>
     <t xml:space="preserve">1.86045074462891</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">1.82809507846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85236179828644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89280652999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90089535713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88471758365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.85236191749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280641078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90089547634125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8847177028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
@@ -1520,28 +1520,28 @@
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
+    <t xml:space="preserve">1.90898418426514</t>
   </si>
   <si>
     <t xml:space="preserve">1.94133996963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93325102329254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751798152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99796259403229</t>
+    <t xml:space="preserve">1.93325114250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516219615936</t>
+    <t xml:space="preserve">1.92516231536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.7472060918808</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">1.75529503822327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66631674766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56924974918365</t>
+    <t xml:space="preserve">1.66631686687469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
     <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56116092205048</t>
+    <t xml:space="preserve">1.56116080284119</t>
   </si>
   <si>
     <t xml:space="preserve">1.49644958972931</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">1.34276020526886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31849336624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29827117919922</t>
+    <t xml:space="preserve">1.31849348545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29827105998993</t>
   </si>
   <si>
     <t xml:space="preserve">1.17289304733276</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">1.19715964794159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22951543331146</t>
+    <t xml:space="preserve">1.22951531410217</t>
   </si>
   <si>
     <t xml:space="preserve">1.15267062187195</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">1.01515901088715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16480398178101</t>
+    <t xml:space="preserve">1.1648041009903</t>
   </si>
   <si>
     <t xml:space="preserve">1.03538143634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178151607513</t>
+    <t xml:space="preserve">1.07178139686584</t>
   </si>
   <si>
     <t xml:space="preserve">1.15671503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14053726196289</t>
+    <t xml:space="preserve">1.1405371427536</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693746089935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09604823589325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502640724182</t>
+    <t xml:space="preserve">1.09604835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364928483963</t>
+    <t xml:space="preserve">1.13649272918701</t>
   </si>
   <si>
     <t xml:space="preserve">1.16075944900513</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">1.26187098026276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30231559276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995980739594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25378203392029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524859428406</t>
+    <t xml:space="preserve">1.3023157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995992660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.253781914711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524871349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
+    <t xml:space="preserve">1.18098199367523</t>
   </si>
   <si>
     <t xml:space="preserve">1.21333742141724</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031495571136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14458167552948</t>
+    <t xml:space="preserve">1.12031507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14458155632019</t>
   </si>
   <si>
     <t xml:space="preserve">1.11627054214478</t>
@@ -1679,37 +1679,37 @@
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840390205383</t>
+    <t xml:space="preserve">1.12840378284454</t>
   </si>
   <si>
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1688483953476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20929300785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24973750114441</t>
+    <t xml:space="preserve">1.16884851455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20929312705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
     <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
+    <t xml:space="preserve">1.07582592964172</t>
   </si>
   <si>
     <t xml:space="preserve">1.05964803695679</t>
@@ -1718,31 +1718,31 @@
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08391499519348</t>
+    <t xml:space="preserve">1.0839147567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05560350418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0232480764389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02729249000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00302577018738</t>
+    <t xml:space="preserve">1.0556036233902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155920982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324795722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0272923707962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00302565097809</t>
   </si>
   <si>
     <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492151737213</t>
+    <t xml:space="preserve">0.954492092132568</t>
   </si>
   <si>
     <t xml:space="preserve">0.970669984817505</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847937107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962581098079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966625511646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758990764618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01920342445374</t>
+    <t xml:space="preserve">0.986847817897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962581157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966625571250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978759050369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
     <t xml:space="preserve">1.10413718223572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23355972766876</t>
+    <t xml:space="preserve">1.23355984687805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">1.20120406150818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29422664642334</t>
+    <t xml:space="preserve">1.29422676563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.31040441989899</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4681384563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51262736320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55307197570801</t>
+    <t xml:space="preserve">1.46813833713531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51262748241425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55307185649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.57733881473541</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498302936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52071630954742</t>
+    <t xml:space="preserve">1.54498314857483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52071642875671</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284966945648</t>
+    <t xml:space="preserve">1.53284978866577</t>
   </si>
   <si>
     <t xml:space="preserve">1.51667189598083</t>
@@ -1835,16 +1835,16 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947217464447</t>
+    <t xml:space="preserve">1.58947229385376</t>
   </si>
   <si>
     <t xml:space="preserve">1.57329440116882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56520521640778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836076259613</t>
+    <t xml:space="preserve">1.56520533561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836064338684</t>
   </si>
   <si>
     <t xml:space="preserve">1.5004940032959</t>
@@ -1853,25 +1853,25 @@
     <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247608423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.52476072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52880537509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69867241382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69058346748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68249452114105</t>
+    <t xml:space="preserve">1.69867253303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69058358669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68249464035034</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440569400787</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.72293937206268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6137387752533</t>
+    <t xml:space="preserve">1.61373889446259</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205002784729</t>
+    <t xml:space="preserve">1.60565006732941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205014705658</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1907,40 +1907,40 @@
     <t xml:space="preserve">1.5571163892746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48431634902954</t>
+    <t xml:space="preserve">1.48431622982025</t>
   </si>
   <si>
     <t xml:space="preserve">1.49240517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47218286991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351670742035</t>
+    <t xml:space="preserve">1.47218298912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351658821106</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37107145786285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3306268453598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893797874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44791615009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409380435944</t>
+    <t xml:space="preserve">1.37107133865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33062672615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3589380979538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44791603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60160541534424</t>
+    <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
     <t xml:space="preserve">1.59756112098694</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72660851478577</t>
+    <t xml:space="preserve">1.72660839557648</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343998908997</t>
+    <t xml:space="preserve">1.64659488201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343986988068</t>
   </si>
   <si>
     <t xml:space="preserve">1.63817250728607</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64238357543945</t>
+    <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
     <t xml:space="preserve">1.61711609363556</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59605991840363</t>
+    <t xml:space="preserve">1.59606003761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
+    <t xml:space="preserve">1.53289151191711</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4360328912735</t>
+    <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499022960663</t>
+    <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077904224396</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.54131388664246</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868008613586</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869359970093</t>
+    <t xml:space="preserve">1.60869371891022</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60027134418488</t>
+    <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
     <t xml:space="preserve">1.62553858757019</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501737594604</t>
+    <t xml:space="preserve">1.65501749515533</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290490627289</t>
+    <t xml:space="preserve">1.61290502548218</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184885025024</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025759220123</t>
+    <t xml:space="preserve">1.52025771141052</t>
   </si>
   <si>
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763754367828</t>
+    <t xml:space="preserve">1.58763742446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
@@ -67947,7 +67947,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6853819444</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>17138</v>
@@ -67968,6 +67968,32 @@
         <v>839</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6514583333</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>27610</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>849</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="857">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892954826355</t>
+    <t xml:space="preserve">0.994893014431</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978407025337219</t>
+    <t xml:space="preserve">0.978406965732574</t>
   </si>
   <si>
     <t xml:space="preserve">0.95116925239563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959053754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487484931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9447181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005042076111</t>
+    <t xml:space="preserve">0.959053874015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938376426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487425327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718241691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816041469574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005101680756</t>
   </si>
   <si>
     <t xml:space="preserve">0.874473631381989</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">0.849386155605316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900994658470154</t>
+    <t xml:space="preserve">0.900994598865509</t>
   </si>
   <si>
     <t xml:space="preserve">0.878057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88737565279007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428150177002</t>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902427971363068</t>
   </si>
   <si>
     <t xml:space="preserve">0.899560928344727</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">0.898844063282013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866588890552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466555595398</t>
+    <t xml:space="preserve">0.866589069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466674804688</t>
   </si>
   <si>
     <t xml:space="preserve">0.820714950561523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812869548798</t>
+    <t xml:space="preserve">0.807812929153442</t>
   </si>
   <si>
     <t xml:space="preserve">0.74545282125473</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">0.713197708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731117308139801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704238057136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723949432373047</t>
+    <t xml:space="preserve">0.731117248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704237937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723949491977692</t>
   </si>
   <si>
     <t xml:space="preserve">0.774124205112457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788459956645966</t>
+    <t xml:space="preserve">0.788459837436676</t>
   </si>
   <si>
     <t xml:space="preserve">0.800645112991333</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">0.802795469760895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802307128906</t>
+    <t xml:space="preserve">0.824298799037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802366733551</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">0.804945826530457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835050642490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834333896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634490966797</t>
+    <t xml:space="preserve">0.835050523281097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333777427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634550571442</t>
   </si>
   <si>
     <t xml:space="preserve">0.886658847332001</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">0.880207896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839351296424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873040199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340734004974</t>
+    <t xml:space="preserve">0.839351236820221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819885730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87304025888443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340614795685</t>
   </si>
   <si>
     <t xml:space="preserve">0.888809144496918</t>
@@ -185,34 +185,34 @@
     <t xml:space="preserve">0.892393231391907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895977020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225355625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85297018289566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305934429169</t>
+    <t xml:space="preserve">0.895976901054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225415229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852970123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305815219879</t>
   </si>
   <si>
     <t xml:space="preserve">0.880924701690674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830750048160553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704268932343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120480060577</t>
+    <t xml:space="preserve">0.860137939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704388141632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120539665222</t>
   </si>
   <si>
     <t xml:space="preserve">0.851536571979523</t>
@@ -227,31 +227,31 @@
     <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893329143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547194004059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858529567719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781291961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875988960266</t>
+    <t xml:space="preserve">0.79921156167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893388748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292080879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875929355621</t>
   </si>
   <si>
     <t xml:space="preserve">0.80924654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817131102085114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917804718018</t>
+    <t xml:space="preserve">0.817131161689758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917685508728</t>
   </si>
   <si>
     <t xml:space="preserve">0.821431815624237</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">0.814980745315552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812113523483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396837234497</t>
+    <t xml:space="preserve">0.812113583087921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396777629852</t>
   </si>
   <si>
     <t xml:space="preserve">0.799928367137909</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">0.794194161891937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787026166915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921410560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788572788239</t>
+    <t xml:space="preserve">0.787026286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512275218964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921470165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788513183594</t>
   </si>
   <si>
     <t xml:space="preserve">0.76265561580658</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">0.763372540473938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767673194408417</t>
+    <t xml:space="preserve">0.767673134803772</t>
   </si>
   <si>
     <t xml:space="preserve">0.780575275421143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77555775642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627653598785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159123897552</t>
+    <t xml:space="preserve">0.775557816028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159183502197</t>
   </si>
   <si>
     <t xml:space="preserve">0.842218458652496</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">0.851380527019501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872164070606232</t>
+    <t xml:space="preserve">0.872164011001587</t>
   </si>
   <si>
     <t xml:space="preserve">0.869937181472778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861029922962189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576383113861</t>
+    <t xml:space="preserve">0.861029982566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576442718506</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741265773773</t>
@@ -347,16 +347,19 @@
     <t xml:space="preserve">0.855834186077118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837277412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83059698343277</t>
+    <t xml:space="preserve">0.837277472019196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401127338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112589359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830597043037415</t>
   </si>
   <si>
     <t xml:space="preserve">0.85880309343338</t>
@@ -365,22 +368,22 @@
     <t xml:space="preserve">0.839504241943359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84469997882843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843957841396332</t>
+    <t xml:space="preserve">0.84470009803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843957781791687</t>
   </si>
   <si>
     <t xml:space="preserve">0.84618467092514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83579295873642</t>
+    <t xml:space="preserve">0.835792899131775</t>
   </si>
   <si>
     <t xml:space="preserve">0.833566129207611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838761985301971</t>
+    <t xml:space="preserve">0.838762044906616</t>
   </si>
   <si>
     <t xml:space="preserve">0.816494047641754</t>
@@ -389,64 +392,64 @@
     <t xml:space="preserve">0.809813559055328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823916614055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810555875301361</t>
+    <t xml:space="preserve">0.823916554450989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810555815696716</t>
   </si>
   <si>
     <t xml:space="preserve">0.801648616790771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817978501319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720757961273</t>
+    <t xml:space="preserve">0.81797856092453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720817565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.819462954998016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278270483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808329105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133130073547</t>
+    <t xml:space="preserve">0.826143443584442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808329164981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133189678192</t>
   </si>
   <si>
     <t xml:space="preserve">0.805359899997711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796452701091766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514707565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999161243439</t>
+    <t xml:space="preserve">0.796452641487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906300544739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514647960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999101638794</t>
   </si>
   <si>
     <t xml:space="preserve">0.791256904602051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807586848735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814267158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617702960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798679649829865</t>
+    <t xml:space="preserve">0.807586789131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814267098903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617583751678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798679530620575</t>
   </si>
   <si>
     <t xml:space="preserve">0.794225931167603</t>
@@ -455,34 +458,34 @@
     <t xml:space="preserve">0.786803245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77938050031662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777895987033844</t>
+    <t xml:space="preserve">0.779380559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77715390920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
     <t xml:space="preserve">0.788287818431854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771957874298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838019728660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927020072937</t>
+    <t xml:space="preserve">0.771957814693451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838019669055939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844413280487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774927079677582</t>
   </si>
   <si>
     <t xml:space="preserve">0.773442566394806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783834218978882</t>
+    <t xml:space="preserve">0.783834159374237</t>
   </si>
   <si>
     <t xml:space="preserve">0.765277564525604</t>
@@ -491,10 +494,10 @@
     <t xml:space="preserve">0.778638303279877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783091902732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545502185822</t>
+    <t xml:space="preserve">0.783091962337494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545561790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.78606104850769</t>
@@ -503,46 +506,46 @@
     <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318613052368</t>
+    <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
     <t xml:space="preserve">0.806102156639099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868452548980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411500453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215584754944</t>
+    <t xml:space="preserve">0.868452668190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411381244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215644359589</t>
   </si>
   <si>
     <t xml:space="preserve">0.852865099906921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845442414283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153697490692</t>
+    <t xml:space="preserve">0.845442354679108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153757095337</t>
   </si>
   <si>
     <t xml:space="preserve">0.874390840530396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862514495849609</t>
+    <t xml:space="preserve">0.86251437664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85509181022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857318639755249</t>
+    <t xml:space="preserve">0.855091750621796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857318580150604</t>
   </si>
   <si>
     <t xml:space="preserve">0.832823753356934</t>
@@ -551,61 +554,61 @@
     <t xml:space="preserve">0.834308385848999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827627897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86028778553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349672794342</t>
+    <t xml:space="preserve">0.827627956867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287725925446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349553585052</t>
   </si>
   <si>
     <t xml:space="preserve">0.86771035194397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880329012870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648643493652</t>
+    <t xml:space="preserve">0.880328834056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648583889008</t>
   </si>
   <si>
     <t xml:space="preserve">0.919669032096863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923380374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913730978965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916700005531311</t>
+    <t xml:space="preserve">0.923380434513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913730919361115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916700184345245</t>
   </si>
   <si>
     <t xml:space="preserve">0.927091717720032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931545376777649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915957689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504209041595</t>
+    <t xml:space="preserve">0.931545317173004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915957808494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504149436951</t>
   </si>
   <si>
     <t xml:space="preserve">0.908535122871399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898885548114777</t>
+    <t xml:space="preserve">0.898885667324066</t>
   </si>
   <si>
     <t xml:space="preserve">0.991668939590454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979792654514313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768968582153</t>
+    <t xml:space="preserve">0.979792833328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768956661224</t>
   </si>
   <si>
     <t xml:space="preserve">1.06960701942444</t>
@@ -614,28 +617,28 @@
     <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0688648223877</t>
+    <t xml:space="preserve">1.06886470317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659676551819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05327725410461</t>
+    <t xml:space="preserve">1.05327701568604</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249371051788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02432882785797</t>
+    <t xml:space="preserve">1.03249382972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02432894706726</t>
   </si>
   <si>
     <t xml:space="preserve">1.03175139427185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467907428741</t>
+    <t xml:space="preserve">1.0146791934967</t>
   </si>
   <si>
     <t xml:space="preserve">1.00206077098846</t>
@@ -644,10 +647,10 @@
     <t xml:space="preserve">1.02284419536591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03026700019836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0592155456543</t>
+    <t xml:space="preserve">1.03026688098907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05921542644501</t>
   </si>
   <si>
     <t xml:space="preserve">1.06812262535095</t>
@@ -659,13 +662,13 @@
     <t xml:space="preserve">1.06663811206818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449373722076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11191618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11933898925781</t>
+    <t xml:space="preserve">1.10449361801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11191642284393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1193391084671</t>
   </si>
   <si>
     <t xml:space="preserve">1.117112159729</t>
@@ -674,7 +677,7 @@
     <t xml:space="preserve">1.12898850440979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14160704612732</t>
+    <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
@@ -683,16 +686,16 @@
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23142147064209</t>
+    <t xml:space="preserve">1.2314213514328</t>
   </si>
   <si>
     <t xml:space="preserve">1.21731817722321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22177195549011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880280971527</t>
+    <t xml:space="preserve">1.22177183628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880269050598</t>
   </si>
   <si>
     <t xml:space="preserve">1.23216366767883</t>
@@ -707,7 +710,7 @@
     <t xml:space="preserve">1.22474098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286451816559</t>
+    <t xml:space="preserve">1.21286463737488</t>
   </si>
   <si>
     <t xml:space="preserve">1.21360683441162</t>
@@ -716,13 +719,13 @@
     <t xml:space="preserve">1.20098829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700903892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779222488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923586845398</t>
+    <t xml:space="preserve">1.24700880050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26779246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923574924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
@@ -734,19 +737,19 @@
     <t xml:space="preserve">1.25888526439667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26927697658539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639040470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34424614906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.239586353302</t>
+    <t xml:space="preserve">1.2692768573761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
@@ -755,16 +758,16 @@
     <t xml:space="preserve">1.17426669597626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17278230190277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055523395538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17723572254181</t>
+    <t xml:space="preserve">1.17278218269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1653596162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055547237396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1772358417511</t>
   </si>
   <si>
     <t xml:space="preserve">1.17649352550507</t>
@@ -776,31 +779,31 @@
     <t xml:space="preserve">1.16164827346802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15051424503326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1534835100174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12824618816376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14383387565613</t>
+    <t xml:space="preserve">1.15051412582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12824630737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14383375644684</t>
   </si>
   <si>
     <t xml:space="preserve">1.18911218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247280597687</t>
+    <t xml:space="preserve">1.20247292518616</t>
   </si>
   <si>
     <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28486454486847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31307077407837</t>
+    <t xml:space="preserve">1.28486466407776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31307065486908</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
@@ -809,10 +812,10 @@
     <t xml:space="preserve">1.32791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35834896564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34350347518921</t>
+    <t xml:space="preserve">1.35834908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3435035943985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311200141907</t>
@@ -824,19 +827,19 @@
     <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32855689525604</t>
+    <t xml:space="preserve">1.32855677604675</t>
   </si>
   <si>
     <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031137943268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36651563644409</t>
+    <t xml:space="preserve">1.35512816905975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031149864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36651575565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.37410736083984</t>
@@ -845,7 +848,7 @@
     <t xml:space="preserve">1.39080929756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39688265323639</t>
+    <t xml:space="preserve">1.39688277244568</t>
   </si>
   <si>
     <t xml:space="preserve">1.38169932365417</t>
@@ -857,7 +860,7 @@
     <t xml:space="preserve">1.36727488040924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3915684223175</t>
+    <t xml:space="preserve">1.39156830310822</t>
   </si>
   <si>
     <t xml:space="preserve">1.39232754707336</t>
@@ -866,31 +869,31 @@
     <t xml:space="preserve">1.38549506664276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701331615448</t>
+    <t xml:space="preserve">1.37258887290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701343536377</t>
   </si>
   <si>
     <t xml:space="preserve">1.36879301071167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120128631592</t>
+    <t xml:space="preserve">1.36120140552521</t>
   </si>
   <si>
     <t xml:space="preserve">1.35133218765259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31565082073212</t>
+    <t xml:space="preserve">1.3156510591507</t>
   </si>
   <si>
     <t xml:space="preserve">1.33842611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3429811000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868755817413</t>
+    <t xml:space="preserve">1.34298121929169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868767738342</t>
   </si>
   <si>
     <t xml:space="preserve">1.29363477230072</t>
@@ -899,40 +902,40 @@
     <t xml:space="preserve">1.29818987846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30122649669647</t>
+    <t xml:space="preserve">1.30122661590576</t>
   </si>
   <si>
     <t xml:space="preserve">1.320965051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31413233280182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3695524930954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536428451538</t>
+    <t xml:space="preserve">1.3141325712204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36955225467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536440372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143752098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625407218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397669792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38929092884064</t>
+    <t xml:space="preserve">1.40143764019012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625419139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38929104804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37866258621216</t>
+    <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
     <t xml:space="preserve">1.38473582267761</t>
@@ -941,7 +944,7 @@
     <t xml:space="preserve">1.34829545021057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42497229576111</t>
+    <t xml:space="preserve">1.42497205734253</t>
   </si>
   <si>
     <t xml:space="preserve">1.4523024559021</t>
@@ -950,28 +953,28 @@
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630958080292</t>
+    <t xml:space="preserve">1.47735524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.51835060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54568111896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379573345184</t>
+    <t xml:space="preserve">1.54568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379561424255</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594244480133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51075899600983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52897918224335</t>
+    <t xml:space="preserve">1.51075887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52897906303406</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316727161407</t>
@@ -980,16 +983,16 @@
     <t xml:space="preserve">1.53049755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53353416919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746093273163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51607322692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47887361049652</t>
+    <t xml:space="preserve">1.53353428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746081352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51607298851013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47887349128723</t>
   </si>
   <si>
     <t xml:space="preserve">1.43484139442444</t>
@@ -998,13 +1001,13 @@
     <t xml:space="preserve">1.40599274635315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38777267932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33614861965179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2905980348587</t>
+    <t xml:space="preserve">1.38777232170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3361485004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29059815406799</t>
   </si>
   <si>
     <t xml:space="preserve">1.29970824718475</t>
@@ -1016,31 +1019,31 @@
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052264213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659623622894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48798358440399</t>
+    <t xml:space="preserve">1.47052276134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659599781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
     <t xml:space="preserve">1.48722457885742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269444465637</t>
+    <t xml:space="preserve">1.42269456386566</t>
   </si>
   <si>
     <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41738045215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40447437763214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39308679103851</t>
+    <t xml:space="preserve">1.41738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40447449684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3930869102478</t>
   </si>
   <si>
     <t xml:space="preserve">1.40371513366699</t>
@@ -1049,16 +1052,16 @@
     <t xml:space="preserve">1.37182986736298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36271965503693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423826217651</t>
+    <t xml:space="preserve">1.36271977424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36499738693237</t>
+    <t xml:space="preserve">1.36499726772308</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575639247894</t>
@@ -1067,10 +1070,10 @@
     <t xml:space="preserve">1.37107074260712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4272495508194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039197921753</t>
+    <t xml:space="preserve">1.42724967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039186000824</t>
   </si>
   <si>
     <t xml:space="preserve">1.4993714094162</t>
@@ -1079,40 +1082,40 @@
     <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49177968502045</t>
+    <t xml:space="preserve">1.49177956581116</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761656761169</t>
+    <t xml:space="preserve">1.45761668682098</t>
   </si>
   <si>
     <t xml:space="preserve">1.43863725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37790322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33235263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30957758426666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33994448184967</t>
+    <t xml:space="preserve">1.3779034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33235275745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30957746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33994436264038</t>
   </si>
   <si>
     <t xml:space="preserve">1.32476091384888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34753620624542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161860466003</t>
+    <t xml:space="preserve">1.34753632545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337332725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161848545074</t>
   </si>
   <si>
     <t xml:space="preserve">1.31716918945312</t>
@@ -1121,22 +1124,22 @@
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965782642365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44243323802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45382082462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46900427341461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418796062469</t>
+    <t xml:space="preserve">1.44243311882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45382070541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46900415420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520829200745</t>
@@ -1145,25 +1148,22 @@
     <t xml:space="preserve">1.42345380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41586208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002472400665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46141254901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54112589359283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47280025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51455497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418784141541</t>
+    <t xml:space="preserve">1.41586184501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002484321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46141242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54112601280212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47280013561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51455473899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.51551628112793</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">1.50376808643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49201989173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46852350234985</t>
+    <t xml:space="preserve">1.49202001094818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46852362155914</t>
   </si>
   <si>
     <t xml:space="preserve">1.48027181625366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46069157123566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44894337654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46460747718811</t>
+    <t xml:space="preserve">1.46069133281708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44894325733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46460735797882</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677542686462</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">1.47635567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44111108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4254469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36278986930847</t>
+    <t xml:space="preserve">1.44111120700836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42544710636139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36278975009918</t>
   </si>
   <si>
     <t xml:space="preserve">1.40978264808655</t>
@@ -1226,19 +1226,19 @@
     <t xml:space="preserve">1.42936301231384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43327915668488</t>
+    <t xml:space="preserve">1.43327903747559</t>
   </si>
   <si>
     <t xml:space="preserve">1.45285928249359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39803445339203</t>
+    <t xml:space="preserve">1.39803433418274</t>
   </si>
   <si>
     <t xml:space="preserve">1.39411842823029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3471257686615</t>
+    <t xml:space="preserve">1.34712564945221</t>
   </si>
   <si>
     <t xml:space="preserve">1.32362937927246</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">1.30404889583588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33146142959595</t>
+    <t xml:space="preserve">1.33146131038666</t>
   </si>
   <si>
     <t xml:space="preserve">1.28055250644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2962167263031</t>
+    <t xml:space="preserve">1.29621660709381</t>
   </si>
   <si>
     <t xml:space="preserve">1.31188094615936</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845408916473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32754528522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838455677032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195035934448</t>
+    <t xml:space="preserve">1.37845420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3275454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195059776306</t>
   </si>
   <si>
     <t xml:space="preserve">1.30013287067413</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31971311569214</t>
+    <t xml:space="preserve">1.31971299648285</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1328,43 +1328,43 @@
     <t xml:space="preserve">1.49593591690063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49985206127167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51160025596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334868907928</t>
+    <t xml:space="preserve">1.49985194206238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5116001367569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334856987</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55076098442078</t>
+    <t xml:space="preserve">1.55076086521149</t>
   </si>
   <si>
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62124979496002</t>
+    <t xml:space="preserve">1.58992159366608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61341798305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208930492401</t>
+    <t xml:space="preserve">1.61341774463654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64474642276764</t>
+    <t xml:space="preserve">1.64474618434906</t>
   </si>
   <si>
     <t xml:space="preserve">1.63691425323486</t>
@@ -1379,49 +1379,49 @@
     <t xml:space="preserve">1.66824281215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70740354061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439608097076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74656403064728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222813129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80138885974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838140010834</t>
+    <t xml:space="preserve">1.70740342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439620018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74656391143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222848892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80138874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006030082703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77789270877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922091007233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271729946136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054958820343</t>
+    <t xml:space="preserve">1.7778924703598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82488536834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922102928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271718025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054946899414</t>
   </si>
   <si>
     <t xml:space="preserve">1.87971031665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87187826633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404585838318</t>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404609680176</t>
   </si>
   <si>
     <t xml:space="preserve">1.85621380805969</t>
@@ -1430,115 +1430,115 @@
     <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94236743450165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97369587421417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99719178676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9658637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670285701752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942879676819</t>
+    <t xml:space="preserve">1.94236719608307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95803141593933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97369563579559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99719214439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96586358547211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453526496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9267030954361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178470134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942903518677</t>
   </si>
   <si>
     <t xml:space="preserve">1.9656069278717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87662851810455</t>
+    <t xml:space="preserve">1.87662863731384</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956175804138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338398456573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765082359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573965072632</t>
+    <t xml:space="preserve">1.76338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191742420197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573953151703</t>
   </si>
   <si>
     <t xml:space="preserve">1.80382835865021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82000625133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8604508638382</t>
+    <t xml:space="preserve">1.82000637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86045062541962</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809507846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85236203670502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8928062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90089523792267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88471746444702</t>
+    <t xml:space="preserve">1.85236191749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280641078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90089535713196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88471758365631</t>
   </si>
   <si>
     <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86853981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83618402481079</t>
+    <t xml:space="preserve">1.86853969097137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83618414402008</t>
   </si>
   <si>
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9413400888443</t>
+    <t xml:space="preserve">1.90898430347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94134020805359</t>
   </si>
   <si>
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987352848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751774311066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.997962474823</t>
+    <t xml:space="preserve">1.98987376689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751786231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516231536865</t>
+    <t xml:space="preserve">1.92516207695007</t>
   </si>
   <si>
     <t xml:space="preserve">1.74720597267151</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">1.75529491901398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66631674766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56924974918365</t>
+    <t xml:space="preserve">1.66631686687469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
     <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56116092205048</t>
+    <t xml:space="preserve">1.56116080284119</t>
   </si>
   <si>
     <t xml:space="preserve">1.49644958972931</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">1.31849336624146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29827129840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17289292812347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715964794159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951531410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15267062187195</t>
+    <t xml:space="preserve">1.29827117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17289304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951543331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15267050266266</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">1.03538131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178151607513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15671515464783</t>
+    <t xml:space="preserve">1.07178139686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15671503543854</t>
   </si>
   <si>
     <t xml:space="preserve">1.1405371427536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693734169006</t>
+    <t xml:space="preserve">1.17693746089935</t>
   </si>
   <si>
     <t xml:space="preserve">1.09604823589325</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18907082080841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1364928483963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24569320678711</t>
+    <t xml:space="preserve">1.18907070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13649272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075956821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24569308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">1.3023157119751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995992660522</t>
+    <t xml:space="preserve">1.26995980739594</t>
   </si>
   <si>
     <t xml:space="preserve">1.25378203392029</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
+    <t xml:space="preserve">1.18098199367523</t>
   </si>
   <si>
     <t xml:space="preserve">1.21333754062653</t>
@@ -1658,37 +1658,37 @@
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031507492065</t>
+    <t xml:space="preserve">1.12031495571136</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11627054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14862608909607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10009276866913</t>
+    <t xml:space="preserve">1.11627042293549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14862620830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10009264945984</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840390205383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.12840378284454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24164879322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.2173820734024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1688483953476</t>
+    <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
     <t xml:space="preserve">1.20929312705994</t>
@@ -1700,64 +1700,64 @@
     <t xml:space="preserve">1.22142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0596479177475</t>
+    <t xml:space="preserve">1.07582592964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05964803695679</t>
   </si>
   <si>
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08391487598419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07987034320831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560350418091</t>
+    <t xml:space="preserve">1.0839147567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0798704624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0556036233902</t>
   </si>
   <si>
     <t xml:space="preserve">1.05155909061432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02324783802032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0272923707962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00302577018738</t>
+    <t xml:space="preserve">1.02324795722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02729249000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00302565097809</t>
   </si>
   <si>
     <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97067004442215</t>
+    <t xml:space="preserve">0.954492151737213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970670104026794</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847937107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962581157684326</t>
+    <t xml:space="preserve">0.986847817897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962581038475037</t>
   </si>
   <si>
     <t xml:space="preserve">0.966625571250916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978758871555328</t>
+    <t xml:space="preserve">0.978758931159973</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
@@ -1766,43 +1766,43 @@
     <t xml:space="preserve">1.10413718223572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23355972766876</t>
+    <t xml:space="preserve">1.23355984687805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120418071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29422676563263</t>
+    <t xml:space="preserve">1.20120406150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
     <t xml:space="preserve">1.31040441989899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32253789901733</t>
+    <t xml:space="preserve">1.32253777980804</t>
   </si>
   <si>
     <t xml:space="preserve">1.32658231258392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680449962616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33467137813568</t>
+    <t xml:space="preserve">1.34680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33467125892639</t>
   </si>
   <si>
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4681384563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51262748241425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55307197570801</t>
+    <t xml:space="preserve">1.46813857555389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51262736320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55307185649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.57733869552612</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">1.54498302936554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52071642875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453865528107</t>
+    <t xml:space="preserve">1.52071630954742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
     <t xml:space="preserve">1.53284966945648</t>
@@ -1835,16 +1835,16 @@
     <t xml:space="preserve">1.58947217464447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57329428195953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56520533561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836064338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50049412250519</t>
+    <t xml:space="preserve">1.57329440116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56520521640778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836076259613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">1.54902756214142</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">1.52880525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65822780132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70676147937775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69867241382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69058346748352</t>
+    <t xml:space="preserve">1.65822803974152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70676136016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6986722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
     <t xml:space="preserve">1.68249464035034</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">1.67440569400787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72293949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61373889446259</t>
+    <t xml:space="preserve">1.72293937206268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6137387752533</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1886,52 +1886,52 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205002784729</t>
+    <t xml:space="preserve">1.60565006732941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205014705658</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61778342723846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71485030651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55711650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48431622982025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49240505695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47218286991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351670742035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50858306884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37107145786285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3306268453598</t>
+    <t xml:space="preserve">1.61778330802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71485018730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48431634902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49240517616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47218298912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50858283042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37107133865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33062672615051</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893797874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44791615009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409380435944</t>
+    <t xml:space="preserve">1.44791603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
@@ -1940,22 +1940,22 @@
     <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59756100177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.609694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75187575817108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72660839557648</t>
+    <t xml:space="preserve">1.59756112098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75187587738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72660851478577</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70976340770721</t>
+    <t xml:space="preserve">1.7097635269165</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">1.64659488201141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63817238807678</t>
+    <t xml:space="preserve">1.66343986988068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63817250728607</t>
   </si>
   <si>
     <t xml:space="preserve">1.62974977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66765117645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64238369464874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61711621284485</t>
+    <t xml:space="preserve">1.66765105724335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64238357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61711609363556</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58342635631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500386238098</t>
+    <t xml:space="preserve">1.58342623710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500374317169</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59606003761292</t>
+    <t xml:space="preserve">1.59605991840363</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5118350982666</t>
+    <t xml:space="preserve">1.53289151191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51183521747589</t>
   </si>
   <si>
     <t xml:space="preserve">1.47393405437469</t>
@@ -2039,37 +2039,37 @@
     <t xml:space="preserve">1.38970923423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3981317281723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603301048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44866669178009</t>
+    <t xml:space="preserve">1.39813160896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4360328912735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4486665725708</t>
   </si>
   <si>
     <t xml:space="preserve">1.41497659683228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44024407863617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4107654094696</t>
+    <t xml:space="preserve">1.44024419784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41076529026031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40234303474426</t>
+    <t xml:space="preserve">1.40234291553497</t>
   </si>
   <si>
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49077892303467</t>
+    <t xml:space="preserve">1.49499022960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49077904224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131376743317</t>
+    <t xml:space="preserve">1.54131400585175</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868032455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869371891022</t>
+    <t xml:space="preserve">1.60869359970093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553870677948</t>
+    <t xml:space="preserve">1.62553858757019</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">1.59184873104095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604628562927</t>
+    <t xml:space="preserve">1.51604652404785</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2144,55 +2144,55 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025771141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57079255580902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58763742446899</t>
+    <t xml:space="preserve">1.52025759220123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57079243659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58763754367828</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79398846626282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84452331066132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8393189907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584758758545</t>
+    <t xml:space="preserve">1.79398834705353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84452319145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83931910991669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584770679474</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510462284088</t>
+    <t xml:space="preserve">1.79510474205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92774796485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700476169586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237642288208</t>
+    <t xml:space="preserve">1.9277480840683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700488090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237654209137</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006219387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93659090995789</t>
+    <t xml:space="preserve">1.91006231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365907907486</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154800415039</t>
+    <t xml:space="preserve">2.05154824256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0869197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923413276672</t>
+    <t xml:space="preserve">2.08691954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923389434814</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039094924927</t>
+    <t xml:space="preserve">2.06039118766785</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353371620178</t>
+    <t xml:space="preserve">1.88353359699249</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427668094635</t>
+    <t xml:space="preserve">1.95427656173706</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163321971893</t>
+    <t xml:space="preserve">1.82163333892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130434513092</t>
+    <t xml:space="preserve">1.69783294200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130446434021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940420627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62709009647369</t>
+    <t xml:space="preserve">1.60940432548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171831607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60498285293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824703216553</t>
+    <t xml:space="preserve">1.59171843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6049827337265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824715137482</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762595653534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7243617773056</t>
+    <t xml:space="preserve">1.73762607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72436165809631</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -2580,6 +2580,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.45000004768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3199999332428</t>
   </si>
 </sst>
 </file>
@@ -7226,7 +7229,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7252,7 +7255,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7278,7 +7281,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7304,7 +7307,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7330,7 +7333,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7356,7 +7359,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7382,7 +7385,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7408,7 +7411,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7434,7 +7437,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7460,7 +7463,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7486,7 +7489,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7512,7 +7515,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7538,7 +7541,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7564,7 +7567,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7590,7 +7593,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7616,7 +7619,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7642,7 +7645,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7668,7 +7671,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7720,7 +7723,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7746,7 +7749,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7772,7 +7775,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7798,7 +7801,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7824,7 +7827,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7850,7 +7853,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7876,7 +7879,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7902,7 +7905,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7928,7 +7931,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7954,7 +7957,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7980,7 +7983,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8006,7 +8009,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8032,7 +8035,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8058,7 +8061,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8084,7 +8087,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8110,7 +8113,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8136,7 +8139,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8162,7 +8165,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8188,7 +8191,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8214,7 +8217,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8240,7 +8243,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8266,7 +8269,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8292,7 +8295,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8318,7 +8321,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8344,7 +8347,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8370,7 +8373,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8396,7 +8399,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8422,7 +8425,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8448,7 +8451,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8474,7 +8477,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8500,7 +8503,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8526,7 +8529,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8552,7 +8555,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8578,7 +8581,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8604,7 +8607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8630,7 +8633,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8656,7 +8659,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8682,7 +8685,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8708,7 +8711,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8734,7 +8737,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8760,7 +8763,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8786,7 +8789,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8812,7 +8815,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8838,7 +8841,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8864,7 +8867,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8890,7 +8893,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8916,7 +8919,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8942,7 +8945,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8968,7 +8971,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8994,7 +8997,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9020,7 +9023,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9046,7 +9049,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9072,7 +9075,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9098,7 +9101,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9124,7 +9127,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9150,7 +9153,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9176,7 +9179,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9202,7 +9205,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9228,7 +9231,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9254,7 +9257,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9280,7 +9283,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9306,7 +9309,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9332,7 +9335,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9358,7 +9361,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9384,7 +9387,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9410,7 +9413,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9462,7 +9465,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9488,7 +9491,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9514,7 +9517,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9540,7 +9543,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9566,7 +9569,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9592,7 +9595,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9618,7 +9621,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9644,7 +9647,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9670,7 +9673,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9696,7 +9699,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9722,7 +9725,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9748,7 +9751,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9800,7 +9803,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9826,7 +9829,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9852,7 +9855,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9878,7 +9881,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9904,7 +9907,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9930,7 +9933,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9956,7 +9959,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10034,7 +10037,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10060,7 +10063,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10086,7 +10089,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10112,7 +10115,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10138,7 +10141,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10164,7 +10167,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10190,7 +10193,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10216,7 +10219,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10242,7 +10245,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10268,7 +10271,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10294,7 +10297,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10346,7 +10349,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10372,7 +10375,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10398,7 +10401,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10424,7 +10427,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10450,7 +10453,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10476,7 +10479,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10606,7 +10609,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10632,7 +10635,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10658,7 +10661,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10684,7 +10687,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10710,7 +10713,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10736,7 +10739,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10762,7 +10765,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10788,7 +10791,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10814,7 +10817,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10840,7 +10843,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10866,7 +10869,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10892,7 +10895,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10918,7 +10921,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10944,7 +10947,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10970,7 +10973,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10996,7 +10999,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11022,7 +11025,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11048,7 +11051,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11074,7 +11077,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11100,7 +11103,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11126,7 +11129,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11152,7 +11155,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11178,7 +11181,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11204,7 +11207,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11230,7 +11233,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11256,7 +11259,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11282,7 +11285,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11308,7 +11311,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11334,7 +11337,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11360,7 +11363,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11386,7 +11389,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11412,7 +11415,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11438,7 +11441,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11464,7 +11467,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11490,7 +11493,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11516,7 +11519,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11542,7 +11545,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11568,7 +11571,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11594,7 +11597,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11620,7 +11623,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11646,7 +11649,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11672,7 +11675,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11698,7 +11701,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11724,7 +11727,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11750,7 +11753,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11776,7 +11779,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11802,7 +11805,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11828,7 +11831,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11854,7 +11857,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11880,7 +11883,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11906,7 +11909,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11932,7 +11935,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11958,7 +11961,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11984,7 +11987,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12010,7 +12013,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12036,7 +12039,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12062,7 +12065,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12088,7 +12091,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12114,7 +12117,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12140,7 +12143,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12166,7 +12169,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12192,7 +12195,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12218,7 +12221,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12244,7 +12247,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12270,7 +12273,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12296,7 +12299,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12322,7 +12325,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12348,7 +12351,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12374,7 +12377,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12400,7 +12403,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12426,7 +12429,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12452,7 +12455,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12478,7 +12481,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12504,7 +12507,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12530,7 +12533,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12556,7 +12559,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12582,7 +12585,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12608,7 +12611,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12634,7 +12637,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12660,7 +12663,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12686,7 +12689,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12712,7 +12715,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12738,7 +12741,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12764,7 +12767,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12790,7 +12793,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12816,7 +12819,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12842,7 +12845,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12868,7 +12871,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12894,7 +12897,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12920,7 +12923,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12946,7 +12949,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12972,7 +12975,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12998,7 +13001,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13024,7 +13027,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13050,7 +13053,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13076,7 +13079,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13102,7 +13105,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13128,7 +13131,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13154,7 +13157,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13180,7 +13183,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13206,7 +13209,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13232,7 +13235,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13258,7 +13261,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13284,7 +13287,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13310,7 +13313,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13336,7 +13339,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13362,7 +13365,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13388,7 +13391,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13414,7 +13417,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13440,7 +13443,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13466,7 +13469,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13492,7 +13495,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13518,7 +13521,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13544,7 +13547,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13570,7 +13573,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13596,7 +13599,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13622,7 +13625,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13648,7 +13651,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13674,7 +13677,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13700,7 +13703,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13726,7 +13729,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13752,7 +13755,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13778,7 +13781,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13804,7 +13807,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13830,7 +13833,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13856,7 +13859,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13882,7 +13885,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13908,7 +13911,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13934,7 +13937,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13960,7 +13963,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13986,7 +13989,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14012,7 +14015,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14038,7 +14041,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14064,7 +14067,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14090,7 +14093,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14116,7 +14119,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14142,7 +14145,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14168,7 +14171,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14194,7 +14197,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14220,7 +14223,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14246,7 +14249,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14272,7 +14275,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14298,7 +14301,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14324,7 +14327,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14350,7 +14353,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14376,7 +14379,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14402,7 +14405,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14428,7 +14431,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14454,7 +14457,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14480,7 +14483,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14506,7 +14509,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14532,7 +14535,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14558,7 +14561,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14584,7 +14587,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14610,7 +14613,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14636,7 +14639,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14662,7 +14665,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14688,7 +14691,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14714,7 +14717,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14740,7 +14743,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14766,7 +14769,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14792,7 +14795,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14818,7 +14821,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14844,7 +14847,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14870,7 +14873,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14896,7 +14899,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14922,7 +14925,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14948,7 +14951,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14974,7 +14977,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15000,7 +15003,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15026,7 +15029,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15052,7 +15055,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15078,7 +15081,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15104,7 +15107,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15130,7 +15133,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15156,7 +15159,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15182,7 +15185,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15208,7 +15211,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15234,7 +15237,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15260,7 +15263,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15286,7 +15289,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15312,7 +15315,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15338,7 +15341,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15364,7 +15367,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15390,7 +15393,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15416,7 +15419,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15442,7 +15445,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15468,7 +15471,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15494,7 +15497,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15520,7 +15523,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15546,7 +15549,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15572,7 +15575,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15598,7 +15601,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15624,7 +15627,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15650,7 +15653,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15676,7 +15679,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15702,7 +15705,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15728,7 +15731,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15754,7 +15757,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15780,7 +15783,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15806,7 +15809,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15832,7 +15835,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15858,7 +15861,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15884,7 +15887,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15910,7 +15913,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15936,7 +15939,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15962,7 +15965,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15988,7 +15991,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16014,7 +16017,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16040,7 +16043,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16066,7 +16069,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16092,7 +16095,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16118,7 +16121,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16144,7 +16147,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16170,7 +16173,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16196,7 +16199,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16222,7 +16225,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16248,7 +16251,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16274,7 +16277,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16300,7 +16303,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16326,7 +16329,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16352,7 +16355,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16378,7 +16381,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16404,7 +16407,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16430,7 +16433,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16456,7 +16459,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16482,7 +16485,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16508,7 +16511,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16534,7 +16537,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16560,7 +16563,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16586,7 +16589,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16612,7 +16615,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16638,7 +16641,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16664,7 +16667,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16690,7 +16693,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16716,7 +16719,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16742,7 +16745,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16768,7 +16771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16794,7 +16797,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16820,7 +16823,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16846,7 +16849,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16872,7 +16875,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16898,7 +16901,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16924,7 +16927,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16950,7 +16953,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16976,7 +16979,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17002,7 +17005,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17028,7 +17031,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17054,7 +17057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17080,7 +17083,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17106,7 +17109,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17132,7 +17135,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17158,7 +17161,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17184,7 +17187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17210,7 +17213,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17236,7 +17239,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17262,7 +17265,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17288,7 +17291,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17314,7 +17317,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17340,7 +17343,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17366,7 +17369,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17392,7 +17395,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17418,7 +17421,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17444,7 +17447,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17470,7 +17473,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17496,7 +17499,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17522,7 +17525,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17548,7 +17551,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17574,7 +17577,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17600,7 +17603,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17626,7 +17629,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17652,7 +17655,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17678,7 +17681,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17704,7 +17707,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17730,7 +17733,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17756,7 +17759,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17782,7 +17785,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17808,7 +17811,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17834,7 +17837,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17860,7 +17863,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17886,7 +17889,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17912,7 +17915,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17938,7 +17941,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17964,7 +17967,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17990,7 +17993,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18016,7 +18019,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18042,7 +18045,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18068,7 +18071,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18094,7 +18097,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18120,7 +18123,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18146,7 +18149,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18172,7 +18175,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18198,7 +18201,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18224,7 +18227,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18250,7 +18253,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18276,7 +18279,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18302,7 +18305,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18328,7 +18331,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18354,7 +18357,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18380,7 +18383,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18406,7 +18409,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18432,7 +18435,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18458,7 +18461,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18484,7 +18487,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18510,7 +18513,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18536,7 +18539,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18562,7 +18565,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18588,7 +18591,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18614,7 +18617,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18640,7 +18643,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18666,7 +18669,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18692,7 +18695,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18718,7 +18721,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18744,7 +18747,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18770,7 +18773,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18796,7 +18799,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18822,7 +18825,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18848,7 +18851,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18874,7 +18877,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18900,7 +18903,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18926,7 +18929,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18952,7 +18955,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18978,7 +18981,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19004,7 +19007,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19030,7 +19033,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19056,7 +19059,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19082,7 +19085,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19108,7 +19111,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19134,7 +19137,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19160,7 +19163,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19186,7 +19189,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19212,7 +19215,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19238,7 +19241,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19264,7 +19267,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19290,7 +19293,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19316,7 +19319,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19342,7 +19345,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19368,7 +19371,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19394,7 +19397,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19420,7 +19423,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19446,7 +19449,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19472,7 +19475,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19498,7 +19501,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19524,7 +19527,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19550,7 +19553,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19576,7 +19579,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19602,7 +19605,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19628,7 +19631,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19654,7 +19657,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19680,7 +19683,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19706,7 +19709,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19732,7 +19735,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19758,7 +19761,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19784,7 +19787,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19810,7 +19813,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19836,7 +19839,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19862,7 +19865,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19888,7 +19891,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19914,7 +19917,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19940,7 +19943,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19966,7 +19969,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19992,7 +19995,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20018,7 +20021,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -68022,25 +68025,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911805556</v>
+        <v>45967.6940740741</v>
       </c>
       <c r="B2505" t="n">
-        <v>37304</v>
+        <v>15748</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.36999988555908</v>
+        <v>2.35999989509583</v>
       </c>
       <c r="D2505" t="n">
         <v>2.3199999332428</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.34999990463257</v>
+        <v>2.35999989509583</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.35999989509583</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="G2505" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="860">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994893014431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980557262897491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978406846523285</t>
+    <t xml:space="preserve">0.99489289522171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980557322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978407084941864</t>
   </si>
   <si>
     <t xml:space="preserve">0.95116925239563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959053933620453</t>
+    <t xml:space="preserve">0.959053993225098</t>
   </si>
   <si>
     <t xml:space="preserve">0.966938436031342</t>
@@ -65,67 +65,67 @@
     <t xml:space="preserve">0.960487365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9447181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816220283508</t>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816160678864</t>
   </si>
   <si>
     <t xml:space="preserve">0.863005101680756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874473750591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386274814606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994479656219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057539463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899561047554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86658900976181</t>
+    <t xml:space="preserve">0.874473631381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994598865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057420253754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428030967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899561107158661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606469154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844063282013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866588950157166</t>
   </si>
   <si>
     <t xml:space="preserve">0.831466734409332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820714950561523</t>
+    <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
     <t xml:space="preserve">0.807812929153442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.74545282125473</t>
+    <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
     <t xml:space="preserve">0.713197708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731117248535156</t>
+    <t xml:space="preserve">0.731117308139801</t>
   </si>
   <si>
     <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.723949432373047</t>
+    <t xml:space="preserve">0.723949491977692</t>
   </si>
   <si>
     <t xml:space="preserve">0.774124205112457</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">0.788459718227386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800645053386688</t>
+    <t xml:space="preserve">0.800645172595978</t>
   </si>
   <si>
     <t xml:space="preserve">0.80279541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298739433289</t>
+    <t xml:space="preserve">0.824298858642578</t>
   </si>
   <si>
     <t xml:space="preserve">0.845802307128906</t>
@@ -149,43 +149,43 @@
     <t xml:space="preserve">0.827882766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804945766925812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050523281097</t>
+    <t xml:space="preserve">0.804945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050582885742</t>
   </si>
   <si>
     <t xml:space="preserve">0.834333837032318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838634490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658847332001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207896232605</t>
+    <t xml:space="preserve">0.838634610176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658906936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88020795583725</t>
   </si>
   <si>
     <t xml:space="preserve">0.839351296424866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850819826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873040020465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87734067440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809323310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393052577972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977139472961</t>
+    <t xml:space="preserve">0.850819885730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040080070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340734004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977079868317</t>
   </si>
   <si>
     <t xml:space="preserve">0.885225296020508</t>
@@ -194,34 +194,34 @@
     <t xml:space="preserve">0.85297018289566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870889782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305934429169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924582481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
+    <t xml:space="preserve">0.870889663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924642086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860138177871704</t>
   </si>
   <si>
     <t xml:space="preserve">0.830749988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858704388141632</t>
+    <t xml:space="preserve">0.858704447746277</t>
   </si>
   <si>
     <t xml:space="preserve">0.855120480060577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851536631584167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784907341003</t>
+    <t xml:space="preserve">0.851536512374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421193599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784847736359</t>
   </si>
   <si>
     <t xml:space="preserve">0.82644921541214</t>
@@ -230,37 +230,37 @@
     <t xml:space="preserve">0.79921156167984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789893388748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547253608704</t>
+    <t xml:space="preserve">0.789893329143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547134399414</t>
   </si>
   <si>
     <t xml:space="preserve">0.779858469963074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781292080879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875988960266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80924654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131102085114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917685508728</t>
+    <t xml:space="preserve">0.781291961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875929355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246420860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131042480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917745113373</t>
   </si>
   <si>
     <t xml:space="preserve">0.821431875228882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814980626106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113642692566</t>
+    <t xml:space="preserve">0.814980685710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113583087921</t>
   </si>
   <si>
     <t xml:space="preserve">0.811396837234497</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">0.799928367137909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.794194102287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026345729828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512334823608</t>
+    <t xml:space="preserve">0.794194161891937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026226520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512275218964</t>
   </si>
   <si>
     <t xml:space="preserve">0.815697550773621</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.759788513183594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.76265561580658</t>
+    <t xml:space="preserve">0.762655735015869</t>
   </si>
   <si>
     <t xml:space="preserve">0.756204545497894</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">0.750470399856567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77914160490036</t>
+    <t xml:space="preserve">0.779141664505005</t>
   </si>
   <si>
     <t xml:space="preserve">0.763372540473938</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">0.767673134803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780575275421143</t>
+    <t xml:space="preserve">0.780575215816498</t>
   </si>
   <si>
     <t xml:space="preserve">0.775557816028595</t>
@@ -314,31 +314,31 @@
     <t xml:space="preserve">0.795627534389496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784159064292908</t>
+    <t xml:space="preserve">0.784159123897552</t>
   </si>
   <si>
     <t xml:space="preserve">0.842218458652496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851380467414856</t>
+    <t xml:space="preserve">0.851380527019501</t>
   </si>
   <si>
     <t xml:space="preserve">0.872164011001587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869937300682068</t>
+    <t xml:space="preserve">0.869937121868134</t>
   </si>
   <si>
     <t xml:space="preserve">0.861029982566833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861772298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853607177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576502323151</t>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607296943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576383113861</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741265773773</t>
@@ -347,121 +347,121 @@
     <t xml:space="preserve">0.855834066867828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837277412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401127338409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112470149994</t>
+    <t xml:space="preserve">0.83727753162384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401186943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112589359283</t>
   </si>
   <si>
     <t xml:space="preserve">0.83059698343277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85880309343338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504182338715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84470009803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843957662582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84618467092514</t>
+    <t xml:space="preserve">0.858803153038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504301548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844700157642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843957781791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846184611320496</t>
   </si>
   <si>
     <t xml:space="preserve">0.835793018341064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833566069602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838761866092682</t>
+    <t xml:space="preserve">0.833566129207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761925697327</t>
   </si>
   <si>
     <t xml:space="preserve">0.81649386882782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916494846344</t>
+    <t xml:space="preserve">0.809813439846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916554450989</t>
   </si>
   <si>
     <t xml:space="preserve">0.810555875301361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801648676395416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817978501319885</t>
+    <t xml:space="preserve">0.801648616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81797844171524</t>
   </si>
   <si>
     <t xml:space="preserve">0.818720757961273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819463074207306</t>
+    <t xml:space="preserve">0.819463014602661</t>
   </si>
   <si>
     <t xml:space="preserve">0.826143443584442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81278270483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808329045772552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133130073547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805359959602356</t>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808328986167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133189678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805360019207001</t>
   </si>
   <si>
     <t xml:space="preserve">0.796452701091766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800906300544739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514647960663</t>
+    <t xml:space="preserve">0.800906360149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514707565308</t>
   </si>
   <si>
     <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256785392761</t>
+    <t xml:space="preserve">0.791256904602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.807586789131165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267158508301</t>
+    <t xml:space="preserve">0.814267218112946</t>
   </si>
   <si>
     <t xml:space="preserve">0.804617643356323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794226050376892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803185939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779380559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777153849601746</t>
+    <t xml:space="preserve">0.79867947101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225931167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77938050031662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777153789997101</t>
   </si>
   <si>
     <t xml:space="preserve">0.777895987033844</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838019728660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844413280487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927079677582</t>
+    <t xml:space="preserve">0.838019669055939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844472885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774927020072937</t>
   </si>
   <si>
     <t xml:space="preserve">0.773442506790161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783834218978882</t>
+    <t xml:space="preserve">0.783834159374237</t>
   </si>
   <si>
     <t xml:space="preserve">0.765277564525604</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">0.806102216243744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868452608585358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411381244659</t>
+    <t xml:space="preserve">0.868452727794647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411500453949</t>
   </si>
   <si>
     <t xml:space="preserve">0.843215703964233</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">0.845442354679108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849153637886047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390840530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514495849609</t>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514436244965</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85509181022644</t>
+    <t xml:space="preserve">0.855091750621796</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">0.834308326244354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827628016471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860287725925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349553585052</t>
+    <t xml:space="preserve">0.827627956867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86028778553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349493980408</t>
   </si>
   <si>
     <t xml:space="preserve">0.867710411548615</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">0.880328953266144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873648524284363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380374908447</t>
+    <t xml:space="preserve">0.873648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669091701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380434513092</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730919361115</t>
@@ -590,22 +590,22 @@
     <t xml:space="preserve">0.931545495986938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915957868099213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504209041595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885548114777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991669058799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792773723602</t>
+    <t xml:space="preserve">0.915957629680634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91150426864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535063266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991668999195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792892932892</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768968582153</t>
@@ -617,37 +617,37 @@
     <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06886506080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04659688472748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05327725410461</t>
+    <t xml:space="preserve">1.0688648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04659676551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05327713489532</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249371051788</t>
+    <t xml:space="preserve">1.03249382972717</t>
   </si>
   <si>
     <t xml:space="preserve">1.02432882785797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03175139427185</t>
+    <t xml:space="preserve">1.03175127506256</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467931270599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00206065177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02284407615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03026700019836</t>
+    <t xml:space="preserve">1.00206077098846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02284419536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03026688098907</t>
   </si>
   <si>
     <t xml:space="preserve">1.05921542644501</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">1.06812238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585468769073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06663823127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449361801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11191630363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1193391084671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.117112159729</t>
+    <t xml:space="preserve">1.04585433006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06663811206818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449373722076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11191618442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11933898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11711204051971</t>
   </si>
   <si>
     <t xml:space="preserve">1.12898850440979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14160692691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18762767314911</t>
+    <t xml:space="preserve">1.14160704612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18762743473053</t>
   </si>
   <si>
     <t xml:space="preserve">1.21509146690369</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">1.2314213514328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21731841564178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177171707153</t>
+    <t xml:space="preserve">1.2173182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177183628082</t>
   </si>
   <si>
     <t xml:space="preserve">1.21880280971527</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">1.23216366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22845208644867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23513245582581</t>
+    <t xml:space="preserve">1.22845220565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23513281345367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474086284637</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">1.20098841190338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700903892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779246330261</t>
+    <t xml:space="preserve">1.2470086812973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26779222488403</t>
   </si>
   <si>
     <t xml:space="preserve">1.24923586845398</t>
@@ -734,79 +734,79 @@
     <t xml:space="preserve">1.26036965847015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25888538360596</t>
+    <t xml:space="preserve">1.25888514518738</t>
   </si>
   <si>
     <t xml:space="preserve">1.26927697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521514892578</t>
+    <t xml:space="preserve">1.27521526813507</t>
   </si>
   <si>
     <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34424602985382</t>
+    <t xml:space="preserve">1.34424591064453</t>
   </si>
   <si>
     <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2032151222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17278230190277</t>
+    <t xml:space="preserve">1.20321536064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17426693439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17278218269348</t>
   </si>
   <si>
     <t xml:space="preserve">1.1653596162796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17055535316467</t>
+    <t xml:space="preserve">1.17055547237396</t>
   </si>
   <si>
     <t xml:space="preserve">1.17723572254181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17649364471436</t>
+    <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.16387510299683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16164827346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15051412582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15348339080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12824606895447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14383375644684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1891120672226</t>
+    <t xml:space="preserve">1.16164815425873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15051424503326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348327159882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12824630737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14383387565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18911194801331</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28412234783173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28486442565918</t>
+    <t xml:space="preserve">1.28412222862244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28486454486847</t>
   </si>
   <si>
     <t xml:space="preserve">1.31307065486908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018396377563</t>
+    <t xml:space="preserve">1.35018420219421</t>
   </si>
   <si>
     <t xml:space="preserve">1.32791614532471</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">1.35834896564484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34350371360779</t>
+    <t xml:space="preserve">1.3435035943985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311200141907</t>
@@ -824,22 +824,22 @@
     <t xml:space="preserve">1.35057294368744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34374034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32855677604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35816466808319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512793064117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031137943268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3665155172348</t>
+    <t xml:space="preserve">1.34374022483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32855689525604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35816478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031161785126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36651539802551</t>
   </si>
   <si>
     <t xml:space="preserve">1.37410736083984</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">1.39080929756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3968825340271</t>
+    <t xml:space="preserve">1.39688265323639</t>
   </si>
   <si>
     <t xml:space="preserve">1.38169920444489</t>
@@ -857,25 +857,25 @@
     <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36727499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39156830310822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39232766628265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549506664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701343536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36879312992096</t>
+    <t xml:space="preserve">1.36727464199066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3915684223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39232754707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549494743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258899211884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701331615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36879324913025</t>
   </si>
   <si>
     <t xml:space="preserve">1.36120140552521</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">1.3513320684433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31565082073212</t>
+    <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
     <t xml:space="preserve">1.33842623233795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3429811000824</t>
+    <t xml:space="preserve">1.34298121929169</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">1.36955225467682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536428451538</t>
+    <t xml:space="preserve">1.39536440372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143764019012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625407218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397657871246</t>
+    <t xml:space="preserve">1.40143775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625419139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397645950317</t>
   </si>
   <si>
     <t xml:space="preserve">1.38929080963135</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473582267761</t>
+    <t xml:space="preserve">1.3847359418869</t>
   </si>
   <si>
     <t xml:space="preserve">1.34829545021057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42497229576111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45230233669281</t>
+    <t xml:space="preserve">1.42497217655182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630958080292</t>
+    <t xml:space="preserve">1.4773553609848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.51835060119629</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">1.54568111896515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379573345184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594256401062</t>
+    <t xml:space="preserve">1.51379561424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594244480133</t>
   </si>
   <si>
     <t xml:space="preserve">1.51075899600983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52897918224335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50316715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53049767017365</t>
+    <t xml:space="preserve">1.52897906303406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50316727161407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53049743175507</t>
   </si>
   <si>
     <t xml:space="preserve">1.53353416919708</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">1.51607310771942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47887372970581</t>
+    <t xml:space="preserve">1.47887361049652</t>
   </si>
   <si>
     <t xml:space="preserve">1.43484139442444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40599262714386</t>
+    <t xml:space="preserve">1.40599274635315</t>
   </si>
   <si>
     <t xml:space="preserve">1.38777256011963</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29059815406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29970812797546</t>
+    <t xml:space="preserve">1.2905980348587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29970824718475</t>
   </si>
   <si>
     <t xml:space="preserve">1.30502235889435</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052264213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659623622894</t>
+    <t xml:space="preserve">1.47052276134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659587860107</t>
   </si>
   <si>
     <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48722457885742</t>
+    <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
     <t xml:space="preserve">1.42269468307495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41434371471405</t>
+    <t xml:space="preserve">1.41434383392334</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738045215607</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39308679103851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40371513366699</t>
+    <t xml:space="preserve">1.3930869102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40371525287628</t>
   </si>
   <si>
     <t xml:space="preserve">1.37182998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36271977424622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423826217651</t>
+    <t xml:space="preserve">1.36271965503693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4272495508194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4993714094162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49557542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49177956581116</t>
+    <t xml:space="preserve">1.42724967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039209842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49937129020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49557530879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49177968502045</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761668682098</t>
+    <t xml:space="preserve">1.45761680603027</t>
   </si>
   <si>
     <t xml:space="preserve">1.43863725662231</t>
@@ -1100,31 +1100,31 @@
     <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30957746505737</t>
+    <t xml:space="preserve">1.30957758426666</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476103305817</t>
+    <t xml:space="preserve">1.32476091384888</t>
   </si>
   <si>
     <t xml:space="preserve">1.34753632545471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161872386932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716918945312</t>
+    <t xml:space="preserve">1.31337332725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716930866241</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206610202789</t>
+    <t xml:space="preserve">1.41206622123718</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
@@ -1133,37 +1133,37 @@
     <t xml:space="preserve">1.44243311882019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45382082462311</t>
+    <t xml:space="preserve">1.45382070541382</t>
   </si>
   <si>
     <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418796062469</t>
+    <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42345368862152</t>
+    <t xml:space="preserve">1.42345380783081</t>
   </si>
   <si>
     <t xml:space="preserve">1.41586208343506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45002496242523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46141254901886</t>
+    <t xml:space="preserve">1.45002484321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46141242980957</t>
   </si>
   <si>
     <t xml:space="preserve">1.54112589359283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47280013561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51455497741699</t>
+    <t xml:space="preserve">1.47280025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51455473899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418784141541</t>
@@ -1175,25 +1175,25 @@
     <t xml:space="preserve">1.50768411159515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52726459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943230628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376808643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49202001094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46852350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48027181625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46069145202637</t>
+    <t xml:space="preserve">1.52726471424103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376832485199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49201989173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46852362155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48027169704437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46069157123566</t>
   </si>
   <si>
     <t xml:space="preserve">1.44894337654114</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">1.45677542686462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4724395275116</t>
+    <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
     <t xml:space="preserve">1.47635567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44111108779907</t>
+    <t xml:space="preserve">1.44111120700836</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40978252887726</t>
+    <t xml:space="preserve">1.40978240966797</t>
   </si>
   <si>
     <t xml:space="preserve">1.42153084278107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936301231384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43327903747559</t>
+    <t xml:space="preserve">1.42936289310455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4332789182663</t>
   </si>
   <si>
     <t xml:space="preserve">1.45285928249359</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">1.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
@@ -1256,52 +1256,52 @@
     <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146142959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055262565613</t>
+    <t xml:space="preserve">1.30404901504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146131038666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055250644684</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962167263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188106536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34320962429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35104167461395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38628625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4058666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37062191963196</t>
+    <t xml:space="preserve">1.31188118457794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34320950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35104179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38628613948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40586650371552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
     <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32754528522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838455677032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195035934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30013287067413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33537745475769</t>
+    <t xml:space="preserve">1.3275454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195047855377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30013298988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537757396698</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230070114136</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31579720973969</t>
+    <t xml:space="preserve">1.31579697132111</t>
   </si>
   <si>
     <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37453818321228</t>
+    <t xml:space="preserve">1.37453806400299</t>
   </si>
   <si>
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761481761932</t>
+    <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
     <t xml:space="preserve">1.48810386657715</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">1.49593591690063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49985218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5116001367569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334856987</t>
+    <t xml:space="preserve">1.49985194206238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51160025596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334833145142</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55076086521149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59775352478027</t>
+    <t xml:space="preserve">1.55076098442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
     <t xml:space="preserve">1.58992147445679</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">1.61341774463654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58208930492401</t>
+    <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64474642276764</t>
+    <t xml:space="preserve">1.64474618434906</t>
   </si>
   <si>
     <t xml:space="preserve">1.63691425323486</t>
@@ -1376,34 +1376,34 @@
     <t xml:space="preserve">1.65257835388184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66041052341461</t>
+    <t xml:space="preserve">1.6604106426239</t>
   </si>
   <si>
     <t xml:space="preserve">1.66824293136597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70740354061127</t>
+    <t xml:space="preserve">1.70740342140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.75439620018005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74656414985657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80138862133026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838163852692</t>
+    <t xml:space="preserve">1.74656403064728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222836971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80138874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006030082703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77789270877838</t>
+    <t xml:space="preserve">1.7778924703598</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488512992859</t>
@@ -1412,85 +1412,85 @@
     <t xml:space="preserve">1.80922102928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83271729946136</t>
+    <t xml:space="preserve">1.83271753787994</t>
   </si>
   <si>
     <t xml:space="preserve">1.84054958820343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87971043586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187826633453</t>
+    <t xml:space="preserve">1.8797105550766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187802791595</t>
   </si>
   <si>
     <t xml:space="preserve">1.86404597759247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85621380805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79355669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94236731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95803153514862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97369587421417</t>
+    <t xml:space="preserve">1.8562136888504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79355680942535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94236719608307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95803141593933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97369563579559</t>
   </si>
   <si>
     <t xml:space="preserve">1.99719190597534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9658637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.934534907341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670273780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178470134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942891597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662851810455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77956175804138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76338398456573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191742420197</t>
+    <t xml:space="preserve">1.96586382389069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91887068748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9267030954361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178446292877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942903518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9656069278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77956163883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
     <t xml:space="preserve">1.78765082359314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573965072632</t>
+    <t xml:space="preserve">1.79573941230774</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8604508638382</t>
+    <t xml:space="preserve">1.82000625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86045074462891</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809507846832</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">1.85236191749573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8928062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90089535713196</t>
+    <t xml:space="preserve">1.89280664920807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90089547634125</t>
   </si>
   <si>
     <t xml:space="preserve">1.88471746444702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
@@ -1520,22 +1520,22 @@
     <t xml:space="preserve">1.7714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94134032726288</t>
+    <t xml:space="preserve">1.90898442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94134020805359</t>
   </si>
   <si>
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.997962474823</t>
+    <t xml:space="preserve">1.98987376689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">1.75529503822327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66631686687469</t>
+    <t xml:space="preserve">1.66631674766541</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">1.49644958972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747165679932</t>
+    <t xml:space="preserve">1.40747153759003</t>
   </si>
   <si>
     <t xml:space="preserve">1.4155604839325</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.17289292812347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19715964794159</t>
+    <t xml:space="preserve">1.1971595287323</t>
   </si>
   <si>
     <t xml:space="preserve">1.22951543331146</t>
@@ -1604,43 +1604,43 @@
     <t xml:space="preserve">1.03538131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178151607513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15671515464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14053726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693734169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09604811668396</t>
+    <t xml:space="preserve">1.07178139686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15671503543854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1405371427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693746089935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09604835510254</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18907082080841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13649272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24569320678711</t>
+    <t xml:space="preserve">1.18907070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1364928483963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075956821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24569308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30231559276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995980739594</t>
+    <t xml:space="preserve">1.3023157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995992660522</t>
   </si>
   <si>
     <t xml:space="preserve">1.25378203392029</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21333754062653</t>
+    <t xml:space="preserve">1.18098199367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21333742141724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031495571136</t>
+    <t xml:space="preserve">1.12031507492065</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862620830536</t>
+    <t xml:space="preserve">1.14862608909607</t>
   </si>
   <si>
     <t xml:space="preserve">1.10009264945984</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760426044464</t>
+    <t xml:space="preserve">1.23760437965393</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20929300785065</t>
+    <t xml:space="preserve">1.20929312705994</t>
   </si>
   <si>
     <t xml:space="preserve">1.2497376203537</t>
@@ -1703,31 +1703,31 @@
     <t xml:space="preserve">1.22142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
+    <t xml:space="preserve">1.07582592964172</t>
   </si>
   <si>
     <t xml:space="preserve">1.05964803695679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09200370311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08391487598419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0798704624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0556036233902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155909061432</t>
+    <t xml:space="preserve">1.09200382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0839147567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07987034320831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560350418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155920982361</t>
   </si>
   <si>
     <t xml:space="preserve">1.02324795722961</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">1.00302565097809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982803344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954492151737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970670163631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01111447811127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986847937107086</t>
+    <t xml:space="preserve">0.982803463935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954492211341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970670104026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01111459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986847817897797</t>
   </si>
   <si>
     <t xml:space="preserve">0.962581157684326</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">0.966625571250916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978758931159973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01920342445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10413706302643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23355972766876</t>
+    <t xml:space="preserve">0.978759050369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01920354366302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10413718223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23355984687805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">1.29422676563263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31040453910828</t>
+    <t xml:space="preserve">1.31040441989899</t>
   </si>
   <si>
     <t xml:space="preserve">1.32253789901733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32658243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34680461883545</t>
+    <t xml:space="preserve">1.32658231258392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34680473804474</t>
   </si>
   <si>
     <t xml:space="preserve">1.33467125892639</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46813833713531</t>
+    <t xml:space="preserve">1.4681384563446</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498302936554</t>
+    <t xml:space="preserve">1.54498314857483</t>
   </si>
   <si>
     <t xml:space="preserve">1.52071642875671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50453865528107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53284955024719</t>
+    <t xml:space="preserve">1.50453853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53284978866577</t>
   </si>
   <si>
     <t xml:space="preserve">1.51667189598083</t>
@@ -1835,34 +1835,34 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57329440116882</t>
+    <t xml:space="preserve">1.58947217464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57329428195953</t>
   </si>
   <si>
     <t xml:space="preserve">1.56520521640778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48836088180542</t>
+    <t xml:space="preserve">1.48836076259613</t>
   </si>
   <si>
     <t xml:space="preserve">1.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54902744293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5247608423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5288051366806</t>
+    <t xml:space="preserve">1.54902756214142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52476072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52880525588989</t>
   </si>
   <si>
     <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70676136016846</t>
+    <t xml:space="preserve">1.70676124095917</t>
   </si>
   <si>
     <t xml:space="preserve">1.69867241382599</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249464035034</t>
+    <t xml:space="preserve">1.68249452114105</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440569400787</t>
@@ -1904,28 +1904,28 @@
     <t xml:space="preserve">1.71485030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55711650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48431622982025</t>
+    <t xml:space="preserve">1.5571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48431634902954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49240517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47218298912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351670742035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50858306884766</t>
+    <t xml:space="preserve">1.47218286991119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50858294963837</t>
   </si>
   <si>
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3306268453598</t>
+    <t xml:space="preserve">1.33062672615051</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893797874451</t>
@@ -1934,22 +1934,22 @@
     <t xml:space="preserve">1.44791603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46409380435944</t>
+    <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60160553455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59756112098694</t>
+    <t xml:space="preserve">1.60160565376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59756100177765</t>
   </si>
   <si>
     <t xml:space="preserve">1.60969436168671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75187587738037</t>
+    <t xml:space="preserve">1.75187575817108</t>
   </si>
   <si>
     <t xml:space="preserve">1.72660839557648</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6465950012207</t>
+    <t xml:space="preserve">1.64659488201141</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343975067139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63817250728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62974989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66765105724335</t>
+    <t xml:space="preserve">1.63817238807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62974977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66765117645264</t>
   </si>
   <si>
     <t xml:space="preserve">1.64238369464874</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58342623710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500374317169</t>
+    <t xml:space="preserve">1.58342635631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500386238098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59605991840363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56658124923706</t>
+    <t xml:space="preserve">1.59606003761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56658136844635</t>
   </si>
   <si>
     <t xml:space="preserve">1.54552519321442</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289151191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51183521747589</t>
+    <t xml:space="preserve">1.53289139270782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5118350982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.47393405437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43182158470154</t>
+    <t xml:space="preserve">1.43182170391083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38970923423767</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4360328912735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4486665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41497671604156</t>
+    <t xml:space="preserve">1.43603301048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44866669178009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41497659683228</t>
   </si>
   <si>
     <t xml:space="preserve">1.44024407863617</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">1.40655422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40234291553497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4613002538681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499022960663</t>
+    <t xml:space="preserve">1.40234303474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46130037307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077892303467</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.54131376743317</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">1.71818590164185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186224460602</t>
+    <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
     <t xml:space="preserve">1.61290490627289</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">1.59184873104095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604640483856</t>
+    <t xml:space="preserve">1.51604628562927</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">1.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48235654830933</t>
+    <t xml:space="preserve">1.48235642910004</t>
   </si>
   <si>
     <t xml:space="preserve">1.45708906650543</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763754367828</t>
+    <t xml:space="preserve">1.58763742446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79398834705353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84452319145203</t>
+    <t xml:space="preserve">1.79398846626282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84452331066132</t>
   </si>
   <si>
     <t xml:space="preserve">1.8393189907074</t>
@@ -2589,6 +2589,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.30999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26999998092651</t>
   </si>
 </sst>
 </file>
@@ -68109,7 +68112,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6084027778</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>8532</v>
@@ -68130,6 +68133,32 @@
         <v>858</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6815162037</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>31783</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>859</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="862">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965505003929138</t>
+    <t xml:space="preserve">0.965504825115204</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">0.994892835617065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980557501316071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97840690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169192790985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053874015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938376426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944718241691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005101680756</t>
+    <t xml:space="preserve">0.980557382106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978406846523285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95116925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053754806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938436031342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487425327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863004922866821</t>
   </si>
   <si>
     <t xml:space="preserve">0.874473571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849386274814606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994598865509</t>
+    <t xml:space="preserve">0.849386215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994539260864</t>
   </si>
   <si>
     <t xml:space="preserve">0.878057539463043</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">0.88737565279007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902428150177002</t>
+    <t xml:space="preserve">0.902428090572357</t>
   </si>
   <si>
     <t xml:space="preserve">0.899560928344727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871606409549713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8665891289711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466734409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820714950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807812929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74545282125473</t>
+    <t xml:space="preserve">0.871606528759003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86658900976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466615200043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820714890956879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807812809944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
     <t xml:space="preserve">0.713197767734528</t>
@@ -122,124 +122,124 @@
     <t xml:space="preserve">0.731117308139801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.704237937927246</t>
+    <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
     <t xml:space="preserve">0.723949432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774124264717102</t>
+    <t xml:space="preserve">0.774124145507812</t>
   </si>
   <si>
     <t xml:space="preserve">0.788459837436676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800645053386688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802795469760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802307128906</t>
+    <t xml:space="preserve">0.800645172595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80279552936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298918247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802247524261</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882826328278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804945826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050523281097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834334015846252</t>
+    <t xml:space="preserve">0.804945886135101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050463676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333837032318</t>
   </si>
   <si>
     <t xml:space="preserve">0.838634550571442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886658906936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207777023315</t>
+    <t xml:space="preserve">0.886658847332001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880208015441895</t>
   </si>
   <si>
     <t xml:space="preserve">0.839351236820221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850819826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873040020465851</t>
+    <t xml:space="preserve">0.850819945335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87304013967514</t>
   </si>
   <si>
     <t xml:space="preserve">0.877340793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888809382915497</t>
+    <t xml:space="preserve">0.888809204101562</t>
   </si>
   <si>
     <t xml:space="preserve">0.892393112182617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895977139472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225355625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852970242500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889663696289</t>
+    <t xml:space="preserve">0.895976960659027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225236415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85297018289566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889604091644</t>
   </si>
   <si>
     <t xml:space="preserve">0.867305815219879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880924701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86013799905777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830750048160553</t>
+    <t xml:space="preserve">0.880924761295319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86013787984848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
   </si>
   <si>
     <t xml:space="preserve">0.858704328536987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855120480060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536512374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449334621429</t>
+    <t xml:space="preserve">0.855120599269867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536631584167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421193599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784966945648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
     <t xml:space="preserve">0.799211502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789893448352814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858589172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781291961669922</t>
+    <t xml:space="preserve">0.789893388748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547194004059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292021274567</t>
   </si>
   <si>
     <t xml:space="preserve">0.784875929355621</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">0.809246420860291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817130982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431756019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980626106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113642692566</t>
+    <t xml:space="preserve">0.817131102085114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917745113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431815624237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980685710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113583087921</t>
   </si>
   <si>
     <t xml:space="preserve">0.811396777629852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799928426742554</t>
+    <t xml:space="preserve">0.799928307533264</t>
   </si>
   <si>
     <t xml:space="preserve">0.794194102287292</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">0.787026286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803512215614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921470165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76265561580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204545497894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470340251923</t>
+    <t xml:space="preserve">0.803512275218964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697550773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921410560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788572788239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655675411224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470399856567</t>
   </si>
   <si>
     <t xml:space="preserve">0.779141664505005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763372421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673075199127</t>
+    <t xml:space="preserve">0.763372600078583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673194408417</t>
   </si>
   <si>
     <t xml:space="preserve">0.780575215816498</t>
@@ -314,58 +314,58 @@
     <t xml:space="preserve">0.795627653598785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784159183502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218458652496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380407810211</t>
+    <t xml:space="preserve">0.784159123897552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380527019501</t>
   </si>
   <si>
     <t xml:space="preserve">0.872164011001587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869937300682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029982566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576502323151</t>
+    <t xml:space="preserve">0.869937181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029922962189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576383113861</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855834245681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277472019196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401127338409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050642490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112529754639</t>
+    <t xml:space="preserve">0.855834126472473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277352809906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401246547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112589359283</t>
   </si>
   <si>
     <t xml:space="preserve">0.830597043037415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85880309343338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83950412273407</t>
+    <t xml:space="preserve">0.858803153038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504241943359</t>
   </si>
   <si>
     <t xml:space="preserve">0.844700157642365</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.843957781791687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846184611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835792899131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833566129207611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838761985301971</t>
+    <t xml:space="preserve">0.84618467092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83579295873642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833566188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761925697327</t>
   </si>
   <si>
     <t xml:space="preserve">0.816493988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916673660278</t>
+    <t xml:space="preserve">0.809813439846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916554450989</t>
   </si>
   <si>
     <t xml:space="preserve">0.810555815696716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801648676395416</t>
+    <t xml:space="preserve">0.801648557186127</t>
   </si>
   <si>
     <t xml:space="preserve">0.81797856092453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818720817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819463014602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278258562088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808328986167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133189678192</t>
+    <t xml:space="preserve">0.818720698356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819462895393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143443584442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808329045772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133249282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.805359959602356</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">0.800906360149384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790514588356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999161243439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791256785392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586908340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814267218112946</t>
+    <t xml:space="preserve">0.790514707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791256844997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807586789131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814267098903656</t>
   </si>
   <si>
     <t xml:space="preserve">0.804617702960968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79867947101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225990772247</t>
+    <t xml:space="preserve">0.798679530620575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225931167603</t>
   </si>
   <si>
     <t xml:space="preserve">0.786803245544434</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">0.77938050031662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777153789997101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777895987033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788287937641144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771957814693451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838019609451294</t>
+    <t xml:space="preserve">0.777153849601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777896046638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788287758827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771957874298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838019669055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.806844472885132</t>
@@ -485,37 +485,37 @@
     <t xml:space="preserve">0.773442506790161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783834218978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765277504920959</t>
+    <t xml:space="preserve">0.783834159374237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765277564525604</t>
   </si>
   <si>
     <t xml:space="preserve">0.778638362884521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783091843128204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545442581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786060988903046</t>
+    <t xml:space="preserve">0.783091902732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545561790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786061108112335</t>
   </si>
   <si>
     <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318732261658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806102097034454</t>
+    <t xml:space="preserve">0.785318672657013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806102216243744</t>
   </si>
   <si>
     <t xml:space="preserve">0.868452727794647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841731011867523</t>
+    <t xml:space="preserve">0.841730892658234</t>
   </si>
   <si>
     <t xml:space="preserve">0.848411500453949</t>
@@ -527,22 +527,22 @@
     <t xml:space="preserve">0.852865099906921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845442414283752</t>
+    <t xml:space="preserve">0.845442354679108</t>
   </si>
   <si>
     <t xml:space="preserve">0.849153757095337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874390661716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514555454254</t>
+    <t xml:space="preserve">0.874390780925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514317035675</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855091691017151</t>
+    <t xml:space="preserve">0.855091869831085</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318699359894</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">0.832823812961578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834308385848999</t>
+    <t xml:space="preserve">0.834308207035065</t>
   </si>
   <si>
     <t xml:space="preserve">0.827627956867218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86028778553009</t>
+    <t xml:space="preserve">0.860287666320801</t>
   </si>
   <si>
     <t xml:space="preserve">0.854349613189697</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.880328893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873648464679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669032096863</t>
+    <t xml:space="preserve">0.873648583889008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919668972492218</t>
   </si>
   <si>
     <t xml:space="preserve">0.923380374908447</t>
@@ -581,58 +581,58 @@
     <t xml:space="preserve">0.913730978965759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916700065135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091598510742</t>
+    <t xml:space="preserve">0.916699886322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091777324677</t>
   </si>
   <si>
     <t xml:space="preserve">0.931545317173004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915957689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504089832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885488510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668999195099</t>
+    <t xml:space="preserve">0.915957808494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504328250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535182476044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991669058799744</t>
   </si>
   <si>
     <t xml:space="preserve">0.979792773723602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03768968582153</t>
+    <t xml:space="preserve">1.03768956661224</t>
   </si>
   <si>
     <t xml:space="preserve">1.06960701942444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07480299472809</t>
+    <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
     <t xml:space="preserve">1.0688648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04659676551819</t>
+    <t xml:space="preserve">1.0465966463089</t>
   </si>
   <si>
     <t xml:space="preserve">1.05327713489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05179274082184</t>
+    <t xml:space="preserve">1.05179262161255</t>
   </si>
   <si>
     <t xml:space="preserve">1.03249371051788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02432858943939</t>
+    <t xml:space="preserve">1.02432882785797</t>
   </si>
   <si>
     <t xml:space="preserve">1.03175139427185</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">1.00206077098846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0228443145752</t>
+    <t xml:space="preserve">1.02284419536591</t>
   </si>
   <si>
     <t xml:space="preserve">1.03026688098907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05921530723572</t>
+    <t xml:space="preserve">1.05921542644501</t>
   </si>
   <si>
     <t xml:space="preserve">1.06812250614166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585468769073</t>
+    <t xml:space="preserve">1.04585444927216</t>
   </si>
   <si>
     <t xml:space="preserve">1.06663799285889</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">1.10449361801147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11191618442535</t>
+    <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
     <t xml:space="preserve">1.11933898925781</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">1.117112159729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1289883852005</t>
+    <t xml:space="preserve">1.12898850440979</t>
   </si>
   <si>
     <t xml:space="preserve">1.14160704612732</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2314213514328</t>
+    <t xml:space="preserve">1.23142123222351</t>
   </si>
   <si>
     <t xml:space="preserve">1.21731817722321</t>
@@ -695,25 +695,25 @@
     <t xml:space="preserve">1.22177183628082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21880292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23216366767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22845220565796</t>
+    <t xml:space="preserve">1.21880280971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23216342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22845232486725</t>
   </si>
   <si>
     <t xml:space="preserve">1.23513269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22474074363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286463737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21360695362091</t>
+    <t xml:space="preserve">1.22474098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286451816559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21360683441162</t>
   </si>
   <si>
     <t xml:space="preserve">1.20098841190338</t>
@@ -722,22 +722,22 @@
     <t xml:space="preserve">1.24700880050659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26779246330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923574924469</t>
+    <t xml:space="preserve">1.26779234409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923586845398</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443160533905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26037001609802</t>
+    <t xml:space="preserve">1.26036977767944</t>
   </si>
   <si>
     <t xml:space="preserve">1.25888514518738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26927709579468</t>
+    <t xml:space="preserve">1.2692768573761</t>
   </si>
   <si>
     <t xml:space="preserve">1.27521526813507</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">1.34424602985382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23958623409271</t>
+    <t xml:space="preserve">1.23958611488342</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17278242111206</t>
+    <t xml:space="preserve">1.17426669597626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17278230190277</t>
   </si>
   <si>
     <t xml:space="preserve">1.1653596162796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17055559158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17723572254181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649340629578</t>
+    <t xml:space="preserve">1.17055547237396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1772358417511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.16387498378754</t>
@@ -779,46 +779,46 @@
     <t xml:space="preserve">1.16164815425873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15051412582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15348339080811</t>
+    <t xml:space="preserve">1.15051436424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348327159882</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824618816376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14383399486542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18911194801331</t>
+    <t xml:space="preserve">1.14383387565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18911218643188</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28412222862244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28486442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31307077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018396377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.327916264534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35834896564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34350371360779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33311188220978</t>
+    <t xml:space="preserve">1.28412234783173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28486454486847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31307065486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018408298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32791614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35834908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3435035943985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33311200141907</t>
   </si>
   <si>
     <t xml:space="preserve">1.35057294368744</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">1.35512793064117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37031161785126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36651575565338</t>
+    <t xml:space="preserve">1.37031149864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3665155172348</t>
   </si>
   <si>
     <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39080917835236</t>
+    <t xml:space="preserve">1.39080929756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.39688265323639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38169920444489</t>
+    <t xml:space="preserve">1.3816990852356</t>
   </si>
   <si>
     <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36727476119995</t>
+    <t xml:space="preserve">1.36727464199066</t>
   </si>
   <si>
     <t xml:space="preserve">1.3915684223175</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">1.39232766628265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38549518585205</t>
+    <t xml:space="preserve">1.38549506664276</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258899211884</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120128631592</t>
+    <t xml:space="preserve">1.36120140552521</t>
   </si>
   <si>
     <t xml:space="preserve">1.3513320684433</t>
@@ -887,58 +887,58 @@
     <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842623233795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34298133850098</t>
+    <t xml:space="preserve">1.33842611312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34298121929169</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363477230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818987846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30122649669647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32096493244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31413245201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36955225467682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536428451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37562584877014</t>
+    <t xml:space="preserve">1.29363489151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818999767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30122661590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.320965051651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3141325712204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36955237388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536440372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38625419139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397657871246</t>
+    <t xml:space="preserve">1.38625407218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397645950317</t>
   </si>
   <si>
     <t xml:space="preserve">1.38929092884064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3832174539566</t>
+    <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
     <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473570346832</t>
+    <t xml:space="preserve">1.38473582267761</t>
   </si>
   <si>
     <t xml:space="preserve">1.34829545021057</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4523024559021</t>
+    <t xml:space="preserve">1.45230233669281</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
+    <t xml:space="preserve">1.4773553609848</t>
   </si>
   <si>
     <t xml:space="preserve">1.55630946159363</t>
@@ -962,37 +962,37 @@
     <t xml:space="preserve">1.51835072040558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54568099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379561424255</t>
+    <t xml:space="preserve">1.54568111896515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379573345184</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594244480133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51075887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52897918224335</t>
+    <t xml:space="preserve">1.51075899600983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52897906303406</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53049755096436</t>
+    <t xml:space="preserve">1.53049731254578</t>
   </si>
   <si>
     <t xml:space="preserve">1.53353416919708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52746081352234</t>
+    <t xml:space="preserve">1.52746093273163</t>
   </si>
   <si>
     <t xml:space="preserve">1.51607310771942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47887349128723</t>
+    <t xml:space="preserve">1.47887361049652</t>
   </si>
   <si>
     <t xml:space="preserve">1.43484151363373</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">1.38777244091034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33614873886108</t>
+    <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
     <t xml:space="preserve">1.2905980348587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29970824718475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30502259731293</t>
+    <t xml:space="preserve">1.29970812797546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30502235889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052264213562</t>
+    <t xml:space="preserve">1.47052276134491</t>
   </si>
   <si>
     <t xml:space="preserve">1.47659599781036</t>
@@ -1031,34 +1031,34 @@
     <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269444465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41434359550476</t>
+    <t xml:space="preserve">1.42269456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40447449684143</t>
+    <t xml:space="preserve">1.40447437763214</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371513366699</t>
+    <t xml:space="preserve">1.40371525287628</t>
   </si>
   <si>
     <t xml:space="preserve">1.37182998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36271965503693</t>
+    <t xml:space="preserve">1.36271977424622</t>
   </si>
   <si>
     <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35209131240845</t>
+    <t xml:space="preserve">1.35209119319916</t>
   </si>
   <si>
     <t xml:space="preserve">1.36499726772308</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4272495508194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039186000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4993714094162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49557554721832</t>
+    <t xml:space="preserve">1.42724967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49937129020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
     <t xml:space="preserve">1.49177956581116</t>
@@ -1088,19 +1088,19 @@
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761656761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4386373758316</t>
+    <t xml:space="preserve">1.45761668682098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43863725662231</t>
   </si>
   <si>
     <t xml:space="preserve">1.37790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33235287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30957746505737</t>
+    <t xml:space="preserve">1.33235275745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30957758426666</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">1.34753620624542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161860466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716918945312</t>
+    <t xml:space="preserve">1.31337332725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3171694278717</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206610202789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41965794563293</t>
+    <t xml:space="preserve">1.41206622123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41965782642365</t>
   </si>
   <si>
     <t xml:space="preserve">1.44243311882019</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418772220612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46520841121674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42345368862152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586196422577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002472400665</t>
+    <t xml:space="preserve">1.48418784141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520829200745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002484321594</t>
   </si>
   <si>
     <t xml:space="preserve">1.46141254901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54112601280212</t>
+    <t xml:space="preserve">1.54112589359283</t>
   </si>
   <si>
     <t xml:space="preserve">1.47280025482178</t>
@@ -1172,19 +1172,19 @@
     <t xml:space="preserve">1.50768423080444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52726447582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376808643341</t>
+    <t xml:space="preserve">1.52726459503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5037682056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852350234985</t>
+    <t xml:space="preserve">1.46852362155914</t>
   </si>
   <si>
     <t xml:space="preserve">1.48027181625366</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">1.46069145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44894337654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4646075963974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677530765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4724395275116</t>
+    <t xml:space="preserve">1.44894325733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46460747718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677542686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
     <t xml:space="preserve">1.47635567188263</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">1.44111120700836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4254469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36278975009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40978276729584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42153096199036</t>
+    <t xml:space="preserve">1.42544686794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36278986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40978252887726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42153084278107</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936301231384</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">1.39803433418274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39411842823029</t>
+    <t xml:space="preserve">1.394118309021</t>
   </si>
   <si>
     <t xml:space="preserve">1.34712564945221</t>
@@ -1253,52 +1253,52 @@
     <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146142959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055262565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2962167263031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31188094615936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34320962429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35104167461395</t>
+    <t xml:space="preserve">1.30404901504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146131038666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055250644684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29621660709381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31188118457794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34320950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35104179382324</t>
   </si>
   <si>
     <t xml:space="preserve">1.38628625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40586650371552</t>
+    <t xml:space="preserve">1.4058666229248</t>
   </si>
   <si>
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845420837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32754528522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838467597961</t>
+    <t xml:space="preserve">1.37845408916473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3275454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2883847951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30013275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33537745475769</t>
+    <t xml:space="preserve">1.30013298988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537769317627</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230070114136</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31579697132111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31971323490143</t>
+    <t xml:space="preserve">1.3157970905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810374736786</t>
+    <t xml:space="preserve">1.48810386657715</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593591690063</t>
@@ -1337,28 +1337,28 @@
     <t xml:space="preserve">1.52334845066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53509676456451</t>
+    <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55076098442078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59775364398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58992159366608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6212500333786</t>
+    <t xml:space="preserve">1.59775352478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58992147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61341786384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208930492401</t>
+    <t xml:space="preserve">1.61341774463654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908208370209</t>
@@ -1370,37 +1370,37 @@
     <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65257835388184</t>
+    <t xml:space="preserve">1.65257847309113</t>
   </si>
   <si>
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824281215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740330219269</t>
+    <t xml:space="preserve">1.66824293136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740342140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.75439608097076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74656403064728</t>
+    <t xml:space="preserve">1.74656414985657</t>
   </si>
   <si>
     <t xml:space="preserve">1.76222836971283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80138897895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7778924703598</t>
+    <t xml:space="preserve">1.80138874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838163852692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006018161774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77789258956909</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488512992859</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">1.80922102928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83271741867065</t>
+    <t xml:space="preserve">1.83271729946136</t>
   </si>
   <si>
     <t xml:space="preserve">1.84054970741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187826633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85621380805969</t>
+    <t xml:space="preserve">1.87971031665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404621601105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85621356964111</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355669021606</t>
@@ -1436,106 +1436,106 @@
     <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369587421417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99719202518463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96586358547211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453526496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670297622681</t>
+    <t xml:space="preserve">1.97369563579559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99719190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96586334705353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92670285701752</t>
   </si>
   <si>
     <t xml:space="preserve">1.98178470134735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94942891597748</t>
+    <t xml:space="preserve">1.94942903518677</t>
   </si>
   <si>
     <t xml:space="preserve">1.9656069278717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87662863731384</t>
+    <t xml:space="preserve">1.87662851810455</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338374614716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191742420197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573941230774</t>
+    <t xml:space="preserve">1.76338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191718578339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573953151703</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82000625133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8604508638382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809519767761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236179828644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8928062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90089535713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88471758365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.82000637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86045062541962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809507846832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236191749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90089523792267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88471746444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427285194397</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83618402481079</t>
+    <t xml:space="preserve">1.83618414402008</t>
   </si>
   <si>
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
+    <t xml:space="preserve">1.90898442268372</t>
   </si>
   <si>
     <t xml:space="preserve">1.94134020805359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93325126171112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751774311066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99796259403229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73911702632904</t>
+    <t xml:space="preserve">1.93325114250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751786231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73911726474762</t>
   </si>
   <si>
     <t xml:space="preserve">1.92516231536865</t>
@@ -1553,19 +1553,19 @@
     <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58542764186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56116080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4964497089386</t>
+    <t xml:space="preserve">1.58542776107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56116092205048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49644958972931</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747153759003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41556036472321</t>
+    <t xml:space="preserve">1.4155604839325</t>
   </si>
   <si>
     <t xml:space="preserve">1.34276020526886</t>
@@ -1574,61 +1574,61 @@
     <t xml:space="preserve">1.31849336624146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29827105998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17289304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951543331146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15267050266266</t>
+    <t xml:space="preserve">1.29827117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17289292812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715964794159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951531410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15267062187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01515913009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1648041009903</t>
+    <t xml:space="preserve">1.01515901088715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480398178101</t>
   </si>
   <si>
     <t xml:space="preserve">1.03538131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178151607513</t>
+    <t xml:space="preserve">1.07178139686584</t>
   </si>
   <si>
     <t xml:space="preserve">1.15671503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14053726196289</t>
+    <t xml:space="preserve">1.1405371427536</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693746089935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09604811668396</t>
+    <t xml:space="preserve">1.09604823589325</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18907082080841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1364928483963</t>
+    <t xml:space="preserve">1.18907070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13649272918701</t>
   </si>
   <si>
     <t xml:space="preserve">1.16075956821442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24569320678711</t>
+    <t xml:space="preserve">1.24569308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">1.30231559276581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995980739594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25378215312958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524871349335</t>
+    <t xml:space="preserve">1.26996004581451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25378203392029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524859428406</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098175525665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21333742141724</t>
+    <t xml:space="preserve">1.18098187446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21333754062653</t>
   </si>
   <si>
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031483650208</t>
+    <t xml:space="preserve">1.12031507492065</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862620830536</t>
+    <t xml:space="preserve">1.14862608909607</t>
   </si>
   <si>
     <t xml:space="preserve">1.10009264945984</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">1.12840390205383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2173820734024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16884851455688</t>
+    <t xml:space="preserve">1.24164879322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23760426044464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21738195419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16884863376617</t>
   </si>
   <si>
     <t xml:space="preserve">1.20929300785065</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">1.22142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
@@ -1709,55 +1709,55 @@
     <t xml:space="preserve">1.07582592964172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05964803695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09200370311737</t>
+    <t xml:space="preserve">1.05964815616608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
     <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0798704624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560350418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0232480764389</t>
+    <t xml:space="preserve">1.07987034320831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0556036233902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155920982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324783802032</t>
   </si>
   <si>
     <t xml:space="preserve">1.02729249000549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00302577018738</t>
+    <t xml:space="preserve">1.00302565097809</t>
   </si>
   <si>
     <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492151737213</t>
+    <t xml:space="preserve">0.954492211341858</t>
   </si>
   <si>
     <t xml:space="preserve">0.970670104026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01111471652985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986847937107086</t>
+    <t xml:space="preserve">1.01111459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986847817897797</t>
   </si>
   <si>
     <t xml:space="preserve">0.962581157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96662563085556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758871555328</t>
+    <t xml:space="preserve">0.966625571250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978758931159973</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120418071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29422664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31040453910828</t>
+    <t xml:space="preserve">1.20120406150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29422676563263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31040441989899</t>
   </si>
   <si>
     <t xml:space="preserve">1.32253789901733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32658219337463</t>
+    <t xml:space="preserve">1.32658231258392</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680461883545</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">1.33467125892639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3872492313385</t>
+    <t xml:space="preserve">1.38724935054779</t>
   </si>
   <si>
     <t xml:space="preserve">1.4681384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51262736320496</t>
+    <t xml:space="preserve">1.51262748241425</t>
   </si>
   <si>
     <t xml:space="preserve">1.55307197570801</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498302936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52071630954742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453841686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53284955024719</t>
+    <t xml:space="preserve">1.54498314857483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52071642875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53284966945648</t>
   </si>
   <si>
     <t xml:space="preserve">1.51667189598083</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947205543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57329440116882</t>
+    <t xml:space="preserve">1.58947217464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57329428195953</t>
   </si>
   <si>
     <t xml:space="preserve">1.56520533561707</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">1.48836076259613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50049388408661</t>
+    <t xml:space="preserve">1.5004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">1.54902756214142</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">1.5247608423233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5288051366806</t>
+    <t xml:space="preserve">1.52880525588989</t>
   </si>
   <si>
     <t xml:space="preserve">1.65822792053223</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">1.69867241382599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69058358669281</t>
+    <t xml:space="preserve">1.69058346748352</t>
   </si>
   <si>
     <t xml:space="preserve">1.68249464035034</t>
@@ -1874,139 +1874,142 @@
     <t xml:space="preserve">1.67440569400787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72293937206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61373889446259</t>
+    <t xml:space="preserve">1.72293949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6137387752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63396108150482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65013897418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60564994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205002784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62587225437164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61778330802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71485018730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48431634902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49240505695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47218286991119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351670742035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50858294963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37107145786285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33062672615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3589380979538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44791603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409380435944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47622740268707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60160565376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59756100177765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75187587738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72660839557648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74345338344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70976340770721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69291853904724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68028473854065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68449604511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67607355117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65080618858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64659488201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63817238807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62974989414215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66765117645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64238369464874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61711621284485</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65013897418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60565006732941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205014705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62587225437164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61778330802917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71485018730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55711627006531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48431634902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49240529537201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47218286991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50858294963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37107145786285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3306268453598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893797874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44791615009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409392356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47622728347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60160553455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59756112098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.609694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75187587738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72660851478577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74345338344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7097635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69291853904724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68028473854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68449604511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67607355117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65080618858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64659488201141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343986988068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63817250728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62974977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66765105724335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64238357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61711609363556</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
     <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58342623710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500374317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55394768714905</t>
+    <t xml:space="preserve">1.58342635631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500386238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55394756793976</t>
   </si>
   <si>
     <t xml:space="preserve">1.59605991840363</t>
@@ -2024,7 +2027,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289151191711</t>
+    <t xml:space="preserve">1.53289139270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2033,28 +2036,28 @@
     <t xml:space="preserve">1.47393405437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43182170391083</t>
+    <t xml:space="preserve">1.43182158470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38970923423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39813160896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4360328912735</t>
+    <t xml:space="preserve">1.3981317281723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41497659683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44024419784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41076529026031</t>
+    <t xml:space="preserve">1.41497671604156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44024407863617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4107654094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
@@ -2069,22 +2072,22 @@
     <t xml:space="preserve">1.49499022960663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49077904224396</t>
+    <t xml:space="preserve">1.49077892303467</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52446889877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.5244687795639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54131388664246</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868032455444</t>
+    <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2093,7 +2096,7 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869359970093</t>
+    <t xml:space="preserve">1.60869371891022</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
@@ -2102,7 +2105,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553858757019</t>
+    <t xml:space="preserve">1.62553870677948</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2117,7 +2120,7 @@
     <t xml:space="preserve">1.71818590164185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186236381531</t>
+    <t xml:space="preserve">1.67186224460602</t>
   </si>
   <si>
     <t xml:space="preserve">1.61290490627289</t>
@@ -2126,73 +2129,73 @@
     <t xml:space="preserve">1.59184873104095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604652404785</t>
+    <t xml:space="preserve">1.51604628562927</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761039733887</t>
+    <t xml:space="preserve">1.42761051654816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48235642910004</t>
+    <t xml:space="preserve">1.48235654830933</t>
   </si>
   <si>
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025759220123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57079243659973</t>
+    <t xml:space="preserve">1.52025771141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
     <t xml:space="preserve">1.58763754367828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65922856330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79398834705353</t>
+    <t xml:space="preserve">1.65922868251801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79398846626282</t>
   </si>
   <si>
     <t xml:space="preserve">1.84452319145203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83931910991669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584770679474</t>
+    <t xml:space="preserve">1.8393189907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584758758545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510474205017</t>
+    <t xml:space="preserve">1.79510462284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9277480840683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700488090515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237654209137</t>
+    <t xml:space="preserve">1.92774796485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237642288208</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365907907486</t>
+    <t xml:space="preserve">1.91006219387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93659090995789</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2207,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154824256897</t>
+    <t xml:space="preserve">2.05154800415039</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923389434814</t>
+    <t xml:space="preserve">2.0869197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923413276672</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2228,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039118766785</t>
+    <t xml:space="preserve">2.06039094924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353359699249</t>
+    <t xml:space="preserve">1.88353371620178</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2261,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427656173706</t>
+    <t xml:space="preserve">1.95427668094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163333892822</t>
+    <t xml:space="preserve">1.82163321971893</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2285,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783294200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130446434021</t>
+    <t xml:space="preserve">1.69783306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130434513092</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2297,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940432548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6270899772644</t>
+    <t xml:space="preserve">1.60940420627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62709009647369</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171843528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6049827337265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824715137482</t>
+    <t xml:space="preserve">1.59171831607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60498285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824703216553</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2333,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72436165809631</t>
+    <t xml:space="preserve">1.73762595653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7243617773056</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -2592,6 +2595,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.27999997138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25999999046326</t>
   </si>
 </sst>
 </file>
@@ -46966,7 +46972,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1694" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46992,7 +46998,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1695" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47018,7 +47024,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47044,7 +47050,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1697" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47096,7 +47102,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1699" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47122,7 +47128,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1700" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47148,7 +47154,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1701" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -47174,7 +47180,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1702" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47200,7 +47206,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1703" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47226,7 +47232,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1704" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47252,7 +47258,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47278,7 +47284,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47304,7 +47310,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1707" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47330,7 +47336,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47356,7 +47362,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47382,7 +47388,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1710" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47408,7 +47414,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1711" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47434,7 +47440,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1712" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47460,7 +47466,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1713" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47486,7 +47492,7 @@
         <v>1.75</v>
       </c>
       <c r="G1714" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47512,7 +47518,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1715" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47538,7 +47544,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47564,7 +47570,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1717" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47590,7 +47596,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1718" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47616,7 +47622,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1719" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47642,7 +47648,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1720" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47668,7 +47674,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1721" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47694,7 +47700,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47720,7 +47726,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1723" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47746,7 +47752,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1724" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47772,7 +47778,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1725" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47798,7 +47804,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1726" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47824,7 +47830,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1727" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47850,7 +47856,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47876,7 +47882,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1729" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47902,7 +47908,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1730" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47928,7 +47934,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1731" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47954,7 +47960,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1732" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47980,7 +47986,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1733" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48006,7 +48012,7 @@
         <v>1.75</v>
       </c>
       <c r="G1734" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48032,7 +48038,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48058,7 +48064,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1736" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48084,7 +48090,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1737" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48110,7 +48116,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1738" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48136,7 +48142,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1739" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48162,7 +48168,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1740" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48188,7 +48194,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1741" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48214,7 +48220,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1742" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48240,7 +48246,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1743" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48266,7 +48272,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1744" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48292,7 +48298,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1745" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48318,7 +48324,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1746" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48344,7 +48350,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1747" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48370,7 +48376,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1748" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48396,7 +48402,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1749" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48422,7 +48428,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1750" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48448,7 +48454,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48474,7 +48480,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1752" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48500,7 +48506,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1753" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48526,7 +48532,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1754" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48578,7 +48584,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1756" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48604,7 +48610,7 @@
         <v>1.875</v>
       </c>
       <c r="G1757" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48630,7 +48636,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1758" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48656,7 +48662,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1759" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48682,7 +48688,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1760" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48734,7 +48740,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1762" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48760,7 +48766,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1763" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48786,7 +48792,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1764" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48838,7 +48844,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1766" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48864,7 +48870,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48890,7 +48896,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1768" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48916,7 +48922,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48994,7 +49000,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1772" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49020,7 +49026,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1773" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49046,7 +49052,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1774" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49072,7 +49078,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1775" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49098,7 +49104,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1776" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49124,7 +49130,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1777" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49150,7 +49156,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1778" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49176,7 +49182,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1779" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49202,7 +49208,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1780" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49228,7 +49234,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1781" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49254,7 +49260,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1782" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49306,7 +49312,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1784" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49462,7 +49468,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49514,7 +49520,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1792" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49566,7 +49572,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1794" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49670,7 +49676,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1798" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49774,7 +49780,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1802" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49826,7 +49832,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1804" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49852,7 +49858,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1805" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49904,7 +49910,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1807" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49930,7 +49936,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50112,7 +50118,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1815" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -50138,7 +50144,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1816" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -50164,7 +50170,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1817" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50190,7 +50196,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1818" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50216,7 +50222,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1819" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50242,7 +50248,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1820" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50268,7 +50274,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1821" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50294,7 +50300,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1822" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50320,7 +50326,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50346,7 +50352,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1824" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50372,7 +50378,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1825" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50398,7 +50404,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50424,7 +50430,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1827" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50450,7 +50456,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1828" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50476,7 +50482,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1829" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50502,7 +50508,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1830" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50528,7 +50534,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50554,7 +50560,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1832" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50580,7 +50586,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50606,7 +50612,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1834" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50632,7 +50638,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1835" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50658,7 +50664,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1836" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50684,7 +50690,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1837" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50710,7 +50716,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1838" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50736,7 +50742,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1839" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50762,7 +50768,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1840" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50788,7 +50794,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1841" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50814,7 +50820,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50840,7 +50846,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50866,7 +50872,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1844" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50892,7 +50898,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1845" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50918,7 +50924,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1846" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50944,7 +50950,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1847" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50970,7 +50976,7 @@
         <v>1.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50996,7 +51002,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51022,7 +51028,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51048,7 +51054,7 @@
         <v>1.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51074,7 +51080,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1852" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -51100,7 +51106,7 @@
         <v>1.75</v>
       </c>
       <c r="G1853" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -51126,7 +51132,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1854" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51152,7 +51158,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51178,7 +51184,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51204,7 +51210,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51230,7 +51236,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51256,7 +51262,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51282,7 +51288,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51308,7 +51314,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1861" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51334,7 +51340,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1862" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51360,7 +51366,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1863" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51386,7 +51392,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1864" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51412,7 +51418,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1865" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51438,7 +51444,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1866" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51464,7 +51470,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51490,7 +51496,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51516,7 +51522,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1869" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51542,7 +51548,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1870" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51568,7 +51574,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1871" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51594,7 +51600,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1872" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51620,7 +51626,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1873" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51646,7 +51652,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1874" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51672,7 +51678,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1875" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51698,7 +51704,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51724,7 +51730,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1877" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51750,7 +51756,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1878" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51776,7 +51782,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1879" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51880,7 +51886,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51906,7 +51912,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1884" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51932,7 +51938,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1885" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51958,7 +51964,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1886" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51984,7 +51990,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1887" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52010,7 +52016,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1888" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52036,7 +52042,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1889" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52062,7 +52068,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1890" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52088,7 +52094,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1891" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52114,7 +52120,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1892" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52140,7 +52146,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1893" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52166,7 +52172,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1894" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52218,7 +52224,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1896" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52296,7 +52302,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1899" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52348,7 +52354,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1901" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52374,7 +52380,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1902" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52400,7 +52406,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1903" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52452,7 +52458,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1905" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52478,7 +52484,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1906" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52504,7 +52510,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1907" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52530,7 +52536,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1908" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52608,7 +52614,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1911" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52660,7 +52666,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1913" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52764,7 +52770,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52842,7 +52848,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1920" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53050,7 +53056,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1928" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53076,7 +53082,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1929" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53102,7 +53108,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1930" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53128,7 +53134,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1931" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53154,7 +53160,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1932" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53180,7 +53186,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1933" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53206,7 +53212,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1934" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53232,7 +53238,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1935" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53258,7 +53264,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1936" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53284,7 +53290,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1937" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53310,7 +53316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1938" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53336,7 +53342,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1939" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53362,7 +53368,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1940" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53388,7 +53394,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1941" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53414,7 +53420,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1942" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53440,7 +53446,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1943" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53466,7 +53472,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1944" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53492,7 +53498,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1945" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53518,7 +53524,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1946" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53544,7 +53550,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1947" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53570,7 +53576,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1948" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53596,7 +53602,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1949" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53622,7 +53628,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1950" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53648,7 +53654,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1951" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53674,7 +53680,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1952" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53700,7 +53706,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1953" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53726,7 +53732,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1954" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53752,7 +53758,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1955" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53778,7 +53784,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1956" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53804,7 +53810,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1957" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53830,7 +53836,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1958" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53856,7 +53862,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1959" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53882,7 +53888,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1960" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53908,7 +53914,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1961" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53934,7 +53940,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1962" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53960,7 +53966,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53986,7 +53992,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1964" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54012,7 +54018,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1965" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54038,7 +54044,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1966" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54064,7 +54070,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1967" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54090,7 +54096,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1968" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54116,7 +54122,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1969" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54142,7 +54148,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1970" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54168,7 +54174,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54194,7 +54200,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1972" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54220,7 +54226,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54246,7 +54252,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1974" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54272,7 +54278,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1975" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54298,7 +54304,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54324,7 +54330,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54350,7 +54356,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1978" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54376,7 +54382,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1979" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54402,7 +54408,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1980" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54428,7 +54434,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54454,7 +54460,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1982" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54480,7 +54486,7 @@
         <v>2.25</v>
       </c>
       <c r="G1983" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54506,7 +54512,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1984" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54532,7 +54538,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1985" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54558,7 +54564,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1986" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54584,7 +54590,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1987" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54610,7 +54616,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1988" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54636,7 +54642,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54662,7 +54668,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1990" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54688,7 +54694,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1991" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54714,7 +54720,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1992" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54740,7 +54746,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1993" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54766,7 +54772,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1994" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54792,7 +54798,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1995" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54818,7 +54824,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1996" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54844,7 +54850,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1997" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54870,7 +54876,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1998" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54896,7 +54902,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1999" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54922,7 +54928,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2000" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54948,7 +54954,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2001" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54974,7 +54980,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2002" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55000,7 +55006,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2003" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55026,7 +55032,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2004" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55052,7 +55058,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2005" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55078,7 +55084,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2006" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55104,7 +55110,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2007" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55130,7 +55136,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2008" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55156,7 +55162,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2009" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55182,7 +55188,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2010" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55208,7 +55214,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2011" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55234,7 +55240,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2012" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55260,7 +55266,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2013" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55286,7 +55292,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2014" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55312,7 +55318,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2015" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55338,7 +55344,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2016" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55364,7 +55370,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2017" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55390,7 +55396,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2018" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55416,7 +55422,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2019" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55442,7 +55448,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2020" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55468,7 +55474,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2021" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55494,7 +55500,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2022" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55520,7 +55526,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2023" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55546,7 +55552,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2024" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55572,7 +55578,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2025" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55598,7 +55604,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2026" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55624,7 +55630,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2027" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55650,7 +55656,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55676,7 +55682,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2029" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55702,7 +55708,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2030" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55728,7 +55734,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2031" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55754,7 +55760,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2032" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55780,7 +55786,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2033" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55806,7 +55812,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2034" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55832,7 +55838,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2035" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55858,7 +55864,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55884,7 +55890,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2037" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55910,7 +55916,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2038" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55936,7 +55942,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2039" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55962,7 +55968,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2040" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55988,7 +55994,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2041" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56014,7 +56020,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2042" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56040,7 +56046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2043" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56066,7 +56072,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2044" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56092,7 +56098,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2045" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56118,7 +56124,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2046" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56144,7 +56150,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56170,7 +56176,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2048" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56196,7 +56202,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2049" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56222,7 +56228,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2050" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56248,7 +56254,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2051" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56274,7 +56280,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2052" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56300,7 +56306,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2053" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56326,7 +56332,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2054" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56352,7 +56358,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2055" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56378,7 +56384,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2056" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56404,7 +56410,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2057" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56430,7 +56436,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2058" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56456,7 +56462,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2059" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56482,7 +56488,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56508,7 +56514,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2061" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56534,7 +56540,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2062" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56560,7 +56566,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2063" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56586,7 +56592,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2064" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56612,7 +56618,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2065" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56638,7 +56644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56664,7 +56670,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2067" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56690,7 +56696,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2068" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56716,7 +56722,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2069" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56742,7 +56748,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2070" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56768,7 +56774,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2071" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56794,7 +56800,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2072" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56820,7 +56826,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56846,7 +56852,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2074" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56872,7 +56878,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2075" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56898,7 +56904,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2076" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56924,7 +56930,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2077" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56950,7 +56956,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2078" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56976,7 +56982,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2079" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57002,7 +57008,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2080" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57028,7 +57034,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2081" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57054,7 +57060,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2082" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57080,7 +57086,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2083" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57106,7 +57112,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2084" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57132,7 +57138,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2085" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57158,7 +57164,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2086" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57184,7 +57190,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2087" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57210,7 +57216,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2088" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57236,7 +57242,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2089" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57262,7 +57268,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2090" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57288,7 +57294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57314,7 +57320,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2092" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57340,7 +57346,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2093" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57366,7 +57372,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57392,7 +57398,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2095" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57418,7 +57424,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2096" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57444,7 +57450,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2097" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57470,7 +57476,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2098" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57496,7 +57502,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57522,7 +57528,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2100" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57548,7 +57554,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2101" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57574,7 +57580,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2102" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57600,7 +57606,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2103" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57626,7 +57632,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2104" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57652,7 +57658,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2105" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57678,7 +57684,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2106" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57704,7 +57710,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G2107" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57730,7 +57736,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2108" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57756,7 +57762,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2109" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57782,7 +57788,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2110" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57808,7 +57814,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2111" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57834,7 +57840,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2112" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57860,7 +57866,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2113" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57886,7 +57892,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2114" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57912,7 +57918,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2115" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57938,7 +57944,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2116" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57964,7 +57970,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2117" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57990,7 +57996,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2118" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58016,7 +58022,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2119" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58042,7 +58048,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2120" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58068,7 +58074,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2121" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58094,7 +58100,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2122" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58120,7 +58126,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2123" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58146,7 +58152,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58172,7 +58178,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2125" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58198,7 +58204,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2126" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58224,7 +58230,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2127" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58250,7 +58256,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58276,7 +58282,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2129" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58302,7 +58308,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2130" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58328,7 +58334,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2131" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58354,7 +58360,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2132" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58380,7 +58386,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2133" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58406,7 +58412,7 @@
         <v>1.875</v>
       </c>
       <c r="G2134" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58432,7 +58438,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2135" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58458,7 +58464,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2136" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58484,7 +58490,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2137" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58510,7 +58516,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2138" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58536,7 +58542,7 @@
         <v>2</v>
       </c>
       <c r="G2139" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58562,7 +58568,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2140" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58588,7 +58594,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2141" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58614,7 +58620,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2142" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58640,7 +58646,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58666,7 +58672,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2144" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58692,7 +58698,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2145" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58718,7 +58724,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2146" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58744,7 +58750,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2147" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58770,7 +58776,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2148" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58796,7 +58802,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2149" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58822,7 +58828,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2150" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58848,7 +58854,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2151" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58874,7 +58880,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2152" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58900,7 +58906,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2153" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58926,7 +58932,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2154" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58952,7 +58958,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2155" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58978,7 +58984,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59004,7 +59010,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59030,7 +59036,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2158" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59056,7 +59062,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2159" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59082,7 +59088,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2160" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59108,7 +59114,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2161" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59134,7 +59140,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2162" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59160,7 +59166,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2163" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59186,7 +59192,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2164" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59212,7 +59218,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2165" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59238,7 +59244,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2166" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59264,7 +59270,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2167" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59290,7 +59296,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2168" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59316,7 +59322,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2169" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59342,7 +59348,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2170" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59368,7 +59374,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59394,7 +59400,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2172" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59420,7 +59426,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2173" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59446,7 +59452,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2174" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59472,7 +59478,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2175" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59498,7 +59504,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2176" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59524,7 +59530,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2177" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59550,7 +59556,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2178" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59576,7 +59582,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59602,7 +59608,7 @@
         <v>2.25</v>
       </c>
       <c r="G2180" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59628,7 +59634,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59654,7 +59660,7 @@
         <v>2.25</v>
       </c>
       <c r="G2182" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59680,7 +59686,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2183" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59706,7 +59712,7 @@
         <v>2.25</v>
       </c>
       <c r="G2184" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59732,7 +59738,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2185" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59758,7 +59764,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2186" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59784,7 +59790,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59810,7 +59816,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2188" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59836,7 +59842,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2189" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59862,7 +59868,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2190" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59888,7 +59894,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2191" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59914,7 +59920,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2192" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59940,7 +59946,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2193" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59966,7 +59972,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2194" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59992,7 +59998,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2195" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60018,7 +60024,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2196" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60044,7 +60050,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2197" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60070,7 +60076,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2198" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60096,7 +60102,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2199" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60122,7 +60128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2200" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60148,7 +60154,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2201" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60174,7 +60180,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2202" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60200,7 +60206,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2203" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60226,7 +60232,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2204" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60252,7 +60258,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2205" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60278,7 +60284,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2206" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60304,7 +60310,7 @@
         <v>2</v>
       </c>
       <c r="G2207" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60330,7 +60336,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2208" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60356,7 +60362,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2209" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60382,7 +60388,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2210" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60408,7 +60414,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2211" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60434,7 +60440,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2212" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60460,7 +60466,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2213" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60486,7 +60492,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2214" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60512,7 +60518,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60538,7 +60544,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60564,7 +60570,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2217" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60590,7 +60596,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2218" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60616,7 +60622,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2219" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60642,7 +60648,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2220" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60668,7 +60674,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60694,7 +60700,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2222" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60720,7 +60726,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2223" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60746,7 +60752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2224" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60772,7 +60778,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2225" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60798,7 +60804,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60824,7 +60830,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2227" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60850,7 +60856,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60876,7 +60882,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2229" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60902,7 +60908,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2230" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60928,7 +60934,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2231" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60954,7 +60960,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2232" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60980,7 +60986,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2233" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61006,7 +61012,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61032,7 +61038,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2235" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61058,7 +61064,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2236" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61084,7 +61090,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61110,7 +61116,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2238" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61136,7 +61142,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2239" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61162,7 +61168,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2240" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61188,7 +61194,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2241" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61214,7 +61220,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2242" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61240,7 +61246,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2243" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61266,7 +61272,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61292,7 +61298,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2245" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61318,7 +61324,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2246" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61344,7 +61350,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2247" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61370,7 +61376,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2248" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61396,7 +61402,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61422,7 +61428,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2250" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61448,7 +61454,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2251" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61474,7 +61480,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2252" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61500,7 +61506,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2253" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61526,7 +61532,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2254" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61552,7 +61558,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2255" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61578,7 +61584,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2256" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61604,7 +61610,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61630,7 +61636,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2258" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61656,7 +61662,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2259" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61682,7 +61688,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2260" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61708,7 +61714,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2261" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61734,7 +61740,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2262" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61760,7 +61766,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2263" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61786,7 +61792,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2264" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61812,7 +61818,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61838,7 +61844,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2266" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61864,7 +61870,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2267" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61890,7 +61896,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2268" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61916,7 +61922,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2269" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61942,7 +61948,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2270" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61968,7 +61974,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2271" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61994,7 +62000,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2272" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62020,7 +62026,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2273" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62046,7 +62052,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2274" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62072,7 +62078,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2275" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62098,7 +62104,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2276" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62124,7 +62130,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2277" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62150,7 +62156,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62176,7 +62182,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2279" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62202,7 +62208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2280" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62228,7 +62234,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2281" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62254,7 +62260,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2282" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62280,7 +62286,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2283" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62306,7 +62312,7 @@
         <v>2</v>
       </c>
       <c r="G2284" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62332,7 +62338,7 @@
         <v>2</v>
       </c>
       <c r="G2285" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62358,7 +62364,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2286" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62384,7 +62390,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2287" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62410,7 +62416,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2288" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62436,7 +62442,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2289" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62462,7 +62468,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2290" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62488,7 +62494,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2291" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62514,7 +62520,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62540,7 +62546,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2293" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62566,7 +62572,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62592,7 +62598,7 @@
         <v>2</v>
       </c>
       <c r="G2295" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62618,7 +62624,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62644,7 +62650,7 @@
         <v>2</v>
       </c>
       <c r="G2297" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62670,7 +62676,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2298" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62696,7 +62702,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2299" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62722,7 +62728,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2300" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62748,7 +62754,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2301" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62774,7 +62780,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2302" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62800,7 +62806,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2303" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62826,7 +62832,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2304" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62852,7 +62858,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2305" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62878,7 +62884,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2306" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62904,7 +62910,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2307" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62930,7 +62936,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2308" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62956,7 +62962,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2309" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62982,7 +62988,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2310" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63008,7 +63014,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63034,7 +63040,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2312" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63060,7 +63066,7 @@
         <v>2</v>
       </c>
       <c r="G2313" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63086,7 +63092,7 @@
         <v>2</v>
       </c>
       <c r="G2314" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63112,7 +63118,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2315" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63138,7 +63144,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63164,7 +63170,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63190,7 +63196,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2318" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63216,7 +63222,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2319" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63242,7 +63248,7 @@
         <v>2</v>
       </c>
       <c r="G2320" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63268,7 +63274,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2321" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63294,7 +63300,7 @@
         <v>2</v>
       </c>
       <c r="G2322" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63320,7 +63326,7 @@
         <v>2</v>
       </c>
       <c r="G2323" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63346,7 +63352,7 @@
         <v>2</v>
       </c>
       <c r="G2324" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63372,7 +63378,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2325" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63398,7 +63404,7 @@
         <v>2</v>
       </c>
       <c r="G2326" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63424,7 +63430,7 @@
         <v>2</v>
       </c>
       <c r="G2327" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63450,7 +63456,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2328" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63476,7 +63482,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2329" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63502,7 +63508,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2330" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63528,7 +63534,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2331" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63554,7 +63560,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63580,7 +63586,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2333" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63606,7 +63612,7 @@
         <v>2</v>
       </c>
       <c r="G2334" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63632,7 +63638,7 @@
         <v>2</v>
       </c>
       <c r="G2335" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63658,7 +63664,7 @@
         <v>2</v>
       </c>
       <c r="G2336" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63684,7 +63690,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2337" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63710,7 +63716,7 @@
         <v>2</v>
       </c>
       <c r="G2338" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63736,7 +63742,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2339" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63762,7 +63768,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2340" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63788,7 +63794,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2341" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63814,7 +63820,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2342" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63840,7 +63846,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2343" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63866,7 +63872,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2344" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63892,7 +63898,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2345" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63918,7 +63924,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2346" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63944,7 +63950,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63970,7 +63976,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2348" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63996,7 +64002,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64022,7 +64028,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2350" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64048,7 +64054,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2351" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64074,7 +64080,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2352" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64100,7 +64106,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2353" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64126,7 +64132,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2354" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64152,7 +64158,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2355" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64178,7 +64184,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2356" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64204,7 +64210,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2357" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64230,7 +64236,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2358" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64256,7 +64262,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2359" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64282,7 +64288,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64308,7 +64314,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2361" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64334,7 +64340,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2362" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64360,7 +64366,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2363" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64386,7 +64392,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2364" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64412,7 +64418,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2365" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64438,7 +64444,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2366" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64464,7 +64470,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2367" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64490,7 +64496,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2368" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64516,7 +64522,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2369" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64542,7 +64548,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2370" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64568,7 +64574,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2371" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64594,7 +64600,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2372" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64620,7 +64626,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2373" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64646,7 +64652,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2374" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64672,7 +64678,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2375" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64698,7 +64704,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2376" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64724,7 +64730,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2377" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64750,7 +64756,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2378" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64776,7 +64782,7 @@
         <v>2</v>
       </c>
       <c r="G2379" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64802,7 +64808,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2380" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64828,7 +64834,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2381" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64854,7 +64860,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2382" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64880,7 +64886,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2383" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64906,7 +64912,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2384" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64932,7 +64938,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2385" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64958,7 +64964,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2386" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64984,7 +64990,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2387" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65010,7 +65016,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2388" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65036,7 +65042,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2389" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65062,7 +65068,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2390" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65088,7 +65094,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2391" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65114,7 +65120,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2392" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65140,7 +65146,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65166,7 +65172,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2394" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65192,7 +65198,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2395" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65218,7 +65224,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2396" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65244,7 +65250,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65270,7 +65276,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2398" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65296,7 +65302,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2399" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65322,7 +65328,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2400" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65348,7 +65354,7 @@
         <v>2.25</v>
       </c>
       <c r="G2401" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65374,7 +65380,7 @@
         <v>2.25</v>
       </c>
       <c r="G2402" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65400,7 +65406,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2403" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65426,7 +65432,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2404" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65452,7 +65458,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2405" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65478,7 +65484,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G2406" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65504,7 +65510,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2407" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65530,7 +65536,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2408" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65556,7 +65562,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2409" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65582,7 +65588,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2410" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65608,7 +65614,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2411" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65634,7 +65640,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G2412" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65660,7 +65666,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2413" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65686,7 +65692,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2414" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65712,7 +65718,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2415" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65738,7 +65744,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65764,7 +65770,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2417" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65790,7 +65796,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2418" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65816,7 +65822,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2419" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65842,7 +65848,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2420" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65868,7 +65874,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2421" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65894,7 +65900,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2422" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65920,7 +65926,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2423" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65946,7 +65952,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2424" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65972,7 +65978,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2425" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65998,7 +66004,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2426" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66024,7 +66030,7 @@
         <v>2.5</v>
       </c>
       <c r="G2427" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66050,7 +66056,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G2428" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66076,7 +66082,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2429" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66102,7 +66108,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G2430" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66128,7 +66134,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2431" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66154,7 +66160,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2432" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66180,7 +66186,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2433" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66206,7 +66212,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G2434" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66232,7 +66238,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G2435" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66258,7 +66264,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G2436" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66284,7 +66290,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G2437" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66310,7 +66316,7 @@
         <v>2.75</v>
       </c>
       <c r="G2438" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66336,7 +66342,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2439" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66362,7 +66368,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2440" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66388,7 +66394,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66414,7 +66420,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2442" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66440,7 +66446,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66466,7 +66472,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G2444" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66492,7 +66498,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G2445" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66518,7 +66524,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G2446" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66544,7 +66550,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G2447" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66570,7 +66576,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2448" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66596,7 +66602,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2449" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66622,7 +66628,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2450" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66648,7 +66654,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66674,7 +66680,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66700,7 +66706,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2453" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66726,7 +66732,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2454" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66752,7 +66758,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2455" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66778,7 +66784,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2456" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66804,7 +66810,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2457" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66830,7 +66836,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G2458" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66856,7 +66862,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2459" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66882,7 +66888,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2460" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66908,7 +66914,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2461" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66934,7 +66940,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2462" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66960,7 +66966,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2463" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66986,7 +66992,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2464" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67012,7 +67018,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G2465" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67038,7 +67044,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67064,7 +67070,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2467" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67090,7 +67096,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G2468" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67116,7 +67122,7 @@
         <v>2.5</v>
       </c>
       <c r="G2469" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67142,7 +67148,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67168,7 +67174,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2471" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67194,7 +67200,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2472" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67220,7 +67226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2473" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67246,7 +67252,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2474" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67272,7 +67278,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2475" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67298,7 +67304,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2476" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67324,7 +67330,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2477" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67350,7 +67356,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2478" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67376,7 +67382,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67402,7 +67408,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2480" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67428,7 +67434,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2481" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67454,7 +67460,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2482" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67480,7 +67486,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2483" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67506,7 +67512,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67532,7 +67538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2485" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67558,7 +67564,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2486" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67584,7 +67590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2487" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67610,7 +67616,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2488" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67636,7 +67642,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2489" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67662,7 +67668,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2490" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67688,7 +67694,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67714,7 +67720,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2492" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67740,7 +67746,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2493" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67766,7 +67772,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2494" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67792,7 +67798,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67818,7 +67824,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2496" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67844,7 +67850,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2497" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67870,7 +67876,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2498" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67896,7 +67902,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2499" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67922,7 +67928,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2500" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67948,7 +67954,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2501" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67974,7 +67980,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2502" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68000,7 +68006,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68026,7 +68032,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2504" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68052,7 +68058,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G2505" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68078,7 +68084,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2506" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68104,7 +68110,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2507" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68130,7 +68136,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2508" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68156,7 +68162,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2509" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68182,7 +68188,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2510" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68208,7 +68214,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2511" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68216,7 +68222,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6845023148</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>15162</v>
@@ -68234,9 +68240,35 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2512" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6912962963</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>28816</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>861</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="862">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965505003929138</t>
+    <t xml:space="preserve">0.965504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
@@ -50,70 +50,70 @@
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97840690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169192790985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053933620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487425327301</t>
+    <t xml:space="preserve">0.978407025337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169371604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938376426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487365722656</t>
   </si>
   <si>
     <t xml:space="preserve">0.9447181224823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931816160678864</t>
+    <t xml:space="preserve">0.931816101074219</t>
   </si>
   <si>
     <t xml:space="preserve">0.863005101680756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874473690986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386274814606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994420051575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057658672333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375771999359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428090572357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560987949371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606409549713</t>
+    <t xml:space="preserve">0.874473512172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386155605316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994479656219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057539463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428030967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899561047554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606469154358</t>
   </si>
   <si>
     <t xml:space="preserve">0.898844122886658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866589069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466674804688</t>
+    <t xml:space="preserve">0.866588950157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466734409332</t>
   </si>
   <si>
     <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745452880859375</t>
+    <t xml:space="preserve">0.807812869548798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74545282125473</t>
   </si>
   <si>
     <t xml:space="preserve">0.713197767734528</t>
@@ -122,52 +122,52 @@
     <t xml:space="preserve">0.731117248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.704237937927246</t>
+    <t xml:space="preserve">0.704238057136536</t>
   </si>
   <si>
     <t xml:space="preserve">0.723949491977692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774124205112457</t>
+    <t xml:space="preserve">0.774124145507812</t>
   </si>
   <si>
     <t xml:space="preserve">0.788459837436676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800645053386688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802795469760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802366733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827882647514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804945826530457</t>
+    <t xml:space="preserve">0.800645172595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298799037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827882766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804945766925812</t>
   </si>
   <si>
     <t xml:space="preserve">0.835050702095032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333837032318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634431362152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658906936646</t>
+    <t xml:space="preserve">0.834333896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634610176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658787727356</t>
   </si>
   <si>
     <t xml:space="preserve">0.88020783662796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839351177215576</t>
+    <t xml:space="preserve">0.839351236820221</t>
   </si>
   <si>
     <t xml:space="preserve">0.850819885730743</t>
@@ -176,43 +176,43 @@
     <t xml:space="preserve">0.873040080070496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809263706207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977079868317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225355625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85297018289566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889723300934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86730569601059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86013799905777</t>
+    <t xml:space="preserve">0.877340614795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809144496918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977139472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225415229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85297030210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889782905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924642086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860138058662415</t>
   </si>
   <si>
     <t xml:space="preserve">0.830749988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858704507350922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120599269867</t>
+    <t xml:space="preserve">0.858704328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120539665222</t>
   </si>
   <si>
     <t xml:space="preserve">0.851536512374878</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">0.859421193599701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449334621429</t>
+    <t xml:space="preserve">0.840784907341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449155807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.79921156167984</t>
@@ -233,73 +233,73 @@
     <t xml:space="preserve">0.789893329143524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.813547134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858529567719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781291961669922</t>
+    <t xml:space="preserve">0.813547074794769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292021274567</t>
   </si>
   <si>
     <t xml:space="preserve">0.784875929355621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809246420860291</t>
+    <t xml:space="preserve">0.809246480464935</t>
   </si>
   <si>
     <t xml:space="preserve">0.817130982875824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837917804718018</t>
+    <t xml:space="preserve">0.837917745113373</t>
   </si>
   <si>
     <t xml:space="preserve">0.821431756019592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814980626106262</t>
+    <t xml:space="preserve">0.814980745315552</t>
   </si>
   <si>
     <t xml:space="preserve">0.812113583087921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811396718025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928247928619</t>
+    <t xml:space="preserve">0.811396777629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928426742554</t>
   </si>
   <si>
     <t xml:space="preserve">0.794194102287292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787026226520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512275218964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921529769897</t>
+    <t xml:space="preserve">0.787026286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512156009674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697610378265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921470165253</t>
   </si>
   <si>
     <t xml:space="preserve">0.759788513183594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762655675411224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204545497894</t>
+    <t xml:space="preserve">0.762655735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204664707184</t>
   </si>
   <si>
     <t xml:space="preserve">0.750470459461212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77914172410965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372480869293</t>
+    <t xml:space="preserve">0.779141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372540473938</t>
   </si>
   <si>
     <t xml:space="preserve">0.767673134803772</t>
@@ -308,64 +308,64 @@
     <t xml:space="preserve">0.780575156211853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775557816028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159123897552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218458652496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380407810211</t>
+    <t xml:space="preserve">0.775557696819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627653598785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380586624146</t>
   </si>
   <si>
     <t xml:space="preserve">0.872163951396942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869937181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029922962189</t>
+    <t xml:space="preserve">0.869937241077423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029982566833</t>
   </si>
   <si>
     <t xml:space="preserve">0.861772298812866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853607296943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576442718506</t>
+    <t xml:space="preserve">0.85360723733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576502323151</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741384983063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855834126472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277352809906</t>
+    <t xml:space="preserve">0.855834066867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277472019196</t>
   </si>
   <si>
     <t xml:space="preserve">0.825401186943054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829112470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83059698343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85880309343338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84470009803772</t>
+    <t xml:space="preserve">0.829112529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830597043037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858803153038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504301548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844700217247009</t>
   </si>
   <si>
     <t xml:space="preserve">0.843957781791687</t>
@@ -374,49 +374,49 @@
     <t xml:space="preserve">0.846184611320496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83579283952713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833566188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838761985301971</t>
+    <t xml:space="preserve">0.83579295873642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833566129207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761925697327</t>
   </si>
   <si>
     <t xml:space="preserve">0.816493988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809813559055328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916554450989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810555875301361</t>
+    <t xml:space="preserve">0.809813499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916614055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810555756092072</t>
   </si>
   <si>
     <t xml:space="preserve">0.801648676395416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81797844171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720877170563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819463014602661</t>
+    <t xml:space="preserve">0.817978501319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720698356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819462954998016</t>
   </si>
   <si>
     <t xml:space="preserve">0.826143443584442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81278258562088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808328986167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133189678192</t>
+    <t xml:space="preserve">0.81278270483017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808329105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133130073547</t>
   </si>
   <si>
     <t xml:space="preserve">0.805359959602356</t>
@@ -425,37 +425,37 @@
     <t xml:space="preserve">0.796452701091766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800906240940094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514707565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999220848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791256785392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586789131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814267039299011</t>
+    <t xml:space="preserve">0.800906360149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514588356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999161243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791256904602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807586848735809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814267158508301</t>
   </si>
   <si>
     <t xml:space="preserve">0.804617643356323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225931167603</t>
+    <t xml:space="preserve">0.79867959022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225990772247</t>
   </si>
   <si>
     <t xml:space="preserve">0.786803245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77938050031662</t>
+    <t xml:space="preserve">0.779380559921265</t>
   </si>
   <si>
     <t xml:space="preserve">0.777153849601746</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838019669055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844472885132</t>
+    <t xml:space="preserve">0.838019728660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844413280487</t>
   </si>
   <si>
     <t xml:space="preserve">0.774927020072937</t>
@@ -485,55 +485,55 @@
     <t xml:space="preserve">0.783834159374237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765277504920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778638303279877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091902732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545442581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786060988903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774184763431549</t>
+    <t xml:space="preserve">0.765277445316315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778638422489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091962337494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545561790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786061108112335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102216243744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452608585358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731131076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215584754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865040302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442414283752</t>
+    <t xml:space="preserve">0.806102156639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452548980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841731011867523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411440849304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215703964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865099906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442354679108</t>
   </si>
   <si>
     <t xml:space="preserve">0.849153757095337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874390840530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514436244965</t>
+    <t xml:space="preserve">0.874390780925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86251437664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225957870483</t>
@@ -542,55 +542,55 @@
     <t xml:space="preserve">0.85509181022644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857318639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832823812961578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834308385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827627897262573</t>
+    <t xml:space="preserve">0.857318580150604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832823753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834308326244354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827627956867218</t>
   </si>
   <si>
     <t xml:space="preserve">0.860287725925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.854349613189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867710411548615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880328893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648583889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380315303802</t>
+    <t xml:space="preserve">0.854349553585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867710292339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880328834056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648464679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669032096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380374908447</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916699945926666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091717720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545376777649</t>
+    <t xml:space="preserve">0.916700005531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091777324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545436382294</t>
   </si>
   <si>
     <t xml:space="preserve">0.915957748889923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911504209041595</t>
+    <t xml:space="preserve">0.911504149436951</t>
   </si>
   <si>
     <t xml:space="preserve">0.908535003662109</t>
@@ -599,49 +599,49 @@
     <t xml:space="preserve">0.898885548114777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991668999195099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792892932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768968582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06960701942444</t>
+    <t xml:space="preserve">0.991668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792773723602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768956661224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06960713863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06886494159698</t>
+    <t xml:space="preserve">1.06886470317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659676551819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05327725410461</t>
+    <t xml:space="preserve">1.05327713489532</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249371051788</t>
+    <t xml:space="preserve">1.03249382972717</t>
   </si>
   <si>
     <t xml:space="preserve">1.02432870864868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03175127506256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467931270599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00206065177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02284443378448</t>
+    <t xml:space="preserve">1.03175139427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0146791934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00206077098846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02284419536591</t>
   </si>
   <si>
     <t xml:space="preserve">1.03026700019836</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">1.06812250614166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585468769073</t>
+    <t xml:space="preserve">1.04585456848145</t>
   </si>
   <si>
     <t xml:space="preserve">1.06663811206818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449361801147</t>
+    <t xml:space="preserve">1.10449373722076</t>
   </si>
   <si>
     <t xml:space="preserve">1.11191630363464</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">1.2314213514328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2173182964325</t>
+    <t xml:space="preserve">1.21731817722321</t>
   </si>
   <si>
     <t xml:space="preserve">1.22177195549011</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">1.23216366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22845232486725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23513281345367</t>
+    <t xml:space="preserve">1.22845220565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2351325750351</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474086284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2128643989563</t>
+    <t xml:space="preserve">1.21286451816559</t>
   </si>
   <si>
     <t xml:space="preserve">1.21360695362091</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">1.20098829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700880050659</t>
+    <t xml:space="preserve">1.24700903892517</t>
   </si>
   <si>
     <t xml:space="preserve">1.26779234409332</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">1.26036977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25888514518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26927709579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639040470123</t>
+    <t xml:space="preserve">1.25888526439667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26927697658539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
     <t xml:space="preserve">1.34424602985382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23958623409271</t>
+    <t xml:space="preserve">1.239586353302</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
@@ -758,49 +758,49 @@
     <t xml:space="preserve">1.17278218269348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1653596162796</t>
+    <t xml:space="preserve">1.16535949707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.17055547237396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17723572254181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16387498378754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16164827346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15051400661469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15348327159882</t>
+    <t xml:space="preserve">1.1772358417511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649376392365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16387510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16164839267731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15051412582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348339080811</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824618816376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14383375644684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1891120672226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20247292518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28412222862244</t>
+    <t xml:space="preserve">1.14383387565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18911218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20247280597687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
     <t xml:space="preserve">1.28486442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31307089328766</t>
+    <t xml:space="preserve">1.31307077407837</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057306289673</t>
+    <t xml:space="preserve">1.35057282447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32855689525604</t>
+    <t xml:space="preserve">1.32855701446533</t>
   </si>
   <si>
     <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031149864197</t>
+    <t xml:space="preserve">1.35512793064117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031161785126</t>
   </si>
   <si>
     <t xml:space="preserve">1.3665155172348</t>
@@ -854,34 +854,34 @@
     <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36727476119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3915684223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39232754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701331615448</t>
+    <t xml:space="preserve">1.36727488040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39156830310822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39232742786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549494743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258887290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701343536377</t>
   </si>
   <si>
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3513320684433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31565093994141</t>
+    <t xml:space="preserve">1.36120140552521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35133218765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3156510591507</t>
   </si>
   <si>
     <t xml:space="preserve">1.33842611312866</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">1.34298121929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31868767738342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29363465309143</t>
+    <t xml:space="preserve">1.31868755817413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29363477230072</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">1.320965051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31413245201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36955237388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536440372467</t>
+    <t xml:space="preserve">1.31413233280182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3695524930954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562584877014</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">1.40143764019012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38625419139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397657871246</t>
+    <t xml:space="preserve">1.38625407218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397669792175</t>
   </si>
   <si>
     <t xml:space="preserve">1.38929092884064</t>
@@ -932,52 +932,52 @@
     <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37866246700287</t>
+    <t xml:space="preserve">1.37866234779358</t>
   </si>
   <si>
     <t xml:space="preserve">1.38473570346832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34829556941986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42497205734253</t>
+    <t xml:space="preserve">1.34829545021057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42497229576111</t>
   </si>
   <si>
     <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50164878368378</t>
+    <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">1.47735524177551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55630934238434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51835072040558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568111896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379549503326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594244480133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51075899600983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52897906303406</t>
+    <t xml:space="preserve">1.55630946159363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51835060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379573345184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51075887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52897918224335</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53049755096436</t>
+    <t xml:space="preserve">1.53049743175507</t>
   </si>
   <si>
     <t xml:space="preserve">1.53353416919708</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40599274635315</t>
+    <t xml:space="preserve">1.40599286556244</t>
   </si>
   <si>
     <t xml:space="preserve">1.38777256011963</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2905980348587</t>
+    <t xml:space="preserve">1.29059815406799</t>
   </si>
   <si>
     <t xml:space="preserve">1.29970824718475</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">1.30502247810364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42573142051697</t>
+    <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
     <t xml:space="preserve">1.47052264213562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47659599781036</t>
+    <t xml:space="preserve">1.47659611701965</t>
   </si>
   <si>
     <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48722445964813</t>
+    <t xml:space="preserve">1.48722434043884</t>
   </si>
   <si>
     <t xml:space="preserve">1.42269456386566</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">1.40447437763214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39308679103851</t>
+    <t xml:space="preserve">1.39308667182922</t>
   </si>
   <si>
     <t xml:space="preserve">1.40371513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37182998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36271965503693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423814296722</t>
+    <t xml:space="preserve">1.37182986736298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36271977424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423802375793</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
@@ -1061,22 +1061,22 @@
     <t xml:space="preserve">1.36499726772308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36575651168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37107050418854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4272495508194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49937117099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49557566642761</t>
+    <t xml:space="preserve">1.36575639247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37107062339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42724967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4993714094162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
     <t xml:space="preserve">1.49177956581116</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.45761656761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43863725662231</t>
+    <t xml:space="preserve">1.4386373758316</t>
   </si>
   <si>
     <t xml:space="preserve">1.37790322303772</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30957746505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33994448184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32476103305817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161872386932</t>
+    <t xml:space="preserve">1.30957758426666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33994460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32476091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753620624542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337332725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161860466003</t>
   </si>
   <si>
     <t xml:space="preserve">1.31716918945312</t>
@@ -1121,40 +1121,40 @@
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206610202789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41965782642365</t>
+    <t xml:space="preserve">1.41206622123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
     <t xml:space="preserve">1.44243323802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45382070541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46900415420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418772220612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46520853042603</t>
+    <t xml:space="preserve">1.45382082462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46900427341461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48418784141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520829200745</t>
   </si>
   <si>
     <t xml:space="preserve">1.42345380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41586220264435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002496242523</t>
+    <t xml:space="preserve">1.41586208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002484321594</t>
   </si>
   <si>
     <t xml:space="preserve">1.46141254901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54112577438354</t>
+    <t xml:space="preserve">1.54112601280212</t>
   </si>
   <si>
     <t xml:space="preserve">1.47280025482178</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">1.51551640033722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50768423080444</t>
+    <t xml:space="preserve">1.50768411159515</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726447582245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51943254470825</t>
+    <t xml:space="preserve">1.51943242549896</t>
   </si>
   <si>
     <t xml:space="preserve">1.50376808643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49202001094818</t>
+    <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
     <t xml:space="preserve">1.46852362155914</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4646075963974</t>
+    <t xml:space="preserve">1.46460747718811</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677530765533</t>
@@ -1205,61 +1205,61 @@
     <t xml:space="preserve">1.47635567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44111120700836</t>
+    <t xml:space="preserve">1.44111108779907</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278975009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40978252887726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42153084278107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936289310455</t>
+    <t xml:space="preserve">1.36278986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40978264808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42153072357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936301231384</t>
   </si>
   <si>
     <t xml:space="preserve">1.43327915668488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45285940170288</t>
+    <t xml:space="preserve">1.45285928249359</t>
   </si>
   <si>
     <t xml:space="preserve">1.39803445339203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.394118309021</t>
+    <t xml:space="preserve">1.39411842823029</t>
   </si>
   <si>
     <t xml:space="preserve">1.34712564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362926006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.32362937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30796492099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146131038666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055250644684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29621660709381</t>
+    <t xml:space="preserve">1.30796504020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30404877662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146142959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055262565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29621684551239</t>
   </si>
   <si>
     <t xml:space="preserve">1.31188094615936</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">1.34320962429047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35104167461395</t>
+    <t xml:space="preserve">1.35104179382324</t>
   </si>
   <si>
     <t xml:space="preserve">1.3862863779068</t>
@@ -1280,31 +1280,31 @@
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845408916473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3275454044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838467597961</t>
+    <t xml:space="preserve">1.37845396995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32754528522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838455677032</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30013298988342</t>
+    <t xml:space="preserve">1.30013287067413</t>
   </si>
   <si>
     <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230082035065</t>
+    <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31579720973969</t>
+    <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
     <t xml:space="preserve">1.31971323490143</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761469841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48810398578644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49593591690063</t>
+    <t xml:space="preserve">1.41761457920074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48810386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49593603610992</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985206127167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5116001367569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334845066071</t>
+    <t xml:space="preserve">1.51160025596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334856987</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509676456451</t>
@@ -1343,31 +1343,31 @@
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992147445679</t>
+    <t xml:space="preserve">1.58992159366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.6212500333786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60558581352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61341798305511</t>
+    <t xml:space="preserve">1.60558569431305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61341786384583</t>
   </si>
   <si>
     <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62908208370209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64474618434906</t>
+    <t xml:space="preserve">1.62908220291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64474642276764</t>
   </si>
   <si>
     <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65257859230042</t>
+    <t xml:space="preserve">1.65257847309113</t>
   </si>
   <si>
     <t xml:space="preserve">1.66041052341461</t>
@@ -1376,70 +1376,70 @@
     <t xml:space="preserve">1.66824293136597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70740365982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439608097076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74656414985657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222836971283</t>
+    <t xml:space="preserve">1.70740354061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439620018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74656403064728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222825050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.80138885974884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838163852692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006030082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7778924703598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82488524913788</t>
+    <t xml:space="preserve">1.84838151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006018161774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77789258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82488536834717</t>
   </si>
   <si>
     <t xml:space="preserve">1.80922091007233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83271718025208</t>
+    <t xml:space="preserve">1.83271729946136</t>
   </si>
   <si>
     <t xml:space="preserve">1.84054958820343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87971043586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404585838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85621380805969</t>
+    <t xml:space="preserve">1.87971019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85621392726898</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94236719608307</t>
+    <t xml:space="preserve">1.94236743450165</t>
   </si>
   <si>
     <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369587421417</t>
+    <t xml:space="preserve">1.97369563579559</t>
   </si>
   <si>
     <t xml:space="preserve">1.99719202518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96586334705353</t>
+    <t xml:space="preserve">1.96586346626282</t>
   </si>
   <si>
     <t xml:space="preserve">1.93453502655029</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">1.91887080669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92670273780823</t>
+    <t xml:space="preserve">1.92670285701752</t>
   </si>
   <si>
     <t xml:space="preserve">1.98178458213806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94942891597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9656069278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662863731384</t>
+    <t xml:space="preserve">1.94942879676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662875652313</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338398456573</t>
+    <t xml:space="preserve">1.76338410377502</t>
   </si>
   <si>
     <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78765070438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573941230774</t>
+    <t xml:space="preserve">1.78765058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573953151703</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
@@ -1487,22 +1487,22 @@
     <t xml:space="preserve">1.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82809507846832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236191749573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8928062915802</t>
+    <t xml:space="preserve">1.82809495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236203670502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280641078949</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88471758365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.8847177028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
@@ -1514,37 +1514,37 @@
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94134020805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93325126171112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751774311066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99796235561371</t>
+    <t xml:space="preserve">1.90898418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9413400888443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93325114250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751798152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.997962474823</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516219615936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74720621109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75529503822327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631686687469</t>
+    <t xml:space="preserve">1.92516231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7472060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75529491901398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631674766541</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">1.56116080284119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4964497089386</t>
+    <t xml:space="preserve">1.49644958972931</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747141838074</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">1.4155604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34276032447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31849336624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29827117919922</t>
+    <t xml:space="preserve">1.34276020526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31849348545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29827105998993</t>
   </si>
   <si>
     <t xml:space="preserve">1.17289304733276</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.22951531410217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15267050266266</t>
+    <t xml:space="preserve">1.15267062187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">1.03538143634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15671503543854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14053726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693746089935</t>
+    <t xml:space="preserve">1.07178151607513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15671515464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1405371427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693734169006</t>
   </si>
   <si>
     <t xml:space="preserve">1.09604823589325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18502628803253</t>
+    <t xml:space="preserve">1.18502616882324</t>
   </si>
   <si>
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364928483963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075956821442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24569308757782</t>
+    <t xml:space="preserve">1.13649272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075944900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24569320678711</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862620830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10009253025055</t>
+    <t xml:space="preserve">1.14862608909607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10009264945984</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.12840390205383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24164879322052</t>
+    <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
     <t xml:space="preserve">1.23760414123535</t>
@@ -1685,106 +1685,106 @@
     <t xml:space="preserve">1.21738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1688483953476</t>
+    <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
     <t xml:space="preserve">1.20929312705994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24973750114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2214263677597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.2497376203537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22142624855042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582592964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05964803695679</t>
+    <t xml:space="preserve">1.07582604885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0596479177475</t>
   </si>
   <si>
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0839147567749</t>
+    <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
     <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05560350418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155920982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02324795722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02729249000549</t>
+    <t xml:space="preserve">1.0556036233902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155909061432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324783802032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0272923707962</t>
   </si>
   <si>
     <t xml:space="preserve">1.00302577018738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982803463935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954492151737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970670104026794</t>
+    <t xml:space="preserve">0.982803344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954492092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97067004442215</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847937107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962581098079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96662563085556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758871555328</t>
+    <t xml:space="preserve">0.986847817897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962581157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966625571250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978758990764618</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10413730144501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23355972766876</t>
+    <t xml:space="preserve">1.10413706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23355984687805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120406150818</t>
+    <t xml:space="preserve">1.20120418071747</t>
   </si>
   <si>
     <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31040453910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32253777980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32658243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34680461883545</t>
+    <t xml:space="preserve">1.31040441989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32253789901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32658231258392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34680449962616</t>
   </si>
   <si>
     <t xml:space="preserve">1.33467125892639</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4681384563446</t>
+    <t xml:space="preserve">1.46813833713531</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498291015625</t>
+    <t xml:space="preserve">1.54498302936554</t>
   </si>
   <si>
     <t xml:space="preserve">1.52071642875671</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">1.51667189598083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689432144165</t>
+    <t xml:space="preserve">1.53689420223236</t>
   </si>
   <si>
     <t xml:space="preserve">1.581383228302</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247608423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822792053223</t>
+    <t xml:space="preserve">1.52476072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52880537509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822780132294</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69867241382599</t>
+    <t xml:space="preserve">1.69867253303528</t>
   </si>
   <si>
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249452114105</t>
+    <t xml:space="preserve">1.68249475955963</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440581321716</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">1.62587225437164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61778342723846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71485018730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5571163892746</t>
+    <t xml:space="preserve">1.61778330802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71485030651093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55711650848389</t>
   </si>
   <si>
     <t xml:space="preserve">1.48431622982025</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">1.47218286991119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59351658821106</t>
+    <t xml:space="preserve">1.59351670742035</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3306268453598</t>
+    <t xml:space="preserve">1.33062672615051</t>
   </si>
   <si>
     <t xml:space="preserve">1.3589380979538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44791615009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409392356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47622728347778</t>
+    <t xml:space="preserve">1.44791603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409380435944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
     <t xml:space="preserve">1.60160553455353</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">1.59756112098694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60969436168671</t>
+    <t xml:space="preserve">1.609694480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72660851478577</t>
+    <t xml:space="preserve">1.72660839557648</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343998908997</t>
+    <t xml:space="preserve">1.64659488201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343986988068</t>
   </si>
   <si>
     <t xml:space="preserve">1.63817250728607</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64238357543945</t>
+    <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
     <t xml:space="preserve">1.61711609363556</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59605991840363</t>
+    <t xml:space="preserve">1.59606003761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
+    <t xml:space="preserve">1.53289151191711</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4360328912735</t>
+    <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499022960663</t>
+    <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077904224396</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.54131388664246</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868008613586</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869359970093</t>
+    <t xml:space="preserve">1.60869371891022</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60027134418488</t>
+    <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
     <t xml:space="preserve">1.62553858757019</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501737594604</t>
+    <t xml:space="preserve">1.65501749515533</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290490627289</t>
+    <t xml:space="preserve">1.61290502548218</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184885025024</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025759220123</t>
+    <t xml:space="preserve">1.52025771141052</t>
   </si>
   <si>
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763754367828</t>
+    <t xml:space="preserve">1.58763742446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
@@ -2595,6 +2595,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.24000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25</t>
   </si>
 </sst>
 </file>
@@ -68271,7 +68274,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6923958333</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>11007</v>
@@ -68292,6 +68295,32 @@
         <v>860</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6919907407</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>21855</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>861</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504884719849</t>
+    <t xml:space="preserve">0.965504944324493</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892954826355</t>
+    <t xml:space="preserve">0.994893014431</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978407025337219</t>
+    <t xml:space="preserve">0.978406965732574</t>
   </si>
   <si>
     <t xml:space="preserve">0.951169371604919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959053993225098</t>
+    <t xml:space="preserve">0.959053933620453</t>
   </si>
   <si>
     <t xml:space="preserve">0.966938376426697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960487365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9447181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473512172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386155605316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994479656219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057539463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375712394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428030967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899561047554016</t>
+    <t xml:space="preserve">0.960487425327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816041469574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8630051612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473690986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994539260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375771999359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560868740082</t>
   </si>
   <si>
     <t xml:space="preserve">0.871606469154358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866588950157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466734409332</t>
+    <t xml:space="preserve">0.898844182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86658900976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466555595398</t>
   </si>
   <si>
     <t xml:space="preserve">0.820715010166168</t>
@@ -113,106 +113,106 @@
     <t xml:space="preserve">0.807812869548798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.74545282125473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713197767734528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704238057136536</t>
+    <t xml:space="preserve">0.745452880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713197827339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117308139801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
     <t xml:space="preserve">0.723949491977692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774124145507812</t>
+    <t xml:space="preserve">0.774124264717102</t>
   </si>
   <si>
     <t xml:space="preserve">0.788459837436676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800645172595978</t>
+    <t xml:space="preserve">0.800645112991333</t>
   </si>
   <si>
     <t xml:space="preserve">0.80279541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298799037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802307128906</t>
+    <t xml:space="preserve">0.824298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802247524261</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804945766925812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050702095032</t>
+    <t xml:space="preserve">0.804945707321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050582885742</t>
   </si>
   <si>
     <t xml:space="preserve">0.834333896636963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838634610176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658787727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88020783662796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351236820221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819885730743</t>
+    <t xml:space="preserve">0.838634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658847332001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351296424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819826126099</t>
   </si>
   <si>
     <t xml:space="preserve">0.873040080070496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877340614795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809144496918</t>
+    <t xml:space="preserve">0.87734067440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809323310852</t>
   </si>
   <si>
     <t xml:space="preserve">0.892393112182617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895977139472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225415229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85297030210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924642086029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830749988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704328536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120539665222</t>
+    <t xml:space="preserve">0.895977020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852970242500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305815219879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88092452287674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86013787984848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704388141632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120420455933</t>
   </si>
   <si>
     <t xml:space="preserve">0.851536512374878</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">0.859421193599701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840784907341003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449155807495</t>
+    <t xml:space="preserve">0.840784788131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
     <t xml:space="preserve">0.79921156167984</t>
@@ -233,85 +233,85 @@
     <t xml:space="preserve">0.789893329143524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.813547074794769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858469963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781292021274567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875929355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246480464935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817130982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917745113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431756019592</t>
+    <t xml:space="preserve">0.813547134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858529567719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292080879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875988960266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246420860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131102085114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431875228882</t>
   </si>
   <si>
     <t xml:space="preserve">0.814980745315552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812113583087921</t>
+    <t xml:space="preserve">0.812113642692566</t>
   </si>
   <si>
     <t xml:space="preserve">0.811396777629852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799928426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194102287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512156009674</t>
+    <t xml:space="preserve">0.799928486347198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026345729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512275218964</t>
   </si>
   <si>
     <t xml:space="preserve">0.815697610378265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756921470165253</t>
+    <t xml:space="preserve">0.756921410560608</t>
   </si>
   <si>
     <t xml:space="preserve">0.759788513183594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762655735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204664707184</t>
+    <t xml:space="preserve">0.76265561580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204605102539</t>
   </si>
   <si>
     <t xml:space="preserve">0.750470459461212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779141664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372540473938</t>
+    <t xml:space="preserve">0.77914172410965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372480869293</t>
   </si>
   <si>
     <t xml:space="preserve">0.767673134803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780575156211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775557696819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627653598785</t>
+    <t xml:space="preserve">0.780575215816498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77555775642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627593994141</t>
   </si>
   <si>
     <t xml:space="preserve">0.784159064292908</t>
@@ -320,55 +320,55 @@
     <t xml:space="preserve">0.842218399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851380586624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937241077423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029982566833</t>
+    <t xml:space="preserve">0.851380467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872164011001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937300682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029863357544</t>
   </si>
   <si>
     <t xml:space="preserve">0.861772298812866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576502323151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864741384983063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834066867828</t>
+    <t xml:space="preserve">0.853607296943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864741325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834126472473</t>
   </si>
   <si>
     <t xml:space="preserve">0.837277472019196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825401186943054</t>
+    <t xml:space="preserve">0.825401127338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.829112529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830597043037415</t>
+    <t xml:space="preserve">0.830597102642059</t>
   </si>
   <si>
     <t xml:space="preserve">0.858803153038025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839504301548004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844700217247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843957781791687</t>
+    <t xml:space="preserve">0.839504182338715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844700157642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843957841396332</t>
   </si>
   <si>
     <t xml:space="preserve">0.846184611320496</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">0.83579295873642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833566129207611</t>
+    <t xml:space="preserve">0.833566069602966</t>
   </si>
   <si>
     <t xml:space="preserve">0.838761925697327</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">0.816493988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916614055634</t>
+    <t xml:space="preserve">0.809813439846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916554450989</t>
   </si>
   <si>
     <t xml:space="preserve">0.810555756092072</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">0.801648676395416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817978501319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720698356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819462954998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143443584442</t>
+    <t xml:space="preserve">0.81797844171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819463014602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143503189087</t>
   </si>
   <si>
     <t xml:space="preserve">0.81278270483017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808329105377197</t>
+    <t xml:space="preserve">0.808329045772552</t>
   </si>
   <si>
     <t xml:space="preserve">0.803133130073547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805359959602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796452701091766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906360149384</t>
+    <t xml:space="preserve">0.805360019207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796452641487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906300544739</t>
   </si>
   <si>
     <t xml:space="preserve">0.790514588356018</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256904602051</t>
+    <t xml:space="preserve">0.791256785392761</t>
   </si>
   <si>
     <t xml:space="preserve">0.807586848735809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617643356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79867959022522</t>
+    <t xml:space="preserve">0.814267098903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617583751678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798679530620575</t>
   </si>
   <si>
     <t xml:space="preserve">0.794225990772247</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788287818431854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771957874298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838019728660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844413280487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927020072937</t>
+    <t xml:space="preserve">0.788287758827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77195793390274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838019609451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844532489777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774927079677582</t>
   </si>
   <si>
     <t xml:space="preserve">0.773442506790161</t>
@@ -485,61 +485,61 @@
     <t xml:space="preserve">0.783834159374237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765277445316315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778638422489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091962337494</t>
+    <t xml:space="preserve">0.765277504920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778638362884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091902732849</t>
   </si>
   <si>
     <t xml:space="preserve">0.787545561790466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786061108112335</t>
+    <t xml:space="preserve">0.78606104850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318672657013</t>
+    <t xml:space="preserve">0.785318732261658</t>
   </si>
   <si>
     <t xml:space="preserve">0.806102156639099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868452548980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411440849304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215703964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865099906921</t>
+    <t xml:space="preserve">0.868452608585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411500453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215644359589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865040302277</t>
   </si>
   <si>
     <t xml:space="preserve">0.845442354679108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849153757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390780925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86251437664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866225957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85509181022644</t>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866225838661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855091750621796</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318580150604</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">0.834308326244354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827627956867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860287725925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349553585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867710292339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880328834056854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648464679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669032096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380374908447</t>
+    <t xml:space="preserve">0.827628016471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349613189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867710471153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880328893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669091701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380315303802</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">0.916700005531311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927091777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915957748889923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504149436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885548114777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668939590454</t>
+    <t xml:space="preserve">0.927091658115387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915957689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504209041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535063266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885667324066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991669058799744</t>
   </si>
   <si>
     <t xml:space="preserve">0.979792773723602</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">1.06960713863373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0748028755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06886470317841</t>
+    <t xml:space="preserve">1.07480275630951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0688648223877</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659676551819</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249382972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02432870864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03175139427185</t>
+    <t xml:space="preserve">1.03249371051788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02432882785797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03175151348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.0146791934967</t>
@@ -641,28 +641,28 @@
     <t xml:space="preserve">1.00206077098846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02284419536591</t>
+    <t xml:space="preserve">1.0228443145752</t>
   </si>
   <si>
     <t xml:space="preserve">1.03026700019836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05921542644501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06812250614166</t>
+    <t xml:space="preserve">1.05921518802643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06812262535095</t>
   </si>
   <si>
     <t xml:space="preserve">1.04585456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06663811206818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449373722076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11191630363464</t>
+    <t xml:space="preserve">1.06663799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449361801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11191642284393</t>
   </si>
   <si>
     <t xml:space="preserve">1.11933898925781</t>
@@ -671,109 +671,109 @@
     <t xml:space="preserve">1.11711227893829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1289883852005</t>
+    <t xml:space="preserve">1.12898850440979</t>
   </si>
   <si>
     <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18762755393982</t>
+    <t xml:space="preserve">1.18762767314911</t>
   </si>
   <si>
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2314213514328</t>
+    <t xml:space="preserve">1.23142123222351</t>
   </si>
   <si>
     <t xml:space="preserve">1.21731817722321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22177195549011</t>
+    <t xml:space="preserve">1.22177159786224</t>
   </si>
   <si>
     <t xml:space="preserve">1.21880280971527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23216366767883</t>
+    <t xml:space="preserve">1.23216354846954</t>
   </si>
   <si>
     <t xml:space="preserve">1.22845220565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2351325750351</t>
+    <t xml:space="preserve">1.23513269424438</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474086284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286451816559</t>
+    <t xml:space="preserve">1.21286463737488</t>
   </si>
   <si>
     <t xml:space="preserve">1.21360695362091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20098829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24700903892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779234409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923574924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443160533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26036977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888526439667</t>
+    <t xml:space="preserve">1.20098841190338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24700880050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26779246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2492356300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443172454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26036989688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888514518738</t>
   </si>
   <si>
     <t xml:space="preserve">1.26927697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639028549194</t>
+    <t xml:space="preserve">1.27521526813507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639040470123</t>
   </si>
   <si>
     <t xml:space="preserve">1.34424602985382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.239586353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20321524143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17426669597626</t>
+    <t xml:space="preserve">1.23958623409271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20321536064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">1.17278218269348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055547237396</t>
+    <t xml:space="preserve">1.1653596162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055535316467</t>
   </si>
   <si>
     <t xml:space="preserve">1.1772358417511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17649376392365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16387510299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16164839267731</t>
+    <t xml:space="preserve">1.17649352550507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16387498378754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16164815425873</t>
   </si>
   <si>
     <t xml:space="preserve">1.15051412582397</t>
@@ -791,49 +791,49 @@
     <t xml:space="preserve">1.18911218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247280597687</t>
+    <t xml:space="preserve">1.20247292518616</t>
   </si>
   <si>
     <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28486442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31307077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018408298492</t>
+    <t xml:space="preserve">1.28486454486847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31307065486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018420219421</t>
   </si>
   <si>
     <t xml:space="preserve">1.32791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35834896564484</t>
+    <t xml:space="preserve">1.35834908485413</t>
   </si>
   <si>
     <t xml:space="preserve">1.34350371360779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33311188220978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057282447815</t>
+    <t xml:space="preserve">1.33311176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057294368744</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32855701446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35816478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512793064117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031161785126</t>
+    <t xml:space="preserve">1.32855689525604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35816466808319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031149864197</t>
   </si>
   <si>
     <t xml:space="preserve">1.3665155172348</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39080929756165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39688265323639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38169920444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3680340051651</t>
+    <t xml:space="preserve">1.39080941677094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39688277244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38169932365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36803412437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.36727488040924</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">1.39156830310822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232742786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258887290955</t>
+    <t xml:space="preserve">1.39232754707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549506664276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258899211884</t>
   </si>
   <si>
     <t xml:space="preserve">1.38701343536377</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120140552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35133218765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3156510591507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33842611312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34298121929169</t>
+    <t xml:space="preserve">1.3612015247345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3513320684433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31565093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33842599391937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3429811000824</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363477230072</t>
+    <t xml:space="preserve">1.29363465309143</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.320965051651</t>
+    <t xml:space="preserve">1.32096517086029</t>
   </si>
   <si>
     <t xml:space="preserve">1.31413233280182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3695524930954</t>
+    <t xml:space="preserve">1.36955237388611</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37562584877014</t>
+    <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143764019012</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37866234779358</t>
+    <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
     <t xml:space="preserve">1.38473570346832</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">1.34829545021057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42497229576111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4523024559021</t>
+    <t xml:space="preserve">1.42497217655182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45230257511139</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164890289307</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51835060119629</t>
+    <t xml:space="preserve">1.51835072040558</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568099975586</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">1.51379573345184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52594256401062</t>
+    <t xml:space="preserve">1.52594244480133</t>
   </si>
   <si>
     <t xml:space="preserve">1.51075887680054</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">1.50316727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53049743175507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53353416919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746093273163</t>
+    <t xml:space="preserve">1.53049731254578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53353428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746105194092</t>
   </si>
   <si>
     <t xml:space="preserve">1.51607310771942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47887349128723</t>
+    <t xml:space="preserve">1.47887337207794</t>
   </si>
   <si>
     <t xml:space="preserve">1.43484151363373</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">1.40599286556244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38777256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33614861965179</t>
+    <t xml:space="preserve">1.38777244091034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3361485004425</t>
   </si>
   <si>
     <t xml:space="preserve">1.29059815406799</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">1.29970824718475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30502247810364</t>
+    <t xml:space="preserve">1.30502235889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052264213562</t>
+    <t xml:space="preserve">1.47052276134491</t>
   </si>
   <si>
     <t xml:space="preserve">1.47659611701965</t>
@@ -1025,28 +1025,28 @@
     <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48722434043884</t>
+    <t xml:space="preserve">1.48722457885742</t>
   </si>
   <si>
     <t xml:space="preserve">1.42269456386566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41434371471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41738033294678</t>
+    <t xml:space="preserve">1.41434383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41738021373749</t>
   </si>
   <si>
     <t xml:space="preserve">1.40447437763214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39308667182922</t>
+    <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
     <t xml:space="preserve">1.40371513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37182986736298</t>
+    <t xml:space="preserve">1.37182974815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.36271977424622</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">1.42724967002869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48039186000824</t>
+    <t xml:space="preserve">1.48039197921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.4993714094162</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49177956581116</t>
+    <t xml:space="preserve">1.49177968502045</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761656761169</t>
+    <t xml:space="preserve">1.45761668682098</t>
   </si>
   <si>
     <t xml:space="preserve">1.4386373758316</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30957758426666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33994460105896</t>
+    <t xml:space="preserve">1.30957746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
     <t xml:space="preserve">1.32476091384888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34753620624542</t>
+    <t xml:space="preserve">1.34753632545471</t>
   </si>
   <si>
     <t xml:space="preserve">1.31337332725525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27161860466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716918945312</t>
+    <t xml:space="preserve">1.27161848545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716930866241</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">1.44243323802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45382082462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46900427341461</t>
+    <t xml:space="preserve">1.4538209438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46900415420532</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418784141541</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">1.42345380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41586208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002484321594</t>
+    <t xml:space="preserve">1.41586196422577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002496242523</t>
   </si>
   <si>
     <t xml:space="preserve">1.46141254901886</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">1.54112601280212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47280025482178</t>
+    <t xml:space="preserve">1.47280013561249</t>
   </si>
   <si>
     <t xml:space="preserve">1.5145548582077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51551640033722</t>
+    <t xml:space="preserve">1.51551628112793</t>
   </si>
   <si>
     <t xml:space="preserve">1.50768411159515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52726447582245</t>
+    <t xml:space="preserve">1.52726459503174</t>
   </si>
   <si>
     <t xml:space="preserve">1.51943242549896</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">1.46852362155914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48027181625366</t>
+    <t xml:space="preserve">1.48027193546295</t>
   </si>
   <si>
     <t xml:space="preserve">1.46069145202637</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46460747718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677530765533</t>
+    <t xml:space="preserve">1.4646075963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677542686462</t>
   </si>
   <si>
     <t xml:space="preserve">1.47243976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47635567188263</t>
+    <t xml:space="preserve">1.47635555267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.44111108779907</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40978264808655</t>
+    <t xml:space="preserve">1.40978252887726</t>
   </si>
   <si>
     <t xml:space="preserve">1.42153072357178</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">1.42936301231384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43327915668488</t>
+    <t xml:space="preserve">1.4332789182663</t>
   </si>
   <si>
     <t xml:space="preserve">1.45285928249359</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">1.39803445339203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39411842823029</t>
+    <t xml:space="preserve">1.394118309021</t>
   </si>
   <si>
     <t xml:space="preserve">1.34712564945221</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">1.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488816738129</t>
+    <t xml:space="preserve">1.26488828659058</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">1.30796504020691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404877662659</t>
+    <t xml:space="preserve">1.30404889583588</t>
   </si>
   <si>
     <t xml:space="preserve">1.33146142959595</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">1.28055262565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29621684551239</t>
+    <t xml:space="preserve">1.2962167263031</t>
   </si>
   <si>
     <t xml:space="preserve">1.31188094615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34320962429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35104179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3862863779068</t>
+    <t xml:space="preserve">1.34320950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35104167461395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38628625869751</t>
   </si>
   <si>
     <t xml:space="preserve">1.4058666229248</t>
@@ -1280,34 +1280,34 @@
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845396995544</t>
+    <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
     <t xml:space="preserve">1.32754528522491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28838455677032</t>
+    <t xml:space="preserve">1.28838467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30013287067413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33537745475769</t>
+    <t xml:space="preserve">1.30013298988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537757396698</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28446865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3157970905304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31971323490143</t>
+    <t xml:space="preserve">1.28446853160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31579720973969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761457920074</t>
+    <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
     <t xml:space="preserve">1.48810386657715</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">1.49985206127167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51160025596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53509676456451</t>
+    <t xml:space="preserve">1.5116001367569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334845066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55076086521149</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992159366608</t>
+    <t xml:space="preserve">1.58992147445679</t>
   </si>
   <si>
     <t xml:space="preserve">1.6212500333786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60558569431305</t>
+    <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
     <t xml:space="preserve">1.61341786384583</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">1.64474642276764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63691425323486</t>
+    <t xml:space="preserve">1.63691437244415</t>
   </si>
   <si>
     <t xml:space="preserve">1.65257847309113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66041052341461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66824293136597</t>
+    <t xml:space="preserve">1.6604106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66824281215668</t>
   </si>
   <si>
     <t xml:space="preserve">1.70740354061127</t>
@@ -1385,25 +1385,25 @@
     <t xml:space="preserve">1.74656403064728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76222825050354</t>
+    <t xml:space="preserve">1.76222836971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.80138885974884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006018161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77789258956909</t>
+    <t xml:space="preserve">1.84838140010834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006030082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7778924703598</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488536834717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80922091007233</t>
+    <t xml:space="preserve">1.80922102928162</t>
   </si>
   <si>
     <t xml:space="preserve">1.83271729946136</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">1.84054958820343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87971019744873</t>
+    <t xml:space="preserve">1.87971007823944</t>
   </si>
   <si>
     <t xml:space="preserve">1.87187802791595</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">1.86404609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85621392726898</t>
+    <t xml:space="preserve">1.85621380805969</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94236743450165</t>
+    <t xml:space="preserve">1.94236719608307</t>
   </si>
   <si>
     <t xml:space="preserve">1.95803141593933</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">1.97369563579559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99719202518463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96586346626282</t>
+    <t xml:space="preserve">1.99719190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96586358547211</t>
   </si>
   <si>
     <t xml:space="preserve">1.93453502655029</t>
@@ -1451,31 +1451,31 @@
     <t xml:space="preserve">1.92670285701752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98178458213806</t>
+    <t xml:space="preserve">1.98178446292877</t>
   </si>
   <si>
     <t xml:space="preserve">1.94942879676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96560668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662875652313</t>
+    <t xml:space="preserve">1.9656069278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662863731384</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338410377502</t>
+    <t xml:space="preserve">1.76338398456573</t>
   </si>
   <si>
     <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78765058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573953151703</t>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573941230774</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">1.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236203670502</t>
+    <t xml:space="preserve">1.82809507846832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236191749573</t>
   </si>
   <si>
     <t xml:space="preserve">1.89280641078949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90089535713196</t>
+    <t xml:space="preserve">1.90089547634125</t>
   </si>
   <si>
     <t xml:space="preserve">1.8847177028656</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">1.90898418426514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9413400888443</t>
+    <t xml:space="preserve">1.94133996963501</t>
   </si>
   <si>
     <t xml:space="preserve">1.93325114250183</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">1.98987352848053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95751798152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.997962474823</t>
+    <t xml:space="preserve">1.95751810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">1.7472060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75529491901398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631674766541</t>
+    <t xml:space="preserve">1.75529503822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631686687469</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">1.49644958972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747141838074</t>
+    <t xml:space="preserve">1.40747153759003</t>
   </si>
   <si>
     <t xml:space="preserve">1.4155604839325</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">1.17289304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19715976715088</t>
+    <t xml:space="preserve">1.19715964794159</t>
   </si>
   <si>
     <t xml:space="preserve">1.22951531410217</t>
@@ -1598,22 +1598,22 @@
     <t xml:space="preserve">1.03538143634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178151607513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15671515464783</t>
+    <t xml:space="preserve">1.07178139686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15671503543854</t>
   </si>
   <si>
     <t xml:space="preserve">1.1405371427536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693734169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09604823589325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502616882324</t>
+    <t xml:space="preserve">1.17693746089935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09604835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
     <t xml:space="preserve">1.18907082080841</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">1.16075944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24569320678711</t>
+    <t xml:space="preserve">1.24569308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30231559276581</t>
+    <t xml:space="preserve">1.3023157119751</t>
   </si>
   <si>
     <t xml:space="preserve">1.26995992660522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25378203392029</t>
+    <t xml:space="preserve">1.253781914711</t>
   </si>
   <si>
     <t xml:space="preserve">1.20524871349335</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
+    <t xml:space="preserve">1.18098199367523</t>
   </si>
   <si>
     <t xml:space="preserve">1.21333742141724</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862608909607</t>
+    <t xml:space="preserve">1.14862620830536</t>
   </si>
   <si>
     <t xml:space="preserve">1.10009264945984</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840390205383</t>
+    <t xml:space="preserve">1.12840378284454</t>
   </si>
   <si>
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22142624855042</t>
+    <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
     <t xml:space="preserve">1.11222612857819</t>
@@ -1703,16 +1703,16 @@
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0596479177475</t>
+    <t xml:space="preserve">1.07582592964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05964803695679</t>
   </si>
   <si>
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08391487598419</t>
+    <t xml:space="preserve">1.0839147567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.0798704624176</t>
@@ -1721,25 +1721,25 @@
     <t xml:space="preserve">1.0556036233902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05155909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02324783802032</t>
+    <t xml:space="preserve">1.05155920982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324795722961</t>
   </si>
   <si>
     <t xml:space="preserve">1.0272923707962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00302577018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982803344726562</t>
+    <t xml:space="preserve">1.00302565097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
     <t xml:space="preserve">0.954492092132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97067004442215</t>
+    <t xml:space="preserve">0.970669984817505</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">0.966625571250916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978758990764618</t>
+    <t xml:space="preserve">0.978759050369263</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10413706302643</t>
+    <t xml:space="preserve">1.10413718223572</t>
   </si>
   <si>
     <t xml:space="preserve">1.23355984687805</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120418071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29422664642334</t>
+    <t xml:space="preserve">1.20120406150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29422676563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.31040441989899</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">1.32658231258392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680449962616</t>
+    <t xml:space="preserve">1.34680461883545</t>
   </si>
   <si>
     <t xml:space="preserve">1.33467125892639</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">1.51262748241425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55307197570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57733869552612</t>
+    <t xml:space="preserve">1.55307185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57733881473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498302936554</t>
+    <t xml:space="preserve">1.54498314857483</t>
   </si>
   <si>
     <t xml:space="preserve">1.52071642875671</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284966945648</t>
+    <t xml:space="preserve">1.53284978866577</t>
   </si>
   <si>
     <t xml:space="preserve">1.51667189598083</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947217464447</t>
+    <t xml:space="preserve">1.58947229385376</t>
   </si>
   <si>
     <t xml:space="preserve">1.57329440116882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56520545482635</t>
+    <t xml:space="preserve">1.56520533561707</t>
   </si>
   <si>
     <t xml:space="preserve">1.48836064338684</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">1.52880537509918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676136016846</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249475955963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67440581321716</t>
+    <t xml:space="preserve">1.68249464035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67440569400787</t>
   </si>
   <si>
     <t xml:space="preserve">1.72293937206268</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">1.71485030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55711650848389</t>
+    <t xml:space="preserve">1.5571163892746</t>
   </si>
   <si>
     <t xml:space="preserve">1.48431622982025</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">1.49240517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47218286991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351670742035</t>
+    <t xml:space="preserve">1.47218298912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351658821106</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37107145786285</t>
+    <t xml:space="preserve">1.37107133865356</t>
   </si>
   <si>
     <t xml:space="preserve">1.33062672615051</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">1.44791603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46409380435944</t>
+    <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">1.59756112098694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.609694480896</t>
+    <t xml:space="preserve">1.60969436168671</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
@@ -68300,7 +68300,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6919907407</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>21855</v>
@@ -68321,6 +68321,32 @@
         <v>861</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6913078704</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>22306</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>858</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504944324493</t>
+    <t xml:space="preserve">0.965504825115204</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994893014431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980557322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978406965732574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169312000275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053933620453</t>
+    <t xml:space="preserve">0.994892954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980557262897491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978406846523285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95116925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959054052829742</t>
   </si>
   <si>
     <t xml:space="preserve">0.966938436031342</t>
@@ -65,43 +65,43 @@
     <t xml:space="preserve">0.960487484931946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944718301296234</t>
+    <t xml:space="preserve">0.9447181224823</t>
   </si>
   <si>
     <t xml:space="preserve">0.931816101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863005101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473631381989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386274814606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994479656219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057599067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88737553358078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428090572357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560868740082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606409549713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866589069366455</t>
+    <t xml:space="preserve">0.8630051612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994598865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560987949371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606469154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86658900976181</t>
   </si>
   <si>
     <t xml:space="preserve">0.831466734409332</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">0.820714950561523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812988758087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74545282125473</t>
+    <t xml:space="preserve">0.807812869548798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74545294046402</t>
   </si>
   <si>
     <t xml:space="preserve">0.713197708129883</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.723949491977692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459897041321</t>
+    <t xml:space="preserve">0.723949432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124264717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459837436676</t>
   </si>
   <si>
     <t xml:space="preserve">0.800645112991333</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">0.80279541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298918247223</t>
+    <t xml:space="preserve">0.824298799037933</t>
   </si>
   <si>
     <t xml:space="preserve">0.845802307128906</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">0.834333956241608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838634490966797</t>
+    <t xml:space="preserve">0.838634371757507</t>
   </si>
   <si>
     <t xml:space="preserve">0.886658847332001</t>
@@ -167,103 +167,103 @@
     <t xml:space="preserve">0.880207896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83935135602951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819766521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87304013967514</t>
+    <t xml:space="preserve">0.839351177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819885730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040080070496</t>
   </si>
   <si>
     <t xml:space="preserve">0.877340614795685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888809323310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393290996552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977079868317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225474834442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852970123291016</t>
+    <t xml:space="preserve">0.888809144496918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393171787262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977139472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225355625153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85297030210495</t>
   </si>
   <si>
     <t xml:space="preserve">0.870889723300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867305815219879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924582481384</t>
+    <t xml:space="preserve">0.867305874824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924701690674</t>
   </si>
   <si>
     <t xml:space="preserve">0.86013799905777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830750048160553</t>
+    <t xml:space="preserve">0.830749928951263</t>
   </si>
   <si>
     <t xml:space="preserve">0.858704328536987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855120420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536512374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82644921541214</t>
+    <t xml:space="preserve">0.855120480060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536571979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421193599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784907341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
     <t xml:space="preserve">0.79921156167984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789893329143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547074794769</t>
+    <t xml:space="preserve">0.789893448352814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547253608704</t>
   </si>
   <si>
     <t xml:space="preserve">0.779858469963074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781292080879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875929355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246480464935</t>
+    <t xml:space="preserve">0.781291902065277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246361255646</t>
   </si>
   <si>
     <t xml:space="preserve">0.817131102085114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837917685508728</t>
+    <t xml:space="preserve">0.837917745113373</t>
   </si>
   <si>
     <t xml:space="preserve">0.821431815624237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814980745315552</t>
+    <t xml:space="preserve">0.814980626106262</t>
   </si>
   <si>
     <t xml:space="preserve">0.812113523483276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811396896839142</t>
+    <t xml:space="preserve">0.811396777629852</t>
   </si>
   <si>
     <t xml:space="preserve">0.799928307533264</t>
@@ -284,127 +284,124 @@
     <t xml:space="preserve">0.756921410560608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759788572788239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204664707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470459461212</t>
+    <t xml:space="preserve">0.759788513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655675411224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470399856567</t>
   </si>
   <si>
     <t xml:space="preserve">0.779141664505005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763372540473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673194408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575096607208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77555775642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627653598785</t>
+    <t xml:space="preserve">0.763372480869293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673134803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575156211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557696819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79562771320343</t>
   </si>
   <si>
     <t xml:space="preserve">0.784159064292908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.842218458652496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
+    <t xml:space="preserve">0.842218339443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380407810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872163832187653</t>
   </si>
   <si>
     <t xml:space="preserve">0.869937241077423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861030042171478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772239208221</t>
+    <t xml:space="preserve">0.861029922962189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772298812866</t>
   </si>
   <si>
     <t xml:space="preserve">0.853607356548309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856576442718506</t>
+    <t xml:space="preserve">0.856576383113861</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741265773773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855834007263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83727753162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401067733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112529754639</t>
+    <t xml:space="preserve">0.855834066867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401127338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112470149994</t>
   </si>
   <si>
     <t xml:space="preserve">0.830597043037415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85880321264267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504301548004</t>
+    <t xml:space="preserve">0.858803153038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504241943359</t>
   </si>
   <si>
     <t xml:space="preserve">0.84470009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843957901000977</t>
+    <t xml:space="preserve">0.843957781791687</t>
   </si>
   <si>
     <t xml:space="preserve">0.846184611320496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835792899131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833566069602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838761925697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816494047641754</t>
+    <t xml:space="preserve">0.835793018341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833566129207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761985301971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816493988037109</t>
   </si>
   <si>
     <t xml:space="preserve">0.809813499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823916673660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810555815696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81797844171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720698356628</t>
+    <t xml:space="preserve">0.823916614055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810555875301361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801648676395416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817978382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720757961273</t>
   </si>
   <si>
     <t xml:space="preserve">0.819463074207306</t>
@@ -413,46 +410,46 @@
     <t xml:space="preserve">0.826143443584442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81278270483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808328866958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133130073547</t>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808328986167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133249282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.805360019207001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796452701091766</t>
+    <t xml:space="preserve">0.796452760696411</t>
   </si>
   <si>
     <t xml:space="preserve">0.800906240940094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790514707565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999161243439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791256844997406</t>
+    <t xml:space="preserve">0.790514647960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791256785392761</t>
   </si>
   <si>
     <t xml:space="preserve">0.807586789131165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267158508301</t>
+    <t xml:space="preserve">0.814267039299011</t>
   </si>
   <si>
     <t xml:space="preserve">0.804617583751678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225990772247</t>
+    <t xml:space="preserve">0.79867947101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225871562958</t>
   </si>
   <si>
     <t xml:space="preserve">0.786803245544434</t>
@@ -461,16 +458,16 @@
     <t xml:space="preserve">0.779380559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777896046638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788287758827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771957814693451</t>
+    <t xml:space="preserve">0.77715390920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777895987033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788287818431854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
     <t xml:space="preserve">0.838019669055939</t>
@@ -479,16 +476,16 @@
     <t xml:space="preserve">0.806844472885132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774927020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442566394806</t>
+    <t xml:space="preserve">0.774926960468292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442506790161</t>
   </si>
   <si>
     <t xml:space="preserve">0.783834218978882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765277504920959</t>
+    <t xml:space="preserve">0.765277564525604</t>
   </si>
   <si>
     <t xml:space="preserve">0.778638303279877</t>
@@ -503,19 +500,19 @@
     <t xml:space="preserve">0.786060988903046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77418464422226</t>
+    <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102156639099</t>
+    <t xml:space="preserve">0.806102216243744</t>
   </si>
   <si>
     <t xml:space="preserve">0.868452608585358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841731011867523</t>
+    <t xml:space="preserve">0.841730952262878</t>
   </si>
   <si>
     <t xml:space="preserve">0.848411440849304</t>
@@ -524,52 +521,52 @@
     <t xml:space="preserve">0.843215644359589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852865040302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442473888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153816699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390721321106</t>
+    <t xml:space="preserve">0.852865099906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153637886047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390780925751</t>
   </si>
   <si>
     <t xml:space="preserve">0.862514495849609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866226017475128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855091750621796</t>
+    <t xml:space="preserve">0.866225898265839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85509181022644</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823872566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834308326244354</t>
+    <t xml:space="preserve">0.832823812961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834308266639709</t>
   </si>
   <si>
     <t xml:space="preserve">0.827627956867218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86028778553009</t>
+    <t xml:space="preserve">0.860287725925446</t>
   </si>
   <si>
     <t xml:space="preserve">0.854349553585052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86771035194397</t>
+    <t xml:space="preserve">0.867710411548615</t>
   </si>
   <si>
     <t xml:space="preserve">0.880328893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873648703098297</t>
+    <t xml:space="preserve">0.873648643493652</t>
   </si>
   <si>
     <t xml:space="preserve">0.919669151306152</t>
@@ -581,55 +578,55 @@
     <t xml:space="preserve">0.913730919361115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916700184345245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545257568359</t>
+    <t xml:space="preserve">0.916700124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091717720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545317173004</t>
   </si>
   <si>
     <t xml:space="preserve">0.915957748889923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911504209041595</t>
+    <t xml:space="preserve">0.911504089832306</t>
   </si>
   <si>
     <t xml:space="preserve">0.908535003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898885667324066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792892932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768980503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06960701942444</t>
+    <t xml:space="preserve">0.898885548114777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991668879985809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792773723602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768944740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06960713863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.07480299472809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0688648223877</t>
+    <t xml:space="preserve">1.06886470317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659676551819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05327713489532</t>
+    <t xml:space="preserve">1.05327725410461</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179262161255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249382972717</t>
+    <t xml:space="preserve">1.03249371051788</t>
   </si>
   <si>
     <t xml:space="preserve">1.02432882785797</t>
@@ -638,22 +635,22 @@
     <t xml:space="preserve">1.03175139427185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467931270599</t>
+    <t xml:space="preserve">1.01467943191528</t>
   </si>
   <si>
     <t xml:space="preserve">1.00206077098846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02284443378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03026700019836</t>
+    <t xml:space="preserve">1.02284419536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03026688098907</t>
   </si>
   <si>
     <t xml:space="preserve">1.05921530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06812262535095</t>
+    <t xml:space="preserve">1.06812250614166</t>
   </si>
   <si>
     <t xml:space="preserve">1.04585444927216</t>
@@ -665,19 +662,19 @@
     <t xml:space="preserve">1.10449361801147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11191642284393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11711227893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1289883852005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160704612732</t>
+    <t xml:space="preserve">1.11191630363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1193391084671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12898850440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
@@ -686,49 +683,49 @@
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23142123222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21731817722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177183628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880269050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23216354846954</t>
+    <t xml:space="preserve">1.23142147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2173182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177195549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880257129669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23216342926025</t>
   </si>
   <si>
     <t xml:space="preserve">1.22845220565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23513269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22474086284637</t>
+    <t xml:space="preserve">1.23513281345367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22474098205566</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286463737488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21360683441162</t>
+    <t xml:space="preserve">1.21360695362091</t>
   </si>
   <si>
     <t xml:space="preserve">1.20098841190338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700891971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779234409332</t>
+    <t xml:space="preserve">1.24700880050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26779246330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.24923574924469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25443184375763</t>
+    <t xml:space="preserve">1.25443160533905</t>
   </si>
   <si>
     <t xml:space="preserve">1.26036977767944</t>
@@ -746,43 +743,43 @@
     <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34424602985382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.239586353302</t>
+    <t xml:space="preserve">1.34424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321524143219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17426693439484</t>
+    <t xml:space="preserve">1.17426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">1.17278218269348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055559158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1772358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16387510299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16164839267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15051412582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15348339080811</t>
+    <t xml:space="preserve">1.1653596162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055547237396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17723572254181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649352550507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16387498378754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16164827346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15051436424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15348315238953</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824618816376</t>
@@ -791,7 +788,7 @@
     <t xml:space="preserve">1.14383387565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1891120672226</t>
+    <t xml:space="preserve">1.18911218643188</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
@@ -803,7 +800,7 @@
     <t xml:space="preserve">1.28486454486847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31307077407837</t>
+    <t xml:space="preserve">1.31307065486908</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
@@ -812,31 +809,31 @@
     <t xml:space="preserve">1.32791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35834920406342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34350371360779</t>
+    <t xml:space="preserve">1.35834908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3435035943985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057294368744</t>
+    <t xml:space="preserve">1.35057282447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32855701446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35816478729248</t>
+    <t xml:space="preserve">1.32855689525604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35816466808319</t>
   </si>
   <si>
     <t xml:space="preserve">1.35512804985046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37031161785126</t>
+    <t xml:space="preserve">1.37031149864197</t>
   </si>
   <si>
     <t xml:space="preserve">1.36651563644409</t>
@@ -848,34 +845,34 @@
     <t xml:space="preserve">1.39080917835236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39688277244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38169920444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3680340051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36727476119995</t>
+    <t xml:space="preserve">1.39688265323639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3816990852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36803412437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36727464199066</t>
   </si>
   <si>
     <t xml:space="preserve">1.3915684223175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549518585205</t>
+    <t xml:space="preserve">1.39232766628265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549506664276</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38701319694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36879312992096</t>
+    <t xml:space="preserve">1.38701331615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36879324913025</t>
   </si>
   <si>
     <t xml:space="preserve">1.36120128631592</t>
@@ -890,19 +887,19 @@
     <t xml:space="preserve">1.33842623233795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3429811000824</t>
+    <t xml:space="preserve">1.34298121929169</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363489151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818999767303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30122637748718</t>
+    <t xml:space="preserve">1.29363477230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818987846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.32096517086029</t>
@@ -914,10 +911,10 @@
     <t xml:space="preserve">1.36955225467682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536428451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37562584877014</t>
+    <t xml:space="preserve">1.39536440372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143775939941</t>
@@ -932,49 +929,49 @@
     <t xml:space="preserve">1.38929092884064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38321769237518</t>
+    <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
     <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473570346832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34829533100128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42497205734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4523024559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50164890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4773553609848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630934238434</t>
+    <t xml:space="preserve">1.38473582267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34829545021057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42497217655182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45230233669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50164878368378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735512256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.51835060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54568111896515</t>
+    <t xml:space="preserve">1.54568099975586</t>
   </si>
   <si>
     <t xml:space="preserve">1.51379561424255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52594232559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51075875759125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52897918224335</t>
+    <t xml:space="preserve">1.52594256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51075899600983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52897894382477</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316715240479</t>
@@ -989,13 +986,13 @@
     <t xml:space="preserve">1.52746081352234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51607322692871</t>
+    <t xml:space="preserve">1.51607298851013</t>
   </si>
   <si>
     <t xml:space="preserve">1.47887361049652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43484139442444</t>
+    <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
     <t xml:space="preserve">1.40599274635315</t>
@@ -1004,25 +1001,25 @@
     <t xml:space="preserve">1.38777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33614873886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29059827327728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29970812797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30502223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42573130130768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052264213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659599781036</t>
+    <t xml:space="preserve">1.33614861965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29059815406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29970824718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30502247810364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42573118209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052276134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659611701965</t>
   </si>
   <si>
     <t xml:space="preserve">1.48798370361328</t>
@@ -1031,49 +1028,49 @@
     <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269444465637</t>
+    <t xml:space="preserve">1.42269468307495</t>
   </si>
   <si>
     <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41738045215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40447449684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3930869102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40371513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182986736298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36271989345551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423814296722</t>
+    <t xml:space="preserve">1.41738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40447425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39308679103851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40371525287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36271977424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423826217651</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36499726772308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36575639247894</t>
+    <t xml:space="preserve">1.36499714851379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36575651168823</t>
   </si>
   <si>
     <t xml:space="preserve">1.37107074260712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42724967002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039186000824</t>
+    <t xml:space="preserve">1.42724978923798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039197921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.49937129020691</t>
@@ -1082,49 +1079,49 @@
     <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49177944660187</t>
+    <t xml:space="preserve">1.49177968502045</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761668682098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43863725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37790334224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33235287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30957746505737</t>
+    <t xml:space="preserve">1.45761656761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43863713741302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37790310382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30957734584808</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476115226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753632545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161860466003</t>
+    <t xml:space="preserve">1.32476103305817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753620624542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337332725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161872386932</t>
   </si>
   <si>
     <t xml:space="preserve">1.31716930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40827023983002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.40827035903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41206634044647</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
@@ -1136,46 +1133,49 @@
     <t xml:space="preserve">1.45382082462311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46900427341461</t>
+    <t xml:space="preserve">1.46900415420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48418784141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520841121674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002484321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46141254901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54112589359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47280013561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51455473899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46520841121674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42345380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002484321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46141254901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54112589359283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47280025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51455473899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51551628112793</t>
+    <t xml:space="preserve">1.51551616191864</t>
   </si>
   <si>
     <t xml:space="preserve">1.50768423080444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52726447582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943242549896</t>
+    <t xml:space="preserve">1.52726459503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943230628967</t>
   </si>
   <si>
     <t xml:space="preserve">1.50376808643341</t>
@@ -1190,22 +1190,22 @@
     <t xml:space="preserve">1.48027181625366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46069145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44894325733185</t>
+    <t xml:space="preserve">1.46069157123566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44894313812256</t>
   </si>
   <si>
     <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677542686462</t>
+    <t xml:space="preserve">1.45677554607391</t>
   </si>
   <si>
     <t xml:space="preserve">1.47243976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47635579109192</t>
+    <t xml:space="preserve">1.47635591030121</t>
   </si>
   <si>
     <t xml:space="preserve">1.44111120700836</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">1.42544686794281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278986930847</t>
+    <t xml:space="preserve">1.36278998851776</t>
   </si>
   <si>
     <t xml:space="preserve">1.40978264808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42153084278107</t>
+    <t xml:space="preserve">1.42153072357178</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936301231384</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">1.43327903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45285928249359</t>
+    <t xml:space="preserve">1.45285940170288</t>
   </si>
   <si>
     <t xml:space="preserve">1.39803445339203</t>
@@ -1241,37 +1241,37 @@
     <t xml:space="preserve">1.34712564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33929359912872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30796504020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146154880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055250644684</t>
+    <t xml:space="preserve">1.32362926006317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488840579987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33929347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30796492099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30404877662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146142959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055262565613</t>
   </si>
   <si>
     <t xml:space="preserve">1.29621684551239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188094615936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34320974349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35104167461395</t>
+    <t xml:space="preserve">1.31188106536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34320962429047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35104155540466</t>
   </si>
   <si>
     <t xml:space="preserve">1.38628625869751</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37845420837402</t>
+    <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
     <t xml:space="preserve">1.3275454044342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28838455677032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195059776306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30013287067413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33537757396698</t>
+    <t xml:space="preserve">1.28838467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195047855377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30013275146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28446853160858</t>
+    <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
     <t xml:space="preserve">1.3157970905304</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37453806400299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38237011432648</t>
+    <t xml:space="preserve">1.3745379447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
     <t xml:space="preserve">1.41761457920074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810374736786</t>
+    <t xml:space="preserve">1.48810386657715</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593591690063</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">1.51160025596619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52334845066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53509676456451</t>
+    <t xml:space="preserve">1.52334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55076086521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59775352478027</t>
+    <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
     <t xml:space="preserve">1.58992147445679</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">1.62124991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60558569431305</t>
+    <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
     <t xml:space="preserve">1.61341786384583</t>
@@ -1373,46 +1373,46 @@
     <t xml:space="preserve">1.65257859230042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66041076183319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66824293136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740354061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439596176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74656391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222813129425</t>
+    <t xml:space="preserve">1.6604106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66824305057526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439608097076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74656403064728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222825050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.80138897895813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838175773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006018161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7778924703598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82488524913788</t>
+    <t xml:space="preserve">1.84838163852692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006042003632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77789258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82488512992859</t>
   </si>
   <si>
     <t xml:space="preserve">1.80922102928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83271741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054946899414</t>
+    <t xml:space="preserve">1.83271718025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054934978485</t>
   </si>
   <si>
     <t xml:space="preserve">1.87971019744873</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">1.87187814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86404597759247</t>
+    <t xml:space="preserve">1.86404609680176</t>
   </si>
   <si>
     <t xml:space="preserve">1.8562136888504</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94236731529236</t>
+    <t xml:space="preserve">1.94236719608307</t>
   </si>
   <si>
     <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369575500488</t>
+    <t xml:space="preserve">1.9736955165863</t>
   </si>
   <si>
     <t xml:space="preserve">1.99719214439392</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">1.93453514575958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91887104511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670297622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942903518677</t>
+    <t xml:space="preserve">1.91887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9267030954361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178470134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9494286775589</t>
   </si>
   <si>
     <t xml:space="preserve">1.9656069278717</t>
@@ -1466,46 +1466,46 @@
     <t xml:space="preserve">1.97369587421417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87662863731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77956187725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76338398456573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191718578339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765070438385</t>
+    <t xml:space="preserve">1.87662851810455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77956175804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765082359314</t>
   </si>
   <si>
     <t xml:space="preserve">1.79573965072632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80382823944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82000613212585</t>
+    <t xml:space="preserve">1.8038284778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82000625133514</t>
   </si>
   <si>
     <t xml:space="preserve">1.8604508638382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82809495925903</t>
+    <t xml:space="preserve">1.82809519767761</t>
   </si>
   <si>
     <t xml:space="preserve">1.85236191749573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89280652999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90089535713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88471758365631</t>
+    <t xml:space="preserve">1.8928062915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90089523792267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88471746444702</t>
   </si>
   <si>
     <t xml:space="preserve">1.84427297115326</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">1.86853969097137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83618402481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7714729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90898442268372</t>
+    <t xml:space="preserve">1.83618414402008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77147281169891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90898430347443</t>
   </si>
   <si>
     <t xml:space="preserve">1.9413400888443</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987352848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751798152924</t>
+    <t xml:space="preserve">1.98987364768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751786231995</t>
   </si>
   <si>
     <t xml:space="preserve">1.997962474823</t>
@@ -1541,37 +1541,37 @@
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516219615936</t>
+    <t xml:space="preserve">1.92516231536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.7472060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75529491901398</t>
+    <t xml:space="preserve">1.75529503822327</t>
   </si>
   <si>
     <t xml:space="preserve">1.66631674766541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56924986839294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58542776107788</t>
+    <t xml:space="preserve">1.56924974918365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58542764186859</t>
   </si>
   <si>
     <t xml:space="preserve">1.56116092205048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49644958972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747153759003</t>
+    <t xml:space="preserve">1.49644947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747165679932</t>
   </si>
   <si>
     <t xml:space="preserve">1.4155604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34276020526886</t>
+    <t xml:space="preserve">1.34276008605957</t>
   </si>
   <si>
     <t xml:space="preserve">1.31849336624146</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">1.29827117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17289304733276</t>
+    <t xml:space="preserve">1.17289292812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.19715964794159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22951531410217</t>
+    <t xml:space="preserve">1.22951543331146</t>
   </si>
   <si>
     <t xml:space="preserve">1.15267062187195</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">1.01515901088715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1648041009903</t>
+    <t xml:space="preserve">1.16480398178101</t>
   </si>
   <si>
     <t xml:space="preserve">1.03538131713867</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">1.15671515464783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1405371427536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693734169006</t>
+    <t xml:space="preserve">1.14053726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693746089935</t>
   </si>
   <si>
     <t xml:space="preserve">1.09604823589325</t>
@@ -1625,43 +1625,43 @@
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364928483963</t>
+    <t xml:space="preserve">1.13649272918701</t>
   </si>
   <si>
     <t xml:space="preserve">1.16075944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24569320678711</t>
+    <t xml:space="preserve">1.24569308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30231559276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995992660522</t>
+    <t xml:space="preserve">1.3023157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995980739594</t>
   </si>
   <si>
     <t xml:space="preserve">1.25378203392029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20524859428406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.193115234375</t>
+    <t xml:space="preserve">1.20524871349335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19311535358429</t>
   </si>
   <si>
     <t xml:space="preserve">1.18098187446594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21333742141724</t>
+    <t xml:space="preserve">1.21333754062653</t>
   </si>
   <si>
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031507492065</t>
+    <t xml:space="preserve">1.12031495571136</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">1.14862608909607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10009276866913</t>
+    <t xml:space="preserve">1.10009264945984</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16884851455688</t>
+    <t xml:space="preserve">1.1688483953476</t>
   </si>
   <si>
     <t xml:space="preserve">1.20929312705994</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">1.24973750114441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2214263677597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1122260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10818159580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07582604885101</t>
+    <t xml:space="preserve">1.22142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11222612857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1081817150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07582592964172</t>
   </si>
   <si>
     <t xml:space="preserve">1.05964803695679</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08391499519348</t>
+    <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
     <t xml:space="preserve">1.0798704624176</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">1.02324795722961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02729249000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00302577018738</t>
+    <t xml:space="preserve">1.0272923707962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00302565097809</t>
   </si>
   <si>
     <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492211341858</t>
+    <t xml:space="preserve">0.954492151737213</t>
   </si>
   <si>
     <t xml:space="preserve">0.97067004442215</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">0.986847937107086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962581098079681</t>
+    <t xml:space="preserve">0.962581157684326</t>
   </si>
   <si>
     <t xml:space="preserve">0.966625571250916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978758990764618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01920354366302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10413706302643</t>
+    <t xml:space="preserve">0.978758931159973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01920342445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10413718223572</t>
   </si>
   <si>
     <t xml:space="preserve">1.23355972766876</t>
@@ -1775,31 +1775,31 @@
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120418071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29422664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31040441989899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32253777980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32658231258392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34680461883545</t>
+    <t xml:space="preserve">1.20120406150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29422676563263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31040453910828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32253789901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32658243179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34680449962616</t>
   </si>
   <si>
     <t xml:space="preserve">1.33467125892639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724935054779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4681384563446</t>
+    <t xml:space="preserve">1.3872492313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46813833713531</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">1.55307197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57733869552612</t>
+    <t xml:space="preserve">1.57733881473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">1.52071642875671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50453853607178</t>
+    <t xml:space="preserve">1.50453865528107</t>
   </si>
   <si>
     <t xml:space="preserve">1.53284966945648</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">1.51667189598083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689408302307</t>
+    <t xml:space="preserve">1.53689420223236</t>
   </si>
   <si>
     <t xml:space="preserve">1.581383228302</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">1.58947217464447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57329428195953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56520533561707</t>
+    <t xml:space="preserve">1.57329440116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56520521640778</t>
   </si>
   <si>
     <t xml:space="preserve">1.48836076259613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5004940032959</t>
+    <t xml:space="preserve">1.50049412250519</t>
   </si>
   <si>
     <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247608423233</t>
+    <t xml:space="preserve">1.52476096153259</t>
   </si>
   <si>
     <t xml:space="preserve">1.52880525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676147937775</t>
@@ -1877,61 +1877,61 @@
     <t xml:space="preserve">1.67440569400787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72293937206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6137387752533</t>
+    <t xml:space="preserve">1.72293949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61373889446259</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65013885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60564994812012</t>
+    <t xml:space="preserve">1.65013897418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60565006732941</t>
   </si>
   <si>
     <t xml:space="preserve">1.64205002784729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62587225437164</t>
+    <t xml:space="preserve">1.62587237358093</t>
   </si>
   <si>
     <t xml:space="preserve">1.61778330802917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71485042572021</t>
+    <t xml:space="preserve">1.71485030651093</t>
   </si>
   <si>
     <t xml:space="preserve">1.55711650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48431634902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49240517616272</t>
+    <t xml:space="preserve">1.48431622982025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49240505695343</t>
   </si>
   <si>
     <t xml:space="preserve">1.47218286991119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59351670742035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50858294963837</t>
+    <t xml:space="preserve">1.59351658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50858306884766</t>
   </si>
   <si>
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33062672615051</t>
+    <t xml:space="preserve">1.3306268453598</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893797874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44791615009308</t>
+    <t xml:space="preserve">1.44791603088379</t>
   </si>
   <si>
     <t xml:space="preserve">1.46409380435944</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59756112098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60969436168671</t>
+    <t xml:space="preserve">1.59756100177765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.609694480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7097635269165</t>
+    <t xml:space="preserve">1.70976340770721</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68028485774994</t>
+    <t xml:space="preserve">1.68028473854065</t>
   </si>
   <si>
     <t xml:space="preserve">1.68449604511261</t>
@@ -1979,28 +1979,28 @@
     <t xml:space="preserve">1.64659488201141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343986988068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63817250728607</t>
+    <t xml:space="preserve">1.66343975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63817238807678</t>
   </si>
   <si>
     <t xml:space="preserve">1.62974989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66765105724335</t>
+    <t xml:space="preserve">1.66765117645264</t>
   </si>
   <si>
     <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61711609363556</t>
+    <t xml:space="preserve">1.61711621284485</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54973638057709</t>
+    <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
     <t xml:space="preserve">1.58342635631561</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">1.57500386238098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55394768714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59606003761292</t>
+    <t xml:space="preserve">1.55394756793976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59605991840363</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54552507400513</t>
+    <t xml:space="preserve">1.54552519321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815887451172</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289151191711</t>
+    <t xml:space="preserve">1.53289139270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">1.47393405437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43182170391083</t>
+    <t xml:space="preserve">1.43182158470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38970923423767</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">1.44024407863617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41076529026031</t>
+    <t xml:space="preserve">1.4107654094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
@@ -2069,16 +2069,16 @@
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49077904224396</t>
+    <t xml:space="preserve">1.49499022960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49077892303467</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52446889877319</t>
+    <t xml:space="preserve">1.5244687795639</t>
   </si>
   <si>
     <t xml:space="preserve">1.54131388664246</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868008613586</t>
+    <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553858757019</t>
+    <t xml:space="preserve">1.62553870677948</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2114,34 +2114,34 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501749515533</t>
+    <t xml:space="preserve">1.65501737594604</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186236381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61290502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184885025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51604640483856</t>
+    <t xml:space="preserve">1.67186224460602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61290490627289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184873104095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51604628562927</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761039733887</t>
+    <t xml:space="preserve">1.42761051654816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48235642910004</t>
+    <t xml:space="preserve">1.48235654830933</t>
   </si>
   <si>
     <t xml:space="preserve">1.45708906650543</t>
@@ -2153,49 +2153,49 @@
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763742446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65922856330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79398834705353</t>
+    <t xml:space="preserve">1.58763754367828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65922868251801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79398846626282</t>
   </si>
   <si>
     <t xml:space="preserve">1.84452319145203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83931910991669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584770679474</t>
+    <t xml:space="preserve">1.8393189907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584758758545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510474205017</t>
+    <t xml:space="preserve">1.79510462284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9277480840683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700488090515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237654209137</t>
+    <t xml:space="preserve">1.92774796485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237642288208</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365907907486</t>
+    <t xml:space="preserve">1.91006219387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93659090995789</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154824256897</t>
+    <t xml:space="preserve">2.05154800415039</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923389434814</t>
+    <t xml:space="preserve">2.0869197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923413276672</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039118766785</t>
+    <t xml:space="preserve">2.06039094924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353359699249</t>
+    <t xml:space="preserve">1.88353371620178</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427656173706</t>
+    <t xml:space="preserve">1.95427668094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163333892822</t>
+    <t xml:space="preserve">1.82163321971893</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783294200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130446434021</t>
+    <t xml:space="preserve">1.69783306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130434513092</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2297,22 +2297,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940432548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6270899772644</t>
+    <t xml:space="preserve">1.60940420627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62709009647369</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171843528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6049827337265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824715137482</t>
+    <t xml:space="preserve">1.59171831607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60498285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824703216553</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72436165809631</t>
+    <t xml:space="preserve">1.73762595653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7243617773056</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -7250,7 +7250,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7276,7 +7276,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7302,7 +7302,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7328,7 +7328,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7354,7 +7354,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7380,7 +7380,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7406,7 +7406,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7432,7 +7432,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7458,7 +7458,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7484,7 +7484,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7510,7 +7510,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7536,7 +7536,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7562,7 +7562,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7588,7 +7588,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7614,7 +7614,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7640,7 +7640,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7666,7 +7666,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7692,7 +7692,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7744,7 +7744,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7770,7 +7770,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7796,7 +7796,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7822,7 +7822,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7848,7 +7848,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7874,7 +7874,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7900,7 +7900,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7926,7 +7926,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7952,7 +7952,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7978,7 +7978,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -8004,7 +8004,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8030,7 +8030,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8056,7 +8056,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8082,7 +8082,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8108,7 +8108,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8134,7 +8134,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8160,7 +8160,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8186,7 +8186,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8212,7 +8212,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8238,7 +8238,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8264,7 +8264,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8290,7 +8290,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8316,7 +8316,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8342,7 +8342,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8368,7 +8368,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8394,7 +8394,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8420,7 +8420,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8446,7 +8446,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8472,7 +8472,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8498,7 +8498,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8524,7 +8524,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8550,7 +8550,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8576,7 +8576,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8602,7 +8602,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8628,7 +8628,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8654,7 +8654,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8680,7 +8680,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8706,7 +8706,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8732,7 +8732,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8758,7 +8758,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8784,7 +8784,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8810,7 +8810,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8836,7 +8836,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8862,7 +8862,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8888,7 +8888,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8914,7 +8914,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8940,7 +8940,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8966,7 +8966,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8992,7 +8992,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9018,7 +9018,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9044,7 +9044,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9070,7 +9070,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9096,7 +9096,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9122,7 +9122,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9148,7 +9148,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9174,7 +9174,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9200,7 +9200,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9226,7 +9226,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9252,7 +9252,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9278,7 +9278,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9304,7 +9304,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9330,7 +9330,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9356,7 +9356,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9382,7 +9382,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9408,7 +9408,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9434,7 +9434,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9486,7 +9486,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9512,7 +9512,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9538,7 +9538,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9564,7 +9564,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9590,7 +9590,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9616,7 +9616,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9642,7 +9642,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9668,7 +9668,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9694,7 +9694,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9720,7 +9720,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9746,7 +9746,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9772,7 +9772,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9824,7 +9824,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9850,7 +9850,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9876,7 +9876,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9902,7 +9902,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9928,7 +9928,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9954,7 +9954,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9980,7 +9980,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10058,7 +10058,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10084,7 +10084,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10110,7 +10110,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10136,7 +10136,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10162,7 +10162,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10188,7 +10188,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10214,7 +10214,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10240,7 +10240,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10266,7 +10266,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10292,7 +10292,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10318,7 +10318,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10370,7 +10370,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10396,7 +10396,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10422,7 +10422,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10448,7 +10448,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10474,7 +10474,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10500,7 +10500,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10630,7 +10630,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10656,7 +10656,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10682,7 +10682,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10708,7 +10708,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10734,7 +10734,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10760,7 +10760,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10786,7 +10786,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10812,7 +10812,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10838,7 +10838,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10864,7 +10864,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10890,7 +10890,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10916,7 +10916,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10942,7 +10942,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10968,7 +10968,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10994,7 +10994,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11020,7 +11020,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11046,7 +11046,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11072,7 +11072,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11098,7 +11098,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11124,7 +11124,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11150,7 +11150,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11176,7 +11176,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11202,7 +11202,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11228,7 +11228,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11254,7 +11254,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11280,7 +11280,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11306,7 +11306,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11332,7 +11332,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11358,7 +11358,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11410,7 +11410,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11436,7 +11436,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11462,7 +11462,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11488,7 +11488,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11514,7 +11514,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11540,7 +11540,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11566,7 +11566,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11592,7 +11592,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11618,7 +11618,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11644,7 +11644,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11670,7 +11670,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11696,7 +11696,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11722,7 +11722,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11748,7 +11748,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11774,7 +11774,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11800,7 +11800,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11826,7 +11826,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11852,7 +11852,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11878,7 +11878,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11904,7 +11904,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11930,7 +11930,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11956,7 +11956,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11982,7 +11982,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12008,7 +12008,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12034,7 +12034,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12060,7 +12060,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12086,7 +12086,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12112,7 +12112,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12138,7 +12138,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12164,7 +12164,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12190,7 +12190,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12216,7 +12216,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12242,7 +12242,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12268,7 +12268,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12294,7 +12294,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12320,7 +12320,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12346,7 +12346,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12372,7 +12372,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12398,7 +12398,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12424,7 +12424,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12450,7 +12450,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12476,7 +12476,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12502,7 +12502,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12528,7 +12528,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12554,7 +12554,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12580,7 +12580,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12606,7 +12606,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12632,7 +12632,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12658,7 +12658,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12684,7 +12684,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12710,7 +12710,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12736,7 +12736,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12762,7 +12762,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12788,7 +12788,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12814,7 +12814,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12840,7 +12840,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12866,7 +12866,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12892,7 +12892,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12918,7 +12918,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12944,7 +12944,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12970,7 +12970,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12996,7 +12996,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13022,7 +13022,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13048,7 +13048,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13074,7 +13074,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13100,7 +13100,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13126,7 +13126,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13152,7 +13152,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13178,7 +13178,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13204,7 +13204,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13230,7 +13230,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13256,7 +13256,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13282,7 +13282,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13308,7 +13308,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13334,7 +13334,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13360,7 +13360,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13386,7 +13386,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13412,7 +13412,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13438,7 +13438,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13464,7 +13464,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13490,7 +13490,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13516,7 +13516,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13542,7 +13542,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13568,7 +13568,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13594,7 +13594,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13620,7 +13620,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13646,7 +13646,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13672,7 +13672,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13698,7 +13698,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13724,7 +13724,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13750,7 +13750,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13776,7 +13776,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13802,7 +13802,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13828,7 +13828,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13854,7 +13854,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13880,7 +13880,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13906,7 +13906,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13932,7 +13932,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13958,7 +13958,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13984,7 +13984,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14010,7 +14010,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14036,7 +14036,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14062,7 +14062,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14088,7 +14088,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14114,7 +14114,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14140,7 +14140,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14166,7 +14166,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14192,7 +14192,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14218,7 +14218,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14244,7 +14244,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14270,7 +14270,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14296,7 +14296,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14322,7 +14322,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14348,7 +14348,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14374,7 +14374,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14400,7 +14400,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14426,7 +14426,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14452,7 +14452,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14478,7 +14478,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14504,7 +14504,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14530,7 +14530,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14556,7 +14556,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14582,7 +14582,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14608,7 +14608,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14634,7 +14634,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14660,7 +14660,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14686,7 +14686,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14712,7 +14712,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14738,7 +14738,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14764,7 +14764,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14790,7 +14790,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14816,7 +14816,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14842,7 +14842,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14868,7 +14868,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14894,7 +14894,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14920,7 +14920,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14946,7 +14946,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14972,7 +14972,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14998,7 +14998,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15024,7 +15024,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15050,7 +15050,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15076,7 +15076,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15102,7 +15102,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15128,7 +15128,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15154,7 +15154,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15180,7 +15180,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15206,7 +15206,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15232,7 +15232,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15258,7 +15258,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15284,7 +15284,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15310,7 +15310,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15336,7 +15336,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15362,7 +15362,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15388,7 +15388,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15414,7 +15414,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15440,7 +15440,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15466,7 +15466,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15492,7 +15492,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15518,7 +15518,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15544,7 +15544,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15570,7 +15570,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15596,7 +15596,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15622,7 +15622,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15648,7 +15648,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15674,7 +15674,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15700,7 +15700,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15726,7 +15726,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15752,7 +15752,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15778,7 +15778,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15804,7 +15804,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15830,7 +15830,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15856,7 +15856,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15882,7 +15882,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15908,7 +15908,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15934,7 +15934,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15960,7 +15960,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15986,7 +15986,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16012,7 +16012,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16038,7 +16038,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16064,7 +16064,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16090,7 +16090,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16116,7 +16116,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16142,7 +16142,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16168,7 +16168,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16194,7 +16194,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16220,7 +16220,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16246,7 +16246,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16272,7 +16272,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16298,7 +16298,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16324,7 +16324,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16350,7 +16350,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16376,7 +16376,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16402,7 +16402,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16428,7 +16428,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16454,7 +16454,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16480,7 +16480,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16506,7 +16506,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16532,7 +16532,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16558,7 +16558,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16584,7 +16584,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16610,7 +16610,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16636,7 +16636,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16662,7 +16662,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16688,7 +16688,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16714,7 +16714,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16740,7 +16740,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16766,7 +16766,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16792,7 +16792,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16818,7 +16818,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16844,7 +16844,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16870,7 +16870,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16896,7 +16896,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16922,7 +16922,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16948,7 +16948,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16974,7 +16974,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17000,7 +17000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17026,7 +17026,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17052,7 +17052,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17078,7 +17078,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17104,7 +17104,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17130,7 +17130,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17156,7 +17156,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17182,7 +17182,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17208,7 +17208,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17234,7 +17234,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17260,7 +17260,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17286,7 +17286,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17312,7 +17312,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17338,7 +17338,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17364,7 +17364,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17390,7 +17390,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17416,7 +17416,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17442,7 +17442,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17468,7 +17468,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17494,7 +17494,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17520,7 +17520,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17546,7 +17546,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17572,7 +17572,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17598,7 +17598,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17624,7 +17624,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17650,7 +17650,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17676,7 +17676,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17702,7 +17702,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17728,7 +17728,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17754,7 +17754,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17780,7 +17780,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17806,7 +17806,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17832,7 +17832,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17858,7 +17858,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17884,7 +17884,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17910,7 +17910,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17936,7 +17936,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17962,7 +17962,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17988,7 +17988,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18014,7 +18014,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18040,7 +18040,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18066,7 +18066,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18092,7 +18092,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18118,7 +18118,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18144,7 +18144,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18170,7 +18170,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18196,7 +18196,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18222,7 +18222,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18248,7 +18248,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18274,7 +18274,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18300,7 +18300,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18326,7 +18326,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18352,7 +18352,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18378,7 +18378,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18404,7 +18404,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18430,7 +18430,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18456,7 +18456,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18482,7 +18482,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18508,7 +18508,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18534,7 +18534,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18560,7 +18560,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18586,7 +18586,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18612,7 +18612,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18638,7 +18638,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18664,7 +18664,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18690,7 +18690,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18716,7 +18716,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18742,7 +18742,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18768,7 +18768,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18794,7 +18794,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18820,7 +18820,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18846,7 +18846,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18872,7 +18872,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18898,7 +18898,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18924,7 +18924,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18950,7 +18950,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18976,7 +18976,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19002,7 +19002,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19028,7 +19028,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19054,7 +19054,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19080,7 +19080,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19106,7 +19106,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19132,7 +19132,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19158,7 +19158,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19184,7 +19184,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19210,7 +19210,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19236,7 +19236,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19262,7 +19262,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19288,7 +19288,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19314,7 +19314,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19340,7 +19340,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19366,7 +19366,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19392,7 +19392,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19418,7 +19418,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19444,7 +19444,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19470,7 +19470,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19496,7 +19496,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19522,7 +19522,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19548,7 +19548,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19574,7 +19574,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19600,7 +19600,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19626,7 +19626,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19652,7 +19652,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19678,7 +19678,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19704,7 +19704,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19730,7 +19730,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19756,7 +19756,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19782,7 +19782,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19808,7 +19808,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19834,7 +19834,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19860,7 +19860,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19886,7 +19886,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19912,7 +19912,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19938,7 +19938,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19964,7 +19964,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19990,7 +19990,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20016,7 +20016,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20042,7 +20042,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -68358,7 +68358,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6714699074</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>28182</v>
@@ -68379,6 +68379,32 @@
         <v>858</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6735069444</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>15251</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>843</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -44,70 +44,70 @@
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99489289522171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980557262897491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978407084941864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169312000275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053933620453</t>
+    <t xml:space="preserve">0.994892835617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980557382106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97840690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169431209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053874015808</t>
   </si>
   <si>
     <t xml:space="preserve">0.966938495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960487365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944718062877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005042076111</t>
+    <t xml:space="preserve">0.960487484931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718301296234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816279888153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005101680756</t>
   </si>
   <si>
     <t xml:space="preserve">0.874473571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849386155605316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994539260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057599067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88737565279007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428090572357</t>
+    <t xml:space="preserve">0.849386274814606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994420051575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428150177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.899560928344727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871606409549713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844182491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866588950157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466674804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820714950561523</t>
+    <t xml:space="preserve">0.871606469154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844063282013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86658900976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466734409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
     <t xml:space="preserve">0.807812988758087</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117248535156</t>
+    <t xml:space="preserve">0.713197767734528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117308139801</t>
   </si>
   <si>
     <t xml:space="preserve">0.704237997531891</t>
@@ -134,265 +134,268 @@
     <t xml:space="preserve">0.788459897041321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800645172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802795469760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298799037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802366733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827882766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804945826530457</t>
+    <t xml:space="preserve">0.800645053386688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298918247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802247524261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827882826328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804945886135101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050523281097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333956241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634431362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88665896654129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351296424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819885730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87304013967514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340614795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809263706207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393290996552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225415229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852970123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889782905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305874824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880924642086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860138058662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704388141632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120480060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536452770233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421193599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784847736359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82644921541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799211502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893329143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781291961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875929355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246480464935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131042480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917864322662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431815624237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980685710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113702297211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396777629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928307533264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194042682648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512215614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921410560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655675411224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470459461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77914172410965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372540473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673194408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575215816498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557696819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159123897552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380407810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872163951396942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029922962189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85360723733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864741265773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834066867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277472019196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401127338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.835050642490387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333956241608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634431362152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658847332001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88020795583725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351236820221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819766521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87304013967514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809144496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977139472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85297018289566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924642086029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830750048160553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704447746277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120539665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536512374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421372413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449275016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79921156167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893329143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547194004059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858529567719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781292021274567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875988960266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246480464935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131161689758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431815624237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113523483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928367137909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194161891937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026166915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512215614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921470165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788453578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655675411224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204545497894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470459461212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77914172410965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372480869293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673254013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775557816028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159123897552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218458652496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872164011001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937300682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029922962189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772239208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576502323151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864741325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834126472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401186943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112589359283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830597043037415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85880309343338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504241943359</t>
+    <t xml:space="preserve">0.829112470149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83059698343277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858803033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
     <t xml:space="preserve">0.84470009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843957841396332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846184730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83579295873642</t>
+    <t xml:space="preserve">0.843957781791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846184611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835792899131775</t>
   </si>
   <si>
     <t xml:space="preserve">0.833566129207611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838761985301971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816494047641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809813499450684</t>
+    <t xml:space="preserve">0.838761866092682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816493988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809813559055328</t>
   </si>
   <si>
     <t xml:space="preserve">0.823916614055634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810555815696716</t>
+    <t xml:space="preserve">0.810555875301361</t>
   </si>
   <si>
     <t xml:space="preserve">0.801648616790771</t>
@@ -401,31 +404,31 @@
     <t xml:space="preserve">0.81797844171524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818720817565918</t>
+    <t xml:space="preserve">0.818720757961273</t>
   </si>
   <si>
     <t xml:space="preserve">0.819462954998016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278270483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808329045772552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133189678192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805359899997711</t>
+    <t xml:space="preserve">0.826143383979797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808329105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133130073547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805359959602356</t>
   </si>
   <si>
     <t xml:space="preserve">0.796452701091766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800906419754028</t>
+    <t xml:space="preserve">0.800906300544739</t>
   </si>
   <si>
     <t xml:space="preserve">0.790514647960663</t>
@@ -434,19 +437,19 @@
     <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256904602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586848735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814267098903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617702960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798679649829865</t>
+    <t xml:space="preserve">0.791256844997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80758672952652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814267158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617643356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798679530620575</t>
   </si>
   <si>
     <t xml:space="preserve">0.794225931167603</t>
@@ -455,22 +458,22 @@
     <t xml:space="preserve">0.786803185939789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779380559921265</t>
+    <t xml:space="preserve">0.77938050031662</t>
   </si>
   <si>
     <t xml:space="preserve">0.777153849601746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777896046638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788287818431854</t>
+    <t xml:space="preserve">0.777895987033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788287878036499</t>
   </si>
   <si>
     <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838019728660583</t>
+    <t xml:space="preserve">0.838019669055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.806844532489777</t>
@@ -485,85 +488,85 @@
     <t xml:space="preserve">0.783834218978882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765277564525604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778638362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091843128204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545561790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786060988903046</t>
+    <t xml:space="preserve">0.765277445316315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778638422489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091902732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545502185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78606104850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318553447723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806102156639099</t>
+    <t xml:space="preserve">0.785318672657013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806102216243744</t>
   </si>
   <si>
     <t xml:space="preserve">0.868452548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841730892658234</t>
+    <t xml:space="preserve">0.841731011867523</t>
   </si>
   <si>
     <t xml:space="preserve">0.848411440849304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843215525150299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865040302277</t>
+    <t xml:space="preserve">0.843215644359589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865159511566</t>
   </si>
   <si>
     <t xml:space="preserve">0.845442414283752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849153697490692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390840530396</t>
+    <t xml:space="preserve">0.849153757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87439090013504</t>
   </si>
   <si>
     <t xml:space="preserve">0.862514436244965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866225957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855091869831085</t>
+    <t xml:space="preserve">0.866225898265839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855091750621796</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823753356934</t>
+    <t xml:space="preserve">0.832823812961578</t>
   </si>
   <si>
     <t xml:space="preserve">0.834308385848999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827627956867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860287845134735</t>
+    <t xml:space="preserve">0.827628016471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86028778553009</t>
   </si>
   <si>
     <t xml:space="preserve">0.854349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86771035194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880328893661499</t>
+    <t xml:space="preserve">0.867710471153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880329012870789</t>
   </si>
   <si>
     <t xml:space="preserve">0.873648583889008</t>
@@ -575,34 +578,34 @@
     <t xml:space="preserve">0.923380434513092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913730919361115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916700005531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545317173004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915957868099213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91150426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885548114777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668820381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792654514313</t>
+    <t xml:space="preserve">0.913730978965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916700065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545436382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915957748889923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504149436951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792892932892</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768968582153</t>
@@ -614,10 +617,10 @@
     <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06886494159698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04659676551819</t>
+    <t xml:space="preserve">1.0688648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0465966463089</t>
   </si>
   <si>
     <t xml:space="preserve">1.05327713489532</t>
@@ -626,7 +629,7 @@
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249382972717</t>
+    <t xml:space="preserve">1.03249359130859</t>
   </si>
   <si>
     <t xml:space="preserve">1.02432882785797</t>
@@ -635,94 +638,94 @@
     <t xml:space="preserve">1.03175139427185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0146791934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00206089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02284419536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03026688098907</t>
+    <t xml:space="preserve">1.01467931270599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00206065177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0228443145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03026700019836</t>
   </si>
   <si>
     <t xml:space="preserve">1.05921530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06812262535095</t>
+    <t xml:space="preserve">1.06812250614166</t>
   </si>
   <si>
     <t xml:space="preserve">1.04585456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06663811206818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449373722076</t>
+    <t xml:space="preserve">1.06663823127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449361801147</t>
   </si>
   <si>
     <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.117112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12898850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160704612732</t>
+    <t xml:space="preserve">1.11933887004852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11711227893829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1289883852005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160680770874</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21509158611298</t>
+    <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
     <t xml:space="preserve">1.2314213514328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21731817722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177195549011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880292892456</t>
+    <t xml:space="preserve">1.2173182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2217720746994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880269050598</t>
   </si>
   <si>
     <t xml:space="preserve">1.23216366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22845220565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23513269424438</t>
+    <t xml:space="preserve">1.22845232486725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23513281345367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474086284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286463737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21360695362091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20098841190338</t>
+    <t xml:space="preserve">1.21286451816559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21360683441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20098829269409</t>
   </si>
   <si>
     <t xml:space="preserve">1.24700891971588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26779222488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2492356300354</t>
+    <t xml:space="preserve">1.26779246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923586845398</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
@@ -731,10 +734,10 @@
     <t xml:space="preserve">1.26036965847015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25888538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26927697658539</t>
+    <t xml:space="preserve">1.25888526439667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26927709579468</t>
   </si>
   <si>
     <t xml:space="preserve">1.27521514892578</t>
@@ -743,34 +746,34 @@
     <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34424602985382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23958623409271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20321524143219</t>
+    <t xml:space="preserve">1.34424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.239586353302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2032151222229</t>
   </si>
   <si>
     <t xml:space="preserve">1.17426669597626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17278206348419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055523395538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17723572254181</t>
+    <t xml:space="preserve">1.17278218269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16535973548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055535316467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1772358417511</t>
   </si>
   <si>
     <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16387510299683</t>
+    <t xml:space="preserve">1.16387498378754</t>
   </si>
   <si>
     <t xml:space="preserve">1.16164827346802</t>
@@ -779,16 +782,16 @@
     <t xml:space="preserve">1.15051412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15348327159882</t>
+    <t xml:space="preserve">1.15348315238953</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824630737305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14383387565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1891120672226</t>
+    <t xml:space="preserve">1.14383375644684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18911218643188</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
@@ -797,7 +800,7 @@
     <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28486454486847</t>
+    <t xml:space="preserve">1.28486442565918</t>
   </si>
   <si>
     <t xml:space="preserve">1.31307077407837</t>
@@ -812,79 +815,79 @@
     <t xml:space="preserve">1.35834896564484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34350347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33311200141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057294368744</t>
+    <t xml:space="preserve">1.3435035943985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33311188220978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057282447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32855689525604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35816466808319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031149864197</t>
+    <t xml:space="preserve">1.32855701446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35816478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512793064117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031161785126</t>
   </si>
   <si>
     <t xml:space="preserve">1.36651563644409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37410724163055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39080917835236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39688277244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38169932365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3680340051651</t>
+    <t xml:space="preserve">1.37410736083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39080929756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39688265323639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3816990852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36803388595581</t>
   </si>
   <si>
     <t xml:space="preserve">1.36727488040924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3915684223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39232766628265</t>
+    <t xml:space="preserve">1.39156830310822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39232742786407</t>
   </si>
   <si>
     <t xml:space="preserve">1.38549494743347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701331615448</t>
+    <t xml:space="preserve">1.37258899211884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701343536377</t>
   </si>
   <si>
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120140552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3513320684433</t>
+    <t xml:space="preserve">1.36120128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35133218765259</t>
   </si>
   <si>
     <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842599391937</t>
+    <t xml:space="preserve">1.33842623233795</t>
   </si>
   <si>
     <t xml:space="preserve">1.34298121929169</t>
@@ -896,10 +899,10 @@
     <t xml:space="preserve">1.29363477230072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29818987846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30122637748718</t>
+    <t xml:space="preserve">1.29818999767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.320965051651</t>
@@ -914,13 +917,13 @@
     <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37562572956085</t>
+    <t xml:space="preserve">1.37562584877014</t>
   </si>
   <si>
     <t xml:space="preserve">1.40143764019012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38625407218933</t>
+    <t xml:space="preserve">1.38625419139862</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397669792175</t>
@@ -929,13 +932,13 @@
     <t xml:space="preserve">1.38929092884064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3832174539566</t>
+    <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
     <t xml:space="preserve">1.37866234779358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473582267761</t>
+    <t xml:space="preserve">1.38473570346832</t>
   </si>
   <si>
     <t xml:space="preserve">1.34829545021057</t>
@@ -950,19 +953,19 @@
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630958080292</t>
+    <t xml:space="preserve">1.47735524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.51835060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54568111896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379561424255</t>
+    <t xml:space="preserve">1.54568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379573345184</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594244480133</t>
@@ -974,7 +977,7 @@
     <t xml:space="preserve">1.52897906303406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50316715240479</t>
+    <t xml:space="preserve">1.50316727161407</t>
   </si>
   <si>
     <t xml:space="preserve">1.53049755096436</t>
@@ -989,10 +992,10 @@
     <t xml:space="preserve">1.51607310771942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47887372970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43484139442444</t>
+    <t xml:space="preserve">1.47887349128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
     <t xml:space="preserve">1.40599286556244</t>
@@ -1001,7 +1004,7 @@
     <t xml:space="preserve">1.38777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3361485004425</t>
+    <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
     <t xml:space="preserve">1.2905980348587</t>
@@ -1016,34 +1019,34 @@
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052264213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48798370361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48722445964813</t>
+    <t xml:space="preserve">1.47052252292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659599781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48798358440399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48722434043884</t>
   </si>
   <si>
     <t xml:space="preserve">1.42269444465637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41434359550476</t>
+    <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738045215607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40447449684143</t>
+    <t xml:space="preserve">1.40447437763214</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371513366699</t>
+    <t xml:space="preserve">1.40371525287628</t>
   </si>
   <si>
     <t xml:space="preserve">1.37182986736298</t>
@@ -1055,16 +1058,16 @@
     <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35209131240845</t>
+    <t xml:space="preserve">1.35209143161774</t>
   </si>
   <si>
     <t xml:space="preserve">1.36499726772308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36575639247894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37107074260712</t>
+    <t xml:space="preserve">1.36575651168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
     <t xml:space="preserve">1.4272495508194</t>
@@ -1076,10 +1079,10 @@
     <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49557542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49177968502045</t>
+    <t xml:space="preserve">1.49557554721832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49177956581116</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
@@ -1088,13 +1091,13 @@
     <t xml:space="preserve">1.45761656761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43863725662231</t>
+    <t xml:space="preserve">1.4386373758316</t>
   </si>
   <si>
     <t xml:space="preserve">1.37790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33235263824463</t>
+    <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
     <t xml:space="preserve">1.30957758426666</t>
@@ -1112,16 +1115,16 @@
     <t xml:space="preserve">1.31337332725525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27161860466003</t>
+    <t xml:space="preserve">1.27161872386932</t>
   </si>
   <si>
     <t xml:space="preserve">1.31716930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40827035903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.40827023983002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
@@ -1136,10 +1139,10 @@
     <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418796062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46520829200745</t>
+    <t xml:space="preserve">1.48418784141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
     <t xml:space="preserve">1.42345380783081</t>
@@ -1160,10 +1163,7 @@
     <t xml:space="preserve">1.47280025482178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51455497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418784141541</t>
+    <t xml:space="preserve">1.51455473899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.51551628112793</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">1.51943242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50376808643341</t>
+    <t xml:space="preserve">1.5037682056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48027181625366</t>
+    <t xml:space="preserve">1.46852362155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48027169704437</t>
   </si>
   <si>
     <t xml:space="preserve">1.46069145202637</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4646075963974</t>
+    <t xml:space="preserve">1.46460747718811</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677530765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47243964672089</t>
+    <t xml:space="preserve">1.47243976593018</t>
   </si>
   <si>
     <t xml:space="preserve">1.47635567188263</t>
@@ -1217,34 +1217,34 @@
     <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40978264808655</t>
+    <t xml:space="preserve">1.40978252887726</t>
   </si>
   <si>
     <t xml:space="preserve">1.42153084278107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936289310455</t>
+    <t xml:space="preserve">1.42936301231384</t>
   </si>
   <si>
     <t xml:space="preserve">1.43327903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45285940170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39803457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.394118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3471257686615</t>
+    <t xml:space="preserve">1.45285928249359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39803445339203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39411842823029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34712564945221</t>
   </si>
   <si>
     <t xml:space="preserve">1.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">1.30796504020691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404877662659</t>
+    <t xml:space="preserve">1.30404889583588</t>
   </si>
   <si>
     <t xml:space="preserve">1.33146142959595</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">1.28055262565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29621684551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31188094615936</t>
+    <t xml:space="preserve">1.2962167263031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31188106536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.34320962429047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35104167461395</t>
+    <t xml:space="preserve">1.35104179382324</t>
   </si>
   <si>
     <t xml:space="preserve">1.38628625869751</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">1.37845396995544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32754528522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838467597961</t>
+    <t xml:space="preserve">1.3275454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838455677032</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230082035065</t>
+    <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28446865081787</t>
@@ -1322,61 +1322,61 @@
     <t xml:space="preserve">1.41761457920074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810398578644</t>
+    <t xml:space="preserve">1.48810386657715</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49985206127167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5116001367569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334856987</t>
+    <t xml:space="preserve">1.49985194206238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51160037517548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334845066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509676456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55076086521149</t>
+    <t xml:space="preserve">1.55076098442078</t>
   </si>
   <si>
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992159366608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62124991416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60558581352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61341786384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208930492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62908220291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64474642276764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63691413402557</t>
+    <t xml:space="preserve">1.58992147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6212500333786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60558569431305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61341774463654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5820894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62908208370209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64474630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
     <t xml:space="preserve">1.65257835388184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6604106426239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66824293136597</t>
+    <t xml:space="preserve">1.66041052341461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66824305057526</t>
   </si>
   <si>
     <t xml:space="preserve">1.70740354061127</t>
@@ -1391,64 +1391,64 @@
     <t xml:space="preserve">1.76222825050354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80138874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838140010834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006042003632</t>
+    <t xml:space="preserve">1.80138885974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838175773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006018161774</t>
   </si>
   <si>
     <t xml:space="preserve">1.77789258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82488524913788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922114849091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271718025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054970741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187838554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404597759247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85621380805969</t>
+    <t xml:space="preserve">1.82488512992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922091007233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271753787994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054958820343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8562136888504</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94236719608307</t>
+    <t xml:space="preserve">1.94236743450165</t>
   </si>
   <si>
     <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369587421417</t>
+    <t xml:space="preserve">1.97369563579559</t>
   </si>
   <si>
     <t xml:space="preserve">1.99719202518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96586334705353</t>
+    <t xml:space="preserve">1.96586346626282</t>
   </si>
   <si>
     <t xml:space="preserve">1.93453502655029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91887104511261</t>
+    <t xml:space="preserve">1.91887080669403</t>
   </si>
   <si>
     <t xml:space="preserve">1.9267030954361</t>
@@ -1463,85 +1463,85 @@
     <t xml:space="preserve">1.96560668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87662863731384</t>
+    <t xml:space="preserve">1.87662851810455</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338410377502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191718578339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573941230774</t>
+    <t xml:space="preserve">1.76338398456573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573953151703</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8604508638382</t>
+    <t xml:space="preserve">1.82000625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86045074462891</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85236191749573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89280652999878</t>
+    <t xml:space="preserve">1.85236203670502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280664920807</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88471758365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.88471746444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83618414402008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77147281169891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90898418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9413400888443</t>
+    <t xml:space="preserve">1.83618402481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7714729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90898442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94134032726288</t>
   </si>
   <si>
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987352848053</t>
+    <t xml:space="preserve">1.98987376689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.95751798152924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99796223640442</t>
+    <t xml:space="preserve">1.997962474823</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516219615936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74720621109009</t>
+    <t xml:space="preserve">1.92516231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74720597267151</t>
   </si>
   <si>
     <t xml:space="preserve">1.75529491901398</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56116080284119</t>
+    <t xml:space="preserve">1.56116092205048</t>
   </si>
   <si>
     <t xml:space="preserve">1.49644958972931</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">1.29827117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17289304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951519489288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15267050266266</t>
+    <t xml:space="preserve">1.17289292812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715964794159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951531410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15267062187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">1.01515901088715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16480422019958</t>
+    <t xml:space="preserve">1.1648041009903</t>
   </si>
   <si>
     <t xml:space="preserve">1.03538131713867</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18907082080841</t>
+    <t xml:space="preserve">1.18907070159912</t>
   </si>
   <si>
     <t xml:space="preserve">1.1364928483963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16075944900513</t>
+    <t xml:space="preserve">1.16075956821442</t>
   </si>
   <si>
     <t xml:space="preserve">1.24569320678711</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">1.30231559276581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26996004581451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25378203392029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524871349335</t>
+    <t xml:space="preserve">1.26995992660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25378215312958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524859428406</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">1.12031507492065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14458155632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11627042293549</t>
+    <t xml:space="preserve">1.14458167552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
     <t xml:space="preserve">1.14862608909607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10009276866913</t>
+    <t xml:space="preserve">1.10009264945984</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840402126312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24164879322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.12840390205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24164867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582592964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05964803695679</t>
+    <t xml:space="preserve">1.07582604885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0596479177475</t>
   </si>
   <si>
     <t xml:space="preserve">1.09200382232666</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0798704624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0556036233902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155920982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02324795722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02729249000549</t>
+    <t xml:space="preserve">1.07987034320831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560350418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155909061432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324783802032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0272923707962</t>
   </si>
   <si>
     <t xml:space="preserve">1.00302577018738</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">0.982803344726562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97067004442215</t>
+    <t xml:space="preserve">0.954492211341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970670163631439</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847937107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962581098079681</t>
+    <t xml:space="preserve">0.986847817897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962581157684326</t>
   </si>
   <si>
     <t xml:space="preserve">0.966625571250916</t>
@@ -1778,10 +1778,10 @@
     <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31040453910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32253777980804</t>
+    <t xml:space="preserve">1.31040441989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32253789901733</t>
   </si>
   <si>
     <t xml:space="preserve">1.32658231258392</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">1.33467125892639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724935054779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46813833713531</t>
+    <t xml:space="preserve">1.3872492313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4681384563446</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55307185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57733869552612</t>
+    <t xml:space="preserve">1.5530720949173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57733881473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947217464447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57329440116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56520545482635</t>
+    <t xml:space="preserve">1.58947205543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57329428195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56520533561707</t>
   </si>
   <si>
     <t xml:space="preserve">1.48836076259613</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">1.5004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54902756214142</t>
+    <t xml:space="preserve">1.54902744293213</t>
   </si>
   <si>
     <t xml:space="preserve">1.52476072311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52880537509918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70676147937775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69867253303528</t>
+    <t xml:space="preserve">1.52880525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822780132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70676124095917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69867241382599</t>
   </si>
   <si>
     <t xml:space="preserve">1.69058358669281</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">1.67440581321716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72293925285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61373889446259</t>
+    <t xml:space="preserve">1.72293949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6137387752533</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60565006732941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205014705658</t>
+    <t xml:space="preserve">1.60564994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205002784729</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">1.55711650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48431622982025</t>
+    <t xml:space="preserve">1.48431634902954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49240517616272</t>
@@ -1934,19 +1934,19 @@
     <t xml:space="preserve">1.46409380435944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47622728347778</t>
+    <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
     <t xml:space="preserve">1.60160565376282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59756112098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60969436168671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75187587738037</t>
+    <t xml:space="preserve">1.59756100177765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.609694480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75187575817108</t>
   </si>
   <si>
     <t xml:space="preserve">1.72660839557648</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7097635269165</t>
+    <t xml:space="preserve">1.70976340770721</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68028485774994</t>
+    <t xml:space="preserve">1.68028473854065</t>
   </si>
   <si>
     <t xml:space="preserve">1.68449604511261</t>
@@ -1976,28 +1976,28 @@
     <t xml:space="preserve">1.64659488201141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343986988068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63817250728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62974989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66765105724335</t>
+    <t xml:space="preserve">1.66343975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63817238807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62974977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66765117645264</t>
   </si>
   <si>
     <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61711609363556</t>
+    <t xml:space="preserve">1.61711621284485</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54973638057709</t>
+    <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
     <t xml:space="preserve">1.58342635631561</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">1.56658136844635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54552507400513</t>
+    <t xml:space="preserve">1.54552519321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815887451172</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289151191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51183521747589</t>
+    <t xml:space="preserve">1.53289139270782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5118350982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.47393405437469</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4486665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41497671604156</t>
+    <t xml:space="preserve">1.44866669178009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41497659683228</t>
   </si>
   <si>
     <t xml:space="preserve">1.44024407863617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41076529026031</t>
+    <t xml:space="preserve">1.4107654094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40234291553497</t>
+    <t xml:space="preserve">1.40234303474426</t>
   </si>
   <si>
     <t xml:space="preserve">1.46130037307739</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49077904224396</t>
+    <t xml:space="preserve">1.49077892303467</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131388664246</t>
+    <t xml:space="preserve">1.54131376743317</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868008613586</t>
+    <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553858757019</t>
+    <t xml:space="preserve">1.62553870677948</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501749515533</t>
+    <t xml:space="preserve">1.65501737594604</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184885025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51604640483856</t>
+    <t xml:space="preserve">1.61290490627289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184873104095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51604628562927</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761039733887</t>
+    <t xml:space="preserve">1.42761051654816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2156,43 +2156,43 @@
     <t xml:space="preserve">1.65922856330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79398834705353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84452319145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83931910991669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584770679474</t>
+    <t xml:space="preserve">1.79398846626282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84452331066132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8393189907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584758758545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510474205017</t>
+    <t xml:space="preserve">1.79510462284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9277480840683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700488090515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237654209137</t>
+    <t xml:space="preserve">1.92774796485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237642288208</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365907907486</t>
+    <t xml:space="preserve">1.91006219387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93659090995789</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154824256897</t>
+    <t xml:space="preserve">2.05154800415039</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923389434814</t>
+    <t xml:space="preserve">2.0869197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923413276672</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039118766785</t>
+    <t xml:space="preserve">2.06039094924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353359699249</t>
+    <t xml:space="preserve">1.88353371620178</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427656173706</t>
+    <t xml:space="preserve">1.95427668094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163333892822</t>
+    <t xml:space="preserve">1.82163321971893</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783294200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130446434021</t>
+    <t xml:space="preserve">1.69783306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130434513092</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940432548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6270899772644</t>
+    <t xml:space="preserve">1.60940420627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62709009647369</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171843528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6049827337265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824715137482</t>
+    <t xml:space="preserve">1.59171831607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60498285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824703216553</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72436165809631</t>
+    <t xml:space="preserve">1.73762595653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7243617773056</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -7256,7 +7256,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7282,7 +7282,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7308,7 +7308,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7334,7 +7334,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7360,7 +7360,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7386,7 +7386,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7412,7 +7412,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7438,7 +7438,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7464,7 +7464,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7490,7 +7490,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7516,7 +7516,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7542,7 +7542,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7568,7 +7568,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7594,7 +7594,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7620,7 +7620,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7646,7 +7646,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7672,7 +7672,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7698,7 +7698,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7750,7 +7750,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7776,7 +7776,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7802,7 +7802,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7828,7 +7828,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7854,7 +7854,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7880,7 +7880,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7906,7 +7906,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7932,7 +7932,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7958,7 +7958,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7984,7 +7984,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -8010,7 +8010,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8036,7 +8036,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8062,7 +8062,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8088,7 +8088,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8114,7 +8114,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8140,7 +8140,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8166,7 +8166,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8192,7 +8192,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8218,7 +8218,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8244,7 +8244,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8270,7 +8270,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8296,7 +8296,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8322,7 +8322,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8348,7 +8348,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8374,7 +8374,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8400,7 +8400,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8426,7 +8426,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8452,7 +8452,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8478,7 +8478,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8504,7 +8504,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8530,7 +8530,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8556,7 +8556,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8582,7 +8582,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8608,7 +8608,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8634,7 +8634,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8660,7 +8660,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8686,7 +8686,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8712,7 +8712,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8738,7 +8738,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8764,7 +8764,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8790,7 +8790,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8816,7 +8816,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8842,7 +8842,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8868,7 +8868,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8894,7 +8894,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8920,7 +8920,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8946,7 +8946,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8972,7 +8972,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8998,7 +8998,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9024,7 +9024,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9050,7 +9050,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9076,7 +9076,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9102,7 +9102,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9128,7 +9128,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9154,7 +9154,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9180,7 +9180,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9206,7 +9206,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9232,7 +9232,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9258,7 +9258,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9284,7 +9284,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9310,7 +9310,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9336,7 +9336,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9362,7 +9362,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9388,7 +9388,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9414,7 +9414,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9440,7 +9440,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9492,7 +9492,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9518,7 +9518,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9544,7 +9544,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9570,7 +9570,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9596,7 +9596,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9622,7 +9622,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9648,7 +9648,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9674,7 +9674,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9700,7 +9700,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9726,7 +9726,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9752,7 +9752,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9778,7 +9778,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9830,7 +9830,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9856,7 +9856,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9882,7 +9882,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9908,7 +9908,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9934,7 +9934,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9960,7 +9960,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9986,7 +9986,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10064,7 +10064,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10090,7 +10090,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10116,7 +10116,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10142,7 +10142,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10168,7 +10168,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10194,7 +10194,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10220,7 +10220,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10246,7 +10246,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10272,7 +10272,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10298,7 +10298,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10324,7 +10324,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10376,7 +10376,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10402,7 +10402,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10428,7 +10428,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10454,7 +10454,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10480,7 +10480,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10506,7 +10506,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10636,7 +10636,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10662,7 +10662,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10688,7 +10688,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10714,7 +10714,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10740,7 +10740,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10766,7 +10766,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10792,7 +10792,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10818,7 +10818,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10844,7 +10844,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10870,7 +10870,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10896,7 +10896,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10922,7 +10922,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10948,7 +10948,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10974,7 +10974,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11000,7 +11000,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11026,7 +11026,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11052,7 +11052,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11078,7 +11078,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11104,7 +11104,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11130,7 +11130,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11156,7 +11156,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11182,7 +11182,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11208,7 +11208,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11234,7 +11234,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11260,7 +11260,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11286,7 +11286,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11312,7 +11312,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11338,7 +11338,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11364,7 +11364,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11390,7 +11390,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11416,7 +11416,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11442,7 +11442,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11468,7 +11468,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11494,7 +11494,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11520,7 +11520,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11546,7 +11546,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11572,7 +11572,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11598,7 +11598,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11624,7 +11624,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11650,7 +11650,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11676,7 +11676,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11702,7 +11702,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11728,7 +11728,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11754,7 +11754,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11780,7 +11780,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11806,7 +11806,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11832,7 +11832,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11858,7 +11858,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11884,7 +11884,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11910,7 +11910,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11936,7 +11936,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11962,7 +11962,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11988,7 +11988,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12014,7 +12014,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12040,7 +12040,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12066,7 +12066,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12092,7 +12092,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12118,7 +12118,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12144,7 +12144,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12170,7 +12170,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12196,7 +12196,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12222,7 +12222,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12248,7 +12248,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12274,7 +12274,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12300,7 +12300,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12326,7 +12326,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12352,7 +12352,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12378,7 +12378,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12404,7 +12404,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12430,7 +12430,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12456,7 +12456,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12482,7 +12482,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12508,7 +12508,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12534,7 +12534,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12560,7 +12560,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12586,7 +12586,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12612,7 +12612,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12638,7 +12638,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12664,7 +12664,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12690,7 +12690,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12716,7 +12716,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12742,7 +12742,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12768,7 +12768,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12794,7 +12794,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12820,7 +12820,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12846,7 +12846,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12872,7 +12872,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12898,7 +12898,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12924,7 +12924,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12950,7 +12950,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12976,7 +12976,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13002,7 +13002,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13028,7 +13028,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13054,7 +13054,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13080,7 +13080,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13106,7 +13106,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13132,7 +13132,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13158,7 +13158,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13184,7 +13184,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13210,7 +13210,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13236,7 +13236,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13262,7 +13262,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13288,7 +13288,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13314,7 +13314,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13340,7 +13340,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13366,7 +13366,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13392,7 +13392,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13418,7 +13418,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13444,7 +13444,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13470,7 +13470,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13496,7 +13496,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13522,7 +13522,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13548,7 +13548,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13574,7 +13574,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13600,7 +13600,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13626,7 +13626,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13652,7 +13652,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13678,7 +13678,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13704,7 +13704,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13730,7 +13730,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13756,7 +13756,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13782,7 +13782,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13808,7 +13808,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13834,7 +13834,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13860,7 +13860,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13886,7 +13886,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13912,7 +13912,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13938,7 +13938,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13964,7 +13964,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13990,7 +13990,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14016,7 +14016,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14042,7 +14042,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14068,7 +14068,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14094,7 +14094,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14120,7 +14120,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14146,7 +14146,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14172,7 +14172,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14198,7 +14198,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14224,7 +14224,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14250,7 +14250,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14276,7 +14276,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14302,7 +14302,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14328,7 +14328,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14354,7 +14354,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14380,7 +14380,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14406,7 +14406,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14432,7 +14432,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14458,7 +14458,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14484,7 +14484,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14510,7 +14510,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14536,7 +14536,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14562,7 +14562,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14588,7 +14588,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14614,7 +14614,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14640,7 +14640,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14666,7 +14666,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14692,7 +14692,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14718,7 +14718,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14744,7 +14744,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14770,7 +14770,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14796,7 +14796,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14822,7 +14822,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14848,7 +14848,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14874,7 +14874,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14900,7 +14900,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14926,7 +14926,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14952,7 +14952,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14978,7 +14978,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15004,7 +15004,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15030,7 +15030,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15056,7 +15056,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15082,7 +15082,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15108,7 +15108,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15134,7 +15134,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15160,7 +15160,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15186,7 +15186,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15212,7 +15212,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15238,7 +15238,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15264,7 +15264,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15290,7 +15290,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15316,7 +15316,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15342,7 +15342,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15368,7 +15368,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15394,7 +15394,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15420,7 +15420,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15446,7 +15446,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15472,7 +15472,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15498,7 +15498,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15524,7 +15524,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15550,7 +15550,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15576,7 +15576,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15602,7 +15602,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15628,7 +15628,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15654,7 +15654,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15680,7 +15680,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15706,7 +15706,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15732,7 +15732,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15758,7 +15758,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15784,7 +15784,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15810,7 +15810,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15836,7 +15836,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15862,7 +15862,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15888,7 +15888,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15914,7 +15914,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15940,7 +15940,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15966,7 +15966,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15992,7 +15992,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16018,7 +16018,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16044,7 +16044,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16070,7 +16070,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16096,7 +16096,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16122,7 +16122,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16148,7 +16148,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16174,7 +16174,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16200,7 +16200,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16226,7 +16226,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16252,7 +16252,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16278,7 +16278,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16304,7 +16304,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16330,7 +16330,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16356,7 +16356,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16382,7 +16382,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16408,7 +16408,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16434,7 +16434,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16460,7 +16460,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16486,7 +16486,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16512,7 +16512,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16538,7 +16538,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16564,7 +16564,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16590,7 +16590,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16616,7 +16616,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16642,7 +16642,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16668,7 +16668,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16694,7 +16694,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16720,7 +16720,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16746,7 +16746,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16772,7 +16772,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16798,7 +16798,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16824,7 +16824,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16850,7 +16850,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16876,7 +16876,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16902,7 +16902,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16928,7 +16928,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16954,7 +16954,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16980,7 +16980,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17006,7 +17006,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17032,7 +17032,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17058,7 +17058,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17084,7 +17084,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17110,7 +17110,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17136,7 +17136,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17162,7 +17162,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17188,7 +17188,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17214,7 +17214,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17240,7 +17240,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17266,7 +17266,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17292,7 +17292,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17318,7 +17318,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17344,7 +17344,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17370,7 +17370,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17396,7 +17396,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17422,7 +17422,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17448,7 +17448,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17474,7 +17474,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17500,7 +17500,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17526,7 +17526,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17552,7 +17552,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17578,7 +17578,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17604,7 +17604,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17630,7 +17630,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17656,7 +17656,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17682,7 +17682,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17708,7 +17708,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17734,7 +17734,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17760,7 +17760,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17786,7 +17786,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17812,7 +17812,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17838,7 +17838,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17864,7 +17864,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17890,7 +17890,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17916,7 +17916,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17942,7 +17942,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17968,7 +17968,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17994,7 +17994,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18020,7 +18020,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18046,7 +18046,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18072,7 +18072,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18098,7 +18098,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18124,7 +18124,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18150,7 +18150,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18176,7 +18176,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18202,7 +18202,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18228,7 +18228,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18254,7 +18254,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18280,7 +18280,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18306,7 +18306,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18332,7 +18332,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18358,7 +18358,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18384,7 +18384,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18410,7 +18410,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18436,7 +18436,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18462,7 +18462,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18488,7 +18488,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18514,7 +18514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18540,7 +18540,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18566,7 +18566,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18592,7 +18592,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18618,7 +18618,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18644,7 +18644,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18670,7 +18670,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18696,7 +18696,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18722,7 +18722,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18748,7 +18748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18774,7 +18774,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18800,7 +18800,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18826,7 +18826,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18852,7 +18852,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18878,7 +18878,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18982,7 +18982,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19034,7 +19034,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19112,7 +19112,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19138,7 +19138,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19164,7 +19164,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19190,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19216,7 +19216,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19242,7 +19242,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19268,7 +19268,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19294,7 +19294,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19320,7 +19320,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19346,7 +19346,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19372,7 +19372,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19398,7 +19398,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19424,7 +19424,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19450,7 +19450,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19476,7 +19476,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19554,7 +19554,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19606,7 +19606,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19632,7 +19632,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19684,7 +19684,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19710,7 +19710,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19736,7 +19736,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19788,7 +19788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19814,7 +19814,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19918,7 +19918,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19970,7 +19970,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19996,7 +19996,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20022,7 +20022,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -68598,7 +68598,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6874421296</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>46113</v>
@@ -68619,6 +68619,32 @@
         <v>865</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6912847222</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>22920</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>851</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504884719849</t>
+    <t xml:space="preserve">0.965504825115204</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892835617065</t>
+    <t xml:space="preserve">0.994893133640289</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97840690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169431209564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053874015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487484931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944718301296234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816279888153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386274814606</t>
+    <t xml:space="preserve">0.978406965732574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169371604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053814411163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938376426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487425327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9447181224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473690986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
   </si>
   <si>
     <t xml:space="preserve">0.900994420051575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878057479858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560928344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606469154358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844063282013</t>
+    <t xml:space="preserve">0.878057539463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902427971363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899561047554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606528759003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844122886658</t>
   </si>
   <si>
     <t xml:space="preserve">0.86658900976181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831466734409332</t>
+    <t xml:space="preserve">0.831466674804688</t>
   </si>
   <si>
     <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812988758087</t>
+    <t xml:space="preserve">0.807812929153442</t>
   </si>
   <si>
     <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713197767734528</t>
+    <t xml:space="preserve">0.713197708129883</t>
   </si>
   <si>
     <t xml:space="preserve">0.731117308139801</t>
@@ -125,118 +125,118 @@
     <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.723949491977692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124205112457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459897041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800645053386688</t>
+    <t xml:space="preserve">0.723949551582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124145507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459837436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800644993782043</t>
   </si>
   <si>
     <t xml:space="preserve">0.80279541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298918247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802247524261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827882826328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804945886135101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050523281097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834333956241608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634431362152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88665896654129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351296424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819885730743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87304013967514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340614795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809263706207</t>
+    <t xml:space="preserve">0.824298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827882766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804945766925812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634610176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886659026145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880207777023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83935135602951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040020465851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340793609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809382915497</t>
   </si>
   <si>
     <t xml:space="preserve">0.892393290996552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895977020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225415229797</t>
+    <t xml:space="preserve">0.895977139472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225296020508</t>
   </si>
   <si>
     <t xml:space="preserve">0.852970123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870889782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305874824524</t>
+    <t xml:space="preserve">0.870889663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305934429169</t>
   </si>
   <si>
     <t xml:space="preserve">0.880924642086029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830749928951263</t>
+    <t xml:space="preserve">0.86013799905777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830750048160553</t>
   </si>
   <si>
     <t xml:space="preserve">0.858704388141632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855120480060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536452770233</t>
+    <t xml:space="preserve">0.855120360851288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536571979523</t>
   </si>
   <si>
     <t xml:space="preserve">0.859421193599701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82644921541214</t>
+    <t xml:space="preserve">0.840785026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
     <t xml:space="preserve">0.799211502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789893329143524</t>
+    <t xml:space="preserve">0.789893388748169</t>
   </si>
   <si>
     <t xml:space="preserve">0.813547134399414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779858469963074</t>
+    <t xml:space="preserve">0.779858589172363</t>
   </si>
   <si>
     <t xml:space="preserve">0.781291961669922</t>
@@ -245,115 +245,112 @@
     <t xml:space="preserve">0.784875929355621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809246480464935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917864322662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431815624237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980685710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113702297211</t>
+    <t xml:space="preserve">0.809246420860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131102085114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917745113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431875228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980626106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113642692566</t>
   </si>
   <si>
     <t xml:space="preserve">0.811396777629852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799928307533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194042682648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512215614319</t>
+    <t xml:space="preserve">0.799928367137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194161891937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026345729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512275218964</t>
   </si>
   <si>
     <t xml:space="preserve">0.815697491168976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756921410560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655675411224</t>
+    <t xml:space="preserve">0.756921470165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788453578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76265561580658</t>
   </si>
   <si>
     <t xml:space="preserve">0.756204605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750470459461212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77914172410965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372540473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673194408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775557696819305</t>
+    <t xml:space="preserve">0.750470340251923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673075199127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575275421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557816028595</t>
   </si>
   <si>
     <t xml:space="preserve">0.795627593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784159123897552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218399047852</t>
+    <t xml:space="preserve">0.784159183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218279838562</t>
   </si>
   <si>
     <t xml:space="preserve">0.851380407810211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872163951396942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029922962189</t>
+    <t xml:space="preserve">0.872163832187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937121868134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029982566833</t>
   </si>
   <si>
     <t xml:space="preserve">0.861772239208221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85360723733902</t>
+    <t xml:space="preserve">0.853607296943665</t>
   </si>
   <si>
     <t xml:space="preserve">0.856576442718506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.864741265773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834066867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277472019196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401127338409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050642490387</t>
+    <t xml:space="preserve">0.864741325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834186077118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401246547699</t>
   </si>
   <si>
     <t xml:space="preserve">0.829112470149994</t>
@@ -368,58 +365,58 @@
     <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84470009803772</t>
+    <t xml:space="preserve">0.844700217247009</t>
   </si>
   <si>
     <t xml:space="preserve">0.843957781791687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846184611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835792899131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833566129207611</t>
+    <t xml:space="preserve">0.84618467092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83579295873642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833566069602966</t>
   </si>
   <si>
     <t xml:space="preserve">0.838761866092682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816493988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809813559055328</t>
+    <t xml:space="preserve">0.816493928432465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809813439846039</t>
   </si>
   <si>
     <t xml:space="preserve">0.823916614055634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810555875301361</t>
+    <t xml:space="preserve">0.810555815696716</t>
   </si>
   <si>
     <t xml:space="preserve">0.801648616790771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81797844171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720757961273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819462954998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143383979797</t>
+    <t xml:space="preserve">0.81797856092453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819463074207306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143562793732</t>
   </si>
   <si>
     <t xml:space="preserve">0.812782645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808329105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133130073547</t>
+    <t xml:space="preserve">0.808329045772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133189678192</t>
   </si>
   <si>
     <t xml:space="preserve">0.805359959602356</t>
@@ -431,25 +428,25 @@
     <t xml:space="preserve">0.800906300544739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790514647960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999161243439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791256844997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80758672952652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814267158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617643356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798679530620575</t>
+    <t xml:space="preserve">0.790514588356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791256785392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807586848735809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814267218112946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617702960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79867947101593</t>
   </si>
   <si>
     <t xml:space="preserve">0.794225931167603</t>
@@ -458,13 +455,13 @@
     <t xml:space="preserve">0.786803185939789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77938050031662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777895987033844</t>
+    <t xml:space="preserve">0.779380440711975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777153789997101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
     <t xml:space="preserve">0.788287878036499</t>
@@ -473,28 +470,28 @@
     <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838019669055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844532489777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442566394806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783834218978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765277445316315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778638422489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091902732849</t>
+    <t xml:space="preserve">0.838019609451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844472885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774926960468292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442506790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783834278583527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765277564525604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778638362884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091843128204</t>
   </si>
   <si>
     <t xml:space="preserve">0.787545502185822</t>
@@ -509,10 +506,10 @@
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102216243744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452548980713</t>
+    <t xml:space="preserve">0.806102097034454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452787399292</t>
   </si>
   <si>
     <t xml:space="preserve">0.841731011867523</t>
@@ -521,19 +518,19 @@
     <t xml:space="preserve">0.848411440849304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843215644359589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865159511566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442414283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87439090013504</t>
+    <t xml:space="preserve">0.843215584754944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865099906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442473888397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390661716461</t>
   </si>
   <si>
     <t xml:space="preserve">0.862514436244965</t>
@@ -542,40 +539,40 @@
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855091750621796</t>
+    <t xml:space="preserve">0.85509181022644</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823812961578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834308385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827628016471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86028778553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349672794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867710471153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880329012870789</t>
+    <t xml:space="preserve">0.832823753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834308326244354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827627897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287845134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349553585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86771035194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880328834056854</t>
   </si>
   <si>
     <t xml:space="preserve">0.873648583889008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919669032096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380434513092</t>
+    <t xml:space="preserve">0.919668972492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380374908447</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
@@ -584,7 +581,7 @@
     <t xml:space="preserve">0.916700065135956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927091836929321</t>
+    <t xml:space="preserve">0.927091658115387</t>
   </si>
   <si>
     <t xml:space="preserve">0.931545436382294</t>
@@ -593,7 +590,7 @@
     <t xml:space="preserve">0.915957748889923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911504149436951</t>
+    <t xml:space="preserve">0.911504209041595</t>
   </si>
   <si>
     <t xml:space="preserve">0.908535003662109</t>
@@ -605,34 +602,34 @@
     <t xml:space="preserve">0.991668939590454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979792892932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768968582153</t>
+    <t xml:space="preserve">0.979792773723602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768956661224</t>
   </si>
   <si>
     <t xml:space="preserve">1.06960701942444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0748028755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0688648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0465966463089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05327713489532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05179274082184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03249359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02432882785797</t>
+    <t xml:space="preserve">1.07480311393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06886470317841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04659676551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05327725410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05179262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03249371051788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02432870864868</t>
   </si>
   <si>
     <t xml:space="preserve">1.03175139427185</t>
@@ -650,16 +647,16 @@
     <t xml:space="preserve">1.03026700019836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05921530723572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06812250614166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04585456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06663823127747</t>
+    <t xml:space="preserve">1.05921542644501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06812262535095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04585444927216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06663799285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.10449361801147</t>
@@ -668,16 +665,16 @@
     <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11933887004852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11711227893829</t>
+    <t xml:space="preserve">1.1193391084671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11711239814758</t>
   </si>
   <si>
     <t xml:space="preserve">1.1289883852005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14160680770874</t>
+    <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
@@ -689,43 +686,43 @@
     <t xml:space="preserve">1.2314213514328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2173182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2217720746994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880269050598</t>
+    <t xml:space="preserve">1.21731817722321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177183628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880280971527</t>
   </si>
   <si>
     <t xml:space="preserve">1.23216366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22845232486725</t>
+    <t xml:space="preserve">1.22845208644867</t>
   </si>
   <si>
     <t xml:space="preserve">1.23513281345367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22474086284637</t>
+    <t xml:space="preserve">1.22474098205566</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286451816559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21360683441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20098829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24700891971588</t>
+    <t xml:space="preserve">1.21360695362091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20098853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24700880050659</t>
   </si>
   <si>
     <t xml:space="preserve">1.26779246330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24923586845398</t>
+    <t xml:space="preserve">1.24923574924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
@@ -734,46 +731,46 @@
     <t xml:space="preserve">1.26036965847015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25888526439667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26927709579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639028549194</t>
+    <t xml:space="preserve">1.25888514518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2692768573761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521526813507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639040470123</t>
   </si>
   <si>
     <t xml:space="preserve">1.34424591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.239586353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2032151222229</t>
+    <t xml:space="preserve">1.23958623409271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20321536064148</t>
   </si>
   <si>
     <t xml:space="preserve">1.17426669597626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17278218269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16535973548889</t>
+    <t xml:space="preserve">1.17278230190277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16535949707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.17055535316467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1772358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649352550507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16387498378754</t>
+    <t xml:space="preserve">1.17723596096039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649340629578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16387486457825</t>
   </si>
   <si>
     <t xml:space="preserve">1.16164827346802</t>
@@ -782,7 +779,7 @@
     <t xml:space="preserve">1.15051412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15348315238953</t>
+    <t xml:space="preserve">1.15348327159882</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824630737305</t>
@@ -791,28 +788,28 @@
     <t xml:space="preserve">1.14383375644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18911218643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20247292518616</t>
+    <t xml:space="preserve">1.1891120672226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20247268676758</t>
   </si>
   <si>
     <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28486442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31307077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018408298492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32791614532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35834896564484</t>
+    <t xml:space="preserve">1.28486466407776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31307089328766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018396377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.327916264534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35834908485413</t>
   </si>
   <si>
     <t xml:space="preserve">1.3435035943985</t>
@@ -821,13 +818,13 @@
     <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057282447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34374034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32855701446533</t>
+    <t xml:space="preserve">1.35057294368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34374046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32855689525604</t>
   </si>
   <si>
     <t xml:space="preserve">1.35816478729248</t>
@@ -836,10 +833,10 @@
     <t xml:space="preserve">1.35512793064117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37031161785126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36651563644409</t>
+    <t xml:space="preserve">1.37031149864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3665155172348</t>
   </si>
   <si>
     <t xml:space="preserve">1.37410736083984</t>
@@ -848,73 +845,73 @@
     <t xml:space="preserve">1.39080929756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39688265323639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3816990852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36803388595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36727488040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39156830310822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39232742786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258899211884</t>
+    <t xml:space="preserve">1.39688277244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38169920444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36803412437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36727476119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3915684223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39232754707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549506664276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">1.38701343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36879312992096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36120128631592</t>
+    <t xml:space="preserve">1.36879324913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36120140552521</t>
   </si>
   <si>
     <t xml:space="preserve">1.35133218765259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31565093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33842623233795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34298121929169</t>
+    <t xml:space="preserve">1.31565082073212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33842599391937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34298133850098</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363477230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818999767303</t>
+    <t xml:space="preserve">1.29363489151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818987846375</t>
   </si>
   <si>
     <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.320965051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31413233280182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36955237388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536428451538</t>
+    <t xml:space="preserve">1.32096517086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3141325712204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36955225467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536440372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562584877014</t>
@@ -929,13 +926,13 @@
     <t xml:space="preserve">1.38397669792175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929092884064</t>
+    <t xml:space="preserve">1.38929104804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37866234779358</t>
+    <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
     <t xml:space="preserve">1.38473570346832</t>
@@ -944,28 +941,28 @@
     <t xml:space="preserve">1.34829545021057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42497217655182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4523024559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50164890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735524177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630946159363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51835060119629</t>
+    <t xml:space="preserve">1.42497205734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45230233669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50164902210236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735512256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630934238434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51835072040558</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379573345184</t>
+    <t xml:space="preserve">1.51379561424255</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594244480133</t>
@@ -974,97 +971,97 @@
     <t xml:space="preserve">1.51075887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52897906303406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50316727161407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53049755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53353416919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746093273163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51607310771942</t>
+    <t xml:space="preserve">1.52897918224335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50316715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53049767017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53353428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746069431305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51607298851013</t>
   </si>
   <si>
     <t xml:space="preserve">1.47887349128723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43484151363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40599286556244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38777256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33614861965179</t>
+    <t xml:space="preserve">1.43484127521515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40599274635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38777244091034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33614873886108</t>
   </si>
   <si>
     <t xml:space="preserve">1.2905980348587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29970824718475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30502247810364</t>
+    <t xml:space="preserve">1.29970812797546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30502235889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.42573130130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052252292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659599781036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48798358440399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48722434043884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269444465637</t>
+    <t xml:space="preserve">1.47052264213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659611701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48798370361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48722457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269456386566</t>
   </si>
   <si>
     <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41738045215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40447437763214</t>
+    <t xml:space="preserve">1.41738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371525287628</t>
+    <t xml:space="preserve">1.40371513366699</t>
   </si>
   <si>
     <t xml:space="preserve">1.37182986736298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36271965503693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423814296722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35209143161774</t>
+    <t xml:space="preserve">1.36271977424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
     <t xml:space="preserve">1.36499726772308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36575651168823</t>
+    <t xml:space="preserve">1.36575639247894</t>
   </si>
   <si>
     <t xml:space="preserve">1.37107062339783</t>
@@ -1073,13 +1070,13 @@
     <t xml:space="preserve">1.4272495508194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48039197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4993714094162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49557554721832</t>
+    <t xml:space="preserve">1.48039209842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49937129020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
     <t xml:space="preserve">1.49177956581116</t>
@@ -1091,25 +1088,25 @@
     <t xml:space="preserve">1.45761656761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4386373758316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37790322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33235275745392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30957758426666</t>
+    <t xml:space="preserve">1.43863713741302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37790334224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33235287666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30957746505737</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753620624542</t>
+    <t xml:space="preserve">1.32476115226746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753632545471</t>
   </si>
   <si>
     <t xml:space="preserve">1.31337332725525</t>
@@ -1127,16 +1124,16 @@
     <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41965794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44243323802948</t>
+    <t xml:space="preserve">1.41965782642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44243311882019</t>
   </si>
   <si>
     <t xml:space="preserve">1.45382082462311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46900427341461</t>
+    <t xml:space="preserve">1.4690043926239</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418784141541</t>
@@ -1145,13 +1142,13 @@
     <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42345380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586196422577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002484321594</t>
+    <t xml:space="preserve">1.42345368862152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002496242523</t>
   </si>
   <si>
     <t xml:space="preserve">1.46141254901886</t>
@@ -1163,10 +1160,13 @@
     <t xml:space="preserve">1.47280025482178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51455473899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51551628112793</t>
+    <t xml:space="preserve">1.5145548582077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48418772220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51551616191864</t>
   </si>
   <si>
     <t xml:space="preserve">1.50768411159515</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">1.51943242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5037682056427</t>
+    <t xml:space="preserve">1.50376808643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852362155914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48027169704437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46069145202637</t>
+    <t xml:space="preserve">1.46852350234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48027157783508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46069133281708</t>
   </si>
   <si>
     <t xml:space="preserve">1.44894337654114</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">1.46460747718811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677530765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47243976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47635567188263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44111120700836</t>
+    <t xml:space="preserve">1.45677542686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47243964672089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47635579109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44111132621765</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40978252887726</t>
+    <t xml:space="preserve">1.36278998851776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40978264808655</t>
   </si>
   <si>
     <t xml:space="preserve">1.42153084278107</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">1.42936301231384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43327903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45285928249359</t>
+    <t xml:space="preserve">1.43327915668488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4528591632843</t>
   </si>
   <si>
     <t xml:space="preserve">1.39803445339203</t>
@@ -1244,34 +1244,34 @@
     <t xml:space="preserve">1.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488816738129</t>
+    <t xml:space="preserve">1.26488828659058</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30796504020691</t>
+    <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
     <t xml:space="preserve">1.30404889583588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33146142959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055262565613</t>
+    <t xml:space="preserve">1.33146154880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055250644684</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962167263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188106536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34320962429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35104179382324</t>
+    <t xml:space="preserve">1.31188094615936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34320950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35104167461395</t>
   </si>
   <si>
     <t xml:space="preserve">1.38628625869751</t>
@@ -1280,16 +1280,16 @@
     <t xml:space="preserve">1.40586650371552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37062203884125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37845396995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3275454044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838455677032</t>
+    <t xml:space="preserve">1.37062191963196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37845420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32754528522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230070114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28446865081787</t>
+    <t xml:space="preserve">1.29230058193207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28446853160858</t>
   </si>
   <si>
     <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31971323490143</t>
+    <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761457920074</t>
+    <t xml:space="preserve">1.41761481761932</t>
   </si>
   <si>
     <t xml:space="preserve">1.48810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49593603610992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49985194206238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51160037517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334845066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53509676456451</t>
+    <t xml:space="preserve">1.49593591690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49985206127167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5116001367569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53509664535522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55076098442078</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6212500333786</t>
+    <t xml:space="preserve">1.58992159366608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.60558569431305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61341774463654</t>
+    <t xml:space="preserve">1.61341786384583</t>
   </si>
   <si>
     <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62908208370209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64474630355835</t>
+    <t xml:space="preserve">1.62908220291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64474642276764</t>
   </si>
   <si>
     <t xml:space="preserve">1.63691425323486</t>
@@ -1376,40 +1376,40 @@
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824305057526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740354061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439620018005</t>
+    <t xml:space="preserve">1.66824281215668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439631938934</t>
   </si>
   <si>
     <t xml:space="preserve">1.74656403064728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76222825050354</t>
+    <t xml:space="preserve">1.76222836971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.80138885974884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838175773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006018161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77789258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922091007233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271753787994</t>
+    <t xml:space="preserve">1.84838163852692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006042003632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7778924703598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82488524913788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922102928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271729946136</t>
   </si>
   <si>
     <t xml:space="preserve">1.84054958820343</t>
@@ -1418,64 +1418,64 @@
     <t xml:space="preserve">1.87971043586731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87187802791595</t>
+    <t xml:space="preserve">1.87187826633453</t>
   </si>
   <si>
     <t xml:space="preserve">1.86404609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8562136888504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79355680942535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94236743450165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95803141593933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97369563579559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99719202518463</t>
+    <t xml:space="preserve">1.85621380805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79355669021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94236731529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95803153514862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97369587421417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99719214439392</t>
   </si>
   <si>
     <t xml:space="preserve">1.96586346626282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93453502655029</t>
+    <t xml:space="preserve">1.93453514575958</t>
   </si>
   <si>
     <t xml:space="preserve">1.91887080669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9267030954361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178458213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942903518677</t>
+    <t xml:space="preserve">1.92670297622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178470134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942891597748</t>
   </si>
   <si>
     <t xml:space="preserve">1.96560668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87662851810455</t>
+    <t xml:space="preserve">1.87662875652313</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338398456573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765070438385</t>
+    <t xml:space="preserve">1.76338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191742420197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765058517456</t>
   </si>
   <si>
     <t xml:space="preserve">1.79573953151703</t>
@@ -1484,28 +1484,28 @@
     <t xml:space="preserve">1.8038284778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82000625133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86045074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236203670502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89280664920807</t>
+    <t xml:space="preserve">1.82000637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8604508638382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809519767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236191749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8928062915802</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88471746444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427309036255</t>
+    <t xml:space="preserve">1.88471758365631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427297115326</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">1.7714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898442268372</t>
+    <t xml:space="preserve">1.90898430347443</t>
   </si>
   <si>
     <t xml:space="preserve">1.94134032726288</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">1.93325114250183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98987376689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751798152924</t>
+    <t xml:space="preserve">1.98987364768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751786231995</t>
   </si>
   <si>
     <t xml:space="preserve">1.997962474823</t>
@@ -1541,31 +1541,31 @@
     <t xml:space="preserve">1.92516231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74720597267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75529491901398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631674766541</t>
+    <t xml:space="preserve">1.7472060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75529503822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631686687469</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58542776107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56116092205048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49644958972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747141838074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4155604839325</t>
+    <t xml:space="preserve">1.58542764186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56116080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4964497089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747165679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41556036472321</t>
   </si>
   <si>
     <t xml:space="preserve">1.34276020526886</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">1.31849336624146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29827117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17289292812347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715964794159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951531410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15267062187195</t>
+    <t xml:space="preserve">1.29827105998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17289304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951543331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15267050266266</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
@@ -1604,46 +1604,46 @@
     <t xml:space="preserve">1.07178151607513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15671515464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1405371427536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693734169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09604823589325</t>
+    <t xml:space="preserve">1.15671503543854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14053726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693746089935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09604811668396</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18907070159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1364928483963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075956821442</t>
+    <t xml:space="preserve">1.18907082080841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13649272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075944900513</t>
   </si>
   <si>
     <t xml:space="preserve">1.24569320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26187098026276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30231559276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995992660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25378215312958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524859428406</t>
+    <t xml:space="preserve">1.26187109947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30231547355652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995980739594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25378203392029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524871349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">1.18098187446594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21333742141724</t>
+    <t xml:space="preserve">1.21333754062653</t>
   </si>
   <si>
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031507492065</t>
+    <t xml:space="preserve">1.12031483650208</t>
   </si>
   <si>
     <t xml:space="preserve">1.14458167552948</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862608909607</t>
+    <t xml:space="preserve">1.14862620830536</t>
   </si>
   <si>
     <t xml:space="preserve">1.10009264945984</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840390205383</t>
+    <t xml:space="preserve">1.12840378284454</t>
   </si>
   <si>
     <t xml:space="preserve">1.24164867401123</t>
@@ -1691,28 +1691,28 @@
     <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20929312705994</t>
+    <t xml:space="preserve">1.20929300785065</t>
   </si>
   <si>
     <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2214263677597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11222612857819</t>
+    <t xml:space="preserve">1.22142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1122260093689</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0596479177475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09200382232666</t>
+    <t xml:space="preserve">1.07582592964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05964803695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09200370311737</t>
   </si>
   <si>
     <t xml:space="preserve">1.08391487598419</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">1.07987034320831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05560350418091</t>
+    <t xml:space="preserve">1.0556036233902</t>
   </si>
   <si>
     <t xml:space="preserve">1.05155909061432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02324783802032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0272923707962</t>
+    <t xml:space="preserve">1.0232480764389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02729249000549</t>
   </si>
   <si>
     <t xml:space="preserve">1.00302577018738</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">0.982803344726562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492211341858</t>
+    <t xml:space="preserve">0.954492151737213</t>
   </si>
   <si>
     <t xml:space="preserve">0.970670163631439</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847817897797</t>
+    <t xml:space="preserve">0.986847937107086</t>
   </si>
   <si>
     <t xml:space="preserve">0.962581157684326</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">0.966625571250916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978758990764618</t>
+    <t xml:space="preserve">0.978758931159973</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">1.20120418071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29422664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31040441989899</t>
+    <t xml:space="preserve">1.29422676563263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31040453910828</t>
   </si>
   <si>
     <t xml:space="preserve">1.32253789901733</t>
@@ -1790,19 +1790,19 @@
     <t xml:space="preserve">1.34680461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33467125892639</t>
+    <t xml:space="preserve">1.3346711397171</t>
   </si>
   <si>
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4681384563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51262748241425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5530720949173</t>
+    <t xml:space="preserve">1.46813833713531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51262736320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55307197570801</t>
   </si>
   <si>
     <t xml:space="preserve">1.57733881473541</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284966945648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51667189598083</t>
+    <t xml:space="preserve">1.53284955024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51667177677155</t>
   </si>
   <si>
     <t xml:space="preserve">1.53689420223236</t>
@@ -1832,31 +1832,31 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947205543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57329428195953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56520533561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836076259613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5004940032959</t>
+    <t xml:space="preserve">1.58947217464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57329440116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56520521640778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836088180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50049388408661</t>
   </si>
   <si>
     <t xml:space="preserve">1.54902744293213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52476072311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.5247608423233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5288051366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676124095917</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">1.68249464035034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67440581321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72293949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6137387752533</t>
+    <t xml:space="preserve">1.67440569400787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72293937206268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61373889446259</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205002784729</t>
+    <t xml:space="preserve">1.60565006732941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205014705658</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">1.61778330802917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71485030651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55711650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48431634902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49240517616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47218286991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351670742035</t>
+    <t xml:space="preserve">1.71485018730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48431622982025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49240529537201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47218298912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351658821106</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">1.44791603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46409380435944</t>
+    <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60160565376282</t>
+    <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
     <t xml:space="preserve">1.59756100177765</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">1.609694480896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75187575817108</t>
+    <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
     <t xml:space="preserve">1.72660839557648</t>
@@ -1973,19 +1973,19 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64659488201141</t>
+    <t xml:space="preserve">1.6465950012207</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343975067139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63817238807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62974977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66765117645264</t>
+    <t xml:space="preserve">1.63817250728607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62974989414215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.64238369464874</t>
@@ -2000,19 +2000,19 @@
     <t xml:space="preserve">1.54973649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58342635631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500386238098</t>
+    <t xml:space="preserve">1.58342623710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500374317169</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59606003761292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56658136844635</t>
+    <t xml:space="preserve">1.59605991840363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56658124923706</t>
   </si>
   <si>
     <t xml:space="preserve">1.54552519321442</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5118350982666</t>
+    <t xml:space="preserve">1.53289151191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51183521747589</t>
   </si>
   <si>
     <t xml:space="preserve">1.47393405437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43182170391083</t>
+    <t xml:space="preserve">1.43182158470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38970923423767</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43603301048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44866669178009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41497659683228</t>
+    <t xml:space="preserve">1.4360328912735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4486665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41497671604156</t>
   </si>
   <si>
     <t xml:space="preserve">1.44024407863617</t>
@@ -2060,13 +2060,13 @@
     <t xml:space="preserve">1.40655422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40234303474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46130037307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499034881592</t>
+    <t xml:space="preserve">1.40234291553497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4613002538681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499022960663</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077892303467</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131376743317</t>
+    <t xml:space="preserve">1.54131400585175</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">1.71818590164185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186236381531</t>
+    <t xml:space="preserve">1.67186224460602</t>
   </si>
   <si>
     <t xml:space="preserve">1.61290490627289</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">1.59184873104095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604628562927</t>
+    <t xml:space="preserve">1.51604640483856</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">1.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48235642910004</t>
+    <t xml:space="preserve">1.48235654830933</t>
   </si>
   <si>
     <t xml:space="preserve">1.45708906650543</t>
@@ -2150,16 +2150,16 @@
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763742446899</t>
+    <t xml:space="preserve">1.58763754367828</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79398846626282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84452331066132</t>
+    <t xml:space="preserve">1.79398834705353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84452319145203</t>
   </si>
   <si>
     <t xml:space="preserve">1.8393189907074</t>
@@ -7256,7 +7256,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7282,7 +7282,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7308,7 +7308,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7334,7 +7334,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7360,7 +7360,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7386,7 +7386,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7412,7 +7412,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7438,7 +7438,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7464,7 +7464,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7490,7 +7490,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7516,7 +7516,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7542,7 +7542,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7568,7 +7568,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7594,7 +7594,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7620,7 +7620,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7646,7 +7646,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G181" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7672,7 +7672,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G182" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7698,7 +7698,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7750,7 +7750,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7776,7 +7776,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G186" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7802,7 +7802,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7828,7 +7828,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G188" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7854,7 +7854,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G189" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7880,7 +7880,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G190" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7906,7 +7906,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7932,7 +7932,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7958,7 +7958,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7984,7 +7984,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -8010,7 +8010,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8036,7 +8036,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8062,7 +8062,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G197" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8088,7 +8088,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8114,7 +8114,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8140,7 +8140,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8166,7 +8166,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8192,7 +8192,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8218,7 +8218,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8244,7 +8244,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8270,7 +8270,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8296,7 +8296,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G206" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8322,7 +8322,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8348,7 +8348,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8374,7 +8374,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8400,7 +8400,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8426,7 +8426,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8452,7 +8452,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8478,7 +8478,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8504,7 +8504,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8530,7 +8530,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8556,7 +8556,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G216" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8582,7 +8582,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8608,7 +8608,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G218" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8634,7 +8634,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8660,7 +8660,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8686,7 +8686,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8712,7 +8712,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G222" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8738,7 +8738,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G223" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8764,7 +8764,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8790,7 +8790,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8816,7 +8816,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8842,7 +8842,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G227" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8868,7 +8868,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8894,7 +8894,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8920,7 +8920,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8946,7 +8946,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8972,7 +8972,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8998,7 +8998,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9024,7 +9024,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9050,7 +9050,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G235" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9076,7 +9076,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9102,7 +9102,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9128,7 +9128,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G238" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9154,7 +9154,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G239" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9180,7 +9180,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G240" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9206,7 +9206,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9232,7 +9232,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G242" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9258,7 +9258,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G243" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9284,7 +9284,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9310,7 +9310,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9336,7 +9336,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9362,7 +9362,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G247" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9388,7 +9388,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G248" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9414,7 +9414,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9440,7 +9440,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9492,7 +9492,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9518,7 +9518,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9544,7 +9544,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9570,7 +9570,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9596,7 +9596,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G256" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9622,7 +9622,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G257" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9648,7 +9648,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G258" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9674,7 +9674,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9700,7 +9700,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9726,7 +9726,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9752,7 +9752,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G262" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9778,7 +9778,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9830,7 +9830,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9856,7 +9856,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9882,7 +9882,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9908,7 +9908,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9934,7 +9934,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9960,7 +9960,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9986,7 +9986,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G271" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10064,7 +10064,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G274" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10090,7 +10090,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10116,7 +10116,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10142,7 +10142,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10168,7 +10168,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10194,7 +10194,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10220,7 +10220,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10246,7 +10246,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10272,7 +10272,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G282" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10298,7 +10298,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G283" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10324,7 +10324,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10376,7 +10376,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10402,7 +10402,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G287" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10428,7 +10428,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10454,7 +10454,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10480,7 +10480,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10506,7 +10506,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10636,7 +10636,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G296" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10662,7 +10662,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G297" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10688,7 +10688,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G298" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10714,7 +10714,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10740,7 +10740,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10766,7 +10766,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10792,7 +10792,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10818,7 +10818,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G303" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10844,7 +10844,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10870,7 +10870,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10896,7 +10896,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10922,7 +10922,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10948,7 +10948,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10974,7 +10974,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11000,7 +11000,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11026,7 +11026,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11052,7 +11052,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11078,7 +11078,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11104,7 +11104,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11130,7 +11130,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11156,7 +11156,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11182,7 +11182,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11208,7 +11208,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11234,7 +11234,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11260,7 +11260,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G320" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11286,7 +11286,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11312,7 +11312,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G322" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11338,7 +11338,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11364,7 +11364,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11390,7 +11390,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G325" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11416,7 +11416,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11442,7 +11442,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11468,7 +11468,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11494,7 +11494,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11520,7 +11520,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11546,7 +11546,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11572,7 +11572,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11598,7 +11598,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11624,7 +11624,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G334" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11650,7 +11650,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G335" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11676,7 +11676,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11702,7 +11702,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11728,7 +11728,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G338" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11754,7 +11754,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11780,7 +11780,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G340" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11806,7 +11806,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11832,7 +11832,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11858,7 +11858,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11884,7 +11884,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G344" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11910,7 +11910,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G345" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11936,7 +11936,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11962,7 +11962,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G347" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11988,7 +11988,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12014,7 +12014,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G349" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12040,7 +12040,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G350" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12066,7 +12066,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12092,7 +12092,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G352" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12118,7 +12118,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12144,7 +12144,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12170,7 +12170,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12196,7 +12196,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12222,7 +12222,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G357" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12248,7 +12248,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G358" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12274,7 +12274,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12300,7 +12300,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12326,7 +12326,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G361" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12352,7 +12352,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G362" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12378,7 +12378,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G363" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12404,7 +12404,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12430,7 +12430,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12456,7 +12456,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G366" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12482,7 +12482,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G367" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12508,7 +12508,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12534,7 +12534,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G369" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12560,7 +12560,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G370" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12586,7 +12586,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G371" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12612,7 +12612,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12638,7 +12638,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G373" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12664,7 +12664,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G374" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12690,7 +12690,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12716,7 +12716,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12742,7 +12742,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12768,7 +12768,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G378" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12794,7 +12794,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12820,7 +12820,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G380" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12846,7 +12846,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G381" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12872,7 +12872,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G382" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12898,7 +12898,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12924,7 +12924,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12950,7 +12950,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12976,7 +12976,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13002,7 +13002,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13028,7 +13028,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13054,7 +13054,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13080,7 +13080,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13106,7 +13106,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G391" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13132,7 +13132,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13158,7 +13158,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G393" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13184,7 +13184,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13210,7 +13210,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13236,7 +13236,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13262,7 +13262,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13288,7 +13288,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13314,7 +13314,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G399" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13340,7 +13340,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G400" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13366,7 +13366,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G401" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13392,7 +13392,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13418,7 +13418,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G403" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13444,7 +13444,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G404" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13470,7 +13470,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13496,7 +13496,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G406" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13522,7 +13522,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13548,7 +13548,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13574,7 +13574,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13600,7 +13600,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13626,7 +13626,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13652,7 +13652,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G412" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13678,7 +13678,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G413" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13704,7 +13704,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13730,7 +13730,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13756,7 +13756,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13782,7 +13782,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13808,7 +13808,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13834,7 +13834,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13860,7 +13860,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13886,7 +13886,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13912,7 +13912,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G422" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13938,7 +13938,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G423" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13964,7 +13964,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G424" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13990,7 +13990,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14016,7 +14016,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G426" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14042,7 +14042,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14068,7 +14068,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14094,7 +14094,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14120,7 +14120,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14146,7 +14146,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14172,7 +14172,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14198,7 +14198,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G433" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14224,7 +14224,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14250,7 +14250,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G435" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14276,7 +14276,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14302,7 +14302,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G437" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14328,7 +14328,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14354,7 +14354,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14380,7 +14380,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14406,7 +14406,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14432,7 +14432,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14458,7 +14458,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G443" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14484,7 +14484,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14510,7 +14510,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14536,7 +14536,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G446" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14562,7 +14562,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G447" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14588,7 +14588,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14614,7 +14614,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G449" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14640,7 +14640,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14666,7 +14666,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14692,7 +14692,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14718,7 +14718,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G453" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14744,7 +14744,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14770,7 +14770,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G455" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14796,7 +14796,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G456" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14822,7 +14822,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G457" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14848,7 +14848,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14874,7 +14874,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G459" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14900,7 +14900,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14926,7 +14926,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14952,7 +14952,7 @@
         <v>2</v>
       </c>
       <c r="G462" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14978,7 +14978,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15004,7 +15004,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15030,7 +15030,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15056,7 +15056,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G466" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15082,7 +15082,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15108,7 +15108,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15134,7 +15134,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15160,7 +15160,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15186,7 +15186,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15212,7 +15212,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15238,7 +15238,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G473" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15264,7 +15264,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G474" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15290,7 +15290,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15316,7 +15316,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15342,7 +15342,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15368,7 +15368,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15394,7 +15394,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15420,7 +15420,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15446,7 +15446,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15472,7 +15472,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G482" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15498,7 +15498,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G483" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15524,7 +15524,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15550,7 +15550,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G485" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15576,7 +15576,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G486" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15602,7 +15602,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G487" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15628,7 +15628,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15654,7 +15654,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15680,7 +15680,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G490" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15706,7 +15706,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G491" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15732,7 +15732,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15758,7 +15758,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15784,7 +15784,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15810,7 +15810,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15836,7 +15836,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15862,7 +15862,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G497" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15888,7 +15888,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15914,7 +15914,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G499" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15940,7 +15940,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15966,7 +15966,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15992,7 +15992,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16018,7 +16018,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16044,7 +16044,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16070,7 +16070,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16096,7 +16096,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16122,7 +16122,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G507" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16148,7 +16148,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G508" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16174,7 +16174,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G509" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16200,7 +16200,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16226,7 +16226,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16252,7 +16252,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16278,7 +16278,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G513" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16304,7 +16304,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G514" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16330,7 +16330,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16356,7 +16356,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16382,7 +16382,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16408,7 +16408,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16434,7 +16434,7 @@
         <v>2</v>
       </c>
       <c r="G519" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16460,7 +16460,7 @@
         <v>2</v>
       </c>
       <c r="G520" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16486,7 +16486,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G521" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16512,7 +16512,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G522" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16538,7 +16538,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G523" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16564,7 +16564,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16590,7 +16590,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G525" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16616,7 +16616,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16642,7 +16642,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16668,7 +16668,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G528" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16694,7 +16694,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G529" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16720,7 +16720,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G530" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16746,7 +16746,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G531" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16772,7 +16772,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G532" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16798,7 +16798,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16824,7 +16824,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16850,7 +16850,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16876,7 +16876,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16902,7 +16902,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16928,7 +16928,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16954,7 +16954,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16980,7 +16980,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17006,7 +17006,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17032,7 +17032,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17058,7 +17058,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G543" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17084,7 +17084,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17110,7 +17110,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G545" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17136,7 +17136,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17162,7 +17162,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17188,7 +17188,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17214,7 +17214,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G549" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17240,7 +17240,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G550" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17266,7 +17266,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17292,7 +17292,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17318,7 +17318,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17344,7 +17344,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17370,7 +17370,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17396,7 +17396,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17422,7 +17422,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17448,7 +17448,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17474,7 +17474,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17500,7 +17500,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17526,7 +17526,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17552,7 +17552,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G562" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17578,7 +17578,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G563" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17604,7 +17604,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G564" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17630,7 +17630,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17656,7 +17656,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17682,7 +17682,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17708,7 +17708,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G568" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17734,7 +17734,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G569" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17760,7 +17760,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17786,7 +17786,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G571" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17812,7 +17812,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17838,7 +17838,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17864,7 +17864,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17890,7 +17890,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17916,7 +17916,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17942,7 +17942,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17968,7 +17968,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17994,7 +17994,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G579" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18020,7 +18020,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G580" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18046,7 +18046,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18072,7 +18072,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18098,7 +18098,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18124,7 +18124,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18150,7 +18150,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18176,7 +18176,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18202,7 +18202,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18228,7 +18228,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G588" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18254,7 +18254,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18280,7 +18280,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G590" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18306,7 +18306,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18332,7 +18332,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18358,7 +18358,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18384,7 +18384,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G594" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18410,7 +18410,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G595" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18436,7 +18436,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G596" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18462,7 +18462,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18488,7 +18488,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18514,7 +18514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G599" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18540,7 +18540,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18566,7 +18566,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G601" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18592,7 +18592,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G602" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18618,7 +18618,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G603" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18644,7 +18644,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G604" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18670,7 +18670,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G605" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18696,7 +18696,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18722,7 +18722,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G607" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18748,7 +18748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18774,7 +18774,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18800,7 +18800,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18826,7 +18826,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G611" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18852,7 +18852,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18878,7 +18878,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18982,7 +18982,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G617" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G618" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19034,7 +19034,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G619" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19112,7 +19112,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19138,7 +19138,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19164,7 +19164,7 @@
         <v>2</v>
       </c>
       <c r="G624" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19190,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="G625" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19216,7 +19216,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19242,7 +19242,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19268,7 +19268,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19294,7 +19294,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19320,7 +19320,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19346,7 +19346,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19372,7 +19372,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G632" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19398,7 +19398,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G633" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19424,7 +19424,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19450,7 +19450,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19476,7 +19476,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19554,7 +19554,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19606,7 +19606,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19632,7 +19632,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G642" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19684,7 +19684,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19710,7 +19710,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G645" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19736,7 +19736,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19788,7 +19788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19814,7 +19814,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G650" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G651" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G652" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19918,7 +19918,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G653" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19970,7 +19970,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19996,7 +19996,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20022,7 +20022,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -68624,7 +68624,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6912847222</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>22920</v>
@@ -68645,6 +68645,32 @@
         <v>851</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6874421296</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>99</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>842</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504825115204</t>
+    <t xml:space="preserve">0.965504765510559</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994893133640289</t>
+    <t xml:space="preserve">0.994892835617065</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978406965732574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169371604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053814411163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938376426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487425327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9447181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473690986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900994420051575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878057539463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375712394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902427971363068</t>
+    <t xml:space="preserve">0.97840690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169312000275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053933620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938495635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94471800327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816160678864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005101680756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386274814606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900994479656219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375771999359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428150177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.899561047554016</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.898844122886658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86658900976181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466674804688</t>
+    <t xml:space="preserve">0.866588890552521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466734409332</t>
   </si>
   <si>
     <t xml:space="preserve">0.820715010166168</t>
@@ -125,16 +125,16 @@
     <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.723949551582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459837436676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800644993782043</t>
+    <t xml:space="preserve">0.723949432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124264717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800645112991333</t>
   </si>
   <si>
     <t xml:space="preserve">0.80279541015625</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">0.824298858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845802307128906</t>
+    <t xml:space="preserve">0.845802426338196</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804945766925812</t>
+    <t xml:space="preserve">0.804945886135101</t>
   </si>
   <si>
     <t xml:space="preserve">0.835050642490387</t>
@@ -158,46 +158,46 @@
     <t xml:space="preserve">0.834333896636963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838634610176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886659026145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83935135602951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819826126099</t>
+    <t xml:space="preserve">0.838634431362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88665896654129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88020783662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351296424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819706916809</t>
   </si>
   <si>
     <t xml:space="preserve">0.873040020465851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809382915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393290996552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977139472961</t>
+    <t xml:space="preserve">0.877340734004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895976960659027</t>
   </si>
   <si>
     <t xml:space="preserve">0.885225296020508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852970123291016</t>
+    <t xml:space="preserve">0.852970242500305</t>
   </si>
   <si>
     <t xml:space="preserve">0.870889663696289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867305934429169</t>
+    <t xml:space="preserve">0.867305815219879</t>
   </si>
   <si>
     <t xml:space="preserve">0.880924642086029</t>
@@ -206,73 +206,73 @@
     <t xml:space="preserve">0.86013799905777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830750048160553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704388141632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120360851288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536571979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421193599701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840785026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826449275016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799211502075195</t>
+    <t xml:space="preserve">0.830749988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704507350922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120480060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536691188812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784847736359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82644909620285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799211621284485</t>
   </si>
   <si>
     <t xml:space="preserve">0.789893388748169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.813547134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858589172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781291961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875929355621</t>
+    <t xml:space="preserve">0.813547194004059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292080879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875869750977</t>
   </si>
   <si>
     <t xml:space="preserve">0.809246420860291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817131102085114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917745113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431875228882</t>
+    <t xml:space="preserve">0.817130982875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917685508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431696414948</t>
   </si>
   <si>
     <t xml:space="preserve">0.814980626106262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812113642692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396777629852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928367137909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194161891937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026345729828</t>
+    <t xml:space="preserve">0.812113583087921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396837234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194042682648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026286125183</t>
   </si>
   <si>
     <t xml:space="preserve">0.803512275218964</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">0.815697491168976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756921470165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788453578949</t>
+    <t xml:space="preserve">0.756921410560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788632392883</t>
   </si>
   <si>
     <t xml:space="preserve">0.76265561580658</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">0.756204605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750470340251923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779141664505005</t>
+    <t xml:space="preserve">0.750470459461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77914160490036</t>
   </si>
   <si>
     <t xml:space="preserve">0.763372421264648</t>
@@ -305,37 +305,37 @@
     <t xml:space="preserve">0.767673075199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780575275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775557816028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627593994141</t>
+    <t xml:space="preserve">0.780575215816498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77555775642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627534389496</t>
   </si>
   <si>
     <t xml:space="preserve">0.784159183502197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.842218279838562</t>
+    <t xml:space="preserve">0.842218399047852</t>
   </si>
   <si>
     <t xml:space="preserve">0.851380407810211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872163832187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937121868134</t>
+    <t xml:space="preserve">0.872163951396942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937241077423</t>
   </si>
   <si>
     <t xml:space="preserve">0.861029982566833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861772239208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853607296943665</t>
+    <t xml:space="preserve">0.861772298812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607177734375</t>
   </si>
   <si>
     <t xml:space="preserve">0.856576442718506</t>
@@ -350,28 +350,28 @@
     <t xml:space="preserve">0.837277412414551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825401246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83059698343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858803033828735</t>
+    <t xml:space="preserve">0.825401186943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830597043037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858802974224091</t>
   </si>
   <si>
     <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844700217247009</t>
+    <t xml:space="preserve">0.844700157642365</t>
   </si>
   <si>
     <t xml:space="preserve">0.843957781791687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84618467092514</t>
+    <t xml:space="preserve">0.846184611320496</t>
   </si>
   <si>
     <t xml:space="preserve">0.83579295873642</t>
@@ -380,124 +380,124 @@
     <t xml:space="preserve">0.833566069602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838761866092682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816493928432465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809813439846039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916614055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810555815696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81797856092453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819463074207306</t>
+    <t xml:space="preserve">0.838761925697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81649386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809813499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916494846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810555756092072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801648736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817978501319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720757961273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819462954998016</t>
   </si>
   <si>
     <t xml:space="preserve">0.826143562793732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812782645225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808329045772552</t>
+    <t xml:space="preserve">0.81278270483017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808328986167908</t>
   </si>
   <si>
     <t xml:space="preserve">0.803133189678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805359959602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796452701091766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906300544739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514588356018</t>
+    <t xml:space="preserve">0.805359899997711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796452820301056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906360149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514647960663</t>
   </si>
   <si>
     <t xml:space="preserve">0.791999220848083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256785392761</t>
+    <t xml:space="preserve">0.791256844997406</t>
   </si>
   <si>
     <t xml:space="preserve">0.807586848735809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267218112946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617702960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79867947101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803185939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779380440711975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777153789997101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777896046638489</t>
+    <t xml:space="preserve">0.814267039299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617583751678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79867959022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794226050376892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803305149078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77938050031662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77715390920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777895987033844</t>
   </si>
   <si>
     <t xml:space="preserve">0.788287878036499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771957874298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838019609451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774926960468292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442506790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783834278583527</t>
+    <t xml:space="preserve">0.77195793390274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838019728660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844413280487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774927079677582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442447185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783834218978882</t>
   </si>
   <si>
     <t xml:space="preserve">0.765277564525604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778638362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091843128204</t>
+    <t xml:space="preserve">0.778638422489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091962337494</t>
   </si>
   <si>
     <t xml:space="preserve">0.787545502185822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78606104850769</t>
+    <t xml:space="preserve">0.786060988903046</t>
   </si>
   <si>
     <t xml:space="preserve">0.774184703826904</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102097034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452787399292</t>
+    <t xml:space="preserve">0.806102216243744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452608585358</t>
   </si>
   <si>
     <t xml:space="preserve">0.841731011867523</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">0.843215584754944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852865099906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442473888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153697490692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390661716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514436244965</t>
+    <t xml:space="preserve">0.852865159511566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390780925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514495849609</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225898265839</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823753356934</t>
+    <t xml:space="preserve">0.832823872566223</t>
   </si>
   <si>
     <t xml:space="preserve">0.834308326244354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827627897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860287845134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349553585052</t>
+    <t xml:space="preserve">0.827627956867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349613189697</t>
   </si>
   <si>
     <t xml:space="preserve">0.86771035194397</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.873648583889008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919668972492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380374908447</t>
+    <t xml:space="preserve">0.919669091701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380434513092</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">0.916700065135956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927091658115387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545436382294</t>
+    <t xml:space="preserve">0.927091836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545317173004</t>
   </si>
   <si>
     <t xml:space="preserve">0.915957748889923</t>
@@ -593,52 +593,52 @@
     <t xml:space="preserve">0.911504209041595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885607719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792773723602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768956661224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06960701942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07480311393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06886470317841</t>
+    <t xml:space="preserve">0.908535122871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885548114777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991669118404388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792654514313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768968582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06960690021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0748028755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06886494159698</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659676551819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05327725410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05179262161255</t>
+    <t xml:space="preserve">1.05327713489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
     <t xml:space="preserve">1.03249371051788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02432870864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03175139427185</t>
+    <t xml:space="preserve">1.02432858943939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03175151348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467931270599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00206065177917</t>
+    <t xml:space="preserve">1.00206089019775</t>
   </si>
   <si>
     <t xml:space="preserve">1.0228443145752</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">1.06812262535095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585444927216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06663799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449361801147</t>
+    <t xml:space="preserve">1.04585456848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06663811206818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449349880219</t>
   </si>
   <si>
     <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1193391084671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11711239814758</t>
+    <t xml:space="preserve">1.11933898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11711227893829</t>
   </si>
   <si>
     <t xml:space="preserve">1.1289883852005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14160692691803</t>
+    <t xml:space="preserve">1.14160704612732</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
@@ -683,94 +683,94 @@
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2314213514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21731817722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177183628082</t>
+    <t xml:space="preserve">1.23142147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2173182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177195549011</t>
   </si>
   <si>
     <t xml:space="preserve">1.21880280971527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23216366767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22845208644867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23513281345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22474098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286451816559</t>
+    <t xml:space="preserve">1.23216354846954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22845220565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2351325750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22474086284637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286463737488</t>
   </si>
   <si>
     <t xml:space="preserve">1.21360695362091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20098853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24700880050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779246330261</t>
+    <t xml:space="preserve">1.20098841190338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24700891971588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26779234409332</t>
   </si>
   <si>
     <t xml:space="preserve">1.24923574924469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25443172454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26036965847015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888514518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2692768573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521526813507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639040470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23958623409271</t>
+    <t xml:space="preserve">1.25443160533905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26036977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888526439667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26927709579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521502971649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34424614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.239586353302</t>
   </si>
   <si>
     <t xml:space="preserve">1.20321536064148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17426669597626</t>
+    <t xml:space="preserve">1.17426657676697</t>
   </si>
   <si>
     <t xml:space="preserve">1.17278230190277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055535316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17723596096039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17649340629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16387486457825</t>
+    <t xml:space="preserve">1.1653596162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055547237396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17723572254181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17649364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16387498378754</t>
   </si>
   <si>
     <t xml:space="preserve">1.16164827346802</t>
@@ -779,40 +779,40 @@
     <t xml:space="preserve">1.15051412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15348327159882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12824630737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14383375644684</t>
+    <t xml:space="preserve">1.15348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12824618816376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14383387565613</t>
   </si>
   <si>
     <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28412234783173</t>
+    <t xml:space="preserve">1.20247280597687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28412222862244</t>
   </si>
   <si>
     <t xml:space="preserve">1.28486466407776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31307089328766</t>
+    <t xml:space="preserve">1.31307077407837</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018396377563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.327916264534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35834908485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3435035943985</t>
+    <t xml:space="preserve">1.32791614532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35834896564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34350371360779</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311188220978</t>
@@ -821,22 +821,22 @@
     <t xml:space="preserve">1.35057294368744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34374046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32855689525604</t>
+    <t xml:space="preserve">1.34374034404755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32855701446533</t>
   </si>
   <si>
     <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512793064117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031149864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3665155172348</t>
+    <t xml:space="preserve">1.35512804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031137943268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36651563644409</t>
   </si>
   <si>
     <t xml:space="preserve">1.37410736083984</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">1.39080929756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39688277244568</t>
+    <t xml:space="preserve">1.39688265323639</t>
   </si>
   <si>
     <t xml:space="preserve">1.38169920444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36803412437439</t>
+    <t xml:space="preserve">1.3680340051651</t>
   </si>
   <si>
     <t xml:space="preserve">1.36727476119995</t>
@@ -863,37 +863,37 @@
     <t xml:space="preserve">1.39232754707336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38549506664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701343536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36879324913025</t>
+    <t xml:space="preserve">1.38549518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258899211884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701331615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
     <t xml:space="preserve">1.36120140552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35133218765259</t>
+    <t xml:space="preserve">1.3513320684433</t>
   </si>
   <si>
     <t xml:space="preserve">1.31565082073212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842599391937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34298133850098</t>
+    <t xml:space="preserve">1.33842611312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34298121929169</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363489151001</t>
+    <t xml:space="preserve">1.29363465309143</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
@@ -902,49 +902,49 @@
     <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32096517086029</t>
+    <t xml:space="preserve">1.32096493244171</t>
   </si>
   <si>
     <t xml:space="preserve">1.3141325712204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36955225467682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536440372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37562584877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40143764019012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625419139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397669792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38929104804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38321757316589</t>
+    <t xml:space="preserve">1.3695524930954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536428451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37562572956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40143775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625407218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397657871246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38929092884064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3832174539566</t>
   </si>
   <si>
     <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473570346832</t>
+    <t xml:space="preserve">1.38473582267761</t>
   </si>
   <si>
     <t xml:space="preserve">1.34829545021057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42497205734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45230233669281</t>
+    <t xml:space="preserve">1.42497217655182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164902210236</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">1.47735512256622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55630934238434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51835072040558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568099975586</t>
+    <t xml:space="preserve">1.55630946159363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51835083961487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568111896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.51379561424255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52594244480133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51075887680054</t>
+    <t xml:space="preserve">1.52594232559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51075899600983</t>
   </si>
   <si>
     <t xml:space="preserve">1.52897918224335</t>
@@ -977,40 +977,40 @@
     <t xml:space="preserve">1.50316715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53049767017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53353428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746069431305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51607298851013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47887349128723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43484127521515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40599274635315</t>
+    <t xml:space="preserve">1.53049755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53353416919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746093273163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51607322692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47887361049652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43484151363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40599262714386</t>
   </si>
   <si>
     <t xml:space="preserve">1.38777244091034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33614873886108</t>
+    <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
     <t xml:space="preserve">1.2905980348587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29970812797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30502235889435</t>
+    <t xml:space="preserve">1.29970824718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30502247810364</t>
   </si>
   <si>
     <t xml:space="preserve">1.42573130130768</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48722457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269456386566</t>
+    <t xml:space="preserve">1.48722445964813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269444465637</t>
   </si>
   <si>
     <t xml:space="preserve">1.41434371471405</t>
@@ -1037,49 +1037,49 @@
     <t xml:space="preserve">1.41738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40447449684143</t>
+    <t xml:space="preserve">1.40447437763214</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182986736298</t>
+    <t xml:space="preserve">1.40371525287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182998657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.36271977424622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36423826217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35209131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36499726772308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36575639247894</t>
+    <t xml:space="preserve">1.36423814296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35209143161774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36499738693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36575651168823</t>
   </si>
   <si>
     <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4272495508194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48039209842682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49937129020691</t>
+    <t xml:space="preserve">1.42724967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48039186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
     <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49177956581116</t>
+    <t xml:space="preserve">1.49177968502045</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
@@ -1091,40 +1091,40 @@
     <t xml:space="preserve">1.43863713741302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37790334224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33235287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30957746505737</t>
+    <t xml:space="preserve">1.37790322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33235275745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30957758426666</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476115226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753632545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337332725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161872386932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716930866241</t>
+    <t xml:space="preserve">1.32476103305817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753620624542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337320804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161860466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716918945312</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206610202789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41965782642365</t>
+    <t xml:space="preserve">1.41206622123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
     <t xml:space="preserve">1.44243311882019</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">1.45382082462311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4690043926239</t>
+    <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418784141541</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42345368862152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002496242523</t>
+    <t xml:space="preserve">1.42345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586220264435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002484321594</t>
   </si>
   <si>
     <t xml:space="preserve">1.46141254901886</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51551616191864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768411159515</t>
+    <t xml:space="preserve">1.51551628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768423080444</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726459503174</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48027157783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46069133281708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44894337654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46460747718811</t>
+    <t xml:space="preserve">1.46852362155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48027193546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46069145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44894325733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677542686462</t>
@@ -1205,61 +1205,61 @@
     <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47635579109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44111132621765</t>
+    <t xml:space="preserve">1.47635555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44111120700836</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278998851776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40978264808655</t>
+    <t xml:space="preserve">1.36278986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40978252887726</t>
   </si>
   <si>
     <t xml:space="preserve">1.42153084278107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936301231384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43327915668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4528591632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39803445339203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39411842823029</t>
+    <t xml:space="preserve">1.42936289310455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43327903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45285940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39803457260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.394118309021</t>
   </si>
   <si>
     <t xml:space="preserve">1.34712564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.32362926006317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488840579987</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30796492099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146154880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055250644684</t>
+    <t xml:space="preserve">1.30796504020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30404877662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146142959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055262565613</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962167263031</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">1.31188094615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34320950508118</t>
+    <t xml:space="preserve">1.34320962429047</t>
   </si>
   <si>
     <t xml:space="preserve">1.35104167461395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38628625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40586650371552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37062191963196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37845420837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32754528522491</t>
+    <t xml:space="preserve">1.38628613948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4058666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37062215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37845408916473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3275454044342</t>
   </si>
   <si>
     <t xml:space="preserve">1.28838467597961</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230058193207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28446853160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3157970905304</t>
+    <t xml:space="preserve">1.29230082035065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28446865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31579720973969</t>
   </si>
   <si>
     <t xml:space="preserve">1.31971311569214</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">1.38237023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41761481761932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48810386657715</t>
+    <t xml:space="preserve">1.41761469841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48810398578644</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593591690063</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">1.52334856987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53509664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55076098442078</t>
+    <t xml:space="preserve">1.53509676456451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55076086521149</t>
   </si>
   <si>
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992159366608</t>
+    <t xml:space="preserve">1.58992147445679</t>
   </si>
   <si>
     <t xml:space="preserve">1.62124991416931</t>
@@ -1355,34 +1355,34 @@
     <t xml:space="preserve">1.60558569431305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61341786384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5820894241333</t>
+    <t xml:space="preserve">1.61341798305511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208930492401</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908220291138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64474642276764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63691425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65257835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66041052341461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66824281215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740342140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439631938934</t>
+    <t xml:space="preserve">1.64474630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63691413402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65257847309113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66824293136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740354061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439608097076</t>
   </si>
   <si>
     <t xml:space="preserve">1.74656403064728</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">1.80138885974884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838163852692</t>
+    <t xml:space="preserve">1.84838151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006042003632</t>
@@ -1403,49 +1403,49 @@
     <t xml:space="preserve">1.7778924703598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82488524913788</t>
+    <t xml:space="preserve">1.82488548755646</t>
   </si>
   <si>
     <t xml:space="preserve">1.80922102928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83271729946136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054958820343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971043586731</t>
+    <t xml:space="preserve">1.83271718025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971031665802</t>
   </si>
   <si>
     <t xml:space="preserve">1.87187826633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86404609680176</t>
+    <t xml:space="preserve">1.86404597759247</t>
   </si>
   <si>
     <t xml:space="preserve">1.85621380805969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79355669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94236731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95803153514862</t>
+    <t xml:space="preserve">1.79355680942535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94236719608307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
     <t xml:space="preserve">1.97369587421417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99719214439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96586346626282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453514575958</t>
+    <t xml:space="preserve">1.99719178676605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96586334705353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453526496887</t>
   </si>
   <si>
     <t xml:space="preserve">1.91887080669403</t>
@@ -1454,43 +1454,43 @@
     <t xml:space="preserve">1.92670297622681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98178470134735</t>
+    <t xml:space="preserve">1.98178458213806</t>
   </si>
   <si>
     <t xml:space="preserve">1.94942891597748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96560668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662875652313</t>
+    <t xml:space="preserve">1.9656069278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662863731384</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191742420197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573953151703</t>
+    <t xml:space="preserve">1.76338398456573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573941230774</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8604508638382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809519767761</t>
+    <t xml:space="preserve">1.82000625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86045074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809507846832</t>
   </si>
   <si>
     <t xml:space="preserve">1.85236191749573</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">1.83618402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7714729309082</t>
+    <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
     <t xml:space="preserve">1.90898430347443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94134032726288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93325114250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.997962474823</t>
+    <t xml:space="preserve">1.94134020805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93325126171112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751774311066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7472060918808</t>
+    <t xml:space="preserve">1.92516219615936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74720621109009</t>
   </si>
   <si>
     <t xml:space="preserve">1.75529503822327</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58542764186859</t>
+    <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
     <t xml:space="preserve">1.56116080284119</t>
@@ -1562,19 +1562,19 @@
     <t xml:space="preserve">1.4964497089386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41556036472321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34276020526886</t>
+    <t xml:space="preserve">1.40747141838074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4155604839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34276032447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.31849336624146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29827105998993</t>
+    <t xml:space="preserve">1.29827117919922</t>
   </si>
   <si>
     <t xml:space="preserve">1.17289304733276</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22951543331146</t>
+    <t xml:space="preserve">1.22951531410217</t>
   </si>
   <si>
     <t xml:space="preserve">1.15267050266266</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">1.1648041009903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03538131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07178151607513</t>
+    <t xml:space="preserve">1.03538143634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07178163528442</t>
   </si>
   <si>
     <t xml:space="preserve">1.15671503543854</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">1.17693746089935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09604811668396</t>
+    <t xml:space="preserve">1.09604823589325</t>
   </si>
   <si>
     <t xml:space="preserve">1.18502628803253</t>
@@ -1622,22 +1622,22 @@
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13649272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24569320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26187109947205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30231547355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995980739594</t>
+    <t xml:space="preserve">1.1364928483963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075956821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24569308757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26187098026276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30231559276581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995992660522</t>
   </si>
   <si>
     <t xml:space="preserve">1.25378203392029</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">1.18098187446594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21333754062653</t>
+    <t xml:space="preserve">1.21333742141724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031483650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14458167552948</t>
+    <t xml:space="preserve">1.12031507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14458155632019</t>
   </si>
   <si>
     <t xml:space="preserve">1.11627054214478</t>
@@ -1670,34 +1670,34 @@
     <t xml:space="preserve">1.14862620830536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10009264945984</t>
+    <t xml:space="preserve">1.10009253025055</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840378284454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23760426044464</t>
+    <t xml:space="preserve">1.12840390205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24164879322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23760414123535</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16884851455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20929300785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2497376203537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22142648696899</t>
+    <t xml:space="preserve">1.1688483953476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20929312705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24973750114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
     <t xml:space="preserve">1.1122260093689</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">1.05964803695679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09200370311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08391487598419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07987034320831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0556036233902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0232480764389</t>
+    <t xml:space="preserve">1.09200382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0839147567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0798704624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560350418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155920982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324795722961</t>
   </si>
   <si>
     <t xml:space="preserve">1.02729249000549</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">1.00302577018738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982803344726562</t>
+    <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
     <t xml:space="preserve">0.954492151737213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970670163631439</t>
+    <t xml:space="preserve">0.970670104026794</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
@@ -1751,67 +1751,67 @@
     <t xml:space="preserve">0.986847937107086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962581157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966625571250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758931159973</t>
+    <t xml:space="preserve">0.962581098079681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96662563085556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978758871555328</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10413706302643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23355984687805</t>
+    <t xml:space="preserve">1.10413730144501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23355972766876</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120418071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29422676563263</t>
+    <t xml:space="preserve">1.20120406150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
     <t xml:space="preserve">1.31040453910828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32253789901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32658231258392</t>
+    <t xml:space="preserve">1.32253777980804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32658243179321</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3346711397171</t>
+    <t xml:space="preserve">1.33467125892639</t>
   </si>
   <si>
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46813833713531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51262736320496</t>
+    <t xml:space="preserve">1.4681384563446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51262748241425</t>
   </si>
   <si>
     <t xml:space="preserve">1.55307197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57733881473541</t>
+    <t xml:space="preserve">1.57733869552612</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498302936554</t>
+    <t xml:space="preserve">1.54498291015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.52071642875671</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284955024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51667177677155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53689420223236</t>
+    <t xml:space="preserve">1.53284966945648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51667189598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53689432144165</t>
   </si>
   <si>
     <t xml:space="preserve">1.581383228302</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">1.57329440116882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56520521640778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836088180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50049388408661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54902744293213</t>
+    <t xml:space="preserve">1.56520545482635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836064338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.5247608423233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5288051366806</t>
+    <t xml:space="preserve">1.52880525588989</t>
   </si>
   <si>
     <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70676124095917</t>
+    <t xml:space="preserve">1.70676136016846</t>
   </si>
   <si>
     <t xml:space="preserve">1.69867241382599</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249464035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67440569400787</t>
+    <t xml:space="preserve">1.68249452114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67440581321716</t>
   </si>
   <si>
     <t xml:space="preserve">1.72293937206268</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.62587225437164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61778330802917</t>
+    <t xml:space="preserve">1.61778342723846</t>
   </si>
   <si>
     <t xml:space="preserve">1.71485018730164</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">1.48431622982025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49240529537201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47218298912048</t>
+    <t xml:space="preserve">1.49240517616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47218286991119</t>
   </si>
   <si>
     <t xml:space="preserve">1.59351658821106</t>
@@ -1922,46 +1922,46 @@
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33062672615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893797874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44791603088379</t>
+    <t xml:space="preserve">1.3306268453598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3589380979538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44791615009308</t>
   </si>
   <si>
     <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47622740268707</t>
+    <t xml:space="preserve">1.47622728347778</t>
   </si>
   <si>
     <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59756100177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.609694480896</t>
+    <t xml:space="preserve">1.59756112098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60969436168671</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72660839557648</t>
+    <t xml:space="preserve">1.72660851478577</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70976340770721</t>
+    <t xml:space="preserve">1.7097635269165</t>
   </si>
   <si>
     <t xml:space="preserve">1.69291853904724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68028473854065</t>
+    <t xml:space="preserve">1.68028485774994</t>
   </si>
   <si>
     <t xml:space="preserve">1.68449604511261</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">1.6465950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343975067139</t>
+    <t xml:space="preserve">1.66343998908997</t>
   </si>
   <si>
     <t xml:space="preserve">1.63817250728607</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64238369464874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61711621284485</t>
+    <t xml:space="preserve">1.64238357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61711609363556</t>
   </si>
   <si>
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54973649978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58342623710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500374317169</t>
+    <t xml:space="preserve">1.54973638057709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58342635631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500386238098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">1.59605991840363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56658124923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54552519321442</t>
+    <t xml:space="preserve">1.56658136844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54552507400513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815887451172</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289151191711</t>
+    <t xml:space="preserve">1.53289139270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">1.47393405437469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43182158470154</t>
+    <t xml:space="preserve">1.43182170391083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38970923423767</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">1.44024407863617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4107654094696</t>
+    <t xml:space="preserve">1.41076529026031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40655422210693</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">1.40234291553497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4613002538681</t>
+    <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
     <t xml:space="preserve">1.49499022960663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49077892303467</t>
+    <t xml:space="preserve">1.49077904224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.486567735672</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869371891022</t>
+    <t xml:space="preserve">1.60869359970093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60027122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62553870677948</t>
+    <t xml:space="preserve">1.60027134418488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62553858757019</t>
   </si>
   <si>
     <t xml:space="preserve">1.62132740020752</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">1.71818590164185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186224460602</t>
+    <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
     <t xml:space="preserve">1.61290490627289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59184873104095</t>
+    <t xml:space="preserve">1.59184885025024</t>
   </si>
   <si>
     <t xml:space="preserve">1.51604640483856</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">1.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48235654830933</t>
+    <t xml:space="preserve">1.48235642910004</t>
   </si>
   <si>
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025771141052</t>
+    <t xml:space="preserve">1.52025759220123</t>
   </si>
   <si>
     <t xml:space="preserve">1.57079255580902</t>
@@ -2162,37 +2162,37 @@
     <t xml:space="preserve">1.84452319145203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8393189907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86584758758545</t>
+    <t xml:space="preserve">1.83931910991669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86584770679474</t>
   </si>
   <si>
     <t xml:space="preserve">1.81279039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79510462284088</t>
+    <t xml:space="preserve">1.79510474205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.77741897106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92774796485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85700476169586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89237642288208</t>
+    <t xml:space="preserve">1.9277480840683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85700488090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89237654209137</t>
   </si>
   <si>
     <t xml:space="preserve">1.91890513896942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91006219387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93659090995789</t>
+    <t xml:space="preserve">1.91006231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365907907486</t>
   </si>
   <si>
     <t xml:space="preserve">1.84816193580627</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">1.99849081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05154800415039</t>
+    <t xml:space="preserve">2.05154824256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.03386235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0869197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06923413276672</t>
+    <t xml:space="preserve">2.08691954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06923389434814</t>
   </si>
   <si>
     <t xml:space="preserve">2.04270529747009</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">2.01617670059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06039094924927</t>
+    <t xml:space="preserve">2.06039118766785</t>
   </si>
   <si>
     <t xml:space="preserve">2.00733375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353371620178</t>
+    <t xml:space="preserve">1.88353359699249</t>
   </si>
   <si>
     <t xml:space="preserve">2.07807683944702</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.87469053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95427668094635</t>
+    <t xml:space="preserve">1.95427656173706</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047616481781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163321971893</t>
+    <t xml:space="preserve">1.82163333892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.64919722080231</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.68899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69783306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67130434513092</t>
+    <t xml:space="preserve">1.69783294200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67130446434021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66246151924133</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.64035427570343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60940420627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62709009647369</t>
+    <t xml:space="preserve">1.60940432548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.59613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59171831607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60498285293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824703216553</t>
+    <t xml:space="preserve">1.59171843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6049827337265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824715137482</t>
   </si>
   <si>
     <t xml:space="preserve">1.60056126117706</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.71551883220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73762595653534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7243617773056</t>
+    <t xml:space="preserve">1.73762607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72436165809631</t>
   </si>
   <si>
     <t xml:space="preserve">1.75973320007324</t>
@@ -68650,7 +68650,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6874421296</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>99</v>
@@ -68671,6 +68671,32 @@
         <v>842</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6874421296</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>480841</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>863</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504765510559</t>
+    <t xml:space="preserve">0.965504825115204</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
@@ -50,34 +50,34 @@
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97840690612793</t>
+    <t xml:space="preserve">0.978406846523285</t>
   </si>
   <si>
     <t xml:space="preserve">0.951169312000275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959053933620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94471800327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386274814606</t>
+    <t xml:space="preserve">0.959053814411163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938376426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487425327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816220283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473631381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
   </si>
   <si>
     <t xml:space="preserve">0.900994479656219</t>
@@ -86,52 +86,52 @@
     <t xml:space="preserve">0.878057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887375771999359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899561047554016</t>
+    <t xml:space="preserve">0.887375712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428090572357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560868740082</t>
   </si>
   <si>
     <t xml:space="preserve">0.871606528759003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866588890552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466734409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820715010166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807812929153442</t>
+    <t xml:space="preserve">0.898844182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86658900976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466674804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820714950561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807812869548798</t>
   </si>
   <si>
     <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117308139801</t>
+    <t xml:space="preserve">0.713197767734528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117248535156</t>
   </si>
   <si>
     <t xml:space="preserve">0.704237997531891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.723949432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124264717102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459777832031</t>
+    <t xml:space="preserve">0.723949372768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124145507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459897041321</t>
   </si>
   <si>
     <t xml:space="preserve">0.800645112991333</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">0.824298858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845802426338196</t>
+    <t xml:space="preserve">0.845802366733551</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
@@ -155,85 +155,85 @@
     <t xml:space="preserve">0.835050642490387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634431362152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88665896654129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88020783662796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351296424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819706916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873040020465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340734004974</t>
+    <t xml:space="preserve">0.834333837032318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634610176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886658847332001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88020795583725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351236820221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819885730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87304013967514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340793609619</t>
   </si>
   <si>
     <t xml:space="preserve">0.888809204101562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892393112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895976960659027</t>
+    <t xml:space="preserve">0.892393290996552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977079868317</t>
   </si>
   <si>
     <t xml:space="preserve">0.885225296020508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852970242500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305815219879</t>
+    <t xml:space="preserve">0.85297030210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889604091644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305874824524</t>
   </si>
   <si>
     <t xml:space="preserve">0.880924642086029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86013799905777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830749988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704507350922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120480060577</t>
+    <t xml:space="preserve">0.860138058662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704447746277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120539665222</t>
   </si>
   <si>
     <t xml:space="preserve">0.851536691188812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859421253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82644909620285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799211621284485</t>
+    <t xml:space="preserve">0.859421193599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784907341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79921156167984</t>
   </si>
   <si>
     <t xml:space="preserve">0.789893388748169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.813547194004059</t>
+    <t xml:space="preserve">0.813547253608704</t>
   </si>
   <si>
     <t xml:space="preserve">0.779858469963074</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">0.781292080879211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246420860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817130982875824</t>
+    <t xml:space="preserve">0.784875929355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80924654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131102085114</t>
   </si>
   <si>
     <t xml:space="preserve">0.837917685508728</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">0.821431696414948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814980626106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113583087921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928426742554</t>
+    <t xml:space="preserve">0.814980804920197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113523483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396777629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928307533264</t>
   </si>
   <si>
     <t xml:space="preserve">0.794194042682648</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">0.787026286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803512275218964</t>
+    <t xml:space="preserve">0.803512156009674</t>
   </si>
   <si>
     <t xml:space="preserve">0.815697491168976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756921410560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76265561580658</t>
+    <t xml:space="preserve">0.756921470165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655675411224</t>
   </si>
   <si>
     <t xml:space="preserve">0.756204605102539</t>
@@ -296,49 +296,49 @@
     <t xml:space="preserve">0.750470459461212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77914160490036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673075199127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77555775642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627534389496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159183502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380407810211</t>
+    <t xml:space="preserve">0.779141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372540473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673194408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575275421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557816028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627653598785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159243106842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218458652496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380467414856</t>
   </si>
   <si>
     <t xml:space="preserve">0.872163951396942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869937241077423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029982566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853607177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576442718506</t>
+    <t xml:space="preserve">0.869937300682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029922962189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607356548309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576383113861</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741325378418</t>
@@ -347,43 +347,43 @@
     <t xml:space="preserve">0.855834186077118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837277412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401186943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830597043037415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858802974224091</t>
+    <t xml:space="preserve">0.837277352809906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401246547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112470149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83059698343277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85880309343338</t>
   </si>
   <si>
     <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844700157642365</t>
+    <t xml:space="preserve">0.844700038433075</t>
   </si>
   <si>
     <t xml:space="preserve">0.843957781791687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846184611320496</t>
+    <t xml:space="preserve">0.84618467092514</t>
   </si>
   <si>
     <t xml:space="preserve">0.83579295873642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833566069602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838761925697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81649386882782</t>
+    <t xml:space="preserve">0.833566129207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761985301971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816493988037109</t>
   </si>
   <si>
     <t xml:space="preserve">0.809813499450684</t>
@@ -392,46 +392,46 @@
     <t xml:space="preserve">0.823916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810555756092072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801648736000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817978501319885</t>
+    <t xml:space="preserve">0.810555875301361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801648616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81797856092453</t>
   </si>
   <si>
     <t xml:space="preserve">0.818720757961273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819462954998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143562793732</t>
+    <t xml:space="preserve">0.819463014602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143443584442</t>
   </si>
   <si>
     <t xml:space="preserve">0.81278270483017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808328986167908</t>
+    <t xml:space="preserve">0.808329045772552</t>
   </si>
   <si>
     <t xml:space="preserve">0.803133189678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805359899997711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796452820301056</t>
+    <t xml:space="preserve">0.805360019207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796452641487122</t>
   </si>
   <si>
     <t xml:space="preserve">0.800906360149384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790514647960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791999220848083</t>
+    <t xml:space="preserve">0.790514707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
     <t xml:space="preserve">0.791256844997406</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">0.814267039299011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804617583751678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79867959022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794226050376892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803305149078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77938050031662</t>
+    <t xml:space="preserve">0.804617702960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798679530620575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225990772247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803185939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779380559921265</t>
   </si>
   <si>
     <t xml:space="preserve">0.77715390920639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777895987033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788287878036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77195793390274</t>
+    <t xml:space="preserve">0.777896046638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788287818431854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
     <t xml:space="preserve">0.838019728660583</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">0.806844413280487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774927079677582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773442447185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783834218978882</t>
+    <t xml:space="preserve">0.774927020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773442506790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783834159374237</t>
   </si>
   <si>
     <t xml:space="preserve">0.765277564525604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778638422489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783091962337494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545502185822</t>
+    <t xml:space="preserve">0.778638303279877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783091902732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545561790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.786060988903046</t>
@@ -506,46 +506,46 @@
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102216243744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452608585358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841731011867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411440849304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215584754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865159511566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442414283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849153757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874390780925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514495849609</t>
+    <t xml:space="preserve">0.806102156639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452727794647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841730952262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411500453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215644359589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865040302277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442354679108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849153697490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874390721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514436244965</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85509181022644</t>
+    <t xml:space="preserve">0.855091869831085</t>
   </si>
   <si>
     <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832823872566223</t>
+    <t xml:space="preserve">0.832823812961578</t>
   </si>
   <si>
     <t xml:space="preserve">0.834308326244354</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">0.827627956867218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860287666320801</t>
+    <t xml:space="preserve">0.860287725925446</t>
   </si>
   <si>
     <t xml:space="preserve">0.854349613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86771035194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880328834056854</t>
+    <t xml:space="preserve">0.867710411548615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880328893661499</t>
   </si>
   <si>
     <t xml:space="preserve">0.873648583889008</t>
@@ -578,43 +578,43 @@
     <t xml:space="preserve">0.913730978965759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916700065135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091836929321</t>
+    <t xml:space="preserve">0.916700005531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091658115387</t>
   </si>
   <si>
     <t xml:space="preserve">0.931545317173004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915957748889923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504209041595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885548114777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991669118404388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792654514313</t>
+    <t xml:space="preserve">0.915957808494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504089832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885667324066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991669058799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792773723602</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768968582153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06960690021515</t>
+    <t xml:space="preserve">1.06960701942444</t>
   </si>
   <si>
     <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06886494159698</t>
+    <t xml:space="preserve">1.0688648223877</t>
   </si>
   <si>
     <t xml:space="preserve">1.04659676551819</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">1.03249371051788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02432858943939</t>
+    <t xml:space="preserve">1.02432882785797</t>
   </si>
   <si>
     <t xml:space="preserve">1.03175151348114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467931270599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00206089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0228443145752</t>
+    <t xml:space="preserve">1.0146791934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00206065177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02284419536591</t>
   </si>
   <si>
     <t xml:space="preserve">1.03026700019836</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">1.05921542644501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06812262535095</t>
+    <t xml:space="preserve">1.06812274456024</t>
   </si>
   <si>
     <t xml:space="preserve">1.04585456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06663811206818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449349880219</t>
+    <t xml:space="preserve">1.06663799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449373722076</t>
   </si>
   <si>
     <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11711227893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1289883852005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160704612732</t>
+    <t xml:space="preserve">1.1193391084671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12898850440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">1.23142147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2173182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177195549011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880280971527</t>
+    <t xml:space="preserve">1.21731817722321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177171707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880292892456</t>
   </si>
   <si>
     <t xml:space="preserve">1.23216354846954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22845220565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2351325750351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22474086284637</t>
+    <t xml:space="preserve">1.22845232486725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23513269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22474110126495</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286463737488</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">1.20098841190338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700891971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26779234409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923574924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443160533905</t>
+    <t xml:space="preserve">1.24700880050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26779246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923586845398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
     <t xml:space="preserve">1.26036977767944</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">1.26927709579468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34424614906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.239586353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20321536064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17426657676697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17278230190277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1653596162796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055547237396</t>
+    <t xml:space="preserve">1.27521526813507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639040470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34424602985382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23958623409271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20321524143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17426693439484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17278218269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16535949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055535316467</t>
   </si>
   <si>
     <t xml:space="preserve">1.17723572254181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17649364471436</t>
+    <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.16387498378754</t>
@@ -785,46 +785,46 @@
     <t xml:space="preserve">1.12824618816376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14383387565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1891120672226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20247280597687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28412222862244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28486466407776</t>
+    <t xml:space="preserve">1.14383399486542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18911218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20247292518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28412234783173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28486454486847</t>
   </si>
   <si>
     <t xml:space="preserve">1.31307077407837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018396377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32791614532471</t>
+    <t xml:space="preserve">1.35018408298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32791602611542</t>
   </si>
   <si>
     <t xml:space="preserve">1.35834896564484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34350371360779</t>
+    <t xml:space="preserve">1.3435035943985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057294368744</t>
+    <t xml:space="preserve">1.35057282447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32855701446533</t>
+    <t xml:space="preserve">1.32855689525604</t>
   </si>
   <si>
     <t xml:space="preserve">1.35816478729248</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">1.35512804985046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37031137943268</t>
+    <t xml:space="preserve">1.37031149864197</t>
   </si>
   <si>
     <t xml:space="preserve">1.36651563644409</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39080929756165</t>
+    <t xml:space="preserve">1.39080941677094</t>
   </si>
   <si>
     <t xml:space="preserve">1.39688265323639</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">1.38169920444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3680340051651</t>
+    <t xml:space="preserve">1.36803412437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.36727476119995</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">1.39232754707336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38549518585205</t>
+    <t xml:space="preserve">1.38549494743347</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258899211884</t>
@@ -875,43 +875,43 @@
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120140552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3513320684433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31565082073212</t>
+    <t xml:space="preserve">1.3612015247345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35133218765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31565093994141</t>
   </si>
   <si>
     <t xml:space="preserve">1.33842611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34298121929169</t>
+    <t xml:space="preserve">1.34298133850098</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868755817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29363465309143</t>
+    <t xml:space="preserve">1.29363477230072</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818987846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30122649669647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32096493244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3141325712204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3695524930954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536428451538</t>
+    <t xml:space="preserve">1.30122661590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.320965051651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31413245201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36955237388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536440372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562572956085</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">1.38397657871246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929092884064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3832174539566</t>
+    <t xml:space="preserve">1.38929104804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38321757316589</t>
   </si>
   <si>
     <t xml:space="preserve">1.37866246700287</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">1.38473582267761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34829545021057</t>
+    <t xml:space="preserve">1.34829533100128</t>
   </si>
   <si>
     <t xml:space="preserve">1.42497217655182</t>
@@ -947,31 +947,31 @@
     <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50164902210236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735512256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630946159363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51835083961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568111896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379561424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594232559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51075899600983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52897918224335</t>
+    <t xml:space="preserve">1.50164890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630934238434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51835060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568088054657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379573345184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594244480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51075887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52897906303406</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316715240479</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">1.52746093273163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51607322692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47887361049652</t>
+    <t xml:space="preserve">1.51607310771942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47887349128723</t>
   </si>
   <si>
     <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40599262714386</t>
+    <t xml:space="preserve">1.40599286556244</t>
   </si>
   <si>
     <t xml:space="preserve">1.38777244091034</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2905980348587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29970824718475</t>
+    <t xml:space="preserve">1.29059815406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29970812797546</t>
   </si>
   <si>
     <t xml:space="preserve">1.30502247810364</t>
@@ -1022,31 +1022,31 @@
     <t xml:space="preserve">1.47659611701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48798370361328</t>
+    <t xml:space="preserve">1.48798382282257</t>
   </si>
   <si>
     <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269444465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41434371471405</t>
+    <t xml:space="preserve">1.42269456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41434383392334</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40447437763214</t>
+    <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371525287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182998657227</t>
+    <t xml:space="preserve">1.40371513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182986736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.36271977424622</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35209143161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36499738693237</t>
+    <t xml:space="preserve">1.35209131240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36499714851379</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575651168823</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49557542800903</t>
+    <t xml:space="preserve">1.49557530879974</t>
   </si>
   <si>
     <t xml:space="preserve">1.49177968502045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50696313381195</t>
+    <t xml:space="preserve">1.50696325302124</t>
   </si>
   <si>
     <t xml:space="preserve">1.45761656761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43863713741302</t>
+    <t xml:space="preserve">1.43863725662231</t>
   </si>
   <si>
     <t xml:space="preserve">1.37790322303772</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476103305817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753620624542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337320804596</t>
+    <t xml:space="preserve">1.32476091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753632545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337332725525</t>
   </si>
   <si>
     <t xml:space="preserve">1.27161860466003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31716918945312</t>
+    <t xml:space="preserve">1.31716930866241</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206622123718</t>
+    <t xml:space="preserve">1.41206610202789</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
@@ -1136,43 +1136,43 @@
     <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
+    <t xml:space="preserve">1.48418772220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520841121674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002496242523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46141242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54112601280212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47280025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5145548582077</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.48418784141541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46520841121674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42345380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586220264435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002484321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46141254901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54112601280212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47280025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5145548582077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418772220612</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.51551628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50768423080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52726459503174</t>
+    <t xml:space="preserve">1.50768411159515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52726447582245</t>
   </si>
   <si>
     <t xml:space="preserve">1.51943242549896</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">1.46852362155914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48027193546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46069145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44894325733185</t>
+    <t xml:space="preserve">1.48027181625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46069157123566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
     <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677542686462</t>
+    <t xml:space="preserve">1.45677530765533</t>
   </si>
   <si>
     <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47635555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44111120700836</t>
+    <t xml:space="preserve">1.47635567188263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44111108779907</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40978252887726</t>
+    <t xml:space="preserve">1.40978264808655</t>
   </si>
   <si>
     <t xml:space="preserve">1.42153084278107</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">1.42936289310455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43327903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45285940170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39803457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.394118309021</t>
+    <t xml:space="preserve">1.43327915668488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45285928249359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39803445339203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39411842823029</t>
   </si>
   <si>
     <t xml:space="preserve">1.34712564945221</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">1.32362926006317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26488840579987</t>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">1.30796504020691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404877662659</t>
+    <t xml:space="preserve">1.30404889583588</t>
   </si>
   <si>
     <t xml:space="preserve">1.33146142959595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28055262565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2962167263031</t>
+    <t xml:space="preserve">1.28055250644684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29621684551239</t>
   </si>
   <si>
     <t xml:space="preserve">1.31188094615936</t>
@@ -1271,34 +1271,34 @@
     <t xml:space="preserve">1.34320962429047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35104167461395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38628613948822</t>
+    <t xml:space="preserve">1.35104179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38628625869751</t>
   </si>
   <si>
     <t xml:space="preserve">1.4058666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37062215805054</t>
+    <t xml:space="preserve">1.37062203884125</t>
   </si>
   <si>
     <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3275454044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838467597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195047855377</t>
+    <t xml:space="preserve">1.32754528522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838455677032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195035934448</t>
   </si>
   <si>
     <t xml:space="preserve">1.30013287067413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33537745475769</t>
+    <t xml:space="preserve">1.33537757396698</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230082035065</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">1.28446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31579720973969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31971311569214</t>
+    <t xml:space="preserve">1.3157970905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31971323490143</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810398578644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49593591690063</t>
+    <t xml:space="preserve">1.48810386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49593603610992</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985206127167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5116001367569</t>
+    <t xml:space="preserve">1.51160025596619</t>
   </si>
   <si>
     <t xml:space="preserve">1.52334856987</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">1.55076086521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59775364398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58992147445679</t>
+    <t xml:space="preserve">1.59775376319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58992159366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.62124991416931</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">1.61341798305511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58208930492401</t>
+    <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908220291138</t>
@@ -1367,13 +1367,13 @@
     <t xml:space="preserve">1.64474630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63691413402557</t>
+    <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
     <t xml:space="preserve">1.65257847309113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6604106426239</t>
+    <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
     <t xml:space="preserve">1.66824293136597</t>
@@ -1382,103 +1382,103 @@
     <t xml:space="preserve">1.70740354061127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75439608097076</t>
+    <t xml:space="preserve">1.75439620018005</t>
   </si>
   <si>
     <t xml:space="preserve">1.74656403064728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76222836971283</t>
+    <t xml:space="preserve">1.76222825050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.80138885974884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84838151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006042003632</t>
+    <t xml:space="preserve">1.84838140010834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006030082703</t>
   </si>
   <si>
     <t xml:space="preserve">1.7778924703598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82488548755646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922102928162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271718025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054946899414</t>
+    <t xml:space="preserve">1.82488536834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922091007233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271729946136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054958820343</t>
   </si>
   <si>
     <t xml:space="preserve">1.87971031665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87187826633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404597759247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85621380805969</t>
+    <t xml:space="preserve">1.87187802791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404585838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85621392726898</t>
   </si>
   <si>
     <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94236719608307</t>
+    <t xml:space="preserve">1.94236743450165</t>
   </si>
   <si>
     <t xml:space="preserve">1.95803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369587421417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99719178676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96586334705353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453526496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670297622681</t>
+    <t xml:space="preserve">1.97369563579559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99719202518463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9658637046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91887056827545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92670285701752</t>
   </si>
   <si>
     <t xml:space="preserve">1.98178458213806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94942891597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9656069278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662863731384</t>
+    <t xml:space="preserve">1.94942879676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662875652313</t>
   </si>
   <si>
     <t xml:space="preserve">1.77956163883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76338398456573</t>
+    <t xml:space="preserve">1.76338410377502</t>
   </si>
   <si>
     <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78765070438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573941230774</t>
+    <t xml:space="preserve">1.78765058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573953151703</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">1.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82809507846832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236191749573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8928062915802</t>
+    <t xml:space="preserve">1.82809495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236203670502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280641078949</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88471758365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.8847177028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
@@ -1517,37 +1517,37 @@
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94134020805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93325126171112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751774311066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99796235561371</t>
+    <t xml:space="preserve">1.90898418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9413400888443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93325114250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751798152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.997962474823</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516219615936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74720621109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75529503822327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631686687469</t>
+    <t xml:space="preserve">1.92516231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7472060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75529491901398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631674766541</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">1.56116080284119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4964497089386</t>
+    <t xml:space="preserve">1.49644958972931</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747141838074</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">1.4155604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34276032447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31849336624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29827117919922</t>
+    <t xml:space="preserve">1.34276020526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31849348545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29827105998993</t>
   </si>
   <si>
     <t xml:space="preserve">1.17289304733276</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">1.22951531410217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15267050266266</t>
+    <t xml:space="preserve">1.15267062187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.06773698329926</t>
@@ -1601,34 +1601,34 @@
     <t xml:space="preserve">1.03538143634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15671503543854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14053726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693746089935</t>
+    <t xml:space="preserve">1.07178151607513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15671515464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1405371427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693734169006</t>
   </si>
   <si>
     <t xml:space="preserve">1.09604823589325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18502628803253</t>
+    <t xml:space="preserve">1.18502616882324</t>
   </si>
   <si>
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364928483963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075956821442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24569308757782</t>
+    <t xml:space="preserve">1.13649272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075944900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24569320678711</t>
   </si>
   <si>
     <t xml:space="preserve">1.26187098026276</t>
@@ -1667,10 +1667,10 @@
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862620830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10009253025055</t>
+    <t xml:space="preserve">1.14862608909607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10009264945984</t>
   </si>
   <si>
     <t xml:space="preserve">1.12435936927795</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">1.12840390205383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24164879322052</t>
+    <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
     <t xml:space="preserve">1.23760414123535</t>
@@ -1688,106 +1688,106 @@
     <t xml:space="preserve">1.21738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1688483953476</t>
+    <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
     <t xml:space="preserve">1.20929312705994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24973750114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2214263677597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.2497376203537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22142624855042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582592964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05964803695679</t>
+    <t xml:space="preserve">1.07582604885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0596479177475</t>
   </si>
   <si>
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0839147567749</t>
+    <t xml:space="preserve">1.08391487598419</t>
   </si>
   <si>
     <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05560350418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155920982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02324795722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02729249000549</t>
+    <t xml:space="preserve">1.0556036233902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155909061432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324783802032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0272923707962</t>
   </si>
   <si>
     <t xml:space="preserve">1.00302577018738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982803463935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954492151737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970670104026794</t>
+    <t xml:space="preserve">0.982803344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954492092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97067004442215</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847937107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962581098079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96662563085556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758871555328</t>
+    <t xml:space="preserve">0.986847817897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962581157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966625571250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978758990764618</t>
   </si>
   <si>
     <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10413730144501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23355972766876</t>
+    <t xml:space="preserve">1.10413706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23355984687805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120406150818</t>
+    <t xml:space="preserve">1.20120418071747</t>
   </si>
   <si>
     <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31040453910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32253777980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32658243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34680461883545</t>
+    <t xml:space="preserve">1.31040441989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32253789901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32658231258392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34680449962616</t>
   </si>
   <si>
     <t xml:space="preserve">1.33467125892639</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4681384563446</t>
+    <t xml:space="preserve">1.46813833713531</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498291015625</t>
+    <t xml:space="preserve">1.54498302936554</t>
   </si>
   <si>
     <t xml:space="preserve">1.52071642875671</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">1.51667189598083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689432144165</t>
+    <t xml:space="preserve">1.53689420223236</t>
   </si>
   <si>
     <t xml:space="preserve">1.581383228302</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247608423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822792053223</t>
+    <t xml:space="preserve">1.52476072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52880537509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822780132294</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69867241382599</t>
+    <t xml:space="preserve">1.69867253303528</t>
   </si>
   <si>
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249452114105</t>
+    <t xml:space="preserve">1.68249475955963</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440581321716</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">1.62587225437164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61778342723846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71485018730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5571163892746</t>
+    <t xml:space="preserve">1.61778330802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71485030651093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55711650848389</t>
   </si>
   <si>
     <t xml:space="preserve">1.48431622982025</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">1.47218286991119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59351658821106</t>
+    <t xml:space="preserve">1.59351670742035</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3306268453598</t>
+    <t xml:space="preserve">1.33062672615051</t>
   </si>
   <si>
     <t xml:space="preserve">1.3589380979538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44791615009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409392356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47622728347778</t>
+    <t xml:space="preserve">1.44791603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409380435944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
     <t xml:space="preserve">1.60160553455353</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">1.59756112098694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60969436168671</t>
+    <t xml:space="preserve">1.609694480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72660851478577</t>
+    <t xml:space="preserve">1.72660839557648</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343998908997</t>
+    <t xml:space="preserve">1.64659488201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343986988068</t>
   </si>
   <si>
     <t xml:space="preserve">1.63817250728607</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64238357543945</t>
+    <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
     <t xml:space="preserve">1.61711609363556</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59605991840363</t>
+    <t xml:space="preserve">1.59606003761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
+    <t xml:space="preserve">1.53289151191711</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4360328912735</t>
+    <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499022960663</t>
+    <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077904224396</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.54131388664246</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868008613586</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869359970093</t>
+    <t xml:space="preserve">1.60869371891022</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60027134418488</t>
+    <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
     <t xml:space="preserve">1.62553858757019</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501737594604</t>
+    <t xml:space="preserve">1.65501749515533</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290490627289</t>
+    <t xml:space="preserve">1.61290502548218</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184885025024</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025759220123</t>
+    <t xml:space="preserve">1.52025771141052</t>
   </si>
   <si>
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763754367828</t>
+    <t xml:space="preserve">1.58763742446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
@@ -68676,7 +68676,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6874421296</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>480841</v>
@@ -68697,6 +68697,32 @@
         <v>863</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6874421296</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>787</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>864</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504825115204</t>
+    <t xml:space="preserve">0.965504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892835617065</t>
+    <t xml:space="preserve">0.994892954826355</t>
   </si>
   <si>
     <t xml:space="preserve">0.980557382106781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978406846523285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169312000275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959053814411163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966938376426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960487425327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944718182086945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816220283508</t>
+    <t xml:space="preserve">0.978407025337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169192790985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959053933620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966938495635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960487544536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944718241691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816041469574</t>
   </si>
   <si>
     <t xml:space="preserve">0.863005042076111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874473631381989</t>
+    <t xml:space="preserve">0.874473690986633</t>
   </si>
   <si>
     <t xml:space="preserve">0.849386215209961</t>
@@ -83,31 +83,31 @@
     <t xml:space="preserve">0.900994479656219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878057479858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375712394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428090572357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560868740082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606528759003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844182491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86658900976181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831466674804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820714950561523</t>
+    <t xml:space="preserve">0.878057599067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88737565279007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428030967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606409549713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844242095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866588950157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831466615200043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
     <t xml:space="preserve">0.807812869548798</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713197767734528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731117248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704237997531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723949372768402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459897041321</t>
+    <t xml:space="preserve">0.713197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731117308139801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704237937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723949432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124205112457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459837436676</t>
   </si>
   <si>
     <t xml:space="preserve">0.800645112991333</t>
@@ -140,85 +140,85 @@
     <t xml:space="preserve">0.80279541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802366733551</t>
+    <t xml:space="preserve">0.824298918247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802247524261</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804945886135101</t>
+    <t xml:space="preserve">0.804945826530457</t>
   </si>
   <si>
     <t xml:space="preserve">0.835050642490387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333837032318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634610176086</t>
+    <t xml:space="preserve">0.834333896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634431362152</t>
   </si>
   <si>
     <t xml:space="preserve">0.886658847332001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88020795583725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839351236820221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819885730743</t>
+    <t xml:space="preserve">0.88020783662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83935135602951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819766521454</t>
   </si>
   <si>
     <t xml:space="preserve">0.87304013967514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393290996552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977079868317</t>
+    <t xml:space="preserve">0.877340734004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809323310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393231391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895976960659027</t>
   </si>
   <si>
     <t xml:space="preserve">0.885225296020508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85297030210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889604091644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305874824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924642086029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830749928951263</t>
+    <t xml:space="preserve">0.852970242500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889723300934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86730569601059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88092452287674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86013799905777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749988555908</t>
   </si>
   <si>
     <t xml:space="preserve">0.858704447746277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855120539665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536691188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421193599701</t>
+    <t xml:space="preserve">0.855120420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536571979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421253204346</t>
   </si>
   <si>
     <t xml:space="preserve">0.840784907341003</t>
@@ -227,58 +227,58 @@
     <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79921156167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893388748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547253608704</t>
+    <t xml:space="preserve">0.799211502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893329143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547074794769</t>
   </si>
   <si>
     <t xml:space="preserve">0.779858469963074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781292080879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875929355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80924654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131102085114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431696414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980804920197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113523483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396777629852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928307533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194042682648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512156009674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697491168976</t>
+    <t xml:space="preserve">0.781291961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875988960266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246480464935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131161689758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917745113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431875228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113583087921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396837234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928367137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026226520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512215614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697431564331</t>
   </si>
   <si>
     <t xml:space="preserve">0.756921470165253</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.759788513183594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762655675411224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204605102539</t>
+    <t xml:space="preserve">0.76265561580658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204664707184</t>
   </si>
   <si>
     <t xml:space="preserve">0.750470459461212</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">0.763372540473938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767673194408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775557816028595</t>
+    <t xml:space="preserve">0.767673134803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575156211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77555787563324</t>
   </si>
   <si>
     <t xml:space="preserve">0.795627653598785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784159243106842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218458652496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
+    <t xml:space="preserve">0.784159064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218339443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380407810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872164011001587</t>
   </si>
   <si>
     <t xml:space="preserve">0.869937300682068</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.861029922962189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861772239208221</t>
+    <t xml:space="preserve">0.861772298812866</t>
   </si>
   <si>
     <t xml:space="preserve">0.853607356548309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856576383113861</t>
+    <t xml:space="preserve">0.856576442718506</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741325378418</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">0.855834186077118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837277352809906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83059698343277</t>
+    <t xml:space="preserve">0.837277472019196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401186943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830597043037415</t>
   </si>
   <si>
     <t xml:space="preserve">0.85880309343338</t>
@@ -365,97 +365,97 @@
     <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844700038433075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843957781791687</t>
+    <t xml:space="preserve">0.844700157642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843957841396332</t>
   </si>
   <si>
     <t xml:space="preserve">0.84618467092514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83579295873642</t>
+    <t xml:space="preserve">0.835792899131775</t>
   </si>
   <si>
     <t xml:space="preserve">0.833566129207611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838761985301971</t>
+    <t xml:space="preserve">0.838762044906616</t>
   </si>
   <si>
     <t xml:space="preserve">0.816493988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916494846344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810555875301361</t>
+    <t xml:space="preserve">0.809813559055328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916614055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810555934906006</t>
   </si>
   <si>
     <t xml:space="preserve">0.801648616790771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81797856092453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720757961273</t>
+    <t xml:space="preserve">0.817978382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720817565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.819463014602661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826143443584442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278270483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808329045772552</t>
+    <t xml:space="preserve">0.826143503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808328926563263</t>
   </si>
   <si>
     <t xml:space="preserve">0.803133189678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805360019207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796452641487122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906360149384</t>
+    <t xml:space="preserve">0.805359959602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796452760696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906300544739</t>
   </si>
   <si>
     <t xml:space="preserve">0.790514707565308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791999161243439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791256844997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586848735809</t>
+    <t xml:space="preserve">0.791999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791256725788116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807586789131165</t>
   </si>
   <si>
     <t xml:space="preserve">0.814267039299011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804617702960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798679530620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225990772247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803185939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779380559921265</t>
+    <t xml:space="preserve">0.804617583751678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79867947101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794225931167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77938050031662</t>
   </si>
   <si>
     <t xml:space="preserve">0.77715390920639</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">0.777896046638489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788287818431854</t>
+    <t xml:space="preserve">0.788287758827209</t>
   </si>
   <si>
     <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838019728660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806844413280487</t>
+    <t xml:space="preserve">0.838019609451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806844532489777</t>
   </si>
   <si>
     <t xml:space="preserve">0.774927020072937</t>
@@ -482,52 +482,52 @@
     <t xml:space="preserve">0.773442506790161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783834159374237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765277564525604</t>
+    <t xml:space="preserve">0.783834218978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765277504920959</t>
   </si>
   <si>
     <t xml:space="preserve">0.778638303279877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783091902732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787545561790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786060988903046</t>
+    <t xml:space="preserve">0.783091962337494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787545442581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78606104850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.774184703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785318672657013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806102156639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452727794647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841730952262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411500453949</t>
+    <t xml:space="preserve">0.785318732261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806102275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452608585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841731011867523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411381244659</t>
   </si>
   <si>
     <t xml:space="preserve">0.843215644359589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852865040302277</t>
+    <t xml:space="preserve">0.852865099906921</t>
   </si>
   <si>
     <t xml:space="preserve">0.845442354679108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849153697490692</t>
+    <t xml:space="preserve">0.849153757095337</t>
   </si>
   <si>
     <t xml:space="preserve">0.874390721321106</t>
@@ -539,25 +539,25 @@
     <t xml:space="preserve">0.866225898265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855091869831085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857318639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832823812961578</t>
+    <t xml:space="preserve">0.855091691017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857318699359894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832823753356934</t>
   </si>
   <si>
     <t xml:space="preserve">0.834308326244354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827627956867218</t>
+    <t xml:space="preserve">0.827627897262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.860287725925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.854349613189697</t>
+    <t xml:space="preserve">0.854349553585052</t>
   </si>
   <si>
     <t xml:space="preserve">0.867710411548615</t>
@@ -566,40 +566,40 @@
     <t xml:space="preserve">0.880328893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873648583889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669091701508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380434513092</t>
+    <t xml:space="preserve">0.873648524284363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380494117737</t>
   </si>
   <si>
     <t xml:space="preserve">0.913730978965759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916700005531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091658115387</t>
+    <t xml:space="preserve">0.916700124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091777324677</t>
   </si>
   <si>
     <t xml:space="preserve">0.931545317173004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915957808494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504089832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885667324066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991669058799744</t>
+    <t xml:space="preserve">0.915957689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504209041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535122871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991668879985809</t>
   </si>
   <si>
     <t xml:space="preserve">0.979792773723602</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">1.06960701942444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0748028755188</t>
+    <t xml:space="preserve">1.07480299472809</t>
   </si>
   <si>
     <t xml:space="preserve">1.0688648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04659676551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05327713489532</t>
+    <t xml:space="preserve">1.0465966463089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05327725410461</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179274082184</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">1.02432882785797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03175151348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0146791934967</t>
+    <t xml:space="preserve">1.03175139427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01467931270599</t>
   </si>
   <si>
     <t xml:space="preserve">1.00206065177917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02284419536591</t>
+    <t xml:space="preserve">1.0228443145752</t>
   </si>
   <si>
     <t xml:space="preserve">1.03026700019836</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">1.05921542644501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06812274456024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04585456848145</t>
+    <t xml:space="preserve">1.06812250614166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04585468769073</t>
   </si>
   <si>
     <t xml:space="preserve">1.06663799285889</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1193391084671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.117112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12898850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160692691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18762755393982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21509146690369</t>
+    <t xml:space="preserve">1.11933898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11711227893829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1289883852005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160704612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1876277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21509158611298</t>
   </si>
   <si>
     <t xml:space="preserve">1.23142147064209</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">1.21731817722321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22177171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23216354846954</t>
+    <t xml:space="preserve">1.22177183628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880280971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23216342926025</t>
   </si>
   <si>
     <t xml:space="preserve">1.22845232486725</t>
@@ -704,43 +704,43 @@
     <t xml:space="preserve">1.23513269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22474110126495</t>
+    <t xml:space="preserve">1.22474098205566</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286463737488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21360695362091</t>
+    <t xml:space="preserve">1.21360683441162</t>
   </si>
   <si>
     <t xml:space="preserve">1.20098841190338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700880050659</t>
+    <t xml:space="preserve">1.2470086812973</t>
   </si>
   <si>
     <t xml:space="preserve">1.26779246330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24923586845398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443172454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26036977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888526439667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26927709579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521526813507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30639040470123</t>
+    <t xml:space="preserve">1.2492356300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443160533905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26036965847015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888514518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26927697658539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
     <t xml:space="preserve">1.34424602985382</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20321524143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17426693439484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17278218269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16535949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055535316467</t>
+    <t xml:space="preserve">1.2032151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17426657676697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17278230190277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1653596162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055547237396</t>
   </si>
   <si>
     <t xml:space="preserve">1.17723572254181</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">1.12824618816376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14383399486542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18911218643188</t>
+    <t xml:space="preserve">1.14383387565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">1.28486454486847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31307077407837</t>
+    <t xml:space="preserve">1.31307089328766</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">1.32791602611542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35834896564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3435035943985</t>
+    <t xml:space="preserve">1.35834908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34350371360779</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057282447815</t>
+    <t xml:space="preserve">1.35057294368744</t>
   </si>
   <si>
     <t xml:space="preserve">1.34374034404755</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031149864197</t>
+    <t xml:space="preserve">1.35512793064117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031126022339</t>
   </si>
   <si>
     <t xml:space="preserve">1.36651563644409</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39080941677094</t>
+    <t xml:space="preserve">1.39080917835236</t>
   </si>
   <si>
     <t xml:space="preserve">1.39688265323639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38169920444489</t>
+    <t xml:space="preserve">1.3816990852356</t>
   </si>
   <si>
     <t xml:space="preserve">1.36803412437439</t>
@@ -860,31 +860,31 @@
     <t xml:space="preserve">1.3915684223175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38549494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258899211884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701331615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36879312992096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3612015247345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35133218765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31565093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33842611312866</t>
+    <t xml:space="preserve">1.39232766628265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38549506664276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36879324913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36120128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3513320684433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31565082073212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33842623233795</t>
   </si>
   <si>
     <t xml:space="preserve">1.34298133850098</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">1.29818987846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30122661590576</t>
+    <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.320965051651</t>
@@ -911,22 +911,22 @@
     <t xml:space="preserve">1.36955237388611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536440372467</t>
+    <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625407218933</t>
+    <t xml:space="preserve">1.40143764019012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625419139862</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397657871246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929104804993</t>
+    <t xml:space="preserve">1.38929092884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
@@ -938,64 +938,64 @@
     <t xml:space="preserve">1.38473582267761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34829533100128</t>
+    <t xml:space="preserve">1.34829556941986</t>
   </si>
   <si>
     <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4523024559021</t>
+    <t xml:space="preserve">1.45230233669281</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735524177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630934238434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51835060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568088054657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379573345184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594244480133</t>
+    <t xml:space="preserve">1.47735512256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630958080292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51835072040558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379561424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594256401062</t>
   </si>
   <si>
     <t xml:space="preserve">1.51075887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52897906303406</t>
+    <t xml:space="preserve">1.52897918224335</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53049755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53353416919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52746093273163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51607310771942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47887349128723</t>
+    <t xml:space="preserve">1.53049743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53353404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52746069431305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51607322692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47887361049652</t>
   </si>
   <si>
     <t xml:space="preserve">1.43484151363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40599286556244</t>
+    <t xml:space="preserve">1.40599274635315</t>
   </si>
   <si>
     <t xml:space="preserve">1.38777244091034</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">1.33614861965179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29059815406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29970812797546</t>
+    <t xml:space="preserve">1.2905980348587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29970824718475</t>
   </si>
   <si>
     <t xml:space="preserve">1.30502247810364</t>
@@ -1022,43 +1022,43 @@
     <t xml:space="preserve">1.47659611701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48798382282257</t>
+    <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
     <t xml:space="preserve">1.48722445964813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269456386566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41434383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41738033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40447449684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39308679103851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40371513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182986736298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36271977424622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423814296722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35209131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36499714851379</t>
+    <t xml:space="preserve">1.42269468307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41434359550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41738045215607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40447437763214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3930869102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40371525287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36271989345551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423802375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35209143161774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36499738693237</t>
   </si>
   <si>
     <t xml:space="preserve">1.36575651168823</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">1.37107062339783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42724967002869</t>
+    <t xml:space="preserve">1.4272495508194</t>
   </si>
   <si>
     <t xml:space="preserve">1.48039186000824</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49557530879974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49177968502045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50696325302124</t>
+    <t xml:space="preserve">1.49557554721832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49177956581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50696301460266</t>
   </si>
   <si>
     <t xml:space="preserve">1.45761656761169</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">1.43863725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37790322303772</t>
+    <t xml:space="preserve">1.37790334224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30957758426666</t>
+    <t xml:space="preserve">1.30957746505737</t>
   </si>
   <si>
     <t xml:space="preserve">1.33994448184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32476091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753632545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337332725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161860466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716930866241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40827023983002</t>
+    <t xml:space="preserve">1.32476103305817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753620624542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337344646454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40827035903931</t>
   </si>
   <si>
     <t xml:space="preserve">1.41206610202789</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44243311882019</t>
+    <t xml:space="preserve">1.4424329996109</t>
   </si>
   <si>
     <t xml:space="preserve">1.45382082462311</t>
@@ -1136,40 +1136,40 @@
     <t xml:space="preserve">1.46900427341461</t>
   </si>
   <si>
+    <t xml:space="preserve">1.48418784141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46520853042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41586208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45002484321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46141254901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54112589359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47280013561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5145548582077</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.48418772220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46520841121674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42345380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41586208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45002496242523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54112601280212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47280025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5145548582077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48418784141541</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.51551628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50768411159515</t>
+    <t xml:space="preserve">1.50768423080444</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726447582245</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">1.50376808643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49201989173889</t>
+    <t xml:space="preserve">1.49202001094818</t>
   </si>
   <si>
     <t xml:space="preserve">1.46852362155914</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">1.48027181625366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46069157123566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44894337654114</t>
+    <t xml:space="preserve">1.46069145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44894325733185</t>
   </si>
   <si>
     <t xml:space="preserve">1.4646075963974</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">1.45677530765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47243964672089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47635567188263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44111108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4254469871521</t>
+    <t xml:space="preserve">1.4724395275116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47635579109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44111120700836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42544686794281</t>
   </si>
   <si>
     <t xml:space="preserve">1.36278986930847</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">1.40978264808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42153084278107</t>
+    <t xml:space="preserve">1.42153096199036</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936289310455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43327915668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45285928249359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39803445339203</t>
+    <t xml:space="preserve">1.43327903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45285940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39803433418274</t>
   </si>
   <si>
     <t xml:space="preserve">1.39411842823029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34712564945221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362926006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488816738129</t>
+    <t xml:space="preserve">1.3471257686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488828659058</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30796504020691</t>
+    <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
     <t xml:space="preserve">1.30404889583588</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">1.33146142959595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28055250644684</t>
+    <t xml:space="preserve">1.28055262565613</t>
   </si>
   <si>
     <t xml:space="preserve">1.29621684551239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188094615936</t>
+    <t xml:space="preserve">1.31188106536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.34320962429047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35104179382324</t>
+    <t xml:space="preserve">1.35104167461395</t>
   </si>
   <si>
     <t xml:space="preserve">1.38628625869751</t>
@@ -1286,19 +1286,19 @@
     <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32754528522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838455677032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40195035934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30013287067413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33537757396698</t>
+    <t xml:space="preserve">1.3275454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28838467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40195047855377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30013275146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3353773355484</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230082035065</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31971323490143</t>
+    <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49593603610992</t>
+    <t xml:space="preserve">1.48810374736786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49593591690063</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985206127167</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">1.51160025596619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52334856987</t>
+    <t xml:space="preserve">1.52334845066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509676456451</t>
@@ -1343,31 +1343,31 @@
     <t xml:space="preserve">1.55076086521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59775376319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58992159366608</t>
+    <t xml:space="preserve">1.59775352478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58992147445679</t>
   </si>
   <si>
     <t xml:space="preserve">1.62124991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60558569431305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61341798305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5820894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62908220291138</t>
+    <t xml:space="preserve">1.60558581352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61341786384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208930492401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
     <t xml:space="preserve">1.64474630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63691425323486</t>
+    <t xml:space="preserve">1.63691413402557</t>
   </si>
   <si>
     <t xml:space="preserve">1.65257847309113</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824293136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70740354061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75439620018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74656403064728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80138885974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838140010834</t>
+    <t xml:space="preserve">1.66824305057526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70740330219269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75439608097076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74656414985657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222836971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80138897895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006030082703</t>
@@ -1403,82 +1403,82 @@
     <t xml:space="preserve">1.7778924703598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82488536834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80922091007233</t>
+    <t xml:space="preserve">1.82488512992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80922102928162</t>
   </si>
   <si>
     <t xml:space="preserve">1.83271729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84054958820343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971031665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87187802791595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86404585838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85621392726898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79355680942535</t>
+    <t xml:space="preserve">1.84054946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87187826633453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86404609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85621356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79355669021606</t>
   </si>
   <si>
     <t xml:space="preserve">1.94236743450165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95803141593933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97369563579559</t>
+    <t xml:space="preserve">1.95803117752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97369587421417</t>
   </si>
   <si>
     <t xml:space="preserve">1.99719202518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9658637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93453502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91887056827545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670285701752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178458213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942879676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87662875652313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77956163883209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76338410377502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78765058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573953151703</t>
+    <t xml:space="preserve">1.96586334705353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93453526496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91887080669403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92670273780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178470134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942891597748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9656069278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87662839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77956187725067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191742420197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78765070438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573965072632</t>
   </si>
   <si>
     <t xml:space="preserve">1.8038284778595</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">1.82000625133514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86045074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85236203670502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89280641078949</t>
+    <t xml:space="preserve">1.8604508638382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809507846832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85236179828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8928062915802</t>
   </si>
   <si>
     <t xml:space="preserve">1.90089535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8847177028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427309036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86853969097137</t>
+    <t xml:space="preserve">1.88471746444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427297115326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86853981018066</t>
   </si>
   <si>
     <t xml:space="preserve">1.83618402481079</t>
@@ -1517,25 +1517,25 @@
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9413400888443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93325114250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987352848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751798152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.997962474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73911714553833</t>
+    <t xml:space="preserve">1.90898430347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94134020805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93325126171112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987364768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751774311066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73911702632904</t>
   </si>
   <si>
     <t xml:space="preserve">1.92516231536865</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">1.7472060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75529491901398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66631674766541</t>
+    <t xml:space="preserve">1.75529503822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66631686687469</t>
   </si>
   <si>
     <t xml:space="preserve">1.56924986839294</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56116080284119</t>
+    <t xml:space="preserve">1.56116092205048</t>
   </si>
   <si>
     <t xml:space="preserve">1.49644958972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747141838074</t>
+    <t xml:space="preserve">1.40747153759003</t>
   </si>
   <si>
     <t xml:space="preserve">1.4155604839325</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">1.34276020526886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31849348545074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29827105998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17289304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19715976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22951531410217</t>
+    <t xml:space="preserve">1.31849336624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29827117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17289292812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19715964794159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22951543331146</t>
   </si>
   <si>
     <t xml:space="preserve">1.15267062187195</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">1.1648041009903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03538143634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07178151607513</t>
+    <t xml:space="preserve">1.03538131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07178163528442</t>
   </si>
   <si>
     <t xml:space="preserve">1.15671515464783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1405371427536</t>
+    <t xml:space="preserve">1.14053726196289</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693734169006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09604823589325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502616882324</t>
+    <t xml:space="preserve">1.09604811668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13649272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16075944900513</t>
+    <t xml:space="preserve">1.1364928483963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16075956821442</t>
   </si>
   <si>
     <t xml:space="preserve">1.24569320678711</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">1.30231559276581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995992660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25378203392029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524871349335</t>
+    <t xml:space="preserve">1.26995980739594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25378215312958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524859428406</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
+    <t xml:space="preserve">1.18098175525665</t>
   </si>
   <si>
     <t xml:space="preserve">1.21333742141724</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031507492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14458155632019</t>
+    <t xml:space="preserve">1.12031495571136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14458167552948</t>
   </si>
   <si>
     <t xml:space="preserve">1.11627054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14862608909607</t>
+    <t xml:space="preserve">1.14862620830536</t>
   </si>
   <si>
     <t xml:space="preserve">1.10009264945984</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">1.23760414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21738195419312</t>
+    <t xml:space="preserve">1.2173820734024</t>
   </si>
   <si>
     <t xml:space="preserve">1.16884851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20929312705994</t>
+    <t xml:space="preserve">1.20929300785065</t>
   </si>
   <si>
     <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22142624855042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11222612857819</t>
+    <t xml:space="preserve">1.22142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1122260093689</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">1.07582604885101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0596479177475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09200382232666</t>
+    <t xml:space="preserve">1.05964803695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09200370311737</t>
   </si>
   <si>
     <t xml:space="preserve">1.08391487598419</t>
@@ -1721,64 +1721,64 @@
     <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0556036233902</t>
+    <t xml:space="preserve">1.05560350418091</t>
   </si>
   <si>
     <t xml:space="preserve">1.05155909061432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02324783802032</t>
+    <t xml:space="preserve">1.02324795722961</t>
   </si>
   <si>
     <t xml:space="preserve">1.0272923707962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00302577018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982803344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97067004442215</t>
+    <t xml:space="preserve">1.00302565097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982803463935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954492151737213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970670104026794</t>
   </si>
   <si>
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847817897797</t>
+    <t xml:space="preserve">0.986847937107086</t>
   </si>
   <si>
     <t xml:space="preserve">0.962581157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966625571250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758990764618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01920354366302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10413706302643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23355984687805</t>
+    <t xml:space="preserve">0.96662563085556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978758871555328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01920342445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10413718223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23355972766876</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20120418071747</t>
+    <t xml:space="preserve">1.20120406150818</t>
   </si>
   <si>
     <t xml:space="preserve">1.29422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31040441989899</t>
+    <t xml:space="preserve">1.31040453910828</t>
   </si>
   <si>
     <t xml:space="preserve">1.32253789901733</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">1.32658231258392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680449962616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33467125892639</t>
+    <t xml:space="preserve">1.34680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33467137813568</t>
   </si>
   <si>
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46813833713531</t>
+    <t xml:space="preserve">1.4681384563446</t>
   </si>
   <si>
     <t xml:space="preserve">1.51262748241425</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">1.55307197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57733869552612</t>
+    <t xml:space="preserve">1.57733881473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.54093861579895</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">1.54498302936554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52071642875671</t>
+    <t xml:space="preserve">1.52071630954742</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284966945648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51667189598083</t>
+    <t xml:space="preserve">1.53284955024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51667201519012</t>
   </si>
   <si>
     <t xml:space="preserve">1.53689420223236</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">1.57329440116882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56520545482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836064338684</t>
+    <t xml:space="preserve">1.56520533561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836076259613</t>
   </si>
   <si>
     <t xml:space="preserve">1.5004940032959</t>
@@ -1850,34 +1850,34 @@
     <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52476072311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880537509918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.5247608423233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5288051366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69867253303528</t>
+    <t xml:space="preserve">1.69867241382599</t>
   </si>
   <si>
     <t xml:space="preserve">1.69058358669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68249475955963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67440581321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72293937206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61373889446259</t>
+    <t xml:space="preserve">1.68249464035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67440569400787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72293949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6137387752533</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">1.60565006732941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64205014705658</t>
+    <t xml:space="preserve">1.64205002784729</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">1.71485030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55711650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48431622982025</t>
+    <t xml:space="preserve">1.5571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48431634902954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49240517616272</t>
@@ -1916,40 +1916,40 @@
     <t xml:space="preserve">1.59351670742035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50858294963837</t>
+    <t xml:space="preserve">1.50858306884766</t>
   </si>
   <si>
     <t xml:space="preserve">1.37107145786285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33062672615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3589380979538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44791603088379</t>
+    <t xml:space="preserve">1.3306268453598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35893797874451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44791615009308</t>
   </si>
   <si>
     <t xml:space="preserve">1.46409380435944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47622740268707</t>
+    <t xml:space="preserve">1.47622728347778</t>
   </si>
   <si>
     <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59756112098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.609694480896</t>
+    <t xml:space="preserve">1.59756124019623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60969436168671</t>
   </si>
   <si>
     <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72660839557648</t>
+    <t xml:space="preserve">1.72660851478577</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">1.69291853904724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68028485774994</t>
+    <t xml:space="preserve">1.68028473854065</t>
   </si>
   <si>
     <t xml:space="preserve">1.68449604511261</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">1.63817250728607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62974989414215</t>
+    <t xml:space="preserve">1.62974977493286</t>
   </si>
   <si>
     <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64238369464874</t>
+    <t xml:space="preserve">1.64238357543945</t>
   </si>
   <si>
     <t xml:space="preserve">1.61711609363556</t>
@@ -1997,25 +1997,25 @@
     <t xml:space="preserve">1.56237006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54973638057709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58342635631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57500386238098</t>
+    <t xml:space="preserve">1.54973649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58342623710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57500374317169</t>
   </si>
   <si>
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59606003761292</t>
+    <t xml:space="preserve">1.59605991840363</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54552507400513</t>
+    <t xml:space="preserve">1.54552519321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815887451172</t>
@@ -2039,19 +2039,19 @@
     <t xml:space="preserve">1.38970923423767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3981317281723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603301048279</t>
+    <t xml:space="preserve">1.39813160896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4360328912735</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41497671604156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44024407863617</t>
+    <t xml:space="preserve">1.41497659683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44024419784546</t>
   </si>
   <si>
     <t xml:space="preserve">1.41076529026031</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499034881592</t>
+    <t xml:space="preserve">1.49499022960663</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077904224396</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131388664246</t>
+    <t xml:space="preserve">1.54131400585175</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868008613586</t>
+    <t xml:space="preserve">1.52868032455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869371891022</t>
+    <t xml:space="preserve">1.60869359970093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501749515533</t>
+    <t xml:space="preserve">1.65501737594604</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184885025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51604640483856</t>
+    <t xml:space="preserve">1.61290490627289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184873104095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51604652404785</t>
   </si>
   <si>
     <t xml:space="preserve">1.50762391090393</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025771141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57079255580902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58763742446899</t>
+    <t xml:space="preserve">1.52025759220123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57079243659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58763754367828</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
@@ -68702,7 +68702,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6874421296</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>787</v>
@@ -68723,6 +68723,32 @@
         <v>864</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6909837963</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>7894</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>842</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965504884719849</t>
+    <t xml:space="preserve">0.965504944324493</t>
   </si>
   <si>
     <t xml:space="preserve">PQ.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994892954826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980557382106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978407025337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169192790985</t>
+    <t xml:space="preserve">0.994893014431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980557322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978407084941864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95116925239563</t>
   </si>
   <si>
     <t xml:space="preserve">0.959053933620453</t>
@@ -65,31 +65,31 @@
     <t xml:space="preserve">0.960487425327301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944718241691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816160678864</t>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816279888153</t>
   </si>
   <si>
     <t xml:space="preserve">0.863005101680756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874473631381989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386215209961</t>
+    <t xml:space="preserve">0.874473690986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386274814606</t>
   </si>
   <si>
     <t xml:space="preserve">0.900994658470154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878057539463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88737565279007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428209781647</t>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375593185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428150177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.899560987949371</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">0.871606469154358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86658900976181</t>
+    <t xml:space="preserve">0.898844182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866589069366455</t>
   </si>
   <si>
     <t xml:space="preserve">0.831466674804688</t>
@@ -110,67 +110,67 @@
     <t xml:space="preserve">0.820715010166168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812988758087</t>
+    <t xml:space="preserve">0.807812929153442</t>
   </si>
   <si>
     <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713197708129883</t>
+    <t xml:space="preserve">0.713197827339172</t>
   </si>
   <si>
     <t xml:space="preserve">0.731117308139801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.704237937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723949432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459897041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800645172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802795350551605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802366733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827882707118988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804945826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050642490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834333896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658906936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83935135602951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819826126099</t>
+    <t xml:space="preserve">0.704237997531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723949491977692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124264717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298799037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802247524261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827882766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804945766925812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835050582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333777427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634431362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88665896654129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88020795583725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351296424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819885730743</t>
   </si>
   <si>
     <t xml:space="preserve">0.873040080070496</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">0.87734067440033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888809263706207</t>
+    <t xml:space="preserve">0.888809323310852</t>
   </si>
   <si>
     <t xml:space="preserve">0.892393231391907</t>
@@ -188,61 +188,61 @@
     <t xml:space="preserve">0.895977079868317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885225355625153</t>
+    <t xml:space="preserve">0.885225474834442</t>
   </si>
   <si>
     <t xml:space="preserve">0.85297018289566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870889842510223</t>
+    <t xml:space="preserve">0.870889604091644</t>
   </si>
   <si>
     <t xml:space="preserve">0.867305874824524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880924642086029</t>
+    <t xml:space="preserve">0.88092452287674</t>
   </si>
   <si>
     <t xml:space="preserve">0.86013799905777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830749988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704268932343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120539665222</t>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120420455933</t>
   </si>
   <si>
     <t xml:space="preserve">0.851536571979523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859421193599701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784907341003</t>
+    <t xml:space="preserve">0.859421253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784966945648</t>
   </si>
   <si>
     <t xml:space="preserve">0.826449275016785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893269538879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547074794769</t>
+    <t xml:space="preserve">0.79921156167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893388748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547253608704</t>
   </si>
   <si>
     <t xml:space="preserve">0.779858469963074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781292021274567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875988960266</t>
+    <t xml:space="preserve">0.781292080879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875929355621</t>
   </si>
   <si>
     <t xml:space="preserve">0.809246420860291</t>
@@ -254,31 +254,31 @@
     <t xml:space="preserve">0.837917745113373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821431815624237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980804920197</t>
+    <t xml:space="preserve">0.821431696414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980685710907</t>
   </si>
   <si>
     <t xml:space="preserve">0.812113583087921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811396896839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928367137909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194042682648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026226520538</t>
+    <t xml:space="preserve">0.811396718025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026286125183</t>
   </si>
   <si>
     <t xml:space="preserve">0.803512275218964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815697431564331</t>
+    <t xml:space="preserve">0.815697491168976</t>
   </si>
   <si>
     <t xml:space="preserve">0.756921470165253</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">0.750470459461212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77914172410965</t>
+    <t xml:space="preserve">0.779141664505005</t>
   </si>
   <si>
     <t xml:space="preserve">0.763372480869293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767673134803772</t>
+    <t xml:space="preserve">0.767673015594482</t>
   </si>
   <si>
     <t xml:space="preserve">0.780575156211853</t>
@@ -311,70 +311,70 @@
     <t xml:space="preserve">0.77555775642395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795627653598785</t>
+    <t xml:space="preserve">0.795627593994141</t>
   </si>
   <si>
     <t xml:space="preserve">0.784159064292908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.842218518257141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380527019501</t>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380407810211</t>
   </si>
   <si>
     <t xml:space="preserve">0.872164011001587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869937300682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029922962189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772239208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576383113861</t>
+    <t xml:space="preserve">0.869937181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029982566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772298812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576442718506</t>
   </si>
   <si>
     <t xml:space="preserve">0.864741325378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855834186077118</t>
+    <t xml:space="preserve">0.855834126472473</t>
   </si>
   <si>
     <t xml:space="preserve">0.837277412414551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825401186943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112589359283</t>
+    <t xml:space="preserve">0.825401127338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829112529754639</t>
   </si>
   <si>
     <t xml:space="preserve">0.830597043037415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85880309343338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839504241943359</t>
+    <t xml:space="preserve">0.858803033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
     <t xml:space="preserve">0.84470009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843957960605621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846184611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835792899131775</t>
+    <t xml:space="preserve">0.843957781791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846184551715851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83579295873642</t>
   </si>
   <si>
     <t xml:space="preserve">0.833566129207611</t>
@@ -383,40 +383,40 @@
     <t xml:space="preserve">0.838761925697327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816494047641754</t>
+    <t xml:space="preserve">0.816493928432465</t>
   </si>
   <si>
     <t xml:space="preserve">0.809813559055328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823916614055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810555875301361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801648616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817978382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720757961273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819463074207306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278270483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808328926563263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803133189678192</t>
+    <t xml:space="preserve">0.823916554450989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810555815696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801648676395416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817978501319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819463014602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143562793732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812782645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808328986167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803133130073547</t>
   </si>
   <si>
     <t xml:space="preserve">0.805359959602356</t>
@@ -425,40 +425,40 @@
     <t xml:space="preserve">0.796452760696411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800906240940094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790514707565308</t>
+    <t xml:space="preserve">0.800906360149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790514588356018</t>
   </si>
   <si>
     <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256785392761</t>
+    <t xml:space="preserve">0.791256844997406</t>
   </si>
   <si>
     <t xml:space="preserve">0.807586789131165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814267039299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804617643356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79867947101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794225990772247</t>
+    <t xml:space="preserve">0.814267098903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804617583751678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79867959022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794226050376892</t>
   </si>
   <si>
     <t xml:space="preserve">0.786803305149078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77938050031662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77715390920639</t>
+    <t xml:space="preserve">0.779380559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777153849601746</t>
   </si>
   <si>
     <t xml:space="preserve">0.777895987033844</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">0.788287818431854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771957874298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838019669055939</t>
+    <t xml:space="preserve">0.77195793390274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838019609451294</t>
   </si>
   <si>
     <t xml:space="preserve">0.806844472885132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774926960468292</t>
+    <t xml:space="preserve">0.774927079677582</t>
   </si>
   <si>
     <t xml:space="preserve">0.773442506790161</t>
@@ -506,43 +506,43 @@
     <t xml:space="preserve">0.785318672657013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806102156639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868452668190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841730952262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848411440849304</t>
+    <t xml:space="preserve">0.806102216243744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868452608585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841731011867523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848411381244659</t>
   </si>
   <si>
     <t xml:space="preserve">0.843215644359589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852865099906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442354679108</t>
+    <t xml:space="preserve">0.852865278720856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442473888397</t>
   </si>
   <si>
     <t xml:space="preserve">0.849153757095337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874390602111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862514436244965</t>
+    <t xml:space="preserve">0.874390780925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862514495849609</t>
   </si>
   <si>
     <t xml:space="preserve">0.866225957870483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855091869831085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857318580150604</t>
+    <t xml:space="preserve">0.85509181022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857318639755249</t>
   </si>
   <si>
     <t xml:space="preserve">0.832823812961578</t>
@@ -551,67 +551,67 @@
     <t xml:space="preserve">0.834308326244354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827627837657928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86028778553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854349613189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867710411548615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880328893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873648583889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919669032096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380434513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913730978965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916700124740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927091836929321</t>
+    <t xml:space="preserve">0.827628016471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854349672794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86771035194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880328834056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919669151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380494117737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913730919361115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916700184345245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927091717720032</t>
   </si>
   <si>
     <t xml:space="preserve">0.931545376777649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915957748889923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911504149436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885548114777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991668879985809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792892932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03768968582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06960713863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07480299472809</t>
+    <t xml:space="preserve">0.915957629680634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911504209041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908535063266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991669058799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792773723602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03768956661224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06960690021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0748028755188</t>
   </si>
   <si>
     <t xml:space="preserve">1.0688648223877</t>
@@ -620,22 +620,22 @@
     <t xml:space="preserve">1.04659676551819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05327713489532</t>
+    <t xml:space="preserve">1.05327725410461</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249371051788</t>
+    <t xml:space="preserve">1.03249382972717</t>
   </si>
   <si>
     <t xml:space="preserve">1.02432870864868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03175127506256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467931270599</t>
+    <t xml:space="preserve">1.03175151348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0146791934967</t>
   </si>
   <si>
     <t xml:space="preserve">1.00206077098846</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">1.04585456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06663799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449373722076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11191618442535</t>
+    <t xml:space="preserve">1.06663811206818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449361801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
     <t xml:space="preserve">1.11933898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11711227893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1289883852005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14160704612732</t>
+    <t xml:space="preserve">1.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12898826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14160692691803</t>
   </si>
   <si>
     <t xml:space="preserve">1.18762755393982</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23142147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21731817722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22177195549011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21880269050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23216354846954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22845232486725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23513269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22474086284637</t>
+    <t xml:space="preserve">1.2314213514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2173182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22177171707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21880280971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23216366767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22845220565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2351325750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22474098205566</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286463737488</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">1.20098841190338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24700903892517</t>
+    <t xml:space="preserve">1.24700880050659</t>
   </si>
   <si>
     <t xml:space="preserve">1.26779222488403</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">1.24923574924469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25443160533905</t>
+    <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
     <t xml:space="preserve">1.26036977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25888514518738</t>
+    <t xml:space="preserve">1.25888526439667</t>
   </si>
   <si>
     <t xml:space="preserve">1.26927697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521514892578</t>
+    <t xml:space="preserve">1.27521502971649</t>
   </si>
   <si>
     <t xml:space="preserve">1.30639028549194</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">1.23958623409271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2032151222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17426669597626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17278218269348</t>
+    <t xml:space="preserve">1.20321524143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17426657676697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17278230190277</t>
   </si>
   <si>
     <t xml:space="preserve">1.1653596162796</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">1.17055547237396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1772358417511</t>
+    <t xml:space="preserve">1.17723572254181</t>
   </si>
   <si>
     <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16387498378754</t>
+    <t xml:space="preserve">1.16387510299683</t>
   </si>
   <si>
     <t xml:space="preserve">1.16164827346802</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">1.15051412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1534835100174</t>
+    <t xml:space="preserve">1.15348327159882</t>
   </si>
   <si>
     <t xml:space="preserve">1.12824618816376</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247280597687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28412246704102</t>
+    <t xml:space="preserve">1.20247292518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28412234783173</t>
   </si>
   <si>
     <t xml:space="preserve">1.28486454486847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31307077407837</t>
+    <t xml:space="preserve">1.31307065486908</t>
   </si>
   <si>
     <t xml:space="preserve">1.35018408298492</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">1.32791614532471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35834908485413</t>
+    <t xml:space="preserve">1.35834896564484</t>
   </si>
   <si>
     <t xml:space="preserve">1.34350371360779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33311176300049</t>
+    <t xml:space="preserve">1.33311188220978</t>
   </si>
   <si>
     <t xml:space="preserve">1.35057294368744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34374034404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32855689525604</t>
+    <t xml:space="preserve">1.34374046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32855677604675</t>
   </si>
   <si>
     <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512816905975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031137943268</t>
+    <t xml:space="preserve">1.35512804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031126022339</t>
   </si>
   <si>
     <t xml:space="preserve">1.3665155172348</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">1.37410736083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39080917835236</t>
+    <t xml:space="preserve">1.39080929756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.39688277244568</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">1.38169920444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3680340051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36727476119995</t>
+    <t xml:space="preserve">1.36803388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36727488040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.3915684223175</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">1.38549518585205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258911132812</t>
+    <t xml:space="preserve">1.37258899211884</t>
   </si>
   <si>
     <t xml:space="preserve">1.38701343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36879324913025</t>
+    <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
     <t xml:space="preserve">1.36120140552521</t>
@@ -884,49 +884,49 @@
     <t xml:space="preserve">1.31565082073212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842623233795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34298121929169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868755817413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29363489151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818987846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30122649669647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32096517086029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31413245201111</t>
+    <t xml:space="preserve">1.33842611312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3429811000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868743896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29363465309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818999767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30122661590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32096493244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3141325712204</t>
   </si>
   <si>
     <t xml:space="preserve">1.36955237388611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536440372467</t>
+    <t xml:space="preserve">1.39536428451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562572956085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38625419139862</t>
+    <t xml:space="preserve">1.40143764019012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38625407218933</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397657871246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929104804993</t>
+    <t xml:space="preserve">1.38929092884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.38321757316589</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">1.37866246700287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473582267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34829545021057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42497205734253</t>
+    <t xml:space="preserve">1.3847359418869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34829533100128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
     <t xml:space="preserve">1.4523024559021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50164902210236</t>
+    <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">1.47735524177551</t>
@@ -956,25 +956,25 @@
     <t xml:space="preserve">1.55630946159363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51835083961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379561424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594244480133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51075887680054</t>
+    <t xml:space="preserve">1.51835072040558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568111896515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379573345184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594232559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51075899600983</t>
   </si>
   <si>
     <t xml:space="preserve">1.52897918224335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50316715240479</t>
+    <t xml:space="preserve">1.50316739082336</t>
   </si>
   <si>
     <t xml:space="preserve">1.53049755096436</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">1.53353416919708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52746069431305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51607310771942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47887361049652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43484151363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40599274635315</t>
+    <t xml:space="preserve">1.52746093273163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51607322692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47887349128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43484139442444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40599262714386</t>
   </si>
   <si>
     <t xml:space="preserve">1.38777244091034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33614861965179</t>
+    <t xml:space="preserve">1.33614873886108</t>
   </si>
   <si>
     <t xml:space="preserve">1.29059815406799</t>
@@ -1019,103 +1019,103 @@
     <t xml:space="preserve">1.47052276134491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47659611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48798370361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48722445964813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269468307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41434359550476</t>
+    <t xml:space="preserve">1.47659599781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48798358440399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48722457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738045215607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40447437763214</t>
+    <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308679103851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371525287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36271977424622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36423802375793</t>
+    <t xml:space="preserve">1.40371513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182986736298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36271965503693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
     <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36499738693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36575651168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37107062339783</t>
+    <t xml:space="preserve">1.36499726772308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36575639247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37107074260712</t>
   </si>
   <si>
     <t xml:space="preserve">1.42724967002869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48039197921753</t>
+    <t xml:space="preserve">1.48039186000824</t>
   </si>
   <si>
     <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49557554721832</t>
+    <t xml:space="preserve">1.49557542800903</t>
   </si>
   <si>
     <t xml:space="preserve">1.49177956581116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50696301460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45761656761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4386373758316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37790322303772</t>
+    <t xml:space="preserve">1.50696313381195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45761668682098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43863725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37790334224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.33235275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30957758426666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33994448184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32476103305817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34753620624542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31337344646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31716930866241</t>
+    <t xml:space="preserve">1.30957746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33994460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32476091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34753632545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31337320804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161860466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31716918945312</t>
   </si>
   <si>
     <t xml:space="preserve">1.40827023983002</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44243311882019</t>
+    <t xml:space="preserve">1.44243323802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.45382082462311</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">1.48418784141541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46520853042603</t>
+    <t xml:space="preserve">1.46520841121674</t>
   </si>
   <si>
     <t xml:space="preserve">1.42345380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41586208343506</t>
+    <t xml:space="preserve">1.41586196422577</t>
   </si>
   <si>
     <t xml:space="preserve">1.45002484321594</t>
@@ -1154,19 +1154,22 @@
     <t xml:space="preserve">1.46141254901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54112577438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47280013561249</t>
+    <t xml:space="preserve">1.54112589359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47280025482178</t>
   </si>
   <si>
     <t xml:space="preserve">1.5145548582077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51551628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768423080444</t>
+    <t xml:space="preserve">1.48418772220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51551640033722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768411159515</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726459503174</t>
@@ -1175,13 +1178,13 @@
     <t xml:space="preserve">1.51943242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50376808643341</t>
+    <t xml:space="preserve">1.5037682056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852362155914</t>
+    <t xml:space="preserve">1.46852350234985</t>
   </si>
   <si>
     <t xml:space="preserve">1.48027181625366</t>
@@ -1190,28 +1193,28 @@
     <t xml:space="preserve">1.46069145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44894325733185</t>
+    <t xml:space="preserve">1.44894337654114</t>
   </si>
   <si>
     <t xml:space="preserve">1.4646075963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677530765533</t>
+    <t xml:space="preserve">1.45677542686462</t>
   </si>
   <si>
     <t xml:space="preserve">1.47243964672089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47635579109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44111120700836</t>
+    <t xml:space="preserve">1.47635567188263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44111108779907</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36278998851776</t>
+    <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
     <t xml:space="preserve">1.40978252887726</t>
@@ -1220,28 +1223,28 @@
     <t xml:space="preserve">1.42153084278107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936301231384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43327915668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45285928249359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39803457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39411842823029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3471257686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362926006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.42936289310455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43327903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45285940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39803445339203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.394118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34712564945221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362949848175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929347991943</t>
@@ -1250,13 +1253,13 @@
     <t xml:space="preserve">1.30796492099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30404889583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33146154880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28055262565613</t>
+    <t xml:space="preserve">1.30404877662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33146131038666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28055250644684</t>
   </si>
   <si>
     <t xml:space="preserve">1.29621684551239</t>
@@ -1265,16 +1268,16 @@
     <t xml:space="preserve">1.31188106536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34320962429047</t>
+    <t xml:space="preserve">1.34320950508118</t>
   </si>
   <si>
     <t xml:space="preserve">1.35104179382324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38628625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40586650371552</t>
+    <t xml:space="preserve">1.38628613948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4058666229248</t>
   </si>
   <si>
     <t xml:space="preserve">1.37062203884125</t>
@@ -1283,31 +1286,31 @@
     <t xml:space="preserve">1.37845408916473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3275454044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28838455677032</t>
+    <t xml:space="preserve">1.32754528522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2883847951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.40195047855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30013287067413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3353773355484</t>
+    <t xml:space="preserve">1.30013298988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28446853160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31579720973969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31971323490143</t>
+    <t xml:space="preserve">1.28446865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3157970905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31971299648285</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1319,7 +1322,7 @@
     <t xml:space="preserve">1.41761469841003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48810386657715</t>
+    <t xml:space="preserve">1.48810398578644</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593591690063</t>
@@ -1328,7 +1331,7 @@
     <t xml:space="preserve">1.49985206127167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51160025596619</t>
+    <t xml:space="preserve">1.5116001367569</t>
   </si>
   <si>
     <t xml:space="preserve">1.52334845066071</t>
@@ -1349,7 +1352,7 @@
     <t xml:space="preserve">1.62124979496002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60558569431305</t>
+    <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
     <t xml:space="preserve">1.61341786384583</t>
@@ -1358,13 +1361,13 @@
     <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62908208370209</t>
+    <t xml:space="preserve">1.62908220291138</t>
   </si>
   <si>
     <t xml:space="preserve">1.64474630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63691413402557</t>
+    <t xml:space="preserve">1.63691425323486</t>
   </si>
   <si>
     <t xml:space="preserve">1.65257847309113</t>
@@ -1379,40 +1382,40 @@
     <t xml:space="preserve">1.70740354061127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75439596176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74656391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80138885974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838163852692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006030082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7778924703598</t>
+    <t xml:space="preserve">1.75439620018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74656403064728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222836971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80138874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006042003632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77789258956909</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488524913788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80922091007233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83271741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84054970741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87971019744873</t>
+    <t xml:space="preserve">1.80922102928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83271729946136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84054958820343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87971031665802</t>
   </si>
   <si>
     <t xml:space="preserve">1.87187814712524</t>
@@ -1421,10 +1424,10 @@
     <t xml:space="preserve">1.86404597759247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85621380805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79355669021606</t>
+    <t xml:space="preserve">1.85621392726898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79355680942535</t>
   </si>
   <si>
     <t xml:space="preserve">1.94236719608307</t>
@@ -1436,7 +1439,7 @@
     <t xml:space="preserve">1.97369563579559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99719202518463</t>
+    <t xml:space="preserve">1.99719190597534</t>
   </si>
   <si>
     <t xml:space="preserve">1.96586358547211</t>
@@ -1445,46 +1448,43 @@
     <t xml:space="preserve">1.93453526496887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91887080669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92670297622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98178470134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94942915439606</t>
+    <t xml:space="preserve">1.91887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92670285701752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98178446292877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94942879676819</t>
   </si>
   <si>
     <t xml:space="preserve">1.9656069278717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97369587421417</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.87662863731384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77956187725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76338386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81191718578339</t>
+    <t xml:space="preserve">1.77956163883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76338398456573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81191730499268</t>
   </si>
   <si>
     <t xml:space="preserve">1.78765070438385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80382823944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82000613212585</t>
+    <t xml:space="preserve">1.79573941230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8038284778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82000625133514</t>
   </si>
   <si>
     <t xml:space="preserve">1.86045074462891</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">1.82809507846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85236179828644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89280652999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90089535713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88471758365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84427297115326</t>
+    <t xml:space="preserve">1.85236191749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89280641078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90089547634125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8847177028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84427309036255</t>
   </si>
   <si>
     <t xml:space="preserve">1.86853969097137</t>
@@ -1517,28 +1517,28 @@
     <t xml:space="preserve">1.77147281169891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898430347443</t>
+    <t xml:space="preserve">1.90898418426514</t>
   </si>
   <si>
     <t xml:space="preserve">1.94133996963501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93325102329254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98987364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95751798152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99796259403229</t>
+    <t xml:space="preserve">1.93325114250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98987352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95751810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99796235561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92516219615936</t>
+    <t xml:space="preserve">1.92516231536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.7472060918808</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">1.75529503822327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66631674766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56924974918365</t>
+    <t xml:space="preserve">1.66631686687469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56924986839294</t>
   </si>
   <si>
     <t xml:space="preserve">1.58542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56116092205048</t>
+    <t xml:space="preserve">1.56116080284119</t>
   </si>
   <si>
     <t xml:space="preserve">1.49644958972931</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">1.34276020526886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31849336624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29827117919922</t>
+    <t xml:space="preserve">1.31849348545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29827105998993</t>
   </si>
   <si>
     <t xml:space="preserve">1.17289304733276</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.19715964794159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22951543331146</t>
+    <t xml:space="preserve">1.22951531410217</t>
   </si>
   <si>
     <t xml:space="preserve">1.15267062187195</t>
@@ -1595,34 +1595,34 @@
     <t xml:space="preserve">1.01515901088715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16480398178101</t>
+    <t xml:space="preserve">1.1648041009903</t>
   </si>
   <si>
     <t xml:space="preserve">1.03538143634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07178151607513</t>
+    <t xml:space="preserve">1.07178139686584</t>
   </si>
   <si>
     <t xml:space="preserve">1.15671503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14053726196289</t>
+    <t xml:space="preserve">1.1405371427536</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693746089935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09604823589325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18502640724182</t>
+    <t xml:space="preserve">1.09604835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18502628803253</t>
   </si>
   <si>
     <t xml:space="preserve">1.18907082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364928483963</t>
+    <t xml:space="preserve">1.13649272918701</t>
   </si>
   <si>
     <t xml:space="preserve">1.16075944900513</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">1.26187098026276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30231559276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995980739594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25378203392029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20524859428406</t>
+    <t xml:space="preserve">1.3023157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995992660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.253781914711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20524871349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18098187446594</t>
+    <t xml:space="preserve">1.18098199367523</t>
   </si>
   <si>
     <t xml:space="preserve">1.21333742141724</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">1.13244831562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12031495571136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14458167552948</t>
+    <t xml:space="preserve">1.12031507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14458155632019</t>
   </si>
   <si>
     <t xml:space="preserve">1.11627054214478</t>
@@ -1676,37 +1676,37 @@
     <t xml:space="preserve">1.12435936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12840390205383</t>
+    <t xml:space="preserve">1.12840378284454</t>
   </si>
   <si>
     <t xml:space="preserve">1.24164867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23760414123535</t>
+    <t xml:space="preserve">1.23760426044464</t>
   </si>
   <si>
     <t xml:space="preserve">1.21738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1688483953476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20929300785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24973750114441</t>
+    <t xml:space="preserve">1.16884851455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20929312705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2497376203537</t>
   </si>
   <si>
     <t xml:space="preserve">1.2214263677597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1122260093689</t>
+    <t xml:space="preserve">1.11222612857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.10818159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07582604885101</t>
+    <t xml:space="preserve">1.07582592964172</t>
   </si>
   <si>
     <t xml:space="preserve">1.05964803695679</t>
@@ -1715,31 +1715,31 @@
     <t xml:space="preserve">1.09200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08391499519348</t>
+    <t xml:space="preserve">1.0839147567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.0798704624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05560350418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05155909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0232480764389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02729249000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00302577018738</t>
+    <t xml:space="preserve">1.0556036233902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05155920982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02324795722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0272923707962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00302565097809</t>
   </si>
   <si>
     <t xml:space="preserve">0.982803463935852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954492151737213</t>
+    <t xml:space="preserve">0.954492092132568</t>
   </si>
   <si>
     <t xml:space="preserve">0.970669984817505</t>
@@ -1748,25 +1748,25 @@
     <t xml:space="preserve">1.01111459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986847937107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962581098079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966625511646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978758990764618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01920342445374</t>
+    <t xml:space="preserve">0.986847817897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962581157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966625571250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978759050369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01920354366302</t>
   </si>
   <si>
     <t xml:space="preserve">1.10413718223572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23355972766876</t>
+    <t xml:space="preserve">1.23355984687805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22547090053558</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">1.20120406150818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29422664642334</t>
+    <t xml:space="preserve">1.29422676563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.31040441989899</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4681384563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51262736320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55307197570801</t>
+    <t xml:space="preserve">1.46813833713531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51262748241425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55307185649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.57733881473541</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">1.54093861579895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54498302936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52071630954742</t>
+    <t xml:space="preserve">1.54498314857483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52071642875671</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53284966945648</t>
+    <t xml:space="preserve">1.53284978866577</t>
   </si>
   <si>
     <t xml:space="preserve">1.51667189598083</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">1.581383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58947217464447</t>
+    <t xml:space="preserve">1.58947229385376</t>
   </si>
   <si>
     <t xml:space="preserve">1.57329440116882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56520521640778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48836076259613</t>
+    <t xml:space="preserve">1.56520533561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48836064338684</t>
   </si>
   <si>
     <t xml:space="preserve">1.5004940032959</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">1.54902756214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247608423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52880525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65822780132294</t>
+    <t xml:space="preserve">1.52476072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52880537509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">1.70676136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69867241382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69058346748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68249452114105</t>
+    <t xml:space="preserve">1.69867253303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69058358669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68249464035034</t>
   </si>
   <si>
     <t xml:space="preserve">1.67440569400787</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">1.72293937206268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6137387752533</t>
+    <t xml:space="preserve">1.61373889446259</t>
   </si>
   <si>
     <t xml:space="preserve">1.63396120071411</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">1.65013897418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64205002784729</t>
+    <t xml:space="preserve">1.60565006732941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64205014705658</t>
   </si>
   <si>
     <t xml:space="preserve">1.62587225437164</t>
@@ -1904,40 +1904,40 @@
     <t xml:space="preserve">1.5571163892746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48431634902954</t>
+    <t xml:space="preserve">1.48431622982025</t>
   </si>
   <si>
     <t xml:space="preserve">1.49240517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47218286991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59351670742035</t>
+    <t xml:space="preserve">1.47218298912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59351658821106</t>
   </si>
   <si>
     <t xml:space="preserve">1.50858294963837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37107145786285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3306268453598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893797874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44791615009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46409380435944</t>
+    <t xml:space="preserve">1.37107133865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33062672615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3589380979538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44791603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46409392356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.47622740268707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60160541534424</t>
+    <t xml:space="preserve">1.60160553455353</t>
   </si>
   <si>
     <t xml:space="preserve">1.59756112098694</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">1.75187587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72660851478577</t>
+    <t xml:space="preserve">1.72660839557648</t>
   </si>
   <si>
     <t xml:space="preserve">1.74345338344574</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.65080618858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343998908997</t>
+    <t xml:space="preserve">1.64659488201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343986988068</t>
   </si>
   <si>
     <t xml:space="preserve">1.63817250728607</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">1.66765105724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64238357543945</t>
+    <t xml:space="preserve">1.64238369464874</t>
   </si>
   <si>
     <t xml:space="preserve">1.61711609363556</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">1.55394768714905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59605991840363</t>
+    <t xml:space="preserve">1.59606003761292</t>
   </si>
   <si>
     <t xml:space="preserve">1.56658136844635</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.53710269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53289139270782</t>
+    <t xml:space="preserve">1.53289151191711</t>
   </si>
   <si>
     <t xml:space="preserve">1.51183521747589</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">1.3981317281723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4360328912735</t>
+    <t xml:space="preserve">1.43603301048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.4486665725708</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">1.46130037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499022960663</t>
+    <t xml:space="preserve">1.49499034881592</t>
   </si>
   <si>
     <t xml:space="preserve">1.49077904224396</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.52446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131400585175</t>
+    <t xml:space="preserve">1.54131388664246</t>
   </si>
   <si>
     <t xml:space="preserve">1.46972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.52868008613586</t>
   </si>
   <si>
     <t xml:space="preserve">1.4992014169693</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">1.50341272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60869359970093</t>
+    <t xml:space="preserve">1.60869371891022</t>
   </si>
   <si>
     <t xml:space="preserve">1.57921504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60027134418488</t>
+    <t xml:space="preserve">1.60027122497559</t>
   </si>
   <si>
     <t xml:space="preserve">1.62553858757019</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">1.60448241233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65501737594604</t>
+    <t xml:space="preserve">1.65501749515533</t>
   </si>
   <si>
     <t xml:space="preserve">1.71818590164185</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">1.67186236381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61290490627289</t>
+    <t xml:space="preserve">1.61290502548218</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184885025024</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">1.50762391090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42761051654816</t>
+    <t xml:space="preserve">1.42761039733887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46551156044006</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">1.45708906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52025759220123</t>
+    <t xml:space="preserve">1.52025771141052</t>
   </si>
   <si>
     <t xml:space="preserve">1.57079255580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58763754367828</t>
+    <t xml:space="preserve">1.58763742446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.65922856330872</t>
@@ -20048,7 +20048,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20074,7 +20074,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G659" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20100,7 +20100,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G660" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20126,7 +20126,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G661" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20152,7 +20152,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20178,7 +20178,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20204,7 +20204,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G664" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20230,7 +20230,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G665" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20256,7 +20256,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G666" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20282,7 +20282,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G667" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20308,7 +20308,7 @@
         <v>1.875</v>
       </c>
       <c r="G668" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20334,7 +20334,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G669" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20360,7 +20360,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G670" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20386,7 +20386,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G671" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20412,7 +20412,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G672" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20438,7 +20438,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G673" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20464,7 +20464,7 @@
         <v>1.875</v>
       </c>
       <c r="G674" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20490,7 +20490,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G675" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20516,7 +20516,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G676" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20542,7 +20542,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G677" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20568,7 +20568,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G678" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20594,7 +20594,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G679" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20620,7 +20620,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G680" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20646,7 +20646,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G681" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20672,7 +20672,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G682" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20698,7 +20698,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G683" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20724,7 +20724,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G684" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20750,7 +20750,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G685" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20776,7 +20776,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G686" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20802,7 +20802,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G687" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20828,7 +20828,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G688" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20854,7 +20854,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G689" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20880,7 +20880,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G690" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20906,7 +20906,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G691" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20932,7 +20932,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G692" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20958,7 +20958,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G693" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20984,7 +20984,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G694" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21010,7 +21010,7 @@
         <v>1.875</v>
       </c>
       <c r="G695" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21036,7 +21036,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G696" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21062,7 +21062,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G697" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21088,7 +21088,7 @@
         <v>1.875</v>
       </c>
       <c r="G698" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21114,7 +21114,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G699" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21140,7 +21140,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G700" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21166,7 +21166,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G701" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21192,7 +21192,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G702" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21218,7 +21218,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G703" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21244,7 +21244,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G704" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21270,7 +21270,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G705" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21296,7 +21296,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G706" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21322,7 +21322,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G707" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21348,7 +21348,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21374,7 +21374,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G709" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21400,7 +21400,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G710" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21426,7 +21426,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21452,7 +21452,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G712" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21478,7 +21478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G713" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21504,7 +21504,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21530,7 +21530,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G715" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21556,7 +21556,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G716" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21582,7 +21582,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G717" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21608,7 +21608,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G718" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21634,7 +21634,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G719" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21660,7 +21660,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G720" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21686,7 +21686,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G721" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21712,7 +21712,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G722" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21738,7 +21738,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21764,7 +21764,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21790,7 +21790,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G725" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21816,7 +21816,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G726" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21842,7 +21842,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G727" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21868,7 +21868,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21894,7 +21894,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G729" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G730" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21946,7 +21946,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G731" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21972,7 +21972,7 @@
         <v>1.75</v>
       </c>
       <c r="G732" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21998,7 +21998,7 @@
         <v>1.75</v>
       </c>
       <c r="G733" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22024,7 +22024,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G734" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22050,7 +22050,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G735" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22076,7 +22076,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G736" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22102,7 +22102,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22128,7 +22128,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G738" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22154,7 +22154,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G739" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22180,7 +22180,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22206,7 +22206,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G741" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22232,7 +22232,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22258,7 +22258,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22284,7 +22284,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G744" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22310,7 +22310,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G745" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22336,7 +22336,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G746" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22362,7 +22362,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G747" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G748" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22414,7 +22414,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G749" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22440,7 +22440,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G750" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22466,7 +22466,7 @@
         <v>1.75</v>
       </c>
       <c r="G751" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22492,7 +22492,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G752" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22518,7 +22518,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G753" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22544,7 +22544,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22570,7 +22570,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G755" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22596,7 +22596,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G756" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22622,7 +22622,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G757" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22648,7 +22648,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G758" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22674,7 +22674,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G759" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G760" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22726,7 +22726,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G761" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22752,7 +22752,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G762" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22778,7 +22778,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G763" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22804,7 +22804,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G764" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22830,7 +22830,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G765" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22856,7 +22856,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G766" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22882,7 +22882,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G767" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22908,7 +22908,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22934,7 +22934,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G769" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22960,7 +22960,7 @@
         <v>1.75</v>
       </c>
       <c r="G770" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22986,7 +22986,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G771" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23012,7 +23012,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G772" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23038,7 +23038,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G773" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23064,7 +23064,7 @@
         <v>1.75</v>
       </c>
       <c r="G774" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23090,7 +23090,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23116,7 +23116,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G776" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23142,7 +23142,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G777" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23168,7 +23168,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G778" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23194,7 +23194,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G779" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23220,7 +23220,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G780" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23246,7 +23246,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G781" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23272,7 +23272,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G782" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23298,7 +23298,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G783" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23324,7 +23324,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G784" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23350,7 +23350,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G785" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23376,7 +23376,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G786" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23402,7 +23402,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G787" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23428,7 +23428,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G788" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23454,7 +23454,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G789" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23480,7 +23480,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G790" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23506,7 +23506,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G791" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23532,7 +23532,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G792" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23558,7 +23558,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G793" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23584,7 +23584,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G794" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23610,7 +23610,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G795" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23636,7 +23636,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G796" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23662,7 +23662,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G797" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23688,7 +23688,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23714,7 +23714,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G799" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23740,7 +23740,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G800" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23766,7 +23766,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G801" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23792,7 +23792,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G802" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G803" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23844,7 +23844,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G804" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23870,7 +23870,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G805" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23896,7 +23896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23922,7 +23922,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23948,7 +23948,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23974,7 +23974,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G809" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24000,7 +24000,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G810" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G811" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24052,7 +24052,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24078,7 +24078,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24104,7 +24104,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G814" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24130,7 +24130,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G815" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24156,7 +24156,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24182,7 +24182,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G817" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24234,7 +24234,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G819" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24260,7 +24260,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G820" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24286,7 +24286,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G821" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24312,7 +24312,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24338,7 +24338,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G823" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24364,7 +24364,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G824" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24390,7 +24390,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G825" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24416,7 +24416,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G826" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24442,7 +24442,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G827" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G828" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24494,7 +24494,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G829" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24520,7 +24520,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G830" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24546,7 +24546,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G831" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24572,7 +24572,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G832" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24598,7 +24598,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G833" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24624,7 +24624,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G834" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24650,7 +24650,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G835" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24676,7 +24676,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G836" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24702,7 +24702,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G837" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24728,7 +24728,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G838" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24754,7 +24754,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G839" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24780,7 +24780,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G840" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24806,7 +24806,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G841" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24832,7 +24832,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G842" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24858,7 +24858,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G843" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24884,7 +24884,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G844" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24910,7 +24910,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G845" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G846" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24962,7 +24962,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24988,7 +24988,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G848" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25014,7 +25014,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25040,7 +25040,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25066,7 +25066,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G851" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G852" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25118,7 +25118,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G853" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25144,7 +25144,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G854" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25170,7 +25170,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G855" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25196,7 +25196,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G856" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G857" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25248,7 +25248,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G858" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25274,7 +25274,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25300,7 +25300,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G860" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25326,7 +25326,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G861" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25352,7 +25352,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25378,7 +25378,7 @@
         <v>2.25</v>
       </c>
       <c r="G863" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25404,7 +25404,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25430,7 +25430,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G865" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25456,7 +25456,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G866" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25482,7 +25482,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G867" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25508,7 +25508,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G868" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25534,7 +25534,7 @@
         <v>2.25</v>
       </c>
       <c r="G869" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25560,7 +25560,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G870" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25586,7 +25586,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G871" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25612,7 +25612,7 @@
         <v>2.25</v>
       </c>
       <c r="G872" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25638,7 +25638,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G874" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25690,7 +25690,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G875" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25716,7 +25716,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G876" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25742,7 +25742,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G877" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25768,7 +25768,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G878" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25794,7 +25794,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G879" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25820,7 +25820,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G880" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25846,7 +25846,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G881" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25872,7 +25872,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G882" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25898,7 +25898,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25924,7 +25924,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G884" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25950,7 +25950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G885" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25976,7 +25976,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G886" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26002,7 +26002,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G887" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26054,7 +26054,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G889" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26080,7 +26080,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G890" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26106,7 +26106,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G891" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26132,7 +26132,7 @@
         <v>2.5</v>
       </c>
       <c r="G892" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26158,7 +26158,7 @@
         <v>2.5</v>
       </c>
       <c r="G893" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26184,7 +26184,7 @@
         <v>2.5</v>
       </c>
       <c r="G894" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26210,7 +26210,7 @@
         <v>2.5</v>
       </c>
       <c r="G895" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26236,7 +26236,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26262,7 +26262,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G897" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26288,7 +26288,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G898" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G899" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>2.5</v>
       </c>
       <c r="G900" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26366,7 +26366,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G901" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26392,7 +26392,7 @@
         <v>2.5</v>
       </c>
       <c r="G902" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26418,7 +26418,7 @@
         <v>2.5</v>
       </c>
       <c r="G903" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26444,7 +26444,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G904" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26470,7 +26470,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26496,7 +26496,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G906" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26522,7 +26522,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26548,7 +26548,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G908" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26574,7 +26574,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G909" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26600,7 +26600,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G910" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26626,7 +26626,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G911" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G912" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26678,7 +26678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G913" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28394,7 +28394,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G979" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28420,7 +28420,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G980" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28472,7 +28472,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G982" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28524,7 +28524,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G984" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28628,7 +28628,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G988" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28680,7 +28680,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G990" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29122,7 +29122,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1007" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29148,7 +29148,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1008" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29200,7 +29200,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1010" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29226,7 +29226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1011" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29278,7 +29278,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1013" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29304,7 +29304,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1014" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29382,7 +29382,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1017" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29460,7 +29460,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1020" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29486,7 +29486,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1021" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29512,7 +29512,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1022" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29538,7 +29538,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1023" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -68780,7 +68780,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6870023148</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>49990</v>
@@ -68801,6 +68801,32 @@
         <v>839</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6911689815</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>22768</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>850</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="867">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.994892954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980557262897491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97840690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951169192790985</t>
+    <t xml:space="preserve">0.980557382106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978407025337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951169312000275</t>
   </si>
   <si>
     <t xml:space="preserve">0.959053874015808</t>
@@ -65,55 +65,55 @@
     <t xml:space="preserve">0.960487484931946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9447181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931816041469574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863005042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874473512172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849386155605316</t>
+    <t xml:space="preserve">0.944718182086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931816220283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863005101680756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874473690986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849386215209961</t>
   </si>
   <si>
     <t xml:space="preserve">0.900994479656219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878057599067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887375593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902428030967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560868740082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871606469154358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898844122886658</t>
+    <t xml:space="preserve">0.878057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887375771999359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902428090572357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560987949371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871606409549713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898844063282013</t>
   </si>
   <si>
     <t xml:space="preserve">0.866589069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831466674804688</t>
+    <t xml:space="preserve">0.831466734409332</t>
   </si>
   <si>
     <t xml:space="preserve">0.820714950561523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807812809944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74545282125473</t>
+    <t xml:space="preserve">0.807812929153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745452880859375</t>
   </si>
   <si>
     <t xml:space="preserve">0.713197767734528</t>
@@ -122,28 +122,28 @@
     <t xml:space="preserve">0.731117308139801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.704237997531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723949432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774124145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788459897041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80279541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845802307128906</t>
+    <t xml:space="preserve">0.704238057136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723949491977692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774124324321747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788459777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800645172595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802795350551605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824298918247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845802247524261</t>
   </si>
   <si>
     <t xml:space="preserve">0.827882766723633</t>
@@ -152,283 +152,283 @@
     <t xml:space="preserve">0.804945826530457</t>
   </si>
   <si>
+    <t xml:space="preserve">0.835050642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834333956241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838634550571442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88665896654129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839351236820221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850819826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873040020465851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877340614795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888809323310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892393112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895977079868317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885225296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852970123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870889723300934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867305874824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88092452287674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860137939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830749928951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858704388141632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855120599269867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851536512374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859421253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840784907341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826449275016785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79921156167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789893329143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813547194004059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779858529567719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781292021274567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784875869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809246420860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817131042480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837917745113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821431875228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814980745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812113642692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811396777629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799928307533264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794194102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787026286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803512275218964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815697610378265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756921470165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759788572788239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762655735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756204664707184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750470459461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763372480869293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767673194408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780575335025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775557637214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795627593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784159123897552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842218399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851380407810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872163951396942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869937300682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861029982566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861772239208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853607296943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856576502323151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864741325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855834126472473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837277472019196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825401186943054</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.835050702095032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834333837032318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838634550571442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886658906936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880207896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83935135602951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850819885730743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87304013967514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888809204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892393171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895977139472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885225296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852970242500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870889842510223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867305874824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880924582481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860138058662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830750048160553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858704447746277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855120480060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851536571979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859421253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840784847736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82644921541214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799211442470551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789893388748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813547194004059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779858589172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781292021274567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784875929355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809246420860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817131042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837917685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821431875228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814980804920197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812113642692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811396777629852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799928307533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794194102287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787026286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803512275218964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815697550773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756921410560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759788572788239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762655675411224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756204605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750470519065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77914160490036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763372540473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767673194408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780575275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77555775642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795627593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784159004688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842218399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851380467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872163951396942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869937360286713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861029922962189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861772298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85360723733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856576383113861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864741384983063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855834066867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837277352809906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825401246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835050582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829112529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83059698343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85880309343338</t>
+    <t xml:space="preserve">0.829112589359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830597043037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85880321264267</t>
   </si>
   <si>
     <t xml:space="preserve">0.839504301548004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84470009803772</t>
+    <t xml:space="preserve">0.844700157642365</t>
   </si>
   <si>
     <t xml:space="preserve">0.843957901000977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846184611320496</t>
+    <t xml:space="preserve">0.846184551715851</t>
   </si>
   <si>
     <t xml:space="preserve">0.83579295873642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833566129207611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838762044906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816494047641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809813559055328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823916554450989</t>
+    <t xml:space="preserve">0.833566188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838761866092682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816493928432465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809813499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823916614055634</t>
   </si>
   <si>
     <t xml:space="preserve">0.810555815696716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801648557186127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817978501319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818720817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819462895393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81278270483017</t>
+    <t xml:space="preserve">0.801648736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81797844171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818720757961273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819462954998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826143443584442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812782645225525</t>
   </si>
   <si>
     <t xml:space="preserve">0.808329045772552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803133189678192</t>
+    <t xml:space="preserve">0.803133070468903</t>
   </si>
   <si>
     <t xml:space="preserve">0.805359959602356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796452760696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800906300544739</t>
+    <t xml:space="preserve">0.796452701091766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800906360149384</t>
   </si>
   <si>
     <t xml:space="preserve">0.790514647960663</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.791999161243439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791256904602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807586908340454</t>
+    <t xml:space="preserve">0.791256844997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807586848735809</t>
   </si>
   <si>
     <t xml:space="preserve">0.814267098903656</t>
@@ -452,34 +452,34 @@
     <t xml:space="preserve">0.798679530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.794225931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786803245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77938050031662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77715390920639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777896046638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788287758827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771957814693451</t>
+    <t xml:space="preserve">0.794225990772247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786803185939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779380619525909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777153849601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777895987033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788287818431854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771957874298096</t>
   </si>
   <si>
     <t xml:space="preserve">0.838019669055939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806844413280487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774927020072937</t>
+    <t xml:space="preserve">0.806844472885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774927079677582</t>
   </si>
   <si>
     <t xml:space="preserve">0.773442506790161</t>
@@ -491,22 +491,22 @@
     <t xml:space="preserve">0.765277504920959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778638362884521</t>
+    <t xml:space="preserve">0.778638422489166</t>
   </si>
   <si>
     <t xml:space="preserve">0.783091902732849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787545561790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78606104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774184703826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785318613052368</t>
+    <t xml:space="preserve">0.787545502185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786060988903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77418464422226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785318732261658</t>
   </si>
   <si>
     <t xml:space="preserve">0.806102216243744</t>
@@ -518,22 +518,22 @@
     <t xml:space="preserve">0.841731011867523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848411440849304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843215584754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852865099906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845442473888397</t>
+    <t xml:space="preserve">0.848411321640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843215525150299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852865040302277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845442414283752</t>
   </si>
   <si>
     <t xml:space="preserve">0.849153757095337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874390721321106</t>
+    <t xml:space="preserve">0.874390661716461</t>
   </si>
   <si>
     <t xml:space="preserve">0.862514495849609</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">0.866225838661194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85509192943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857318639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832823753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834308385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827627897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860287845134735</t>
+    <t xml:space="preserve">0.85509181022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857318580150604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832823812961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834308266639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827628016471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860287725925446</t>
   </si>
   <si>
     <t xml:space="preserve">0.854349613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86771035194397</t>
+    <t xml:space="preserve">0.867710411548615</t>
   </si>
   <si>
     <t xml:space="preserve">0.880328834056854</t>
@@ -572,67 +572,67 @@
     <t xml:space="preserve">0.873648524284363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919668972492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923380315303802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913730919361115</t>
+    <t xml:space="preserve">0.919669091701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923380434513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913730978965759</t>
   </si>
   <si>
     <t xml:space="preserve">0.916699945926666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927091717720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931545257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915957808494568</t>
+    <t xml:space="preserve">0.927091777324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931545317173004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915957748889923</t>
   </si>
   <si>
     <t xml:space="preserve">0.911504209041595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908535182476044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898885667324066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991669058799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979792773723602</t>
+    <t xml:space="preserve">0.908534944057465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898885548114777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979792654514313</t>
   </si>
   <si>
     <t xml:space="preserve">1.03768956661224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06960701942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0748028755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0688648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04659676551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05327725410461</t>
+    <t xml:space="preserve">1.06960713863373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07480299472809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06886506080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0465966463089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05327713489532</t>
   </si>
   <si>
     <t xml:space="preserve">1.05179274082184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03249359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02432882785797</t>
+    <t xml:space="preserve">1.03249371051788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02432870864868</t>
   </si>
   <si>
     <t xml:space="preserve">1.03175139427185</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">1.01467931270599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00206077098846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02284419536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03026700019836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0592155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06812250614166</t>
+    <t xml:space="preserve">1.00206089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0228443145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03026688098907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05921530723572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06812262535095</t>
   </si>
   <si>
     <t xml:space="preserve">1.04585456848145</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">1.11191630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11711227893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1289883852005</t>
+    <t xml:space="preserve">1.1193391084671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12898850440979</t>
   </si>
   <si>
     <t xml:space="preserve">1.14160704612732</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">1.21509146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2314213514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21731817722321</t>
+    <t xml:space="preserve">1.23142147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2173182964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.22177195549011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21880269050598</t>
+    <t xml:space="preserve">1.21880292892456</t>
   </si>
   <si>
     <t xml:space="preserve">1.23216366767883</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">1.22845220565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23513269424438</t>
+    <t xml:space="preserve">1.2351325750351</t>
   </si>
   <si>
     <t xml:space="preserve">1.22474086284637</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">1.24700891971588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26779234409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24923574924469</t>
+    <t xml:space="preserve">1.26779246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24923551082611</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443172454834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26036965847015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25888538360596</t>
+    <t xml:space="preserve">1.26036989688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25888526439667</t>
   </si>
   <si>
     <t xml:space="preserve">1.26927709579468</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">1.30639028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34424602985382</t>
+    <t xml:space="preserve">1.34424614906311</t>
   </si>
   <si>
     <t xml:space="preserve">1.239586353302</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">1.17426669597626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17278230190277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1653596162796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17055535316467</t>
+    <t xml:space="preserve">1.17278218269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16535973548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17055523395538</t>
   </si>
   <si>
     <t xml:space="preserve">1.17723572254181</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">1.17649352550507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16387510299683</t>
+    <t xml:space="preserve">1.16387498378754</t>
   </si>
   <si>
     <t xml:space="preserve">1.16164827346802</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">1.15051412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1534835100174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12824630737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14383375644684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18911218643188</t>
+    <t xml:space="preserve">1.15348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12824618816376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14383387565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1891120672226</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247292518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28412234783173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28486454486847</t>
+    <t xml:space="preserve">1.28412222862244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28486442565918</t>
   </si>
   <si>
     <t xml:space="preserve">1.31307065486908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018420219421</t>
+    <t xml:space="preserve">1.35018408298492</t>
   </si>
   <si>
     <t xml:space="preserve">1.327916264534</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">1.35834908485413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3435035943985</t>
+    <t xml:space="preserve">1.34350347518921</t>
   </si>
   <si>
     <t xml:space="preserve">1.33311200141907</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">1.32855689525604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35816466808319</t>
+    <t xml:space="preserve">1.35816478729248</t>
   </si>
   <si>
     <t xml:space="preserve">1.35512793064117</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">1.36651563644409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37410736083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39080917835236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39688265323639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3816990852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36803388595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36727476119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39156830310822</t>
+    <t xml:space="preserve">1.37410724163055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39080929756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39688277244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38169932365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3680340051651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36727488040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3915684223175</t>
   </si>
   <si>
     <t xml:space="preserve">1.39232754707336</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">1.38549494743347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38701343536377</t>
+    <t xml:space="preserve">1.37258899211884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38701331615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.36879312992096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36120128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3513320684433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31565093994141</t>
+    <t xml:space="preserve">1.36120140552521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35133218765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3156510591507</t>
   </si>
   <si>
     <t xml:space="preserve">1.33842611312866</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">1.34298121929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31868767738342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29363465309143</t>
+    <t xml:space="preserve">1.31868755817413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29363489151001</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818999767303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30122661590576</t>
+    <t xml:space="preserve">1.30122649669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.320965051651</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">1.36955237388611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536428451538</t>
+    <t xml:space="preserve">1.39536440372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.37562584877014</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">1.37866234779358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38473570346832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34829545021057</t>
+    <t xml:space="preserve">1.38473582267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34829556941986</t>
   </si>
   <si>
     <t xml:space="preserve">1.42497217655182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4523024559021</t>
+    <t xml:space="preserve">1.45230233669281</t>
   </si>
   <si>
     <t xml:space="preserve">1.50164890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735512256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630934238434</t>
+    <t xml:space="preserve">1.47735524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630958080292</t>
   </si>
   <si>
     <t xml:space="preserve">1.51835060119629</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">1.54568111896515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379573345184</t>
+    <t xml:space="preserve">1.51379561424255</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594244480133</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">1.51075887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52897906303406</t>
+    <t xml:space="preserve">1.52897918224335</t>
   </si>
   <si>
     <t xml:space="preserve">1.50316727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53049755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53353416919708</t>
+    <t xml:space="preserve">1.53049743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53353428840637</t>
   </si>
   <si>
     <t xml:space="preserve">1.52746093273163</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">1.47887361049652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43484151363373</t>
+    <t xml:space="preserve">1.43484139442444</t>
   </si>
   <si>
     <t xml:space="preserve">1.40599274635315</t>
@@ -1010,64 +1010,64 @@
     <t xml:space="preserve">1.2905980348587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29970812797546</t>
+    <t xml:space="preserve">1.29970824718475</t>
   </si>
   <si>
     <t xml:space="preserve">1.30502247810364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42573130130768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052252292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47659599781036</t>
+    <t xml:space="preserve">1.42573142051697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052264213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47659611701965</t>
   </si>
   <si>
     <t xml:space="preserve">1.48798370361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48722434043884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269444465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41434383392334</t>
+    <t xml:space="preserve">1.48722445964813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41434371471405</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738045215607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40447437763214</t>
+    <t xml:space="preserve">1.40447449684143</t>
   </si>
   <si>
     <t xml:space="preserve">1.39308667182922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40371525287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37182986736298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36271965503693</t>
+    <t xml:space="preserve">1.40371513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37182998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36271977424622</t>
   </si>
   <si>
     <t xml:space="preserve">1.36423814296722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35209143161774</t>
+    <t xml:space="preserve">1.35209131240845</t>
   </si>
   <si>
     <t xml:space="preserve">1.36499714851379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36575663089752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37107062339783</t>
+    <t xml:space="preserve">1.36575639247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37107074260712</t>
   </si>
   <si>
     <t xml:space="preserve">1.42724967002869</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">1.4993714094162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49557554721832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49177956581116</t>
+    <t xml:space="preserve">1.49557542800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49177968502045</t>
   </si>
   <si>
     <t xml:space="preserve">1.50696313381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45761656761169</t>
+    <t xml:space="preserve">1.4576164484024</t>
   </si>
   <si>
     <t xml:space="preserve">1.43863725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37790322303772</t>
+    <t xml:space="preserve">1.37790310382843</t>
   </si>
   <si>
     <t xml:space="preserve">1.33235263824463</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.34753620624542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31337332725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27161872386932</t>
+    <t xml:space="preserve">1.31337320804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27161860466003</t>
   </si>
   <si>
     <t xml:space="preserve">1.31716918945312</t>
@@ -1124,25 +1124,25 @@
     <t xml:space="preserve">1.40827023983002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41206610202789</t>
+    <t xml:space="preserve">1.41206622123718</t>
   </si>
   <si>
     <t xml:space="preserve">1.41965794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44243323802948</t>
+    <t xml:space="preserve">1.44243311882019</t>
   </si>
   <si>
     <t xml:space="preserve">1.45382082462311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46900427341461</t>
+    <t xml:space="preserve">1.4690043926239</t>
   </si>
   <si>
     <t xml:space="preserve">1.48418784141541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46520841121674</t>
+    <t xml:space="preserve">1.46520829200745</t>
   </si>
   <si>
     <t xml:space="preserve">1.42345380783081</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">1.54112601280212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47280037403107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51455473899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51551628112793</t>
+    <t xml:space="preserve">1.47280025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51455497741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51551640033722</t>
   </si>
   <si>
     <t xml:space="preserve">1.50768411159515</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">1.51943242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50376808643341</t>
+    <t xml:space="preserve">1.50376796722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.49201989173889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46852350234985</t>
+    <t xml:space="preserve">1.46852362155914</t>
   </si>
   <si>
     <t xml:space="preserve">1.48027181625366</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">1.46460747718811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677542686462</t>
+    <t xml:space="preserve">1.45677530765533</t>
   </si>
   <si>
     <t xml:space="preserve">1.47243976593018</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">1.47635567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44111108779907</t>
+    <t xml:space="preserve">1.44111120700836</t>
   </si>
   <si>
     <t xml:space="preserve">1.4254469871521</t>
@@ -1217,40 +1217,40 @@
     <t xml:space="preserve">1.36278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40978252887726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42153084278107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936301231384</t>
+    <t xml:space="preserve">1.40978264808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42153072357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936289310455</t>
   </si>
   <si>
     <t xml:space="preserve">1.43327915668488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45285940170288</t>
+    <t xml:space="preserve">1.45285928249359</t>
   </si>
   <si>
     <t xml:space="preserve">1.39803445339203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.394118309021</t>
+    <t xml:space="preserve">1.39411842823029</t>
   </si>
   <si>
     <t xml:space="preserve">1.34712564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362926006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26488828659058</t>
+    <t xml:space="preserve">1.32362937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26488816738129</t>
   </si>
   <si>
     <t xml:space="preserve">1.33929359912872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30796492099762</t>
+    <t xml:space="preserve">1.30796504020691</t>
   </si>
   <si>
     <t xml:space="preserve">1.30404889583588</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">1.29621684551239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31188106536865</t>
+    <t xml:space="preserve">1.31188094615936</t>
   </si>
   <si>
     <t xml:space="preserve">1.34320962429047</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.33537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230082035065</t>
+    <t xml:space="preserve">1.29230070114136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28446865081787</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">1.3157970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31971335411072</t>
+    <t xml:space="preserve">1.31971311569214</t>
   </si>
   <si>
     <t xml:space="preserve">1.37453806400299</t>
@@ -1331,88 +1331,88 @@
     <t xml:space="preserve">1.49985206127167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51160037517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52334845066071</t>
+    <t xml:space="preserve">1.51160025596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52334856987</t>
   </si>
   <si>
     <t xml:space="preserve">1.53509676456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55076086521149</t>
+    <t xml:space="preserve">1.55076098442078</t>
   </si>
   <si>
     <t xml:space="preserve">1.59775364398956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58992147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62124991416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60558569431305</t>
+    <t xml:space="preserve">1.58992159366608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6212500333786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60558581352234</t>
   </si>
   <si>
     <t xml:space="preserve">1.61341786384583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58208930492401</t>
+    <t xml:space="preserve">1.5820894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.62908208370209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64474630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63691413402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65257847309113</t>
+    <t xml:space="preserve">1.64474642276764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63691425323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65257859230042</t>
   </si>
   <si>
     <t xml:space="preserve">1.66041052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824293136597</t>
+    <t xml:space="preserve">1.66824281215668</t>
   </si>
   <si>
     <t xml:space="preserve">1.70740354061127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75439620018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74656391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80138874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84838175773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006030082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77789258956909</t>
+    <t xml:space="preserve">1.75439608097076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74656403064728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222836971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80138897895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84838151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006018161774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77789270877838</t>
   </si>
   <si>
     <t xml:space="preserve">1.82488524913788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80922102928162</t>
+    <t xml:space="preserve">1.80922091007233</t>
   </si>
   <si>
     <t xml:space="preserve">1.83271741867065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84054946899414</t>
+    <t xml:space="preserve">1.84054958820343</t>
   </si>
   <si>
     <t xml:space="preserve">1.87971019744873</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">1.87187802791595</t>
   </si>
   <si>
-    <t xml:space="